--- a/finance/Greenhouse_CashFlow_2000m2.xlsx
+++ b/finance/Greenhouse_CashFlow_2000m2.xlsx
@@ -1234,15 +1234,15 @@
       </s:c>
       <s:c r="B7" s="18">
         <s:f>B21</s:f>
-        <s:v>90541.21</s:v>
+        <s:v>102741.99</s:v>
       </s:c>
       <s:c r="C7" s="19">
         <s:f>IFERROR(B7/$B$6,0)</s:f>
-        <s:v>0.144865936</s:v>
+        <s:v>0.16438718400000002</s:v>
       </s:c>
       <s:c r="D7" s="20" t="str">
         <s:f>REPT("|",ROUND(C7*40,0))</s:f>
-        <s:v>||||||</s:v>
+        <s:v>|||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="8">
@@ -1253,15 +1253,15 @@
       </s:c>
       <s:c r="B8" s="18">
         <s:f>D34</s:f>
-        <s:v>258563.19999999998</s:v>
+        <s:v>255663.2</s:v>
       </s:c>
       <s:c r="C8" s="19">
         <s:f>IFERROR(B8/$B$6,0)</s:f>
-        <s:v>0.41370112</s:v>
+        <s:v>0.40906112</s:v>
       </s:c>
       <s:c r="D8" s="20" t="str">
         <s:f>REPT("|",ROUND(C8*40,0))</s:f>
-        <s:v>|||||||||||||||||</s:v>
+        <s:v>||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="9">
@@ -1272,15 +1272,15 @@
       </s:c>
       <s:c r="B9" s="22">
         <s:f>B7+B8</s:f>
-        <s:v>349104.41</s:v>
+        <s:v>358405.19</s:v>
       </s:c>
       <s:c r="C9" s="23">
         <s:f>IFERROR(B9/$B$6,0)</s:f>
-        <s:v>0.558567056</s:v>
+        <s:v>0.573448304</s:v>
       </s:c>
       <s:c r="D9" s="24" t="str">
         <s:f>REPT("|",ROUND(C9*40,0))</s:f>
-        <s:v>||||||||||||||||||||||</s:v>
+        <s:v>|||||||||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="10">
@@ -1291,15 +1291,15 @@
       </s:c>
       <s:c r="B10" s="22">
         <s:f>B6-B9</s:f>
-        <s:v>275895.59</s:v>
+        <s:v>266594.81</s:v>
       </s:c>
       <s:c r="C10" s="23">
         <s:f>IFERROR(B10/$B$6,0)</s:f>
-        <s:v>0.44143294400000005</s:v>
+        <s:v>0.426551696</s:v>
       </s:c>
       <s:c r="D10" s="24" t="str">
         <s:f>REPT("|",ROUND(C10*40,0))</s:f>
-        <s:v>||||||||||||||||||</s:v>
+        <s:v>|||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="12">
@@ -1353,12 +1353,12 @@
         </s:is>
       </s:c>
       <s:c r="B14" s="25">
-        <s:f>Actuals!B31</s:f>
-        <s:v>71144.8</s:v>
+        <s:f>Actuals!B45</s:f>
+        <s:v>74044.8</s:v>
       </s:c>
       <s:c r="C14" s="26">
         <s:f>IFERROR(B14/$B$21,0)</s:f>
-        <s:v>0.7857725780338036</s:v>
+        <s:v>0.720686838944817</s:v>
       </s:c>
       <s:c r="D14" s="27" t="inlineStr">
         <s:is>
@@ -1383,12 +1383,12 @@
         </s:is>
       </s:c>
       <s:c r="B15" s="25">
-        <s:f>Actuals!B32</s:f>
-        <s:v>8000.0</s:v>
+        <s:f>Actuals!B46</s:f>
+        <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C15" s="26">
         <s:f>IFERROR(B15/$B$21,0)</s:f>
-        <s:v>0.08835755563681996</s:v>
+        <s:v>0.09733118854326259</s:v>
       </s:c>
       <s:c r="D15" s="27" t="inlineStr">
         <s:is>
@@ -1408,12 +1408,12 @@
         </s:is>
       </s:c>
       <s:c r="B16" s="25">
-        <s:f>Actuals!B33</s:f>
+        <s:f>Actuals!B47</s:f>
         <s:v>1470.0</s:v>
       </s:c>
       <s:c r="C16" s="26">
         <s:f>IFERROR(B16/$B$21,0)</s:f>
-        <s:v>0.016235700848265668</s:v>
+        <s:v>0.0143076847158596</s:v>
       </s:c>
       <s:c r="D16" s="27" t="inlineStr">
         <s:is>
@@ -1433,12 +1433,12 @@
         </s:is>
       </s:c>
       <s:c r="B17" s="25">
-        <s:f>Actuals!B34</s:f>
-        <s:v>2100.0</s:v>
+        <s:f>Actuals!B48</s:f>
+        <s:v>3070.0</s:v>
       </s:c>
       <s:c r="C17" s="26">
         <s:f>IFERROR(B17/$B$21,0)</s:f>
-        <s:v>0.02319385835466524</s:v>
+        <s:v>0.029880674882781615</s:v>
       </s:c>
       <s:c r="D17" s="27" t="inlineStr">
         <s:is>
@@ -1458,12 +1458,12 @@
         </s:is>
       </s:c>
       <s:c r="B18" s="25">
-        <s:f>Actuals!B35</s:f>
-        <s:v>4660.0</s:v>
+        <s:f>Actuals!B49</s:f>
+        <s:v>5722.7</s:v>
       </s:c>
       <s:c r="C18" s="26">
         <s:f>IFERROR(B18/$B$21,0)</s:f>
-        <s:v>0.05146827615844762</s:v>
+        <s:v>0.05569971926765288</s:v>
       </s:c>
       <s:c r="D18" s="27" t="inlineStr">
         <s:is>
@@ -1483,12 +1483,12 @@
         </s:is>
       </s:c>
       <s:c r="B19" s="25">
-        <s:f>Actuals!B36</s:f>
-        <s:v>2859.41</s:v>
+        <s:f>Actuals!B50</s:f>
+        <s:v>7505.41</s:v>
       </s:c>
       <s:c r="C19" s="26">
         <s:f>IFERROR(B19/$B$21,0)</s:f>
-        <s:v>0.03158130977043492</s:v>
+        <s:v>0.07305104758044885</s:v>
       </s:c>
       <s:c r="D19" s="27" t="inlineStr">
         <s:is>
@@ -1508,12 +1508,12 @@
         </s:is>
       </s:c>
       <s:c r="B20" s="25">
-        <s:f>Actuals!B37</s:f>
-        <s:v>307.0</s:v>
+        <s:f>Actuals!B51</s:f>
+        <s:v>929.08</s:v>
       </s:c>
       <s:c r="C20" s="26">
         <s:f>IFERROR(B20/$B$21,0)</s:f>
-        <s:v>0.0033907211975629657</s:v>
+        <s:v>0.009042846065177442</s:v>
       </s:c>
       <s:c r="D20" s="27" t="inlineStr">
         <s:is>
@@ -1534,7 +1534,7 @@
       </s:c>
       <s:c r="B21" s="30">
         <s:f>SUM(B14:B20)</s:f>
-        <s:v>90541.21</s:v>
+        <s:v>102741.99</s:v>
       </s:c>
       <s:c r="C21" s="23">
         <s:f>IFERROR(B21/B21,0)</s:f>
@@ -1591,7 +1591,7 @@
         </s:is>
       </s:c>
       <s:c r="B25" s="25">
-        <s:f>Actuals!B43</s:f>
+        <s:f>Actuals!B57</s:f>
         <s:v>68664.21</s:v>
       </s:c>
       <s:c r="C25" s="31">
@@ -1610,7 +1610,7 @@
         </s:is>
       </s:c>
       <s:c r="B26" s="25">
-        <s:f>Actuals!B44</s:f>
+        <s:f>Actuals!B58</s:f>
         <s:v>21477.0</s:v>
       </s:c>
       <s:c r="C26" s="31">
@@ -1625,20 +1625,20 @@
     <s:row r="27">
       <s:c r="A27" s="20" t="inlineStr">
         <s:is>
-          <s:t>სექტემბერი 2026 (08-მდე) / September (to the 8th)</s:t>
+          <s:t>სექტემბერი 2026 (18-მდე) / September (to the 18th)</s:t>
         </s:is>
       </s:c>
       <s:c r="B27" s="25">
-        <s:f>Actuals!B45</s:f>
-        <s:v>400.0</s:v>
+        <s:f>Actuals!B59</s:f>
+        <s:v>12600.78</s:v>
       </s:c>
       <s:c r="C27" s="31">
         <s:f>SUM($B$25:B27)</s:f>
-        <s:v>90541.21</s:v>
+        <s:v>102741.99</s:v>
       </s:c>
       <s:c r="D27" s="18">
         <s:f>$B$6-C27</s:f>
-        <s:v>534458.79</s:v>
+        <s:v>522258.01</s:v>
       </s:c>
     </s:row>
     <s:row r="28">
@@ -1649,7 +1649,7 @@
       </s:c>
       <s:c r="B28" s="30">
         <s:f>SUM(B25:B27)</s:f>
-        <s:v>90541.21</s:v>
+        <s:v>102741.99</s:v>
       </s:c>
       <s:c r="C28" s="30">
         <s:f>B28-B21</s:f>
@@ -1657,7 +1657,7 @@
       </s:c>
       <s:c r="D28" s="22">
         <s:f>$B$6-B28</s:f>
-        <s:v>534458.79</s:v>
+        <s:v>522258.01</s:v>
       </s:c>
       <s:c r="G28" s="2" t="inlineStr">
         <s:is>
@@ -1729,20 +1729,20 @@
         </s:is>
       </s:c>
       <s:c r="B33" s="34">
-        <s:f>22000+5000</s:f>
-        <s:v>27000.0</s:v>
+        <s:f>22000+5000+2900/Assumptions!$B$28</s:f>
+        <s:v>28099.151000606427</s:v>
       </s:c>
       <s:c r="C33" s="35">
         <s:f>IFERROR(D33/B33,0)</s:f>
-        <s:v>2.6349925925925928</s:v>
+        <s:v>2.635125879725049</s:v>
       </s:c>
       <s:c r="D33" s="25">
-        <s:f>Actuals!B31</s:f>
-        <s:v>71144.8</s:v>
+        <s:f>Actuals!B45</s:f>
+        <s:v>74044.8</s:v>
       </s:c>
       <s:c r="G33" s="2" t="inlineStr">
         <s:is>
-          <s:t>09/07/2026 — 22,000 $ · 04/08/2026 — 5,000 $</s:t>
+          <s:t>09/07/2026 — 22,000 $ · 04/08/2026 — 5,000 $ · 14/09/2026 — 2,900 ₾ ≈ 1,099 $ (ერ.კ. 2.6384)</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -1754,7 +1754,7 @@
       </s:c>
       <s:c r="B34" s="36">
         <s:f>B32-B33</s:f>
-        <s:v>98000.0</s:v>
+        <s:v>96900.84899939358</s:v>
       </s:c>
       <s:c r="C34" s="37">
         <s:f>Assumptions!$B$28</s:f>
@@ -1762,7 +1762,7 @@
       </s:c>
       <s:c r="D34" s="22">
         <s:f>B34*Assumptions!$B$28</s:f>
-        <s:v>258563.19999999998</s:v>
+        <s:v>255663.2</s:v>
       </s:c>
     </s:row>
     <s:row r="35">
@@ -1773,7 +1773,7 @@
       </s:c>
       <s:c r="B35" s="19">
         <s:f>IFERROR(B33/B32,0)</s:f>
-        <s:v>0.216</s:v>
+        <s:v>0.22479320800485142</s:v>
       </s:c>
     </s:row>
     <s:row r="37">
@@ -1796,11 +1796,11 @@
       </s:c>
       <s:c r="B38" s="38">
         <s:f>SUMIF($D$14:$D$20,"CAPEX",$B$14:$B$20)</s:f>
-        <s:v>78971.21</s:v>
+        <s:v>88201.99</s:v>
       </s:c>
       <s:c r="C38" s="19">
         <s:f>IFERROR(B38/$B$21,0)</s:f>
-        <s:v>0.8722128851602491</s:v>
+        <s:v>0.8584804518580962</s:v>
       </s:c>
       <s:c r="G38" s="2" t="inlineStr">
         <s:is>
@@ -1816,11 +1816,11 @@
       </s:c>
       <s:c r="B39" s="38">
         <s:f>SUMIF($D$14:$D$20,"OPEX",$B$14:$B$20)</s:f>
-        <s:v>11570.0</s:v>
+        <s:v>14540.0</s:v>
       </s:c>
       <s:c r="C39" s="19">
         <s:f>IFERROR(B39/$B$21,0)</s:f>
-        <s:v>0.12778711483975086</s:v>
+        <s:v>0.14151954814190382</s:v>
       </s:c>
       <s:c r="G39" s="2" t="inlineStr">
         <s:is>
@@ -2845,7 +2845,7 @@
       </s:c>
       <s:c r="B58" s="56">
         <s:f>Budget!B21</s:f>
-        <s:v>90541.21</s:v>
+        <s:v>102741.99</s:v>
       </s:c>
       <s:c r="C58" s="41" t="inlineStr">
         <s:is>
@@ -2866,7 +2866,7 @@
       </s:c>
       <s:c r="B59" s="56">
         <s:f>Budget!B38</s:f>
-        <s:v>78971.21</s:v>
+        <s:v>88201.99</s:v>
       </s:c>
       <s:c r="C59" s="41" t="inlineStr">
         <s:is>
@@ -13393,7 +13393,7 @@
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
     <s:pageSetUpPr/>
   </s:sheetPr>
-  <s:dimension ref="A1:E56"/>
+  <s:dimension ref="A1:E70"/>
   <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <s:cols>
     <s:col width="13" customWidth="1" min="1" max="1"/>
@@ -13421,12 +13421,12 @@
     <s:row r="4">
       <s:c r="A4" s="17" t="inlineStr">
         <s:is>
-          <s:t>წყარო / Source file</s:t>
+          <s:t>წყარო / Source files</s:t>
         </s:is>
       </s:c>
       <s:c r="B4" s="20" t="inlineStr">
         <s:is>
-          <s:t>transaction_history_all_accounts_20260401_20260909.csv (Google Drive)</s:t>
+          <s:t>transaction_history_all_accounts_20260401_20260909.csv · transaction_history_all_accounts_20260911_20260918.xlsx (Google Drive)</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -13462,7 +13462,7 @@
       </s:c>
       <s:c r="B7" s="20" t="inlineStr">
         <s:is>
-          <s:t>01/04/2026 – 09/09/2026</s:t>
+          <s:t>01/04/2026 – 18/09/2026</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -13474,69 +13474,58 @@
       </s:c>
       <s:c r="B8" s="20" t="inlineStr">
         <s:is>
-          <s:t>01/07/2026 – 08/09/2026 · 15 გადარიცხვა, შემოსავალი არ ფიქსირდება / 15 payments, no inflows</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="10">
-      <s:c r="A10" s="10" t="inlineStr">
+          <s:t>01/07/2026 – 18/09/2026 · 28 გადარიცხვა / 28 payments</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="9">
+      <s:c r="A9" s="17" t="inlineStr">
+        <s:is>
+          <s:t>ჩარიცხვა / Inflow</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B9" s="20" t="inlineStr">
+        <s:is>
+          <s:t>14/09/2026 — 30,000 ₾, კრედიტის ტრანში GA/1-876787-001 — ხარჯი არ არის, ქვემოთ არ ითვლება / a tranche of the credit, not an expense, excluded below</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="11">
+      <s:c r="A11" s="10" t="inlineStr">
         <s:is>
           <s:t>გადარიცხვები / PAYMENTS</s:t>
         </s:is>
       </s:c>
-      <s:c r="B10" s="11" t="n"/>
-      <s:c r="C10" s="11" t="n"/>
-      <s:c r="D10" s="11" t="n"/>
-      <s:c r="E10" s="11" t="n"/>
-    </s:row>
-    <s:row r="11">
-      <s:c r="A11" s="12" t="inlineStr">
+      <s:c r="B11" s="11" t="n"/>
+      <s:c r="C11" s="11" t="n"/>
+      <s:c r="D11" s="11" t="n"/>
+      <s:c r="E11" s="11" t="n"/>
+    </s:row>
+    <s:row r="12">
+      <s:c r="A12" s="12" t="inlineStr">
         <s:is>
           <s:t>თარიღი / Date</s:t>
         </s:is>
       </s:c>
-      <s:c r="B11" s="12" t="inlineStr">
+      <s:c r="B12" s="12" t="inlineStr">
         <s:is>
           <s:t>დანიშნულება / Description</s:t>
         </s:is>
       </s:c>
-      <s:c r="C11" s="12" t="inlineStr">
+      <s:c r="C12" s="12" t="inlineStr">
         <s:is>
           <s:t>მიმღები / Counterparty</s:t>
         </s:is>
       </s:c>
-      <s:c r="D11" s="12" t="inlineStr">
+      <s:c r="D12" s="12" t="inlineStr">
         <s:is>
           <s:t>კატეგორია / Category</s:t>
         </s:is>
       </s:c>
-      <s:c r="E11" s="12" t="inlineStr">
+      <s:c r="E12" s="12" t="inlineStr">
         <s:is>
           <s:t>თანხა GEL / Amount</s:t>
         </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="12">
-      <s:c r="A12" s="71" t="n">
-        <s:v>46204</s:v>
-      </s:c>
-      <s:c r="B12" s="63" t="inlineStr">
-        <s:is>
-          <s:t>ინვოისი</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C12" s="63" t="inlineStr">
-        <s:is>
-          <s:t>შპს ტერმინალ ვესტ თრეიდინგ</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D12" s="63" t="inlineStr">
-        <s:is>
-          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E12" s="72" t="n">
-        <s:v>-1409.41</s:v>
       </s:c>
     </s:row>
     <s:row r="13">
@@ -13545,21 +13534,21 @@
       </s:c>
       <s:c r="B13" s="63" t="inlineStr">
         <s:is>
-          <s:t>მომსახურების ანაზღაურება</s:t>
+          <s:t>ინვოისი</s:t>
         </s:is>
       </s:c>
       <s:c r="C13" s="63" t="inlineStr">
         <s:is>
-          <s:t>ნუგზარი ბუნტური</s:t>
+          <s:t>შპს ტერმინალ ვესტ თრეიდინგ</s:t>
         </s:is>
       </s:c>
       <s:c r="D13" s="63" t="inlineStr">
         <s:is>
-          <s:t>მომსახურება / Services</s:t>
+          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
         </s:is>
       </s:c>
       <s:c r="E13" s="72" t="n">
-        <s:v>-500</s:v>
+        <s:v>-1409.41</s:v>
       </s:c>
     </s:row>
     <s:row r="14">
@@ -13568,21 +13557,21 @@
       </s:c>
       <s:c r="B14" s="63" t="inlineStr">
         <s:is>
-          <s:t>ხელფასი</s:t>
+          <s:t>მომსახურების ანაზღაურება</s:t>
         </s:is>
       </s:c>
       <s:c r="C14" s="63" t="inlineStr">
         <s:is>
-          <s:t>ნატალია ქანანელი</s:t>
+          <s:t>ნუგზარი ბუნტური</s:t>
         </s:is>
       </s:c>
       <s:c r="D14" s="63" t="inlineStr">
         <s:is>
-          <s:t>ხელფასი / Salaries</s:t>
+          <s:t>მომსახურება / Services</s:t>
         </s:is>
       </s:c>
       <s:c r="E14" s="72" t="n">
-        <s:v>-1000</s:v>
+        <s:v>-500</s:v>
       </s:c>
     </s:row>
     <s:row r="15">
@@ -13591,113 +13580,113 @@
       </s:c>
       <s:c r="B15" s="63" t="inlineStr">
         <s:is>
-          <s:t>თანახმად ხელშეკრულებისა; მომსახურება</s:t>
+          <s:t>ხელფასი</s:t>
         </s:is>
       </s:c>
       <s:c r="C15" s="63" t="inlineStr">
         <s:is>
-          <s:t>გიორგი მღებრიშვილი</s:t>
+          <s:t>ნატალია ქანანელი</s:t>
         </s:is>
       </s:c>
       <s:c r="D15" s="63" t="inlineStr">
         <s:is>
-          <s:t>მომსახურება / Services</s:t>
+          <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
       <s:c r="E15" s="72" t="n">
-        <s:v>-1600</s:v>
+        <s:v>-1000</s:v>
       </s:c>
     </s:row>
     <s:row r="16">
       <s:c r="A16" s="71" t="n">
-        <s:v>46212</s:v>
+        <s:v>46204</s:v>
       </s:c>
       <s:c r="B16" s="63" t="inlineStr">
         <s:is>
-          <s:t>ავანსი თანახმად ხელშეკრულება N1 7/6/2026 (22 000 აშშ დოლარი, ერ.კ. 2.6384)</s:t>
+          <s:t>თანახმად ხელშეკრულებისა; მომსახურება</s:t>
         </s:is>
       </s:c>
       <s:c r="C16" s="63" t="inlineStr">
         <s:is>
-          <s:t>შპს ჯიესენ გრუპ</s:t>
+          <s:t>გიორგი მღებრიშვილი</s:t>
         </s:is>
       </s:c>
       <s:c r="D16" s="63" t="inlineStr">
         <s:is>
-          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
+          <s:t>მომსახურება / Services</s:t>
         </s:is>
       </s:c>
       <s:c r="E16" s="72" t="n">
-        <s:v>-58044.8</s:v>
+        <s:v>-1600</s:v>
       </s:c>
     </s:row>
     <s:row r="17">
       <s:c r="A17" s="71" t="n">
-        <s:v>46216</s:v>
+        <s:v>46212</s:v>
       </s:c>
       <s:c r="B17" s="63" t="inlineStr">
         <s:is>
-          <s:t>ელექტრო მასალების შეძენა; ლითონის სამონტაჟო მასალები</s:t>
+          <s:t>ავანსი თანახმად ხელშეკრულება N1 7/6/2026 (22 000 აშშ დოლარი, ერ.კ. 2.6384)</s:t>
         </s:is>
       </s:c>
       <s:c r="C17" s="63" t="inlineStr">
         <s:is>
-          <s:t>ი.მ. შოთა კერესელიძე</s:t>
+          <s:t>შპს ჯიესენ გრუპ</s:t>
         </s:is>
       </s:c>
       <s:c r="D17" s="63" t="inlineStr">
         <s:is>
-          <s:t>მასალები / Materials</s:t>
+          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
       <s:c r="E17" s="72" t="n">
-        <s:v>-4660</s:v>
+        <s:v>-58044.8</s:v>
       </s:c>
     </s:row>
     <s:row r="18">
       <s:c r="A18" s="71" t="n">
-        <s:v>46219</s:v>
+        <s:v>46216</s:v>
       </s:c>
       <s:c r="B18" s="63" t="inlineStr">
         <s:is>
-          <s:t>ინვოისი 154-729 27/06/2026</s:t>
+          <s:t>ელექტრო მასალების შეძენა; ლითონის სამონტაჟო მასალები</s:t>
         </s:is>
       </s:c>
       <s:c r="C18" s="63" t="inlineStr">
         <s:is>
-          <s:t>შპს ენ ბი სი ჯგუფი</s:t>
+          <s:t>ი.მ. შოთა კერესელიძე</s:t>
         </s:is>
       </s:c>
       <s:c r="D18" s="63" t="inlineStr">
         <s:is>
-          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+          <s:t>მასალები / Materials</s:t>
         </s:is>
       </s:c>
       <s:c r="E18" s="72" t="n">
-        <s:v>-1450</s:v>
+        <s:v>-4660</s:v>
       </s:c>
     </s:row>
     <s:row r="19">
       <s:c r="A19" s="71" t="n">
-        <s:v>46238</s:v>
+        <s:v>46219</s:v>
       </s:c>
       <s:c r="B19" s="63" t="inlineStr">
         <s:is>
-          <s:t>ავანსი თანახმად ხელშეკრულება N1 7/6/2026 (5 000 აშშ დოლარი)</s:t>
+          <s:t>ინვოისი 154-729 27/06/2026</s:t>
         </s:is>
       </s:c>
       <s:c r="C19" s="63" t="inlineStr">
         <s:is>
-          <s:t>შპს ჯიესენ გრუპ</s:t>
+          <s:t>შპს ენ ბი სი ჯგუფი</s:t>
         </s:is>
       </s:c>
       <s:c r="D19" s="63" t="inlineStr">
         <s:is>
-          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
+          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
         </s:is>
       </s:c>
       <s:c r="E19" s="72" t="n">
-        <s:v>-13100</s:v>
+        <s:v>-1450</s:v>
       </s:c>
     </s:row>
     <s:row r="20">
@@ -13706,30 +13695,30 @@
       </s:c>
       <s:c r="B20" s="63" t="inlineStr">
         <s:is>
-          <s:t>ხელფასი</s:t>
+          <s:t>ავანსი თანახმად ხელშეკრულება N1 7/6/2026 (5 000 აშშ დოლარი)</s:t>
         </s:is>
       </s:c>
       <s:c r="C20" s="63" t="inlineStr">
         <s:is>
-          <s:t>გოდერძი მეტრეველი</s:t>
+          <s:t>შპს ჯიესენ გრუპ</s:t>
         </s:is>
       </s:c>
       <s:c r="D20" s="63" t="inlineStr">
         <s:is>
-          <s:t>ხელფასი / Salaries</s:t>
+          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
       <s:c r="E20" s="72" t="n">
-        <s:v>-2000</s:v>
+        <s:v>-13100</s:v>
       </s:c>
     </s:row>
     <s:row r="21">
       <s:c r="A21" s="71" t="n">
-        <s:v>46244</s:v>
+        <s:v>46238</s:v>
       </s:c>
       <s:c r="B21" s="63" t="inlineStr">
         <s:is>
-          <s:t>საქვეანგარიშოდ საჯარო რეესტრში გაწეული ხარჯისათვის</s:t>
+          <s:t>ხელფასი</s:t>
         </s:is>
       </s:c>
       <s:c r="C21" s="63" t="inlineStr">
@@ -13739,11 +13728,11 @@
       </s:c>
       <s:c r="D21" s="63" t="inlineStr">
         <s:is>
-          <s:t>სხვა / Other</s:t>
+          <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
       <s:c r="E21" s="72" t="n">
-        <s:v>-307</s:v>
+        <s:v>-2000</s:v>
       </s:c>
     </s:row>
     <s:row r="22">
@@ -13752,35 +13741,35 @@
       </s:c>
       <s:c r="B22" s="63" t="inlineStr">
         <s:is>
-          <s:t>საპენსიო გადასახადი</s:t>
+          <s:t>საქვეანგარიშოდ საჯარო რეესტრში გაწეული ხარჯისათვის</s:t>
         </s:is>
       </s:c>
       <s:c r="C22" s="63" t="inlineStr">
         <s:is>
-          <s:t>სსიპ საქართველოს საპენსიო ფონდი</s:t>
+          <s:t>გოდერძი მეტრეველი</s:t>
         </s:is>
       </s:c>
       <s:c r="D22" s="63" t="inlineStr">
         <s:is>
-          <s:t>გადასახადები / Taxes &amp; pension</s:t>
+          <s:t>სხვა / Other</s:t>
         </s:is>
       </s:c>
       <s:c r="E22" s="72" t="n">
-        <s:v>-170</s:v>
+        <s:v>-307</s:v>
       </s:c>
     </s:row>
     <s:row r="23">
       <s:c r="A23" s="71" t="n">
-        <s:v>46260</s:v>
+        <s:v>46244</s:v>
       </s:c>
       <s:c r="B23" s="63" t="inlineStr">
         <s:is>
-          <s:t>გადასახადების ერთიანი კოდი</s:t>
+          <s:t>საპენსიო გადასახადი</s:t>
         </s:is>
       </s:c>
       <s:c r="C23" s="63" t="inlineStr">
         <s:is>
-          <s:t>ხაზინის ერთიანი ანგარიში (RS)</s:t>
+          <s:t>სსიპ საქართველოს საპენსიო ფონდი</s:t>
         </s:is>
       </s:c>
       <s:c r="D23" s="63" t="inlineStr">
@@ -13789,7 +13778,7 @@
         </s:is>
       </s:c>
       <s:c r="E23" s="72" t="n">
-        <s:v>-900</s:v>
+        <s:v>-170</s:v>
       </s:c>
     </s:row>
     <s:row r="24">
@@ -13798,26 +13787,26 @@
       </s:c>
       <s:c r="B24" s="63" t="inlineStr">
         <s:is>
-          <s:t>ხელფასი</s:t>
+          <s:t>გადასახადების ერთიანი კოდი</s:t>
         </s:is>
       </s:c>
       <s:c r="C24" s="63" t="inlineStr">
         <s:is>
-          <s:t>ნატალია ქანანელი</s:t>
+          <s:t>ხაზინის ერთიანი ანგარიში (RS)</s:t>
         </s:is>
       </s:c>
       <s:c r="D24" s="63" t="inlineStr">
         <s:is>
-          <s:t>ხელფასი / Salaries</s:t>
+          <s:t>გადასახადები / Taxes &amp; pension</s:t>
         </s:is>
       </s:c>
       <s:c r="E24" s="72" t="n">
-        <s:v>-2000</s:v>
+        <s:v>-900</s:v>
       </s:c>
     </s:row>
     <s:row r="25">
       <s:c r="A25" s="71" t="n">
-        <s:v>46265</s:v>
+        <s:v>46260</s:v>
       </s:c>
       <s:c r="B25" s="63" t="inlineStr">
         <s:is>
@@ -13826,7 +13815,7 @@
       </s:c>
       <s:c r="C25" s="63" t="inlineStr">
         <s:is>
-          <s:t>გოდერძი მეტრეველი</s:t>
+          <s:t>ნატალია ქანანელი</s:t>
         </s:is>
       </s:c>
       <s:c r="D25" s="63" t="inlineStr">
@@ -13835,381 +13824,703 @@
         </s:is>
       </s:c>
       <s:c r="E25" s="72" t="n">
-        <s:v>-3000</s:v>
+        <s:v>-2000</s:v>
       </s:c>
     </s:row>
     <s:row r="26">
       <s:c r="A26" s="71" t="n">
+        <s:v>46265</s:v>
+      </s:c>
+      <s:c r="B26" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ხელფასი</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C26" s="63" t="inlineStr">
+        <s:is>
+          <s:t>გოდერძი მეტრეველი</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D26" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ხელფასი / Salaries</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E26" s="72" t="n">
+        <s:v>-3000</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="27">
+      <s:c r="A27" s="71" t="n">
         <s:v>46273</s:v>
       </s:c>
-      <s:c r="B26" s="63" t="inlineStr">
+      <s:c r="B27" s="63" t="inlineStr">
         <s:is>
           <s:t>საპენსიო გადასახადი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C26" s="63" t="inlineStr">
+      <s:c r="C27" s="63" t="inlineStr">
         <s:is>
           <s:t>სსიპ საქართველოს საპენსიო ფონდი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D26" s="63" t="inlineStr">
+      <s:c r="D27" s="63" t="inlineStr">
         <s:is>
           <s:t>გადასახადები / Taxes &amp; pension</s:t>
         </s:is>
       </s:c>
-      <s:c r="E26" s="72" t="n">
+      <s:c r="E27" s="72" t="n">
         <s:v>-400</s:v>
       </s:c>
     </s:row>
-    <s:row r="27">
-      <s:c r="A27" s="21" t="inlineStr">
+    <s:row r="28">
+      <s:c r="A28" s="71" t="n">
+        <s:v>46279</s:v>
+      </s:c>
+      <s:c r="B28" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ავანსი თანახმად ხელშეკრულება (ხელშ. N1)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C28" s="63" t="inlineStr">
+        <s:is>
+          <s:t>შპს ჯიესენ გრუპ</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D28" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E28" s="72" t="n">
+        <s:v>-1500</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="29">
+      <s:c r="A29" s="71" t="n">
+        <s:v>46279</s:v>
+      </s:c>
+      <s:c r="B29" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ავანსი თანახმად ხელშეკრულება (ხელშ. N1)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C29" s="63" t="inlineStr">
+        <s:is>
+          <s:t>შპს ჯიესენ გრუპ</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D29" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E29" s="72" t="n">
+        <s:v>-1400</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="30">
+      <s:c r="A30" s="71" t="n">
+        <s:v>46279</s:v>
+      </s:c>
+      <s:c r="B30" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ხელფასი</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C30" s="63" t="inlineStr">
+        <s:is>
+          <s:t>გოდერძი მეტრეველი</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D30" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ხელფასი / Salaries</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E30" s="72" t="n">
+        <s:v>-2000</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="31">
+      <s:c r="A31" s="71" t="n">
+        <s:v>46279</s:v>
+      </s:c>
+      <s:c r="B31" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ინვოისი 12866 14/09/2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C31" s="63" t="inlineStr">
+        <s:is>
+          <s:t>შპს კლუგერი 1</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D31" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E31" s="72" t="n">
+        <s:v>-1616</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="32">
+      <s:c r="A32" s="71" t="n">
+        <s:v>46279</s:v>
+      </s:c>
+      <s:c r="B32" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მომსახურება</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C32" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ვაჟა ბოდაველი</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D32" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მომსახურება / Services</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E32" s="72" t="n">
+        <s:v>-150</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="33">
+      <s:c r="A33" s="71" t="n">
+        <s:v>46279</s:v>
+      </s:c>
+      <s:c r="B33" s="63" t="inlineStr">
+        <s:is>
+          <s:t>სესხის ერთჯერადი მომსახურების საკომისიო GA/1-876787-001</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C33" s="63" t="inlineStr">
+        <s:is>
+          <s:t>სს ბანკი ქართუ</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D33" s="63" t="inlineStr">
+        <s:is>
+          <s:t>სხვა / Other</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E33" s="72" t="n">
+        <s:v>-60</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="34">
+      <s:c r="A34" s="71" t="n">
+        <s:v>46281</s:v>
+      </s:c>
+      <s:c r="B34" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ინვოისი 20260916A 16/09/2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C34" s="63" t="inlineStr">
+        <s:is>
+          <s:t>შპს იბოსთარ</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D34" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E34" s="72" t="n">
+        <s:v>-3030</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="35">
+      <s:c r="A35" s="71" t="n">
+        <s:v>46281</s:v>
+      </s:c>
+      <s:c r="B35" s="63" t="inlineStr">
+        <s:is>
+          <s:t>სასაქონლო ზედნადებებით პროდუქციის საფასური</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C35" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ი.მ. ლალი ზეიკიძე</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D35" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მასალები / Materials</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E35" s="72" t="n">
+        <s:v>-467.7</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="36">
+      <s:c r="A36" s="71" t="n">
+        <s:v>46281</s:v>
+      </s:c>
+      <s:c r="B36" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ცემენტის ღირებულება</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C36" s="63" t="inlineStr">
+        <s:is>
+          <s:t>სოსო ხლუსიძე</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D36" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მასალები / Materials</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E36" s="72" t="n">
+        <s:v>-170</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="37">
+      <s:c r="A37" s="71" t="n">
+        <s:v>46283</s:v>
+      </s:c>
+      <s:c r="B37" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ცემენტის ღირებულება, ზედნადები 1008422939 18/09/2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C37" s="63" t="inlineStr">
+        <s:is>
+          <s:t>სოსო ხლუსიძე</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D37" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მასალები / Materials</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E37" s="72" t="n">
+        <s:v>-425</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="38">
+      <s:c r="A38" s="71" t="n">
+        <s:v>46283</s:v>
+      </s:c>
+      <s:c r="B38" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მომსახურება</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C38" s="63" t="inlineStr">
+        <s:is>
+          <s:t>რაუფ ბაირამოვი</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D38" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მომსახურება / Services</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E38" s="72" t="n">
+        <s:v>-820</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="39">
+      <s:c r="A39" s="71" t="n">
+        <s:v>46283</s:v>
+      </s:c>
+      <s:c r="B39" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ამწე მომსახურება — სამონტაჟო სამუშაო, კაპიტალიზებული</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C39" s="63" t="inlineStr">
+        <s:is>
+          <s:t>აკაკი ბუჩაშვილი</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D39" s="63" t="inlineStr">
+        <s:is>
+          <s:t>სხვა / Other</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E39" s="72" t="n">
+        <s:v>-550</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="40">
+      <s:c r="A40" s="71" t="n">
+        <s:v>46283</s:v>
+      </s:c>
+      <s:c r="B40" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საბანკო საკომისიოები — 11 გადარიცხვა, 11–18/09/2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C40" s="63" t="inlineStr">
+        <s:is>
+          <s:t>სს ბანკი ქართუ</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D40" s="63" t="inlineStr">
+        <s:is>
+          <s:t>სხვა / Other</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E40" s="72" t="n">
+        <s:v>-12.08</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="41">
+      <s:c r="A41" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B27" s="24" t="inlineStr"/>
-      <s:c r="C27" s="24" t="inlineStr"/>
-      <s:c r="D27" s="24" t="inlineStr"/>
-      <s:c r="E27" s="30">
-        <s:f>SUM(E12:E26)</s:f>
-        <s:v>-90541.21</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="29">
-      <s:c r="A29" s="10" t="inlineStr">
+      <s:c r="B41" s="24" t="inlineStr"/>
+      <s:c r="C41" s="24" t="inlineStr"/>
+      <s:c r="D41" s="24" t="inlineStr"/>
+      <s:c r="E41" s="30">
+        <s:f>SUM(E13:E40)</s:f>
+        <s:v>-102741.99</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="43">
+      <s:c r="A43" s="10" t="inlineStr">
         <s:is>
           <s:t>კატეგორიების მიხედვით / BY CATEGORY</s:t>
         </s:is>
       </s:c>
-      <s:c r="B29" s="11" t="n"/>
-      <s:c r="C29" s="11" t="n"/>
-      <s:c r="D29" s="11" t="n"/>
-      <s:c r="E29" s="11" t="n"/>
-    </s:row>
-    <s:row r="30">
-      <s:c r="A30" s="59" t="inlineStr">
+      <s:c r="B43" s="11" t="n"/>
+      <s:c r="C43" s="11" t="n"/>
+      <s:c r="D43" s="11" t="n"/>
+      <s:c r="E43" s="11" t="n"/>
+    </s:row>
+    <s:row r="44">
+      <s:c r="A44" s="59" t="inlineStr">
         <s:is>
           <s:t>კატეგორია / Category</s:t>
         </s:is>
       </s:c>
-      <s:c r="B30" s="12" t="inlineStr">
+      <s:c r="B44" s="12" t="inlineStr">
         <s:is>
           <s:t>თანხა GEL / Amount</s:t>
         </s:is>
       </s:c>
-      <s:c r="C30" s="12" t="inlineStr">
+      <s:c r="C44" s="12" t="inlineStr">
         <s:is>
           <s:t>% ჯამიდან / of total</s:t>
         </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="31">
-      <s:c r="A31" s="20" t="inlineStr">
-        <s:is>
-          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B31" s="31">
-        <s:f>-SUMIF($D$12:$D$26,$A31,$E$12:$E$26)</s:f>
-        <s:v>71144.8</s:v>
-      </s:c>
-      <s:c r="C31" s="26">
-        <s:f>IFERROR($B31/$B$38,0)</s:f>
-        <s:v>0.7857725780338036</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="32">
-      <s:c r="A32" s="20" t="inlineStr">
-        <s:is>
-          <s:t>ხელფასი / Salaries</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B32" s="31">
-        <s:f>-SUMIF($D$12:$D$26,$A32,$E$12:$E$26)</s:f>
-        <s:v>8000.0</s:v>
-      </s:c>
-      <s:c r="C32" s="26">
-        <s:f>IFERROR($B32/$B$38,0)</s:f>
-        <s:v>0.08835755563681996</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="33">
-      <s:c r="A33" s="20" t="inlineStr">
-        <s:is>
-          <s:t>გადასახადები / Taxes &amp; pension</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B33" s="31">
-        <s:f>-SUMIF($D$12:$D$26,$A33,$E$12:$E$26)</s:f>
-        <s:v>1470.0</s:v>
-      </s:c>
-      <s:c r="C33" s="26">
-        <s:f>IFERROR($B33/$B$38,0)</s:f>
-        <s:v>0.016235700848265668</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="34">
-      <s:c r="A34" s="20" t="inlineStr">
-        <s:is>
-          <s:t>მომსახურება / Services</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B34" s="31">
-        <s:f>-SUMIF($D$12:$D$26,$A34,$E$12:$E$26)</s:f>
-        <s:v>2100.0</s:v>
-      </s:c>
-      <s:c r="C34" s="26">
-        <s:f>IFERROR($B34/$B$38,0)</s:f>
-        <s:v>0.02319385835466524</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="35">
-      <s:c r="A35" s="20" t="inlineStr">
-        <s:is>
-          <s:t>მასალები / Materials</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B35" s="31">
-        <s:f>-SUMIF($D$12:$D$26,$A35,$E$12:$E$26)</s:f>
-        <s:v>4660.0</s:v>
-      </s:c>
-      <s:c r="C35" s="26">
-        <s:f>IFERROR($B35/$B$38,0)</s:f>
-        <s:v>0.05146827615844762</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="36">
-      <s:c r="A36" s="20" t="inlineStr">
-        <s:is>
-          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B36" s="31">
-        <s:f>-SUMIF($D$12:$D$26,$A36,$E$12:$E$26)</s:f>
-        <s:v>2859.41</s:v>
-      </s:c>
-      <s:c r="C36" s="26">
-        <s:f>IFERROR($B36/$B$38,0)</s:f>
-        <s:v>0.03158130977043492</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="37">
-      <s:c r="A37" s="20" t="inlineStr">
-        <s:is>
-          <s:t>სხვა / Other</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B37" s="31">
-        <s:f>-SUMIF($D$12:$D$26,$A37,$E$12:$E$26)</s:f>
-        <s:v>307.0</s:v>
-      </s:c>
-      <s:c r="C37" s="26">
-        <s:f>IFERROR($B37/$B$38,0)</s:f>
-        <s:v>0.0033907211975629657</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="38">
-      <s:c r="A38" s="21" t="inlineStr">
-        <s:is>
-          <s:t>სულ / TOTAL</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B38" s="30">
-        <s:f>SUM(B31:B37)</s:f>
-        <s:v>90541.21</s:v>
-      </s:c>
-      <s:c r="C38" s="23">
-        <s:f>IFERROR(B38/B38,0)</s:f>
-        <s:v>1.0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="39">
-      <s:c r="A39" s="3" t="inlineStr">
-        <s:is>
-          <s:t>შემოწმება / Check vs statement total (must be 0)</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B39" s="73">
-        <s:f>B38+E27</s:f>
-        <s:v>0.0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="41">
-      <s:c r="A41" s="10" t="inlineStr">
-        <s:is>
-          <s:t>თვეების მიხედვით / BY MONTH</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B41" s="11" t="n"/>
-      <s:c r="C41" s="11" t="n"/>
-      <s:c r="D41" s="11" t="n"/>
-      <s:c r="E41" s="11" t="n"/>
-    </s:row>
-    <s:row r="42">
-      <s:c r="A42" s="59" t="inlineStr">
-        <s:is>
-          <s:t>თვე / Month</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B42" s="12" t="inlineStr">
-        <s:is>
-          <s:t>თანხა GEL / Amount</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="43">
-      <s:c r="A43" s="20" t="inlineStr">
-        <s:is>
-          <s:t>ივლისი 2026 / July</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B43" s="31">
-        <s:f>-SUMPRODUCT(($A$12:$A$26&gt;=DATE(2026,7,1))*($A$12:$A$26&lt;=DATE(2026,7,31))*$E$12:$E$26)</s:f>
-        <s:v>68664.21</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="44">
-      <s:c r="A44" s="20" t="inlineStr">
-        <s:is>
-          <s:t>აგვისტო 2026 / August</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B44" s="31">
-        <s:f>-SUMPRODUCT(($A$12:$A$26&gt;=DATE(2026,8,1))*($A$12:$A$26&lt;=DATE(2026,8,31))*$E$12:$E$26)</s:f>
-        <s:v>21477.0</s:v>
       </s:c>
     </s:row>
     <s:row r="45">
       <s:c r="A45" s="20" t="inlineStr">
         <s:is>
-          <s:t>სექტემბერი 2026 (08-მდე) / September (to the 8th)</s:t>
+          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
       <s:c r="B45" s="31">
-        <s:f>-SUMPRODUCT(($A$12:$A$26&gt;=DATE(2026,9,1))*($A$12:$A$26&lt;=DATE(2026,9,30))*$E$12:$E$26)</s:f>
-        <s:v>400.0</s:v>
+        <s:f>-SUMIF($D$13:$D$40,$A45,$E$13:$E$40)</s:f>
+        <s:v>74044.8</s:v>
+      </s:c>
+      <s:c r="C45" s="26">
+        <s:f>IFERROR($B45/$B$52,0)</s:f>
+        <s:v>0.720686838944817</s:v>
       </s:c>
     </s:row>
     <s:row r="46">
-      <s:c r="A46" s="21" t="inlineStr">
+      <s:c r="A46" s="20" t="inlineStr">
+        <s:is>
+          <s:t>ხელფასი / Salaries</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B46" s="31">
+        <s:f>-SUMIF($D$13:$D$40,$A46,$E$13:$E$40)</s:f>
+        <s:v>10000.0</s:v>
+      </s:c>
+      <s:c r="C46" s="26">
+        <s:f>IFERROR($B46/$B$52,0)</s:f>
+        <s:v>0.09733118854326259</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="47">
+      <s:c r="A47" s="20" t="inlineStr">
+        <s:is>
+          <s:t>გადასახადები / Taxes &amp; pension</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B47" s="31">
+        <s:f>-SUMIF($D$13:$D$40,$A47,$E$13:$E$40)</s:f>
+        <s:v>1470.0</s:v>
+      </s:c>
+      <s:c r="C47" s="26">
+        <s:f>IFERROR($B47/$B$52,0)</s:f>
+        <s:v>0.0143076847158596</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="48">
+      <s:c r="A48" s="20" t="inlineStr">
+        <s:is>
+          <s:t>მომსახურება / Services</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B48" s="31">
+        <s:f>-SUMIF($D$13:$D$40,$A48,$E$13:$E$40)</s:f>
+        <s:v>3070.0</s:v>
+      </s:c>
+      <s:c r="C48" s="26">
+        <s:f>IFERROR($B48/$B$52,0)</s:f>
+        <s:v>0.029880674882781615</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="49">
+      <s:c r="A49" s="20" t="inlineStr">
+        <s:is>
+          <s:t>მასალები / Materials</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B49" s="31">
+        <s:f>-SUMIF($D$13:$D$40,$A49,$E$13:$E$40)</s:f>
+        <s:v>5722.7</s:v>
+      </s:c>
+      <s:c r="C49" s="26">
+        <s:f>IFERROR($B49/$B$52,0)</s:f>
+        <s:v>0.05569971926765288</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="50">
+      <s:c r="A50" s="20" t="inlineStr">
+        <s:is>
+          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B50" s="31">
+        <s:f>-SUMIF($D$13:$D$40,$A50,$E$13:$E$40)</s:f>
+        <s:v>7505.41</s:v>
+      </s:c>
+      <s:c r="C50" s="26">
+        <s:f>IFERROR($B50/$B$52,0)</s:f>
+        <s:v>0.07305104758044885</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="51">
+      <s:c r="A51" s="20" t="inlineStr">
+        <s:is>
+          <s:t>სხვა / Other</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B51" s="31">
+        <s:f>-SUMIF($D$13:$D$40,$A51,$E$13:$E$40)</s:f>
+        <s:v>929.08</s:v>
+      </s:c>
+      <s:c r="C51" s="26">
+        <s:f>IFERROR($B51/$B$52,0)</s:f>
+        <s:v>0.009042846065177442</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="52">
+      <s:c r="A52" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B46" s="30">
-        <s:f>SUM(B43:B45)</s:f>
-        <s:v>90541.21</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="48">
-      <s:c r="A48" s="10" t="inlineStr">
+      <s:c r="B52" s="30">
+        <s:f>SUM(B45:B51)</s:f>
+        <s:v>102741.99</s:v>
+      </s:c>
+      <s:c r="C52" s="23">
+        <s:f>IFERROR(B52/B52,0)</s:f>
+        <s:v>1.0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="53">
+      <s:c r="A53" s="3" t="inlineStr">
+        <s:is>
+          <s:t>შემოწმება / Check vs statement total (must be 0)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B53" s="73">
+        <s:f>B52+E41</s:f>
+        <s:v>0.0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="55">
+      <s:c r="A55" s="10" t="inlineStr">
+        <s:is>
+          <s:t>თვეების მიხედვით / BY MONTH</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B55" s="11" t="n"/>
+      <s:c r="C55" s="11" t="n"/>
+      <s:c r="D55" s="11" t="n"/>
+      <s:c r="E55" s="11" t="n"/>
+    </s:row>
+    <s:row r="56">
+      <s:c r="A56" s="59" t="inlineStr">
+        <s:is>
+          <s:t>თვე / Month</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B56" s="12" t="inlineStr">
+        <s:is>
+          <s:t>თანხა GEL / Amount</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="57">
+      <s:c r="A57" s="20" t="inlineStr">
+        <s:is>
+          <s:t>ივლისი 2026 / July</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B57" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$40&gt;=DATE(2026,7,1))*($A$13:$A$40&lt;=DATE(2026,7,31))*$E$13:$E$40)</s:f>
+        <s:v>68664.21</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="58">
+      <s:c r="A58" s="20" t="inlineStr">
+        <s:is>
+          <s:t>აგვისტო 2026 / August</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B58" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$40&gt;=DATE(2026,8,1))*($A$13:$A$40&lt;=DATE(2026,8,31))*$E$13:$E$40)</s:f>
+        <s:v>21477.0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="59">
+      <s:c r="A59" s="20" t="inlineStr">
+        <s:is>
+          <s:t>სექტემბერი 2026 (18-მდე) / September (to the 18th)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B59" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$40&gt;=DATE(2026,9,1))*($A$13:$A$40&lt;=DATE(2026,9,30))*$E$13:$E$40)</s:f>
+        <s:v>12600.78</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="60">
+      <s:c r="A60" s="21" t="inlineStr">
+        <s:is>
+          <s:t>სულ / TOTAL</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B60" s="30">
+        <s:f>SUM(B57:B59)</s:f>
+        <s:v>102741.99</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="62">
+      <s:c r="A62" s="10" t="inlineStr">
         <s:is>
           <s:t>ძირითადი ფაქტები / KEY FACTS</s:t>
         </s:is>
       </s:c>
-      <s:c r="B48" s="11" t="n"/>
-      <s:c r="C48" s="11" t="n"/>
-      <s:c r="D48" s="11" t="n"/>
-      <s:c r="E48" s="11" t="n"/>
-    </s:row>
-    <s:row r="49">
-      <s:c r="A49" s="17" t="inlineStr">
+      <s:c r="B62" s="11" t="n"/>
+      <s:c r="C62" s="11" t="n"/>
+      <s:c r="D62" s="11" t="n"/>
+      <s:c r="E62" s="11" t="n"/>
+    </s:row>
+    <s:row r="63">
+      <s:c r="A63" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 09/07/2026 (22,000 USD) / FX rate on the 09/07/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B49" s="74">
-        <s:f>-E16/22000</s:f>
+      <s:c r="B63" s="74">
+        <s:f>-E17/22000</s:f>
         <s:v>2.6384000000000003</s:v>
       </s:c>
-      <s:c r="C49" s="42" t="inlineStr">
+      <s:c r="C63" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში მითითებული კურსი 2.6384 / the description states 2.6384</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="50">
-      <s:c r="A50" s="17" t="inlineStr">
+    <s:row r="64">
+      <s:c r="A64" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 04/08/2026 (5,000 USD) / FX rate on the 04/08/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B50" s="74">
-        <s:f>-E19/5000</s:f>
+      <s:c r="B64" s="74">
+        <s:f>-E20/5000</s:f>
         <s:v>2.62</s:v>
       </s:c>
-      <s:c r="C50" s="42" t="inlineStr">
+      <s:c r="C64" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში კურსი არ არის მითითებული / no rate stated in the description</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="51">
-      <s:c r="A51" s="17" t="inlineStr">
+    <s:row r="65">
+      <s:c r="A65" s="17" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსები / Construction advances paid (USD)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B51" s="75">
+      <s:c r="B65" s="75">
         <s:f>22000+5000</s:f>
         <s:v>27000.0</s:v>
       </s:c>
-      <s:c r="C51" s="42" t="inlineStr">
+      <s:c r="C65" s="42" t="inlineStr">
         <s:is>
           <s:t>ხელშეკრულება N1, 7/6/2026, შპს ჯიესენ გრუპ / contract N1 of 7/6/2026 with LLC GSN Group</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="52">
-      <s:c r="A52" s="17" t="inlineStr">
+    <s:row r="66">
+      <s:c r="A66" s="17" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსები / Construction advances paid (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B52" s="76">
-        <s:f>B31</s:f>
-        <s:v>71144.8</s:v>
-      </s:c>
-      <s:c r="C52" s="42" t="inlineStr">
+      <s:c r="B66" s="76">
+        <s:f>B45</s:f>
+        <s:v>74044.8</s:v>
+      </s:c>
+      <s:c r="C66" s="42" t="inlineStr">
         <s:is>
           <s:t>ორივე გადარიცხვის ჯამი / the two transfers above</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="53">
-      <s:c r="A53" s="17" t="inlineStr">
+    <s:row r="67">
+      <s:c r="A67" s="17" t="inlineStr">
         <s:is>
           <s:t>სულ გადახდილი / Total paid out (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B53" s="38">
-        <s:f>-E27</s:f>
-        <s:v>90541.21</s:v>
-      </s:c>
-      <s:c r="C53" s="42" t="inlineStr">
+      <s:c r="B67" s="38">
+        <s:f>-E41</s:f>
+        <s:v>102741.99</s:v>
+      </s:c>
+      <s:c r="C67" s="42" t="inlineStr">
         <s:is>
           <s:t>01/07–08/09/2026</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="54">
-      <s:c r="A54" s="17" t="inlineStr">
+    <s:row r="68">
+      <s:c r="A68" s="17" t="inlineStr">
         <s:is>
           <s:t>შემოსავალი ამონაწერში / Inflows in the statement (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B54" s="38">
+      <s:c r="B68" s="38">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C54" s="42" t="inlineStr">
+      <s:c r="C68" s="42" t="inlineStr">
         <s:is>
           <s:t>ამონაწერში შემოსავალი არ ფიქსირდება — 140,000 USD სესხი ამ ანგარიშზე ამ პერიოდში არ ჩანს. / The statement shows no inflows; the USD 140,000 loan is not visible in this account for this period.</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="56">
-      <s:c r="A56" s="2" t="inlineStr">
+    <s:row r="70">
+      <s:c r="A70" s="2" t="inlineStr">
         <s:is>
           <s:t>შენიშვნა: ამონაწერი მხოლოდ ერთ ანგარიშს ფარავს და მასში შემოსავალი არ არის. თუ სესხი სხვა ანგარიშზეა ჩარიცხული, დაამატეთ ის ამონაწერიც. / Note: the statement covers one account and contains no inflows. If the loan was disbursed into another account, add that statement too.</s:t>
         </s:is>

--- a/finance/Greenhouse_CashFlow_2000m2.xlsx
+++ b/finance/Greenhouse_CashFlow_2000m2.xlsx
@@ -1234,15 +1234,15 @@
       </s:c>
       <s:c r="B7" s="18">
         <s:f>B21</s:f>
-        <s:v>102741.99</s:v>
+        <s:v>217241.99</s:v>
       </s:c>
       <s:c r="C7" s="19">
         <s:f>IFERROR(B7/$B$6,0)</s:f>
-        <s:v>0.16438718400000002</s:v>
+        <s:v>0.347587184</s:v>
       </s:c>
       <s:c r="D7" s="20" t="str">
         <s:f>REPT("|",ROUND(C7*40,0))</s:f>
-        <s:v>|||||||</s:v>
+        <s:v>||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="8">
@@ -1253,15 +1253,15 @@
       </s:c>
       <s:c r="B8" s="18">
         <s:f>D34</s:f>
-        <s:v>255663.2</s:v>
+        <s:v>150127.19999999998</s:v>
       </s:c>
       <s:c r="C8" s="19">
         <s:f>IFERROR(B8/$B$6,0)</s:f>
-        <s:v>0.40906112</s:v>
+        <s:v>0.24020351999999998</s:v>
       </s:c>
       <s:c r="D8" s="20" t="str">
         <s:f>REPT("|",ROUND(C8*40,0))</s:f>
-        <s:v>||||||||||||||||</s:v>
+        <s:v>||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="9">
@@ -1272,15 +1272,15 @@
       </s:c>
       <s:c r="B9" s="22">
         <s:f>B7+B8</s:f>
-        <s:v>358405.19</s:v>
+        <s:v>367369.18999999994</s:v>
       </s:c>
       <s:c r="C9" s="23">
         <s:f>IFERROR(B9/$B$6,0)</s:f>
-        <s:v>0.573448304</s:v>
+        <s:v>0.5877907039999999</s:v>
       </s:c>
       <s:c r="D9" s="24" t="str">
         <s:f>REPT("|",ROUND(C9*40,0))</s:f>
-        <s:v>|||||||||||||||||||||||</s:v>
+        <s:v>||||||||||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="10">
@@ -1291,15 +1291,15 @@
       </s:c>
       <s:c r="B10" s="22">
         <s:f>B6-B9</s:f>
-        <s:v>266594.81</s:v>
+        <s:v>257630.81000000006</s:v>
       </s:c>
       <s:c r="C10" s="23">
         <s:f>IFERROR(B10/$B$6,0)</s:f>
-        <s:v>0.426551696</s:v>
+        <s:v>0.4122092960000001</s:v>
       </s:c>
       <s:c r="D10" s="24" t="str">
         <s:f>REPT("|",ROUND(C10*40,0))</s:f>
-        <s:v>|||||||||||||||||</s:v>
+        <s:v>||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="12">
@@ -1353,12 +1353,12 @@
         </s:is>
       </s:c>
       <s:c r="B14" s="25">
-        <s:f>Actuals!B45</s:f>
-        <s:v>74044.8</s:v>
+        <s:f>Actuals!B47</s:f>
+        <s:v>178544.8</s:v>
       </s:c>
       <s:c r="C14" s="26">
         <s:f>IFERROR(B14/$B$21,0)</s:f>
-        <s:v>0.720686838944817</s:v>
+        <s:v>0.8218705785193737</s:v>
       </s:c>
       <s:c r="D14" s="27" t="inlineStr">
         <s:is>
@@ -1383,12 +1383,12 @@
         </s:is>
       </s:c>
       <s:c r="B15" s="25">
-        <s:f>Actuals!B46</s:f>
+        <s:f>Actuals!B48</s:f>
         <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C15" s="26">
         <s:f>IFERROR(B15/$B$21,0)</s:f>
-        <s:v>0.09733118854326259</s:v>
+        <s:v>0.04603161663175706</s:v>
       </s:c>
       <s:c r="D15" s="27" t="inlineStr">
         <s:is>
@@ -1408,12 +1408,12 @@
         </s:is>
       </s:c>
       <s:c r="B16" s="25">
-        <s:f>Actuals!B47</s:f>
+        <s:f>Actuals!B49</s:f>
         <s:v>1470.0</s:v>
       </s:c>
       <s:c r="C16" s="26">
         <s:f>IFERROR(B16/$B$21,0)</s:f>
-        <s:v>0.0143076847158596</s:v>
+        <s:v>0.006766647644868288</s:v>
       </s:c>
       <s:c r="D16" s="27" t="inlineStr">
         <s:is>
@@ -1433,12 +1433,12 @@
         </s:is>
       </s:c>
       <s:c r="B17" s="25">
-        <s:f>Actuals!B48</s:f>
-        <s:v>3070.0</s:v>
+        <s:f>Actuals!B50</s:f>
+        <s:v>13070.0</s:v>
       </s:c>
       <s:c r="C17" s="26">
         <s:f>IFERROR(B17/$B$21,0)</s:f>
-        <s:v>0.029880674882781615</s:v>
+        <s:v>0.06016332293770647</s:v>
       </s:c>
       <s:c r="D17" s="27" t="inlineStr">
         <s:is>
@@ -1458,12 +1458,12 @@
         </s:is>
       </s:c>
       <s:c r="B18" s="25">
-        <s:f>Actuals!B49</s:f>
+        <s:f>Actuals!B51</s:f>
         <s:v>5722.7</s:v>
       </s:c>
       <s:c r="C18" s="26">
         <s:f>IFERROR(B18/$B$21,0)</s:f>
-        <s:v>0.05569971926765288</s:v>
+        <s:v>0.02634251324985561</s:v>
       </s:c>
       <s:c r="D18" s="27" t="inlineStr">
         <s:is>
@@ -1483,12 +1483,12 @@
         </s:is>
       </s:c>
       <s:c r="B19" s="25">
-        <s:f>Actuals!B50</s:f>
+        <s:f>Actuals!B52</s:f>
         <s:v>7505.41</s:v>
       </s:c>
       <s:c r="C19" s="26">
         <s:f>IFERROR(B19/$B$21,0)</s:f>
-        <s:v>0.07305104758044885</s:v>
+        <s:v>0.03454861557841557</s:v>
       </s:c>
       <s:c r="D19" s="27" t="inlineStr">
         <s:is>
@@ -1508,12 +1508,12 @@
         </s:is>
       </s:c>
       <s:c r="B20" s="25">
-        <s:f>Actuals!B51</s:f>
+        <s:f>Actuals!B53</s:f>
         <s:v>929.08</s:v>
       </s:c>
       <s:c r="C20" s="26">
         <s:f>IFERROR(B20/$B$21,0)</s:f>
-        <s:v>0.009042846065177442</s:v>
+        <s:v>0.004276705438023285</s:v>
       </s:c>
       <s:c r="D20" s="27" t="inlineStr">
         <s:is>
@@ -1534,7 +1534,7 @@
       </s:c>
       <s:c r="B21" s="30">
         <s:f>SUM(B14:B20)</s:f>
-        <s:v>102741.99</s:v>
+        <s:v>217241.99</s:v>
       </s:c>
       <s:c r="C21" s="23">
         <s:f>IFERROR(B21/B21,0)</s:f>
@@ -1591,7 +1591,7 @@
         </s:is>
       </s:c>
       <s:c r="B25" s="25">
-        <s:f>Actuals!B57</s:f>
+        <s:f>Actuals!B59</s:f>
         <s:v>68664.21</s:v>
       </s:c>
       <s:c r="C25" s="31">
@@ -1610,7 +1610,7 @@
         </s:is>
       </s:c>
       <s:c r="B26" s="25">
-        <s:f>Actuals!B58</s:f>
+        <s:f>Actuals!B60</s:f>
         <s:v>21477.0</s:v>
       </s:c>
       <s:c r="C26" s="31">
@@ -1625,20 +1625,20 @@
     <s:row r="27">
       <s:c r="A27" s="20" t="inlineStr">
         <s:is>
-          <s:t>სექტემბერი 2026 (18-მდე) / September (to the 18th)</s:t>
+          <s:t>სექტემბერი 2026 (21-მდე) / September (to the 21st)</s:t>
         </s:is>
       </s:c>
       <s:c r="B27" s="25">
-        <s:f>Actuals!B59</s:f>
-        <s:v>12600.78</s:v>
+        <s:f>Actuals!B61</s:f>
+        <s:v>127100.78</s:v>
       </s:c>
       <s:c r="C27" s="31">
         <s:f>SUM($B$25:B27)</s:f>
-        <s:v>102741.99</s:v>
+        <s:v>217241.99</s:v>
       </s:c>
       <s:c r="D27" s="18">
         <s:f>$B$6-C27</s:f>
-        <s:v>522258.01</s:v>
+        <s:v>407758.01</s:v>
       </s:c>
     </s:row>
     <s:row r="28">
@@ -1649,7 +1649,7 @@
       </s:c>
       <s:c r="B28" s="30">
         <s:f>SUM(B25:B27)</s:f>
-        <s:v>102741.99</s:v>
+        <s:v>217241.99</s:v>
       </s:c>
       <s:c r="C28" s="30">
         <s:f>B28-B21</s:f>
@@ -1657,7 +1657,7 @@
       </s:c>
       <s:c r="D28" s="22">
         <s:f>$B$6-B28</s:f>
-        <s:v>522258.01</s:v>
+        <s:v>407758.01</s:v>
       </s:c>
       <s:c r="G28" s="2" t="inlineStr">
         <s:is>
@@ -1729,20 +1729,20 @@
         </s:is>
       </s:c>
       <s:c r="B33" s="34">
-        <s:f>22000+5000+2900/Assumptions!$B$28</s:f>
-        <s:v>28099.151000606427</s:v>
+        <s:f>22000+5000+40000+2900/Assumptions!$B$28</s:f>
+        <s:v>68099.15100060643</s:v>
       </s:c>
       <s:c r="C33" s="35">
         <s:f>IFERROR(D33/B33,0)</s:f>
-        <s:v>2.635125879725049</s:v>
+        <s:v>2.6218359168443968</s:v>
       </s:c>
       <s:c r="D33" s="25">
-        <s:f>Actuals!B45</s:f>
-        <s:v>74044.8</s:v>
+        <s:f>Actuals!B47</s:f>
+        <s:v>178544.8</s:v>
       </s:c>
       <s:c r="G33" s="2" t="inlineStr">
         <s:is>
-          <s:t>09/07/2026 — 22,000 $ · 04/08/2026 — 5,000 $ · 14/09/2026 — 2,900 ₾ ≈ 1,099 $ (ერ.კ. 2.6384)</s:t>
+          <s:t>09/07 — 22,000 $ · 04/08 — 5,000 $ · 14/09 — 2,900 ₾ ≈ 1,099 $ (ერ.კ. 2.6384) · 19/09 — 40,000 $ ერ.კ. 2.6125</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -1754,7 +1754,7 @@
       </s:c>
       <s:c r="B34" s="36">
         <s:f>B32-B33</s:f>
-        <s:v>96900.84899939358</s:v>
+        <s:v>56900.848999393565</s:v>
       </s:c>
       <s:c r="C34" s="37">
         <s:f>Assumptions!$B$28</s:f>
@@ -1762,7 +1762,7 @@
       </s:c>
       <s:c r="D34" s="22">
         <s:f>B34*Assumptions!$B$28</s:f>
-        <s:v>255663.2</s:v>
+        <s:v>150127.19999999998</s:v>
       </s:c>
     </s:row>
     <s:row r="35">
@@ -1773,7 +1773,7 @@
       </s:c>
       <s:c r="B35" s="19">
         <s:f>IFERROR(B33/B32,0)</s:f>
-        <s:v>0.22479320800485142</s:v>
+        <s:v>0.5447932080048514</s:v>
       </s:c>
     </s:row>
     <s:row r="37">
@@ -1796,11 +1796,11 @@
       </s:c>
       <s:c r="B38" s="38">
         <s:f>SUMIF($D$14:$D$20,"CAPEX",$B$14:$B$20)</s:f>
-        <s:v>88201.99</s:v>
+        <s:v>192701.99</s:v>
       </s:c>
       <s:c r="C38" s="19">
         <s:f>IFERROR(B38/$B$21,0)</s:f>
-        <s:v>0.8584804518580962</s:v>
+        <s:v>0.8870384127856682</s:v>
       </s:c>
       <s:c r="G38" s="2" t="inlineStr">
         <s:is>
@@ -1816,11 +1816,11 @@
       </s:c>
       <s:c r="B39" s="38">
         <s:f>SUMIF($D$14:$D$20,"OPEX",$B$14:$B$20)</s:f>
-        <s:v>14540.0</s:v>
+        <s:v>24540.0</s:v>
       </s:c>
       <s:c r="C39" s="19">
         <s:f>IFERROR(B39/$B$21,0)</s:f>
-        <s:v>0.14151954814190382</s:v>
+        <s:v>0.11296158721433182</s:v>
       </s:c>
       <s:c r="G39" s="2" t="inlineStr">
         <s:is>
@@ -2845,7 +2845,7 @@
       </s:c>
       <s:c r="B58" s="56">
         <s:f>Budget!B21</s:f>
-        <s:v>102741.99</s:v>
+        <s:v>217241.99</s:v>
       </s:c>
       <s:c r="C58" s="41" t="inlineStr">
         <s:is>
@@ -2866,7 +2866,7 @@
       </s:c>
       <s:c r="B59" s="56">
         <s:f>Budget!B38</s:f>
-        <s:v>88201.99</s:v>
+        <s:v>192701.99</s:v>
       </s:c>
       <s:c r="C59" s="41" t="inlineStr">
         <s:is>
@@ -13393,7 +13393,7 @@
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
     <s:pageSetUpPr/>
   </s:sheetPr>
-  <s:dimension ref="A1:E70"/>
+  <s:dimension ref="A1:E72"/>
   <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <s:cols>
     <s:col width="13" customWidth="1" min="1" max="1"/>
@@ -13426,7 +13426,7 @@
       </s:c>
       <s:c r="B4" s="20" t="inlineStr">
         <s:is>
-          <s:t>transaction_history_all_accounts_20260401_20260909.csv · transaction_history_all_accounts_20260911_20260918.xlsx (Google Drive)</s:t>
+          <s:t>transaction_history_all_accounts_20260401_20260909.csv · transaction_history_all_accounts_20260911_20260918.xlsx (Google Drive) · 19–21/09 მფლობელის მონაცემი, ამონაწერით დასადასტურებელი / reported by the owner, to be confirmed against the statement</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -13462,7 +13462,7 @@
       </s:c>
       <s:c r="B7" s="20" t="inlineStr">
         <s:is>
-          <s:t>01/04/2026 – 18/09/2026</s:t>
+          <s:t>01/04/2026 – 21/09/2026</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -13474,7 +13474,7 @@
       </s:c>
       <s:c r="B8" s="20" t="inlineStr">
         <s:is>
-          <s:t>01/07/2026 – 18/09/2026 · 28 გადარიცხვა / 28 payments</s:t>
+          <s:t>01/07/2026 – 21/09/2026 · 30 გადარიცხვა / 30 payments</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -14173,354 +14173,400 @@
       </s:c>
     </s:row>
     <s:row r="41">
-      <s:c r="A41" s="21" t="inlineStr">
+      <s:c r="A41" s="71" t="n">
+        <s:v>46284</s:v>
+      </s:c>
+      <s:c r="B41" s="63" t="inlineStr">
+        <s:is>
+          <s:t>ავანსი ხელშეკრულება N1 (40 000 აშშ დოლარი, ერ.კ. 2.6125)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C41" s="63" t="inlineStr">
+        <s:is>
+          <s:t>შპს ჯიესენ გრუპ</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D41" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E41" s="72" t="n">
+        <s:v>-104500</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="42">
+      <s:c r="A42" s="71" t="n">
+        <s:v>46286</s:v>
+      </s:c>
+      <s:c r="B42" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მუშების კვება — საქვეანგარიშოდ დირექტორზე</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C42" s="63" t="inlineStr">
+        <s:is>
+          <s:t>გოდერძი მეტრეველი</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D42" s="63" t="inlineStr">
+        <s:is>
+          <s:t>მომსახურება / Services</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E42" s="72" t="n">
+        <s:v>-10000</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="43">
+      <s:c r="A43" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B41" s="24" t="inlineStr"/>
-      <s:c r="C41" s="24" t="inlineStr"/>
-      <s:c r="D41" s="24" t="inlineStr"/>
-      <s:c r="E41" s="30">
-        <s:f>SUM(E13:E40)</s:f>
-        <s:v>-102741.99</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="43">
-      <s:c r="A43" s="10" t="inlineStr">
+      <s:c r="B43" s="24" t="inlineStr"/>
+      <s:c r="C43" s="24" t="inlineStr"/>
+      <s:c r="D43" s="24" t="inlineStr"/>
+      <s:c r="E43" s="30">
+        <s:f>SUM(E13:E42)</s:f>
+        <s:v>-217241.99</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="45">
+      <s:c r="A45" s="10" t="inlineStr">
         <s:is>
           <s:t>კატეგორიების მიხედვით / BY CATEGORY</s:t>
         </s:is>
       </s:c>
-      <s:c r="B43" s="11" t="n"/>
-      <s:c r="C43" s="11" t="n"/>
-      <s:c r="D43" s="11" t="n"/>
-      <s:c r="E43" s="11" t="n"/>
-    </s:row>
-    <s:row r="44">
-      <s:c r="A44" s="59" t="inlineStr">
+      <s:c r="B45" s="11" t="n"/>
+      <s:c r="C45" s="11" t="n"/>
+      <s:c r="D45" s="11" t="n"/>
+      <s:c r="E45" s="11" t="n"/>
+    </s:row>
+    <s:row r="46">
+      <s:c r="A46" s="59" t="inlineStr">
         <s:is>
           <s:t>კატეგორია / Category</s:t>
         </s:is>
       </s:c>
-      <s:c r="B44" s="12" t="inlineStr">
+      <s:c r="B46" s="12" t="inlineStr">
         <s:is>
           <s:t>თანხა GEL / Amount</s:t>
         </s:is>
       </s:c>
-      <s:c r="C44" s="12" t="inlineStr">
+      <s:c r="C46" s="12" t="inlineStr">
         <s:is>
           <s:t>% ჯამიდან / of total</s:t>
         </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="45">
-      <s:c r="A45" s="20" t="inlineStr">
-        <s:is>
-          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B45" s="31">
-        <s:f>-SUMIF($D$13:$D$40,$A45,$E$13:$E$40)</s:f>
-        <s:v>74044.8</s:v>
-      </s:c>
-      <s:c r="C45" s="26">
-        <s:f>IFERROR($B45/$B$52,0)</s:f>
-        <s:v>0.720686838944817</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="46">
-      <s:c r="A46" s="20" t="inlineStr">
-        <s:is>
-          <s:t>ხელფასი / Salaries</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B46" s="31">
-        <s:f>-SUMIF($D$13:$D$40,$A46,$E$13:$E$40)</s:f>
-        <s:v>10000.0</s:v>
-      </s:c>
-      <s:c r="C46" s="26">
-        <s:f>IFERROR($B46/$B$52,0)</s:f>
-        <s:v>0.09733118854326259</s:v>
       </s:c>
     </s:row>
     <s:row r="47">
       <s:c r="A47" s="20" t="inlineStr">
         <s:is>
-          <s:t>გადასახადები / Taxes &amp; pension</s:t>
+          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
       <s:c r="B47" s="31">
-        <s:f>-SUMIF($D$13:$D$40,$A47,$E$13:$E$40)</s:f>
-        <s:v>1470.0</s:v>
+        <s:f>-SUMIF($D$13:$D$42,$A47,$E$13:$E$42)</s:f>
+        <s:v>178544.8</s:v>
       </s:c>
       <s:c r="C47" s="26">
-        <s:f>IFERROR($B47/$B$52,0)</s:f>
-        <s:v>0.0143076847158596</s:v>
+        <s:f>IFERROR($B47/$B$54,0)</s:f>
+        <s:v>0.8218705785193737</s:v>
       </s:c>
     </s:row>
     <s:row r="48">
       <s:c r="A48" s="20" t="inlineStr">
         <s:is>
-          <s:t>მომსახურება / Services</s:t>
+          <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
       <s:c r="B48" s="31">
-        <s:f>-SUMIF($D$13:$D$40,$A48,$E$13:$E$40)</s:f>
-        <s:v>3070.0</s:v>
+        <s:f>-SUMIF($D$13:$D$42,$A48,$E$13:$E$42)</s:f>
+        <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C48" s="26">
-        <s:f>IFERROR($B48/$B$52,0)</s:f>
-        <s:v>0.029880674882781615</s:v>
+        <s:f>IFERROR($B48/$B$54,0)</s:f>
+        <s:v>0.04603161663175706</s:v>
       </s:c>
     </s:row>
     <s:row r="49">
       <s:c r="A49" s="20" t="inlineStr">
         <s:is>
-          <s:t>მასალები / Materials</s:t>
+          <s:t>გადასახადები / Taxes &amp; pension</s:t>
         </s:is>
       </s:c>
       <s:c r="B49" s="31">
-        <s:f>-SUMIF($D$13:$D$40,$A49,$E$13:$E$40)</s:f>
-        <s:v>5722.7</s:v>
+        <s:f>-SUMIF($D$13:$D$42,$A49,$E$13:$E$42)</s:f>
+        <s:v>1470.0</s:v>
       </s:c>
       <s:c r="C49" s="26">
-        <s:f>IFERROR($B49/$B$52,0)</s:f>
-        <s:v>0.05569971926765288</s:v>
+        <s:f>IFERROR($B49/$B$54,0)</s:f>
+        <s:v>0.006766647644868288</s:v>
       </s:c>
     </s:row>
     <s:row r="50">
       <s:c r="A50" s="20" t="inlineStr">
         <s:is>
-          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+          <s:t>მომსახურება / Services</s:t>
         </s:is>
       </s:c>
       <s:c r="B50" s="31">
-        <s:f>-SUMIF($D$13:$D$40,$A50,$E$13:$E$40)</s:f>
-        <s:v>7505.41</s:v>
+        <s:f>-SUMIF($D$13:$D$42,$A50,$E$13:$E$42)</s:f>
+        <s:v>13070.0</s:v>
       </s:c>
       <s:c r="C50" s="26">
-        <s:f>IFERROR($B50/$B$52,0)</s:f>
-        <s:v>0.07305104758044885</s:v>
+        <s:f>IFERROR($B50/$B$54,0)</s:f>
+        <s:v>0.06016332293770647</s:v>
       </s:c>
     </s:row>
     <s:row r="51">
       <s:c r="A51" s="20" t="inlineStr">
         <s:is>
+          <s:t>მასალები / Materials</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B51" s="31">
+        <s:f>-SUMIF($D$13:$D$42,$A51,$E$13:$E$42)</s:f>
+        <s:v>5722.7</s:v>
+      </s:c>
+      <s:c r="C51" s="26">
+        <s:f>IFERROR($B51/$B$54,0)</s:f>
+        <s:v>0.02634251324985561</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="52">
+      <s:c r="A52" s="20" t="inlineStr">
+        <s:is>
+          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B52" s="31">
+        <s:f>-SUMIF($D$13:$D$42,$A52,$E$13:$E$42)</s:f>
+        <s:v>7505.41</s:v>
+      </s:c>
+      <s:c r="C52" s="26">
+        <s:f>IFERROR($B52/$B$54,0)</s:f>
+        <s:v>0.03454861557841557</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="53">
+      <s:c r="A53" s="20" t="inlineStr">
+        <s:is>
           <s:t>სხვა / Other</s:t>
         </s:is>
       </s:c>
-      <s:c r="B51" s="31">
-        <s:f>-SUMIF($D$13:$D$40,$A51,$E$13:$E$40)</s:f>
+      <s:c r="B53" s="31">
+        <s:f>-SUMIF($D$13:$D$42,$A53,$E$13:$E$42)</s:f>
         <s:v>929.08</s:v>
       </s:c>
-      <s:c r="C51" s="26">
-        <s:f>IFERROR($B51/$B$52,0)</s:f>
-        <s:v>0.009042846065177442</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="52">
-      <s:c r="A52" s="21" t="inlineStr">
+      <s:c r="C53" s="26">
+        <s:f>IFERROR($B53/$B$54,0)</s:f>
+        <s:v>0.004276705438023285</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="54">
+      <s:c r="A54" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B52" s="30">
-        <s:f>SUM(B45:B51)</s:f>
-        <s:v>102741.99</s:v>
-      </s:c>
-      <s:c r="C52" s="23">
-        <s:f>IFERROR(B52/B52,0)</s:f>
+      <s:c r="B54" s="30">
+        <s:f>SUM(B47:B53)</s:f>
+        <s:v>217241.99</s:v>
+      </s:c>
+      <s:c r="C54" s="23">
+        <s:f>IFERROR(B54/B54,0)</s:f>
         <s:v>1.0</s:v>
       </s:c>
     </s:row>
-    <s:row r="53">
-      <s:c r="A53" s="3" t="inlineStr">
+    <s:row r="55">
+      <s:c r="A55" s="3" t="inlineStr">
         <s:is>
           <s:t>შემოწმება / Check vs statement total (must be 0)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B53" s="73">
-        <s:f>B52+E41</s:f>
-        <s:v>0.0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="55">
-      <s:c r="A55" s="10" t="inlineStr">
+      <s:c r="B55" s="73">
+        <s:f>B54+E43</s:f>
+        <s:v>0.0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="57">
+      <s:c r="A57" s="10" t="inlineStr">
         <s:is>
           <s:t>თვეების მიხედვით / BY MONTH</s:t>
         </s:is>
       </s:c>
-      <s:c r="B55" s="11" t="n"/>
-      <s:c r="C55" s="11" t="n"/>
-      <s:c r="D55" s="11" t="n"/>
-      <s:c r="E55" s="11" t="n"/>
-    </s:row>
-    <s:row r="56">
-      <s:c r="A56" s="59" t="inlineStr">
+      <s:c r="B57" s="11" t="n"/>
+      <s:c r="C57" s="11" t="n"/>
+      <s:c r="D57" s="11" t="n"/>
+      <s:c r="E57" s="11" t="n"/>
+    </s:row>
+    <s:row r="58">
+      <s:c r="A58" s="59" t="inlineStr">
         <s:is>
           <s:t>თვე / Month</s:t>
         </s:is>
       </s:c>
-      <s:c r="B56" s="12" t="inlineStr">
+      <s:c r="B58" s="12" t="inlineStr">
         <s:is>
           <s:t>თანხა GEL / Amount</s:t>
         </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="57">
-      <s:c r="A57" s="20" t="inlineStr">
-        <s:is>
-          <s:t>ივლისი 2026 / July</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B57" s="31">
-        <s:f>-SUMPRODUCT(($A$13:$A$40&gt;=DATE(2026,7,1))*($A$13:$A$40&lt;=DATE(2026,7,31))*$E$13:$E$40)</s:f>
-        <s:v>68664.21</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="58">
-      <s:c r="A58" s="20" t="inlineStr">
-        <s:is>
-          <s:t>აგვისტო 2026 / August</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B58" s="31">
-        <s:f>-SUMPRODUCT(($A$13:$A$40&gt;=DATE(2026,8,1))*($A$13:$A$40&lt;=DATE(2026,8,31))*$E$13:$E$40)</s:f>
-        <s:v>21477.0</s:v>
       </s:c>
     </s:row>
     <s:row r="59">
       <s:c r="A59" s="20" t="inlineStr">
         <s:is>
-          <s:t>სექტემბერი 2026 (18-მდე) / September (to the 18th)</s:t>
+          <s:t>ივლისი 2026 / July</s:t>
         </s:is>
       </s:c>
       <s:c r="B59" s="31">
-        <s:f>-SUMPRODUCT(($A$13:$A$40&gt;=DATE(2026,9,1))*($A$13:$A$40&lt;=DATE(2026,9,30))*$E$13:$E$40)</s:f>
-        <s:v>12600.78</s:v>
+        <s:f>-SUMPRODUCT(($A$13:$A$42&gt;=DATE(2026,7,1))*($A$13:$A$42&lt;=DATE(2026,7,31))*$E$13:$E$42)</s:f>
+        <s:v>68664.21</s:v>
       </s:c>
     </s:row>
     <s:row r="60">
-      <s:c r="A60" s="21" t="inlineStr">
+      <s:c r="A60" s="20" t="inlineStr">
+        <s:is>
+          <s:t>აგვისტო 2026 / August</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B60" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$42&gt;=DATE(2026,8,1))*($A$13:$A$42&lt;=DATE(2026,8,31))*$E$13:$E$42)</s:f>
+        <s:v>21477.0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="61">
+      <s:c r="A61" s="20" t="inlineStr">
+        <s:is>
+          <s:t>სექტემბერი 2026 (21-მდე) / September (to the 21st)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B61" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$42&gt;=DATE(2026,9,1))*($A$13:$A$42&lt;=DATE(2026,9,30))*$E$13:$E$42)</s:f>
+        <s:v>127100.78</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="62">
+      <s:c r="A62" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B60" s="30">
-        <s:f>SUM(B57:B59)</s:f>
-        <s:v>102741.99</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="62">
-      <s:c r="A62" s="10" t="inlineStr">
+      <s:c r="B62" s="30">
+        <s:f>SUM(B59:B61)</s:f>
+        <s:v>217241.99</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="64">
+      <s:c r="A64" s="10" t="inlineStr">
         <s:is>
           <s:t>ძირითადი ფაქტები / KEY FACTS</s:t>
         </s:is>
       </s:c>
-      <s:c r="B62" s="11" t="n"/>
-      <s:c r="C62" s="11" t="n"/>
-      <s:c r="D62" s="11" t="n"/>
-      <s:c r="E62" s="11" t="n"/>
-    </s:row>
-    <s:row r="63">
-      <s:c r="A63" s="17" t="inlineStr">
+      <s:c r="B64" s="11" t="n"/>
+      <s:c r="C64" s="11" t="n"/>
+      <s:c r="D64" s="11" t="n"/>
+      <s:c r="E64" s="11" t="n"/>
+    </s:row>
+    <s:row r="65">
+      <s:c r="A65" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 09/07/2026 (22,000 USD) / FX rate on the 09/07/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B63" s="74">
+      <s:c r="B65" s="74">
         <s:f>-E17/22000</s:f>
         <s:v>2.6384000000000003</s:v>
       </s:c>
-      <s:c r="C63" s="42" t="inlineStr">
+      <s:c r="C65" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში მითითებული კურსი 2.6384 / the description states 2.6384</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="64">
-      <s:c r="A64" s="17" t="inlineStr">
+    <s:row r="66">
+      <s:c r="A66" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 04/08/2026 (5,000 USD) / FX rate on the 04/08/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B64" s="74">
+      <s:c r="B66" s="74">
         <s:f>-E20/5000</s:f>
         <s:v>2.62</s:v>
       </s:c>
-      <s:c r="C64" s="42" t="inlineStr">
+      <s:c r="C66" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში კურსი არ არის მითითებული / no rate stated in the description</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="65">
-      <s:c r="A65" s="17" t="inlineStr">
+    <s:row r="67">
+      <s:c r="A67" s="17" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსები / Construction advances paid (USD)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B65" s="75">
+      <s:c r="B67" s="75">
         <s:f>22000+5000</s:f>
         <s:v>27000.0</s:v>
       </s:c>
-      <s:c r="C65" s="42" t="inlineStr">
+      <s:c r="C67" s="42" t="inlineStr">
         <s:is>
           <s:t>ხელშეკრულება N1, 7/6/2026, შპს ჯიესენ გრუპ / contract N1 of 7/6/2026 with LLC GSN Group</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="66">
-      <s:c r="A66" s="17" t="inlineStr">
-        <s:is>
-          <s:t>მშენებლობის ავანსები / Construction advances paid (GEL)</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B66" s="76">
-        <s:f>B45</s:f>
-        <s:v>74044.8</s:v>
-      </s:c>
-      <s:c r="C66" s="42" t="inlineStr">
-        <s:is>
-          <s:t>ორივე გადარიცხვის ჯამი / the two transfers above</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="67">
-      <s:c r="A67" s="17" t="inlineStr">
-        <s:is>
-          <s:t>სულ გადახდილი / Total paid out (GEL)</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B67" s="38">
-        <s:f>-E41</s:f>
-        <s:v>102741.99</s:v>
-      </s:c>
-      <s:c r="C67" s="42" t="inlineStr">
-        <s:is>
-          <s:t>01/07–08/09/2026</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="68">
       <s:c r="A68" s="17" t="inlineStr">
         <s:is>
+          <s:t>მშენებლობის ავანსები / Construction advances paid (GEL)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B68" s="76">
+        <s:f>B47</s:f>
+        <s:v>178544.8</s:v>
+      </s:c>
+      <s:c r="C68" s="42" t="inlineStr">
+        <s:is>
+          <s:t>ორივე გადარიცხვის ჯამი / the two transfers above</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="69">
+      <s:c r="A69" s="17" t="inlineStr">
+        <s:is>
+          <s:t>სულ გადახდილი / Total paid out (GEL)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B69" s="38">
+        <s:f>-E43</s:f>
+        <s:v>217241.99</s:v>
+      </s:c>
+      <s:c r="C69" s="42" t="inlineStr">
+        <s:is>
+          <s:t>01/07–08/09/2026</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="70">
+      <s:c r="A70" s="17" t="inlineStr">
+        <s:is>
           <s:t>შემოსავალი ამონაწერში / Inflows in the statement (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B68" s="38">
+      <s:c r="B70" s="38">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C68" s="42" t="inlineStr">
+      <s:c r="C70" s="42" t="inlineStr">
         <s:is>
           <s:t>ამონაწერში შემოსავალი არ ფიქსირდება — 140,000 USD სესხი ამ ანგარიშზე ამ პერიოდში არ ჩანს. / The statement shows no inflows; the USD 140,000 loan is not visible in this account for this period.</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="70">
-      <s:c r="A70" s="2" t="inlineStr">
+    <s:row r="72">
+      <s:c r="A72" s="2" t="inlineStr">
         <s:is>
           <s:t>შენიშვნა: ამონაწერი მხოლოდ ერთ ანგარიშს ფარავს და მასში შემოსავალი არ არის. თუ სესხი სხვა ანგარიშზეა ჩარიცხული, დაამატეთ ის ამონაწერიც. / Note: the statement covers one account and contains no inflows. If the loan was disbursed into another account, add that statement too.</s:t>
         </s:is>

--- a/finance/Greenhouse_CashFlow_2000m2.xlsx
+++ b/finance/Greenhouse_CashFlow_2000m2.xlsx
@@ -1147,7 +1147,7 @@
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
     <s:pageSetUpPr/>
   </s:sheetPr>
-  <s:dimension ref="A1:G47"/>
+  <s:dimension ref="A1:G49"/>
   <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <s:cols>
     <s:col width="50" customWidth="1" min="1" max="1"/>
@@ -1234,15 +1234,15 @@
       </s:c>
       <s:c r="B7" s="18">
         <s:f>B21</s:f>
-        <s:v>217241.99</s:v>
+        <s:v>7505.41</s:v>
       </s:c>
       <s:c r="C7" s="19">
         <s:f>IFERROR(B7/$B$6,0)</s:f>
-        <s:v>0.347587184</s:v>
+        <s:v>0.012008656</s:v>
       </s:c>
       <s:c r="D7" s="20" t="str">
         <s:f>REPT("|",ROUND(C7*40,0))</s:f>
-        <s:v>||||||||||||||</s:v>
+        <s:v/>
       </s:c>
     </s:row>
     <s:row r="8">
@@ -1253,15 +1253,15 @@
       </s:c>
       <s:c r="B8" s="18">
         <s:f>D34</s:f>
-        <s:v>150127.19999999998</s:v>
+        <s:v>329800.0</s:v>
       </s:c>
       <s:c r="C8" s="19">
         <s:f>IFERROR(B8/$B$6,0)</s:f>
-        <s:v>0.24020351999999998</s:v>
+        <s:v>0.52768</s:v>
       </s:c>
       <s:c r="D8" s="20" t="str">
         <s:f>REPT("|",ROUND(C8*40,0))</s:f>
-        <s:v>||||||||||</s:v>
+        <s:v>|||||||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="9">
@@ -1272,15 +1272,15 @@
       </s:c>
       <s:c r="B9" s="22">
         <s:f>B7+B8</s:f>
-        <s:v>367369.18999999994</s:v>
+        <s:v>337305.41</s:v>
       </s:c>
       <s:c r="C9" s="23">
         <s:f>IFERROR(B9/$B$6,0)</s:f>
-        <s:v>0.5877907039999999</s:v>
+        <s:v>0.5396886559999999</s:v>
       </s:c>
       <s:c r="D9" s="24" t="str">
         <s:f>REPT("|",ROUND(C9*40,0))</s:f>
-        <s:v>||||||||||||||||||||||||</s:v>
+        <s:v>||||||||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="10">
@@ -1291,15 +1291,15 @@
       </s:c>
       <s:c r="B10" s="22">
         <s:f>B6-B9</s:f>
-        <s:v>257630.81000000006</s:v>
+        <s:v>287694.59</s:v>
       </s:c>
       <s:c r="C10" s="23">
         <s:f>IFERROR(B10/$B$6,0)</s:f>
-        <s:v>0.4122092960000001</s:v>
+        <s:v>0.46031134400000007</s:v>
       </s:c>
       <s:c r="D10" s="24" t="str">
         <s:f>REPT("|",ROUND(C10*40,0))</s:f>
-        <s:v>||||||||||||||||</s:v>
+        <s:v>||||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="12">
@@ -1357,8 +1357,8 @@
         <s:v>178544.8</s:v>
       </s:c>
       <s:c r="C14" s="26">
-        <s:f>IFERROR(B14/$B$21,0)</s:f>
-        <s:v>0.8218705785193737</s:v>
+        <s:f>IFERROR(B14/$B$23,0)</s:f>
+        <s:v>0.8218705785193738</s:v>
       </s:c>
       <s:c r="D14" s="27" t="inlineStr">
         <s:is>
@@ -1387,7 +1387,7 @@
         <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C15" s="26">
-        <s:f>IFERROR(B15/$B$21,0)</s:f>
+        <s:f>IFERROR(B15/$B$23,0)</s:f>
         <s:v>0.04603161663175706</s:v>
       </s:c>
       <s:c r="D15" s="27" t="inlineStr">
@@ -1412,8 +1412,8 @@
         <s:v>1470.0</s:v>
       </s:c>
       <s:c r="C16" s="26">
-        <s:f>IFERROR(B16/$B$21,0)</s:f>
-        <s:v>0.006766647644868288</s:v>
+        <s:f>IFERROR(B16/$B$23,0)</s:f>
+        <s:v>0.006766647644868289</s:v>
       </s:c>
       <s:c r="D16" s="27" t="inlineStr">
         <s:is>
@@ -1434,11 +1434,11 @@
       </s:c>
       <s:c r="B17" s="25">
         <s:f>Actuals!B50</s:f>
-        <s:v>13070.0</s:v>
+        <s:v>3070.0</s:v>
       </s:c>
       <s:c r="C17" s="26">
-        <s:f>IFERROR(B17/$B$21,0)</s:f>
-        <s:v>0.06016332293770647</s:v>
+        <s:f>IFERROR(B17/$B$23,0)</s:f>
+        <s:v>0.01413170630594942</s:v>
       </s:c>
       <s:c r="D17" s="27" t="inlineStr">
         <s:is>
@@ -1454,20 +1454,20 @@
     <s:row r="18">
       <s:c r="A18" s="20" t="inlineStr">
         <s:is>
-          <s:t>მასალები / Materials</s:t>
+          <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
       <s:c r="B18" s="25">
         <s:f>Actuals!B51</s:f>
-        <s:v>5722.7</s:v>
+        <s:v>-0.0</s:v>
       </s:c>
       <s:c r="C18" s="26">
-        <s:f>IFERROR(B18/$B$21,0)</s:f>
-        <s:v>0.02634251324985561</s:v>
+        <s:f>IFERROR(B18/$B$23,0)</s:f>
+        <s:v>-0.0</s:v>
       </s:c>
       <s:c r="D18" s="27" t="inlineStr">
         <s:is>
-          <s:t>CAPEX</s:t>
+          <s:t>OPEX</s:t>
         </s:is>
       </s:c>
       <s:c r="E18" s="28" t="n"/>
@@ -1479,20 +1479,20 @@
     <s:row r="19">
       <s:c r="A19" s="20" t="inlineStr">
         <s:is>
-          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+          <s:t>მუშების კვება / Worker meals</s:t>
         </s:is>
       </s:c>
       <s:c r="B19" s="25">
         <s:f>Actuals!B52</s:f>
-        <s:v>7505.41</s:v>
+        <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C19" s="26">
-        <s:f>IFERROR(B19/$B$21,0)</s:f>
-        <s:v>0.03454861557841557</s:v>
+        <s:f>IFERROR(B19/$B$23,0)</s:f>
+        <s:v>0.04603161663175706</s:v>
       </s:c>
       <s:c r="D19" s="27" t="inlineStr">
         <s:is>
-          <s:t>CAPEX</s:t>
+          <s:t>OPEX</s:t>
         </s:is>
       </s:c>
       <s:c r="E19" s="28" t="n"/>
@@ -1504,16 +1504,16 @@
     <s:row r="20">
       <s:c r="A20" s="20" t="inlineStr">
         <s:is>
-          <s:t>სხვა / Other</s:t>
+          <s:t>მასალები / Materials</s:t>
         </s:is>
       </s:c>
       <s:c r="B20" s="25">
         <s:f>Actuals!B53</s:f>
-        <s:v>929.08</s:v>
+        <s:v>5722.7</s:v>
       </s:c>
       <s:c r="C20" s="26">
-        <s:f>IFERROR(B20/$B$21,0)</s:f>
-        <s:v>0.004276705438023285</s:v>
+        <s:f>IFERROR(B20/$B$23,0)</s:f>
+        <s:v>0.026342513249855613</s:v>
       </s:c>
       <s:c r="D20" s="27" t="inlineStr">
         <s:is>
@@ -1527,355 +1527,405 @@
       </s:c>
     </s:row>
     <s:row r="21">
-      <s:c r="A21" s="21" t="inlineStr">
-        <s:is>
-          <s:t>სულ დახარჯული / TOTAL SPENT</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B21" s="30">
-        <s:f>SUM(B14:B20)</s:f>
-        <s:v>217241.99</s:v>
-      </s:c>
-      <s:c r="C21" s="23">
-        <s:f>IFERROR(B21/B21,0)</s:f>
-        <s:v>1.0</s:v>
-      </s:c>
-      <s:c r="D21" s="24" t="inlineStr"/>
-      <s:c r="E21" s="22" t="str">
-        <s:f>IF(COUNT(E14:E20)=0,"",SUM(E14:E20))</s:f>
-        <s:v/>
-      </s:c>
-      <s:c r="F21" s="22" t="str">
+      <s:c r="A21" s="20" t="inlineStr">
+        <s:is>
+          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B21" s="25">
+        <s:f>Actuals!B54</s:f>
+        <s:v>7505.41</s:v>
+      </s:c>
+      <s:c r="C21" s="26">
+        <s:f>IFERROR(B21/$B$23,0)</s:f>
+        <s:v>0.03454861557841558</s:v>
+      </s:c>
+      <s:c r="D21" s="27" t="inlineStr">
+        <s:is>
+          <s:t>CAPEX</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E21" s="28" t="n"/>
+      <s:c r="F21" s="29" t="str">
         <s:f>IF(E21="","",E21-B21)</s:f>
         <s:v/>
       </s:c>
     </s:row>
+    <s:row r="22">
+      <s:c r="A22" s="20" t="inlineStr">
+        <s:is>
+          <s:t>სხვა / Other</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B22" s="25">
+        <s:f>Actuals!B55</s:f>
+        <s:v>929.08</s:v>
+      </s:c>
+      <s:c r="C22" s="26">
+        <s:f>IFERROR(B22/$B$23,0)</s:f>
+        <s:v>0.004276705438023286</s:v>
+      </s:c>
+      <s:c r="D22" s="27" t="inlineStr">
+        <s:is>
+          <s:t>CAPEX</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E22" s="28" t="n"/>
+      <s:c r="F22" s="29" t="str">
+        <s:f>IF(E22="","",E22-B22)</s:f>
+        <s:v/>
+      </s:c>
+    </s:row>
     <s:row r="23">
-      <s:c r="A23" s="10" t="inlineStr">
+      <s:c r="A23" s="21" t="inlineStr">
+        <s:is>
+          <s:t>სულ დახარჯული / TOTAL SPENT</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B23" s="30">
+        <s:f>SUM(B14:B22)</s:f>
+        <s:v>217241.98999999996</s:v>
+      </s:c>
+      <s:c r="C23" s="23">
+        <s:f>IFERROR(B23/B23,0)</s:f>
+        <s:v>1.0</s:v>
+      </s:c>
+      <s:c r="D23" s="24" t="inlineStr"/>
+      <s:c r="E23" s="22" t="str">
+        <s:f>IF(COUNT(E14:E22)=0,"",SUM(E14:E22))</s:f>
+        <s:v/>
+      </s:c>
+      <s:c r="F23" s="22" t="str">
+        <s:f>IF(E23="","",E23-B23)</s:f>
+        <s:v/>
+      </s:c>
+    </s:row>
+    <s:row r="25">
+      <s:c r="A25" s="10" t="inlineStr">
         <s:is>
           <s:t>3. ბიუჯეტის ნაშთი თვეების მიხედვით / BUDGET DRAWDOWN BY MONTH</s:t>
         </s:is>
       </s:c>
-      <s:c r="B23" s="11" t="n"/>
-      <s:c r="C23" s="11" t="n"/>
-      <s:c r="D23" s="11" t="n"/>
-      <s:c r="E23" s="11" t="n"/>
-      <s:c r="F23" s="11" t="n"/>
-    </s:row>
-    <s:row r="24">
-      <s:c r="A24" s="12" t="inlineStr">
+      <s:c r="B25" s="11" t="n"/>
+      <s:c r="C25" s="11" t="n"/>
+      <s:c r="D25" s="11" t="n"/>
+      <s:c r="E25" s="11" t="n"/>
+      <s:c r="F25" s="11" t="n"/>
+    </s:row>
+    <s:row r="26">
+      <s:c r="A26" s="12" t="inlineStr">
         <s:is>
           <s:t>თვე / Month</s:t>
         </s:is>
       </s:c>
-      <s:c r="B24" s="12" t="inlineStr">
+      <s:c r="B26" s="12" t="inlineStr">
         <s:is>
           <s:t>ხარჯი / Spend</s:t>
         </s:is>
       </s:c>
-      <s:c r="C24" s="12" t="inlineStr">
+      <s:c r="C26" s="12" t="inlineStr">
         <s:is>
           <s:t>კუმულატიური / Cumulative</s:t>
         </s:is>
       </s:c>
-      <s:c r="D24" s="12" t="inlineStr">
+      <s:c r="D26" s="12" t="inlineStr">
         <s:is>
           <s:t>ბიუჯეტის ნაშთი / Budget left</s:t>
         </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="25">
-      <s:c r="A25" s="20" t="inlineStr">
-        <s:is>
-          <s:t>ივლისი 2026 / July</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B25" s="25">
-        <s:f>Actuals!B59</s:f>
-        <s:v>68664.21</s:v>
-      </s:c>
-      <s:c r="C25" s="31">
-        <s:f>SUM($B$25:B25)</s:f>
-        <s:v>68664.21</s:v>
-      </s:c>
-      <s:c r="D25" s="18">
-        <s:f>$B$6-C25</s:f>
-        <s:v>556335.79</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="26">
-      <s:c r="A26" s="20" t="inlineStr">
-        <s:is>
-          <s:t>აგვისტო 2026 / August</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B26" s="25">
-        <s:f>Actuals!B60</s:f>
-        <s:v>21477.0</s:v>
-      </s:c>
-      <s:c r="C26" s="31">
-        <s:f>SUM($B$25:B26)</s:f>
-        <s:v>90141.21</s:v>
-      </s:c>
-      <s:c r="D26" s="18">
-        <s:f>$B$6-C26</s:f>
-        <s:v>534858.79</s:v>
       </s:c>
     </s:row>
     <s:row r="27">
       <s:c r="A27" s="20" t="inlineStr">
         <s:is>
-          <s:t>სექტემბერი 2026 (21-მდე) / September (to the 21st)</s:t>
+          <s:t>ივლისი 2026 / July</s:t>
         </s:is>
       </s:c>
       <s:c r="B27" s="25">
         <s:f>Actuals!B61</s:f>
-        <s:v>127100.78</s:v>
+        <s:v>68664.21</s:v>
       </s:c>
       <s:c r="C27" s="31">
-        <s:f>SUM($B$25:B27)</s:f>
-        <s:v>217241.99</s:v>
+        <s:f>SUM($B$27:B27)</s:f>
+        <s:v>68664.21</s:v>
       </s:c>
       <s:c r="D27" s="18">
         <s:f>$B$6-C27</s:f>
+        <s:v>556335.79</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="28">
+      <s:c r="A28" s="20" t="inlineStr">
+        <s:is>
+          <s:t>აგვისტო 2026 / August</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B28" s="25">
+        <s:f>Actuals!B62</s:f>
+        <s:v>21477.0</s:v>
+      </s:c>
+      <s:c r="C28" s="31">
+        <s:f>SUM($B$27:B28)</s:f>
+        <s:v>90141.21</s:v>
+      </s:c>
+      <s:c r="D28" s="18">
+        <s:f>$B$6-C28</s:f>
+        <s:v>534858.79</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="29">
+      <s:c r="A29" s="20" t="inlineStr">
+        <s:is>
+          <s:t>სექტემბერი 2026 (21-მდე) / September (to the 21st)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B29" s="25">
+        <s:f>Actuals!B63</s:f>
+        <s:v>127100.78</s:v>
+      </s:c>
+      <s:c r="C29" s="31">
+        <s:f>SUM($B$27:B29)</s:f>
+        <s:v>217241.99</s:v>
+      </s:c>
+      <s:c r="D29" s="18">
+        <s:f>$B$6-C29</s:f>
         <s:v>407758.01</s:v>
       </s:c>
     </s:row>
-    <s:row r="28">
-      <s:c r="A28" s="21" t="inlineStr">
+    <s:row r="30">
+      <s:c r="A30" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B28" s="30">
-        <s:f>SUM(B25:B27)</s:f>
+      <s:c r="B30" s="30">
+        <s:f>SUM(B27:B29)</s:f>
         <s:v>217241.99</s:v>
       </s:c>
-      <s:c r="C28" s="30">
-        <s:f>B28-B21</s:f>
-        <s:v>0.0</s:v>
-      </s:c>
-      <s:c r="D28" s="22">
-        <s:f>$B$6-B28</s:f>
+      <s:c r="C30" s="30">
+        <s:f>B30-B23</s:f>
+        <s:v>2.9103830456733704e-11</s:v>
+      </s:c>
+      <s:c r="D30" s="22">
+        <s:f>$B$6-B30</s:f>
         <s:v>407758.01</s:v>
       </s:c>
-      <s:c r="G28" s="2" t="inlineStr">
-        <s:is>
-          <s:t>C28 შემოწმებაა — უნდა იყოს 0 / C28 is a check — it must read 0</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="30">
-      <s:c r="A30" s="10" t="inlineStr">
+      <s:c r="G30" s="2" t="inlineStr">
+        <s:is>
+          <s:t>C30 შემოწმებაა — უნდა იყოს 0 / C30 is a check — it must read 0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="32">
+      <s:c r="A32" s="10" t="inlineStr">
         <s:is>
           <s:t>4. ხელშეკრულება N1 — შპს ჯიესენ გრუპი / CONTRACT N1 — LLC GSN GROUP</s:t>
         </s:is>
       </s:c>
-      <s:c r="B30" s="11" t="n"/>
-      <s:c r="C30" s="11" t="n"/>
-      <s:c r="D30" s="11" t="n"/>
-      <s:c r="E30" s="11" t="n"/>
-      <s:c r="F30" s="11" t="n"/>
-    </s:row>
-    <s:row r="31">
-      <s:c r="A31" s="12" t="inlineStr">
+      <s:c r="B32" s="11" t="n"/>
+      <s:c r="C32" s="11" t="n"/>
+      <s:c r="D32" s="11" t="n"/>
+      <s:c r="E32" s="11" t="n"/>
+      <s:c r="F32" s="11" t="n"/>
+    </s:row>
+    <s:row r="33">
+      <s:c r="A33" s="12" t="inlineStr">
         <s:is>
           <s:t>მუხლი / Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="B31" s="12" t="inlineStr">
+      <s:c r="B33" s="12" t="inlineStr">
         <s:is>
           <s:t>USD</s:t>
         </s:is>
       </s:c>
-      <s:c r="C31" s="12" t="inlineStr">
+      <s:c r="C33" s="12" t="inlineStr">
         <s:is>
           <s:t>კურსი / Rate</s:t>
         </s:is>
       </s:c>
-      <s:c r="D31" s="12" t="inlineStr">
+      <s:c r="D33" s="12" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="32">
-      <s:c r="A32" s="17" t="inlineStr">
+    <s:row r="34">
+      <s:c r="A34" s="17" t="inlineStr">
         <s:is>
           <s:t>ჯამური ღირებულება / Total contract value</s:t>
         </s:is>
       </s:c>
-      <s:c r="B32" s="32" t="n">
+      <s:c r="B34" s="32" t="n">
         <s:v>125000</s:v>
       </s:c>
-      <s:c r="C32" s="33">
+      <s:c r="C34" s="33">
         <s:f>Assumptions!$B$28</s:f>
         <s:v>2.6384</s:v>
       </s:c>
-      <s:c r="D32" s="18">
-        <s:f>B32*Assumptions!$B$28</s:f>
+      <s:c r="D34" s="18">
+        <s:f>B34*Assumptions!$B$28</s:f>
         <s:v>329800.0</s:v>
       </s:c>
-      <s:c r="G32" s="2" t="inlineStr">
+      <s:c r="G34" s="2" t="inlineStr">
         <s:is>
           <s:t>მფლობელის მონაცემი / given by the owner</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="33">
-      <s:c r="A33" s="20" t="inlineStr">
+    <s:row r="35">
+      <s:c r="A35" s="20" t="inlineStr">
         <s:is>
           <s:t>გადახდილი ავანსი / Advances paid</s:t>
         </s:is>
       </s:c>
-      <s:c r="B33" s="34">
+      <s:c r="B35" s="34">
         <s:f>22000+5000+40000+2900/Assumptions!$B$28</s:f>
         <s:v>68099.15100060643</s:v>
       </s:c>
-      <s:c r="C33" s="35">
-        <s:f>IFERROR(D33/B33,0)</s:f>
+      <s:c r="C35" s="35">
+        <s:f>IFERROR(D35/B35,0)</s:f>
         <s:v>2.6218359168443968</s:v>
       </s:c>
-      <s:c r="D33" s="25">
+      <s:c r="D35" s="25">
         <s:f>Actuals!B47</s:f>
         <s:v>178544.8</s:v>
       </s:c>
-      <s:c r="G33" s="2" t="inlineStr">
+      <s:c r="G35" s="2" t="inlineStr">
         <s:is>
           <s:t>09/07 — 22,000 $ · 04/08 — 5,000 $ · 14/09 — 2,900 ₾ ≈ 1,099 $ (ერ.კ. 2.6384) · 19/09 — 40,000 $ ერ.კ. 2.6125</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="34">
-      <s:c r="A34" s="21" t="inlineStr">
+    <s:row r="36">
+      <s:c r="A36" s="21" t="inlineStr">
         <s:is>
           <s:t>დარჩენილი გადასახდელი / Outstanding</s:t>
         </s:is>
       </s:c>
-      <s:c r="B34" s="36">
-        <s:f>B32-B33</s:f>
+      <s:c r="B36" s="36">
+        <s:f>B34-B35</s:f>
         <s:v>56900.848999393565</s:v>
       </s:c>
-      <s:c r="C34" s="37">
+      <s:c r="C36" s="37">
         <s:f>Assumptions!$B$28</s:f>
         <s:v>2.6384</s:v>
       </s:c>
-      <s:c r="D34" s="22">
-        <s:f>B34*Assumptions!$B$28</s:f>
+      <s:c r="D36" s="22">
+        <s:f>B36*Assumptions!$B$28</s:f>
         <s:v>150127.19999999998</s:v>
       </s:c>
     </s:row>
-    <s:row r="35">
-      <s:c r="A35" s="17" t="inlineStr">
+    <s:row r="37">
+      <s:c r="A37" s="17" t="inlineStr">
         <s:is>
           <s:t>შესრულების წილი / Share of the contract paid</s:t>
         </s:is>
       </s:c>
-      <s:c r="B35" s="19">
-        <s:f>IFERROR(B33/B32,0)</s:f>
+      <s:c r="B37" s="19">
+        <s:f>IFERROR(B35/B34,0)</s:f>
         <s:v>0.5447932080048514</s:v>
       </s:c>
     </s:row>
-    <s:row r="37">
-      <s:c r="A37" s="10" t="inlineStr">
+    <s:row r="39">
+      <s:c r="A39" s="10" t="inlineStr">
         <s:is>
           <s:t>5. კაპიტალური თუ საოპერაციო / CAPITAL OR OPERATING</s:t>
         </s:is>
       </s:c>
-      <s:c r="B37" s="11" t="n"/>
-      <s:c r="C37" s="11" t="n"/>
-      <s:c r="D37" s="11" t="n"/>
-      <s:c r="E37" s="11" t="n"/>
-      <s:c r="F37" s="11" t="n"/>
-    </s:row>
-    <s:row r="38">
-      <s:c r="A38" s="17" t="inlineStr">
-        <s:is>
-          <s:t>კაპიტალიზებული / Capitalised (CAPEX)</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B38" s="38">
-        <s:f>SUMIF($D$14:$D$20,"CAPEX",$B$14:$B$20)</s:f>
-        <s:v>192701.99</s:v>
-      </s:c>
-      <s:c r="C38" s="19">
-        <s:f>IFERROR(B38/$B$21,0)</s:f>
-        <s:v>0.8870384127856682</s:v>
-      </s:c>
-      <s:c r="G38" s="2" t="inlineStr">
-        <s:is>
-          <s:t>სათბურის ღირებულებაში / into the cost of the greenhouse</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="39">
-      <s:c r="A39" s="17" t="inlineStr">
-        <s:is>
-          <s:t>პრე-საოპერაციო ხარჯი / Pre-operating running costs</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B39" s="38">
-        <s:f>SUMIF($D$14:$D$20,"OPEX",$B$14:$B$20)</s:f>
-        <s:v>24540.0</s:v>
-      </s:c>
-      <s:c r="C39" s="19">
-        <s:f>IFERROR(B39/$B$21,0)</s:f>
-        <s:v>0.11296158721433182</s:v>
-      </s:c>
-      <s:c r="G39" s="2" t="inlineStr">
-        <s:is>
-          <s:t>ხელფასი, გადასახადები, მომსახურება მოსავლამდე / wages, taxes and services before the first crop</s:t>
-        </s:is>
-      </s:c>
+      <s:c r="B39" s="11" t="n"/>
+      <s:c r="C39" s="11" t="n"/>
+      <s:c r="D39" s="11" t="n"/>
+      <s:c r="E39" s="11" t="n"/>
+      <s:c r="F39" s="11" t="n"/>
     </s:row>
     <s:row r="40">
       <s:c r="A40" s="17" t="inlineStr">
         <s:is>
+          <s:t>კაპიტალიზებული / Capitalised (CAPEX)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B40" s="38">
+        <s:f>SUMIF($D$14:$D$22,"CAPEX",$B$14:$B$22)</s:f>
+        <s:v>192701.99</s:v>
+      </s:c>
+      <s:c r="C40" s="19">
+        <s:f>IFERROR(B40/$B$23,0)</s:f>
+        <s:v>0.8870384127856683</s:v>
+      </s:c>
+      <s:c r="G40" s="2" t="inlineStr">
+        <s:is>
+          <s:t>სათბურის ღირებულებაში / into the cost of the greenhouse</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="41">
+      <s:c r="A41" s="17" t="inlineStr">
+        <s:is>
+          <s:t>პრე-საოპერაციო ხარჯი / Pre-operating running costs</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B41" s="38">
+        <s:f>SUMIF($D$14:$D$22,"OPEX",$B$14:$B$22)</s:f>
+        <s:v>24540.0</s:v>
+      </s:c>
+      <s:c r="C41" s="19">
+        <s:f>IFERROR(B41/$B$23,0)</s:f>
+        <s:v>0.11296158721433183</s:v>
+      </s:c>
+      <s:c r="G41" s="2" t="inlineStr">
+        <s:is>
+          <s:t>ხელფასი, გადასახადები, მომსახურება მოსავლამდე / wages, taxes and services before the first crop</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="42">
+      <s:c r="A42" s="17" t="inlineStr">
+        <s:is>
           <s:t>შემოწმება / Check (must be 0)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B40" s="39">
-        <s:f>B38+B39-B21</s:f>
-        <s:v>0.0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="42">
-      <s:c r="A42" s="4" t="inlineStr">
-        <s:is>
-          <s:t>· ბიუჯეტი კრედიტის თანხაა (Assumptions!B27). ხარჯი — ბანკის ამონაწერიდან, ცვლილება Actuals-ზე ხდება.</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="43">
-      <s:c r="A43" s="4" t="inlineStr">
-        <s:is>
-          <s:t>· კრედიტი ტრანშებად გაიცემა, ამიტომ ამონაწერში ერთიანი ჩარიცხვა არ ჩანს.</s:t>
-        </s:is>
+      <s:c r="B42" s="39">
+        <s:f>B40+B41-B23</s:f>
+        <s:v>2.9103830456733704e-11</s:v>
       </s:c>
     </s:row>
     <s:row r="44">
       <s:c r="A44" s="4" t="inlineStr">
         <s:is>
+          <s:t>· ბიუჯეტი კრედიტის თანხაა (Assumptions!B27). ხარჯი — ბანკის ამონაწერიდან, ცვლილება Actuals-ზე ხდება.</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="45">
+      <s:c r="A45" s="4" t="inlineStr">
+        <s:is>
+          <s:t>· კრედიტი ტრანშებად გაიცემა, ამიტომ ამონაწერში ერთიანი ჩარიცხვა არ ჩანს.</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="46">
+      <s:c r="A46" s="4" t="inlineStr">
+        <s:is>
           <s:t>· ეს ფურცელი მშენებლობის ფაზაა; CF_Monthly და Annual პირველ სრულ საოპერაციო წელს ასახავს.</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="45">
-      <s:c r="A45" s="2" t="inlineStr">
-        <s:is>
-          <s:t>· The budget is the credit amount; the spend comes from the bank statement — edit it on Actuals.</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="46">
-      <s:c r="A46" s="2" t="inlineStr">
-        <s:is>
-          <s:t>· The credit is drawn in tranches, so no single disbursement shows in the statement.</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="47">
       <s:c r="A47" s="2" t="inlineStr">
+        <s:is>
+          <s:t>· The budget is the credit amount; the spend comes from the bank statement — edit it on Actuals.</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="48">
+      <s:c r="A48" s="2" t="inlineStr">
+        <s:is>
+          <s:t>· The credit is drawn in tranches, so no single disbursement shows in the statement.</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="49">
+      <s:c r="A49" s="2" t="inlineStr">
         <s:is>
           <s:t>· This sheet is the construction phase; CF_Monthly and Annual are the first full operating year.</s:t>
         </s:is>
@@ -2845,7 +2895,7 @@
       </s:c>
       <s:c r="B58" s="56">
         <s:f>Budget!B21</s:f>
-        <s:v>217241.99</s:v>
+        <s:v>7505.41</s:v>
       </s:c>
       <s:c r="C58" s="41" t="inlineStr">
         <s:is>
@@ -2866,7 +2916,7 @@
       </s:c>
       <s:c r="B59" s="56">
         <s:f>Budget!B38</s:f>
-        <s:v>192701.99</s:v>
+        <s:v>0.0</s:v>
       </s:c>
       <s:c r="C59" s="41" t="inlineStr">
         <s:is>
@@ -13393,7 +13443,7 @@
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
     <s:pageSetUpPr/>
   </s:sheetPr>
-  <s:dimension ref="A1:E72"/>
+  <s:dimension ref="A1:E74"/>
   <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <s:cols>
     <s:col width="13" customWidth="1" min="1" max="1"/>
@@ -14211,7 +14261,7 @@
       </s:c>
       <s:c r="D42" s="63" t="inlineStr">
         <s:is>
-          <s:t>მომსახურება / Services</s:t>
+          <s:t>მუშების კვება / Worker meals</s:t>
         </s:is>
       </s:c>
       <s:c r="E42" s="72" t="n">
@@ -14271,8 +14321,8 @@
         <s:v>178544.8</s:v>
       </s:c>
       <s:c r="C47" s="26">
-        <s:f>IFERROR($B47/$B$54,0)</s:f>
-        <s:v>0.8218705785193737</s:v>
+        <s:f>IFERROR($B47/$B$56,0)</s:f>
+        <s:v>0.8218705785193738</s:v>
       </s:c>
     </s:row>
     <s:row r="48">
@@ -14286,7 +14336,7 @@
         <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C48" s="26">
-        <s:f>IFERROR($B48/$B$54,0)</s:f>
+        <s:f>IFERROR($B48/$B$56,0)</s:f>
         <s:v>0.04603161663175706</s:v>
       </s:c>
     </s:row>
@@ -14301,8 +14351,8 @@
         <s:v>1470.0</s:v>
       </s:c>
       <s:c r="C49" s="26">
-        <s:f>IFERROR($B49/$B$54,0)</s:f>
-        <s:v>0.006766647644868288</s:v>
+        <s:f>IFERROR($B49/$B$56,0)</s:f>
+        <s:v>0.006766647644868289</s:v>
       </s:c>
     </s:row>
     <s:row r="50">
@@ -14313,260 +14363,290 @@
       </s:c>
       <s:c r="B50" s="31">
         <s:f>-SUMIF($D$13:$D$42,$A50,$E$13:$E$42)</s:f>
-        <s:v>13070.0</s:v>
+        <s:v>3070.0</s:v>
       </s:c>
       <s:c r="C50" s="26">
-        <s:f>IFERROR($B50/$B$54,0)</s:f>
-        <s:v>0.06016332293770647</s:v>
+        <s:f>IFERROR($B50/$B$56,0)</s:f>
+        <s:v>0.01413170630594942</s:v>
       </s:c>
     </s:row>
     <s:row r="51">
       <s:c r="A51" s="20" t="inlineStr">
         <s:is>
-          <s:t>მასალები / Materials</s:t>
+          <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
       <s:c r="B51" s="31">
         <s:f>-SUMIF($D$13:$D$42,$A51,$E$13:$E$42)</s:f>
-        <s:v>5722.7</s:v>
+        <s:v>-0.0</s:v>
       </s:c>
       <s:c r="C51" s="26">
-        <s:f>IFERROR($B51/$B$54,0)</s:f>
-        <s:v>0.02634251324985561</s:v>
+        <s:f>IFERROR($B51/$B$56,0)</s:f>
+        <s:v>-0.0</s:v>
       </s:c>
     </s:row>
     <s:row r="52">
       <s:c r="A52" s="20" t="inlineStr">
         <s:is>
-          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+          <s:t>მუშების კვება / Worker meals</s:t>
         </s:is>
       </s:c>
       <s:c r="B52" s="31">
         <s:f>-SUMIF($D$13:$D$42,$A52,$E$13:$E$42)</s:f>
-        <s:v>7505.41</s:v>
+        <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C52" s="26">
-        <s:f>IFERROR($B52/$B$54,0)</s:f>
-        <s:v>0.03454861557841557</s:v>
+        <s:f>IFERROR($B52/$B$56,0)</s:f>
+        <s:v>0.04603161663175706</s:v>
       </s:c>
     </s:row>
     <s:row r="53">
       <s:c r="A53" s="20" t="inlineStr">
         <s:is>
-          <s:t>სხვა / Other</s:t>
+          <s:t>მასალები / Materials</s:t>
         </s:is>
       </s:c>
       <s:c r="B53" s="31">
         <s:f>-SUMIF($D$13:$D$42,$A53,$E$13:$E$42)</s:f>
+        <s:v>5722.7</s:v>
+      </s:c>
+      <s:c r="C53" s="26">
+        <s:f>IFERROR($B53/$B$56,0)</s:f>
+        <s:v>0.026342513249855613</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="54">
+      <s:c r="A54" s="20" t="inlineStr">
+        <s:is>
+          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B54" s="31">
+        <s:f>-SUMIF($D$13:$D$42,$A54,$E$13:$E$42)</s:f>
+        <s:v>7505.41</s:v>
+      </s:c>
+      <s:c r="C54" s="26">
+        <s:f>IFERROR($B54/$B$56,0)</s:f>
+        <s:v>0.03454861557841558</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="55">
+      <s:c r="A55" s="20" t="inlineStr">
+        <s:is>
+          <s:t>სხვა / Other</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B55" s="31">
+        <s:f>-SUMIF($D$13:$D$42,$A55,$E$13:$E$42)</s:f>
         <s:v>929.08</s:v>
       </s:c>
-      <s:c r="C53" s="26">
-        <s:f>IFERROR($B53/$B$54,0)</s:f>
-        <s:v>0.004276705438023285</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="54">
-      <s:c r="A54" s="21" t="inlineStr">
+      <s:c r="C55" s="26">
+        <s:f>IFERROR($B55/$B$56,0)</s:f>
+        <s:v>0.004276705438023286</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="56">
+      <s:c r="A56" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B54" s="30">
-        <s:f>SUM(B47:B53)</s:f>
-        <s:v>217241.99</s:v>
-      </s:c>
-      <s:c r="C54" s="23">
-        <s:f>IFERROR(B54/B54,0)</s:f>
+      <s:c r="B56" s="30">
+        <s:f>SUM(B47:B55)</s:f>
+        <s:v>217241.98999999996</s:v>
+      </s:c>
+      <s:c r="C56" s="23">
+        <s:f>IFERROR(B56/B56,0)</s:f>
         <s:v>1.0</s:v>
       </s:c>
     </s:row>
-    <s:row r="55">
-      <s:c r="A55" s="3" t="inlineStr">
+    <s:row r="57">
+      <s:c r="A57" s="3" t="inlineStr">
         <s:is>
           <s:t>შემოწმება / Check vs statement total (must be 0)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B55" s="73">
-        <s:f>B54+E43</s:f>
-        <s:v>0.0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="57">
-      <s:c r="A57" s="10" t="inlineStr">
+      <s:c r="B57" s="73">
+        <s:f>B56+E43</s:f>
+        <s:v>-2.9103830456733704e-11</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="59">
+      <s:c r="A59" s="10" t="inlineStr">
         <s:is>
           <s:t>თვეების მიხედვით / BY MONTH</s:t>
         </s:is>
       </s:c>
-      <s:c r="B57" s="11" t="n"/>
-      <s:c r="C57" s="11" t="n"/>
-      <s:c r="D57" s="11" t="n"/>
-      <s:c r="E57" s="11" t="n"/>
-    </s:row>
-    <s:row r="58">
-      <s:c r="A58" s="59" t="inlineStr">
+      <s:c r="B59" s="11" t="n"/>
+      <s:c r="C59" s="11" t="n"/>
+      <s:c r="D59" s="11" t="n"/>
+      <s:c r="E59" s="11" t="n"/>
+    </s:row>
+    <s:row r="60">
+      <s:c r="A60" s="59" t="inlineStr">
         <s:is>
           <s:t>თვე / Month</s:t>
         </s:is>
       </s:c>
-      <s:c r="B58" s="12" t="inlineStr">
+      <s:c r="B60" s="12" t="inlineStr">
         <s:is>
           <s:t>თანხა GEL / Amount</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="59">
-      <s:c r="A59" s="20" t="inlineStr">
+    <s:row r="61">
+      <s:c r="A61" s="20" t="inlineStr">
         <s:is>
           <s:t>ივლისი 2026 / July</s:t>
         </s:is>
       </s:c>
-      <s:c r="B59" s="31">
+      <s:c r="B61" s="31">
         <s:f>-SUMPRODUCT(($A$13:$A$42&gt;=DATE(2026,7,1))*($A$13:$A$42&lt;=DATE(2026,7,31))*$E$13:$E$42)</s:f>
         <s:v>68664.21</s:v>
       </s:c>
     </s:row>
-    <s:row r="60">
-      <s:c r="A60" s="20" t="inlineStr">
+    <s:row r="62">
+      <s:c r="A62" s="20" t="inlineStr">
         <s:is>
           <s:t>აგვისტო 2026 / August</s:t>
         </s:is>
       </s:c>
-      <s:c r="B60" s="31">
+      <s:c r="B62" s="31">
         <s:f>-SUMPRODUCT(($A$13:$A$42&gt;=DATE(2026,8,1))*($A$13:$A$42&lt;=DATE(2026,8,31))*$E$13:$E$42)</s:f>
         <s:v>21477.0</s:v>
       </s:c>
     </s:row>
-    <s:row r="61">
-      <s:c r="A61" s="20" t="inlineStr">
+    <s:row r="63">
+      <s:c r="A63" s="20" t="inlineStr">
         <s:is>
           <s:t>სექტემბერი 2026 (21-მდე) / September (to the 21st)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B61" s="31">
+      <s:c r="B63" s="31">
         <s:f>-SUMPRODUCT(($A$13:$A$42&gt;=DATE(2026,9,1))*($A$13:$A$42&lt;=DATE(2026,9,30))*$E$13:$E$42)</s:f>
         <s:v>127100.78</s:v>
       </s:c>
     </s:row>
-    <s:row r="62">
-      <s:c r="A62" s="21" t="inlineStr">
+    <s:row r="64">
+      <s:c r="A64" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B62" s="30">
-        <s:f>SUM(B59:B61)</s:f>
+      <s:c r="B64" s="30">
+        <s:f>SUM(B61:B63)</s:f>
         <s:v>217241.99</s:v>
       </s:c>
     </s:row>
-    <s:row r="64">
-      <s:c r="A64" s="10" t="inlineStr">
+    <s:row r="66">
+      <s:c r="A66" s="10" t="inlineStr">
         <s:is>
           <s:t>ძირითადი ფაქტები / KEY FACTS</s:t>
         </s:is>
       </s:c>
-      <s:c r="B64" s="11" t="n"/>
-      <s:c r="C64" s="11" t="n"/>
-      <s:c r="D64" s="11" t="n"/>
-      <s:c r="E64" s="11" t="n"/>
-    </s:row>
-    <s:row r="65">
-      <s:c r="A65" s="17" t="inlineStr">
+      <s:c r="B66" s="11" t="n"/>
+      <s:c r="C66" s="11" t="n"/>
+      <s:c r="D66" s="11" t="n"/>
+      <s:c r="E66" s="11" t="n"/>
+    </s:row>
+    <s:row r="67">
+      <s:c r="A67" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 09/07/2026 (22,000 USD) / FX rate on the 09/07/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B65" s="74">
+      <s:c r="B67" s="74">
         <s:f>-E17/22000</s:f>
         <s:v>2.6384000000000003</s:v>
       </s:c>
-      <s:c r="C65" s="42" t="inlineStr">
+      <s:c r="C67" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში მითითებული კურსი 2.6384 / the description states 2.6384</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="66">
-      <s:c r="A66" s="17" t="inlineStr">
+    <s:row r="68">
+      <s:c r="A68" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 04/08/2026 (5,000 USD) / FX rate on the 04/08/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B66" s="74">
+      <s:c r="B68" s="74">
         <s:f>-E20/5000</s:f>
         <s:v>2.62</s:v>
       </s:c>
-      <s:c r="C66" s="42" t="inlineStr">
+      <s:c r="C68" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში კურსი არ არის მითითებული / no rate stated in the description</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="67">
-      <s:c r="A67" s="17" t="inlineStr">
+    <s:row r="69">
+      <s:c r="A69" s="17" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსები / Construction advances paid (USD)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B67" s="75">
+      <s:c r="B69" s="75">
         <s:f>22000+5000</s:f>
         <s:v>27000.0</s:v>
       </s:c>
-      <s:c r="C67" s="42" t="inlineStr">
+      <s:c r="C69" s="42" t="inlineStr">
         <s:is>
           <s:t>ხელშეკრულება N1, 7/6/2026, შპს ჯიესენ გრუპ / contract N1 of 7/6/2026 with LLC GSN Group</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="68">
-      <s:c r="A68" s="17" t="inlineStr">
+    <s:row r="70">
+      <s:c r="A70" s="17" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსები / Construction advances paid (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B68" s="76">
+      <s:c r="B70" s="76">
         <s:f>B47</s:f>
         <s:v>178544.8</s:v>
       </s:c>
-      <s:c r="C68" s="42" t="inlineStr">
+      <s:c r="C70" s="42" t="inlineStr">
         <s:is>
           <s:t>ორივე გადარიცხვის ჯამი / the two transfers above</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="69">
-      <s:c r="A69" s="17" t="inlineStr">
+    <s:row r="71">
+      <s:c r="A71" s="17" t="inlineStr">
         <s:is>
           <s:t>სულ გადახდილი / Total paid out (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B69" s="38">
+      <s:c r="B71" s="38">
         <s:f>-E43</s:f>
         <s:v>217241.99</s:v>
       </s:c>
-      <s:c r="C69" s="42" t="inlineStr">
+      <s:c r="C71" s="42" t="inlineStr">
         <s:is>
           <s:t>01/07–08/09/2026</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="70">
-      <s:c r="A70" s="17" t="inlineStr">
+    <s:row r="72">
+      <s:c r="A72" s="17" t="inlineStr">
         <s:is>
           <s:t>შემოსავალი ამონაწერში / Inflows in the statement (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B70" s="38">
+      <s:c r="B72" s="38">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C70" s="42" t="inlineStr">
+      <s:c r="C72" s="42" t="inlineStr">
         <s:is>
           <s:t>ამონაწერში შემოსავალი არ ფიქსირდება — 140,000 USD სესხი ამ ანგარიშზე ამ პერიოდში არ ჩანს. / The statement shows no inflows; the USD 140,000 loan is not visible in this account for this period.</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="72">
-      <s:c r="A72" s="2" t="inlineStr">
+    <s:row r="74">
+      <s:c r="A74" s="2" t="inlineStr">
         <s:is>
           <s:t>შენიშვნა: ამონაწერი მხოლოდ ერთ ანგარიშს ფარავს და მასში შემოსავალი არ არის. თუ სესხი სხვა ანგარიშზეა ჩარიცხული, დაამატეთ ის ამონაწერიც. / Note: the statement covers one account and contains no inflows. If the loan was disbursed into another account, add that statement too.</s:t>
         </s:is>

--- a/finance/Greenhouse_CashFlow_2000m2.xlsx
+++ b/finance/Greenhouse_CashFlow_2000m2.xlsx
@@ -1233,16 +1233,16 @@
         </s:is>
       </s:c>
       <s:c r="B7" s="18">
-        <s:f>B21</s:f>
-        <s:v>7505.41</s:v>
+        <s:f>B23</s:f>
+        <s:v>220061.63999999998</s:v>
       </s:c>
       <s:c r="C7" s="19">
         <s:f>IFERROR(B7/$B$6,0)</s:f>
-        <s:v>0.012008656</s:v>
+        <s:v>0.35209862399999997</s:v>
       </s:c>
       <s:c r="D7" s="20" t="str">
         <s:f>REPT("|",ROUND(C7*40,0))</s:f>
-        <s:v/>
+        <s:v>||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="8">
@@ -1252,16 +1252,16 @@
         </s:is>
       </s:c>
       <s:c r="B8" s="18">
-        <s:f>D34</s:f>
-        <s:v>329800.0</s:v>
+        <s:f>D36</s:f>
+        <s:v>150127.19999999998</s:v>
       </s:c>
       <s:c r="C8" s="19">
         <s:f>IFERROR(B8/$B$6,0)</s:f>
-        <s:v>0.52768</s:v>
+        <s:v>0.24020351999999998</s:v>
       </s:c>
       <s:c r="D8" s="20" t="str">
         <s:f>REPT("|",ROUND(C8*40,0))</s:f>
-        <s:v>|||||||||||||||||||||</s:v>
+        <s:v>||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="9">
@@ -1272,15 +1272,15 @@
       </s:c>
       <s:c r="B9" s="22">
         <s:f>B7+B8</s:f>
-        <s:v>337305.41</s:v>
+        <s:v>370188.83999999997</s:v>
       </s:c>
       <s:c r="C9" s="23">
         <s:f>IFERROR(B9/$B$6,0)</s:f>
-        <s:v>0.5396886559999999</s:v>
+        <s:v>0.5923021439999999</s:v>
       </s:c>
       <s:c r="D9" s="24" t="str">
         <s:f>REPT("|",ROUND(C9*40,0))</s:f>
-        <s:v>||||||||||||||||||||||</s:v>
+        <s:v>||||||||||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="10">
@@ -1291,15 +1291,15 @@
       </s:c>
       <s:c r="B10" s="22">
         <s:f>B6-B9</s:f>
-        <s:v>287694.59</s:v>
+        <s:v>254811.16000000003</s:v>
       </s:c>
       <s:c r="C10" s="23">
         <s:f>IFERROR(B10/$B$6,0)</s:f>
-        <s:v>0.46031134400000007</s:v>
+        <s:v>0.407697856</s:v>
       </s:c>
       <s:c r="D10" s="24" t="str">
         <s:f>REPT("|",ROUND(C10*40,0))</s:f>
-        <s:v>||||||||||||||||||</s:v>
+        <s:v>||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="12">
@@ -1353,12 +1353,12 @@
         </s:is>
       </s:c>
       <s:c r="B14" s="25">
-        <s:f>Actuals!B47</s:f>
+        <s:f>Actuals!B67</s:f>
         <s:v>178544.8</s:v>
       </s:c>
       <s:c r="C14" s="26">
         <s:f>IFERROR(B14/$B$23,0)</s:f>
-        <s:v>0.8218705785193738</s:v>
+        <s:v>0.8113399500249112</s:v>
       </s:c>
       <s:c r="D14" s="27" t="inlineStr">
         <s:is>
@@ -1383,12 +1383,12 @@
         </s:is>
       </s:c>
       <s:c r="B15" s="25">
-        <s:f>Actuals!B48</s:f>
+        <s:f>Actuals!B68</s:f>
         <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C15" s="26">
         <s:f>IFERROR(B15/$B$23,0)</s:f>
-        <s:v>0.04603161663175706</s:v>
+        <s:v>0.045441813484621854</s:v>
       </s:c>
       <s:c r="D15" s="27" t="inlineStr">
         <s:is>
@@ -1408,12 +1408,12 @@
         </s:is>
       </s:c>
       <s:c r="B16" s="25">
-        <s:f>Actuals!B49</s:f>
+        <s:f>Actuals!B69</s:f>
         <s:v>1470.0</s:v>
       </s:c>
       <s:c r="C16" s="26">
         <s:f>IFERROR(B16/$B$23,0)</s:f>
-        <s:v>0.006766647644868289</s:v>
+        <s:v>0.006679946582239413</s:v>
       </s:c>
       <s:c r="D16" s="27" t="inlineStr">
         <s:is>
@@ -1433,12 +1433,12 @@
         </s:is>
       </s:c>
       <s:c r="B17" s="25">
-        <s:f>Actuals!B50</s:f>
+        <s:f>Actuals!B70</s:f>
         <s:v>3070.0</s:v>
       </s:c>
       <s:c r="C17" s="26">
         <s:f>IFERROR(B17/$B$23,0)</s:f>
-        <s:v>0.01413170630594942</s:v>
+        <s:v>0.01395063673977891</s:v>
       </s:c>
       <s:c r="D17" s="27" t="inlineStr">
         <s:is>
@@ -1458,12 +1458,12 @@
         </s:is>
       </s:c>
       <s:c r="B18" s="25">
-        <s:f>Actuals!B51</s:f>
-        <s:v>-0.0</s:v>
+        <s:f>Actuals!B71</s:f>
+        <s:v>2819.65</s:v>
       </s:c>
       <s:c r="C18" s="26">
         <s:f>IFERROR(B18/$B$23,0)</s:f>
-        <s:v>-0.0</s:v>
+        <s:v>0.012813000939191403</s:v>
       </s:c>
       <s:c r="D18" s="27" t="inlineStr">
         <s:is>
@@ -1483,12 +1483,12 @@
         </s:is>
       </s:c>
       <s:c r="B19" s="25">
-        <s:f>Actuals!B52</s:f>
+        <s:f>Actuals!B72</s:f>
         <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C19" s="26">
         <s:f>IFERROR(B19/$B$23,0)</s:f>
-        <s:v>0.04603161663175706</s:v>
+        <s:v>0.045441813484621854</s:v>
       </s:c>
       <s:c r="D19" s="27" t="inlineStr">
         <s:is>
@@ -1508,12 +1508,12 @@
         </s:is>
       </s:c>
       <s:c r="B20" s="25">
-        <s:f>Actuals!B53</s:f>
+        <s:f>Actuals!B73</s:f>
         <s:v>5722.7</s:v>
       </s:c>
       <s:c r="C20" s="26">
         <s:f>IFERROR(B20/$B$23,0)</s:f>
-        <s:v>0.026342513249855613</s:v>
+        <s:v>0.02600498660284455</s:v>
       </s:c>
       <s:c r="D20" s="27" t="inlineStr">
         <s:is>
@@ -1533,12 +1533,12 @@
         </s:is>
       </s:c>
       <s:c r="B21" s="25">
-        <s:f>Actuals!B54</s:f>
+        <s:f>Actuals!B74</s:f>
         <s:v>7505.41</s:v>
       </s:c>
       <s:c r="C21" s="26">
         <s:f>IFERROR(B21/$B$23,0)</s:f>
-        <s:v>0.03454861557841558</s:v>
+        <s:v>0.03410594413456157</s:v>
       </s:c>
       <s:c r="D21" s="27" t="inlineStr">
         <s:is>
@@ -1558,12 +1558,12 @@
         </s:is>
       </s:c>
       <s:c r="B22" s="25">
-        <s:f>Actuals!B55</s:f>
+        <s:f>Actuals!B75</s:f>
         <s:v>929.08</s:v>
       </s:c>
       <s:c r="C22" s="26">
         <s:f>IFERROR(B22/$B$23,0)</s:f>
-        <s:v>0.004276705438023286</s:v>
+        <s:v>0.0042219080072292475</s:v>
       </s:c>
       <s:c r="D22" s="27" t="inlineStr">
         <s:is>
@@ -1584,7 +1584,7 @@
       </s:c>
       <s:c r="B23" s="30">
         <s:f>SUM(B14:B22)</s:f>
-        <s:v>217241.98999999996</s:v>
+        <s:v>220061.63999999998</s:v>
       </s:c>
       <s:c r="C23" s="23">
         <s:f>IFERROR(B23/B23,0)</s:f>
@@ -1641,16 +1641,16 @@
         </s:is>
       </s:c>
       <s:c r="B27" s="25">
-        <s:f>Actuals!B61</s:f>
-        <s:v>68664.21</s:v>
+        <s:f>Actuals!B81</s:f>
+        <s:v>69796.68000000001</s:v>
       </s:c>
       <s:c r="C27" s="31">
         <s:f>SUM($B$27:B27)</s:f>
-        <s:v>68664.21</s:v>
+        <s:v>69796.68000000001</s:v>
       </s:c>
       <s:c r="D27" s="18">
         <s:f>$B$6-C27</s:f>
-        <s:v>556335.79</s:v>
+        <s:v>555203.32</s:v>
       </s:c>
     </s:row>
     <s:row r="28">
@@ -1660,16 +1660,16 @@
         </s:is>
       </s:c>
       <s:c r="B28" s="25">
-        <s:f>Actuals!B62</s:f>
-        <s:v>21477.0</s:v>
+        <s:f>Actuals!B82</s:f>
+        <s:v>22040.5</s:v>
       </s:c>
       <s:c r="C28" s="31">
         <s:f>SUM($B$27:B28)</s:f>
-        <s:v>90141.21</s:v>
+        <s:v>91837.18000000001</s:v>
       </s:c>
       <s:c r="D28" s="18">
         <s:f>$B$6-C28</s:f>
-        <s:v>534858.79</s:v>
+        <s:v>533162.82</s:v>
       </s:c>
     </s:row>
     <s:row r="29">
@@ -1679,16 +1679,16 @@
         </s:is>
       </s:c>
       <s:c r="B29" s="25">
-        <s:f>Actuals!B63</s:f>
-        <s:v>127100.78</s:v>
+        <s:f>Actuals!B83</s:f>
+        <s:v>128224.45999999999</s:v>
       </s:c>
       <s:c r="C29" s="31">
         <s:f>SUM($B$27:B29)</s:f>
-        <s:v>217241.99</s:v>
+        <s:v>220061.64</s:v>
       </s:c>
       <s:c r="D29" s="18">
         <s:f>$B$6-C29</s:f>
-        <s:v>407758.01</s:v>
+        <s:v>404938.36</s:v>
       </s:c>
     </s:row>
     <s:row r="30">
@@ -1699,7 +1699,7 @@
       </s:c>
       <s:c r="B30" s="30">
         <s:f>SUM(B27:B29)</s:f>
-        <s:v>217241.99</s:v>
+        <s:v>220061.64</s:v>
       </s:c>
       <s:c r="C30" s="30">
         <s:f>B30-B23</s:f>
@@ -1707,7 +1707,7 @@
       </s:c>
       <s:c r="D30" s="22">
         <s:f>$B$6-B30</s:f>
-        <s:v>407758.01</s:v>
+        <s:v>404938.36</s:v>
       </s:c>
       <s:c r="G30" s="2" t="inlineStr">
         <s:is>
@@ -1787,7 +1787,7 @@
         <s:v>2.6218359168443968</s:v>
       </s:c>
       <s:c r="D35" s="25">
-        <s:f>Actuals!B47</s:f>
+        <s:f>Actuals!B67</s:f>
         <s:v>178544.8</s:v>
       </s:c>
       <s:c r="G35" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </s:c>
       <s:c r="C40" s="19">
         <s:f>IFERROR(B40/$B$23,0)</s:f>
-        <s:v>0.8870384127856683</s:v>
+        <s:v>0.8756727887695466</s:v>
       </s:c>
       <s:c r="G40" s="2" t="inlineStr">
         <s:is>
@@ -1866,11 +1866,11 @@
       </s:c>
       <s:c r="B41" s="38">
         <s:f>SUMIF($D$14:$D$22,"OPEX",$B$14:$B$22)</s:f>
-        <s:v>24540.0</s:v>
+        <s:v>27359.65</s:v>
       </s:c>
       <s:c r="C41" s="19">
         <s:f>IFERROR(B41/$B$23,0)</s:f>
-        <s:v>0.11296158721433183</s:v>
+        <s:v>0.12432721123045344</s:v>
       </s:c>
       <s:c r="G41" s="2" t="inlineStr">
         <s:is>
@@ -1886,7 +1886,7 @@
       </s:c>
       <s:c r="B42" s="39">
         <s:f>B40+B41-B23</s:f>
-        <s:v>2.9103830456733704e-11</s:v>
+        <s:v>0.0</s:v>
       </s:c>
     </s:row>
     <s:row r="44">
@@ -13443,7 +13443,7 @@
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
     <s:pageSetUpPr/>
   </s:sheetPr>
-  <s:dimension ref="A1:E74"/>
+  <s:dimension ref="A1:E94"/>
   <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <s:cols>
     <s:col width="13" customWidth="1" min="1" max="1"/>
@@ -13524,7 +13524,7 @@
       </s:c>
       <s:c r="B8" s="20" t="inlineStr">
         <s:is>
-          <s:t>01/07/2026 – 21/09/2026 · 30 გადარიცხვა / 30 payments</s:t>
+          <s:t>01/07/2026 – 21/09/2026 · 30 საბანკო + 20 საწვავი / 30 bank + 20 fuel-card</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -14269,384 +14269,764 @@
       </s:c>
     </s:row>
     <s:row r="43">
-      <s:c r="A43" s="21" t="inlineStr">
+      <s:c r="A43" s="71" t="n">
+        <s:v>46205</s:v>
+      </s:c>
+      <s:c r="B43" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 27.62 ლ — SANAPIRO</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C43" s="63" t="inlineStr"/>
+      <s:c r="D43" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E43" s="72" t="n">
+        <s:v>-100</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="44">
+      <s:c r="A44" s="71" t="n">
+        <s:v>46208</s:v>
+      </s:c>
+      <s:c r="B44" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 29.67 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C44" s="63" t="inlineStr"/>
+      <s:c r="D44" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E44" s="72" t="n">
+        <s:v>-100</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="45">
+      <s:c r="A45" s="71" t="n">
+        <s:v>46212</s:v>
+      </s:c>
+      <s:c r="B45" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 65 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C45" s="63" t="inlineStr"/>
+      <s:c r="D45" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E45" s="72" t="n">
+        <s:v>-222.3</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="46">
+      <s:c r="A46" s="71" t="n">
+        <s:v>46220</s:v>
+      </s:c>
+      <s:c r="B46" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 50 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C46" s="63" t="inlineStr"/>
+      <s:c r="D46" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E46" s="72" t="n">
+        <s:v>-171</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="47">
+      <s:c r="A47" s="71" t="n">
+        <s:v>46222</s:v>
+      </s:c>
+      <s:c r="B47" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი Euro Diesel 11.55 ლ — SAGAREJO</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C47" s="63" t="inlineStr"/>
+      <s:c r="D47" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E47" s="72" t="n">
+        <s:v>-44.12</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="48">
+      <s:c r="A48" s="71" t="n">
+        <s:v>46225</s:v>
+      </s:c>
+      <s:c r="B48" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 65 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C48" s="63" t="inlineStr"/>
+      <s:c r="D48" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E48" s="72" t="n">
+        <s:v>-219.05</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="49">
+      <s:c r="A49" s="71" t="n">
+        <s:v>46229</s:v>
+      </s:c>
+      <s:c r="B49" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 30 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C49" s="63" t="inlineStr"/>
+      <s:c r="D49" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E49" s="72" t="n">
+        <s:v>-103.5</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="50">
+      <s:c r="A50" s="71" t="n">
+        <s:v>46232</s:v>
+      </s:c>
+      <s:c r="B50" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 50 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C50" s="63" t="inlineStr"/>
+      <s:c r="D50" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E50" s="72" t="n">
+        <s:v>-172.5</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="51">
+      <s:c r="A51" s="71" t="n">
+        <s:v>46238</s:v>
+      </s:c>
+      <s:c r="B51" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 50 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C51" s="63" t="inlineStr"/>
+      <s:c r="D51" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E51" s="72" t="n">
+        <s:v>-175</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="52">
+      <s:c r="A52" s="71" t="n">
+        <s:v>46240</s:v>
+      </s:c>
+      <s:c r="B52" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 60 ლ — BIO</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C52" s="63" t="inlineStr"/>
+      <s:c r="D52" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E52" s="72" t="n">
+        <s:v>-210</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="53">
+      <s:c r="A53" s="71" t="n">
+        <s:v>46241</s:v>
+      </s:c>
+      <s:c r="B53" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი Euro Diesel 11 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C53" s="63" t="inlineStr"/>
+      <s:c r="D53" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E53" s="72" t="n">
+        <s:v>-42.9</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="54">
+      <s:c r="A54" s="71" t="n">
+        <s:v>46243</s:v>
+      </s:c>
+      <s:c r="B54" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 28.99 ლ — BIO</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C54" s="63" t="inlineStr"/>
+      <s:c r="D54" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E54" s="72" t="n">
+        <s:v>-100</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="55">
+      <s:c r="A55" s="71" t="n">
+        <s:v>46254</s:v>
+      </s:c>
+      <s:c r="B55" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 10 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C55" s="63" t="inlineStr"/>
+      <s:c r="D55" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E55" s="72" t="n">
+        <s:v>-35.6</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="56">
+      <s:c r="A56" s="71" t="n">
+        <s:v>46268</s:v>
+      </s:c>
+      <s:c r="B56" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 10 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C56" s="63" t="inlineStr"/>
+      <s:c r="D56" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E56" s="72" t="n">
+        <s:v>-36.6</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="57">
+      <s:c r="A57" s="71" t="n">
+        <s:v>46268</s:v>
+      </s:c>
+      <s:c r="B57" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 40 ლ — COSMONAVTI EXPRESS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C57" s="63" t="inlineStr"/>
+      <s:c r="D57" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E57" s="72" t="n">
+        <s:v>-146.4</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="58">
+      <s:c r="A58" s="71" t="n">
+        <s:v>46273</s:v>
+      </s:c>
+      <s:c r="B58" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 21.38 ლ — LILO</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C58" s="63" t="inlineStr"/>
+      <s:c r="D58" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E58" s="72" t="n">
+        <s:v>-81.03</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="59">
+      <s:c r="A59" s="71" t="n">
+        <s:v>46274</s:v>
+      </s:c>
+      <s:c r="B59" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 60 ლ — ZESTAPHONI</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C59" s="63" t="inlineStr"/>
+      <s:c r="D59" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E59" s="72" t="n">
+        <s:v>-224.4</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="60">
+      <s:c r="A60" s="71" t="n">
+        <s:v>46276</s:v>
+      </s:c>
+      <s:c r="B60" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 50 ლ — PIKRIS GORA</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C60" s="63" t="inlineStr"/>
+      <s:c r="D60" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E60" s="72" t="n">
+        <s:v>-192.5</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="61">
+      <s:c r="A61" s="71" t="n">
+        <s:v>46279</s:v>
+      </s:c>
+      <s:c r="B61" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 65 ლ — TSEROVANI</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C61" s="63" t="inlineStr"/>
+      <s:c r="D61" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E61" s="72" t="n">
+        <s:v>-250.25</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="62">
+      <s:c r="A62" s="71" t="n">
+        <s:v>46282</s:v>
+      </s:c>
+      <s:c r="B62" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი G-Force Premium 50 ლ — NAREKVAVI</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C62" s="63" t="inlineStr"/>
+      <s:c r="D62" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E62" s="72" t="n">
+        <s:v>-192.5</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="63">
+      <s:c r="A63" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B43" s="24" t="inlineStr"/>
-      <s:c r="C43" s="24" t="inlineStr"/>
-      <s:c r="D43" s="24" t="inlineStr"/>
-      <s:c r="E43" s="30">
-        <s:f>SUM(E13:E42)</s:f>
-        <s:v>-217241.99</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="45">
-      <s:c r="A45" s="10" t="inlineStr">
+      <s:c r="B63" s="24" t="inlineStr"/>
+      <s:c r="C63" s="24" t="inlineStr"/>
+      <s:c r="D63" s="24" t="inlineStr"/>
+      <s:c r="E63" s="30">
+        <s:f>SUM(E13:E62)</s:f>
+        <s:v>-220061.63999999998</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="65">
+      <s:c r="A65" s="10" t="inlineStr">
         <s:is>
           <s:t>კატეგორიების მიხედვით / BY CATEGORY</s:t>
         </s:is>
       </s:c>
-      <s:c r="B45" s="11" t="n"/>
-      <s:c r="C45" s="11" t="n"/>
-      <s:c r="D45" s="11" t="n"/>
-      <s:c r="E45" s="11" t="n"/>
-    </s:row>
-    <s:row r="46">
-      <s:c r="A46" s="59" t="inlineStr">
+      <s:c r="B65" s="11" t="n"/>
+      <s:c r="C65" s="11" t="n"/>
+      <s:c r="D65" s="11" t="n"/>
+      <s:c r="E65" s="11" t="n"/>
+    </s:row>
+    <s:row r="66">
+      <s:c r="A66" s="59" t="inlineStr">
         <s:is>
           <s:t>კატეგორია / Category</s:t>
         </s:is>
       </s:c>
-      <s:c r="B46" s="12" t="inlineStr">
+      <s:c r="B66" s="12" t="inlineStr">
         <s:is>
           <s:t>თანხა GEL / Amount</s:t>
         </s:is>
       </s:c>
-      <s:c r="C46" s="12" t="inlineStr">
+      <s:c r="C66" s="12" t="inlineStr">
         <s:is>
           <s:t>% ჯამიდან / of total</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="47">
-      <s:c r="A47" s="20" t="inlineStr">
+    <s:row r="67">
+      <s:c r="A67" s="20" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
-      <s:c r="B47" s="31">
-        <s:f>-SUMIF($D$13:$D$42,$A47,$E$13:$E$42)</s:f>
+      <s:c r="B67" s="31">
+        <s:f>-SUMIF($D$13:$D$62,$A67,$E$13:$E$62)</s:f>
         <s:v>178544.8</s:v>
       </s:c>
-      <s:c r="C47" s="26">
-        <s:f>IFERROR($B47/$B$56,0)</s:f>
-        <s:v>0.8218705785193738</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="48">
-      <s:c r="A48" s="20" t="inlineStr">
+      <s:c r="C67" s="26">
+        <s:f>IFERROR($B67/$B$76,0)</s:f>
+        <s:v>0.8113399500249112</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="68">
+      <s:c r="A68" s="20" t="inlineStr">
         <s:is>
           <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
-      <s:c r="B48" s="31">
-        <s:f>-SUMIF($D$13:$D$42,$A48,$E$13:$E$42)</s:f>
+      <s:c r="B68" s="31">
+        <s:f>-SUMIF($D$13:$D$62,$A68,$E$13:$E$62)</s:f>
         <s:v>10000.0</s:v>
       </s:c>
-      <s:c r="C48" s="26">
-        <s:f>IFERROR($B48/$B$56,0)</s:f>
-        <s:v>0.04603161663175706</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="49">
-      <s:c r="A49" s="20" t="inlineStr">
+      <s:c r="C68" s="26">
+        <s:f>IFERROR($B68/$B$76,0)</s:f>
+        <s:v>0.045441813484621854</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="69">
+      <s:c r="A69" s="20" t="inlineStr">
         <s:is>
           <s:t>გადასახადები / Taxes &amp; pension</s:t>
         </s:is>
       </s:c>
-      <s:c r="B49" s="31">
-        <s:f>-SUMIF($D$13:$D$42,$A49,$E$13:$E$42)</s:f>
+      <s:c r="B69" s="31">
+        <s:f>-SUMIF($D$13:$D$62,$A69,$E$13:$E$62)</s:f>
         <s:v>1470.0</s:v>
       </s:c>
-      <s:c r="C49" s="26">
-        <s:f>IFERROR($B49/$B$56,0)</s:f>
-        <s:v>0.006766647644868289</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="50">
-      <s:c r="A50" s="20" t="inlineStr">
+      <s:c r="C69" s="26">
+        <s:f>IFERROR($B69/$B$76,0)</s:f>
+        <s:v>0.006679946582239413</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="70">
+      <s:c r="A70" s="20" t="inlineStr">
         <s:is>
           <s:t>მომსახურება / Services</s:t>
         </s:is>
       </s:c>
-      <s:c r="B50" s="31">
-        <s:f>-SUMIF($D$13:$D$42,$A50,$E$13:$E$42)</s:f>
+      <s:c r="B70" s="31">
+        <s:f>-SUMIF($D$13:$D$62,$A70,$E$13:$E$62)</s:f>
         <s:v>3070.0</s:v>
       </s:c>
-      <s:c r="C50" s="26">
-        <s:f>IFERROR($B50/$B$56,0)</s:f>
-        <s:v>0.01413170630594942</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="51">
-      <s:c r="A51" s="20" t="inlineStr">
+      <s:c r="C70" s="26">
+        <s:f>IFERROR($B70/$B$76,0)</s:f>
+        <s:v>0.01395063673977891</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="71">
+      <s:c r="A71" s="20" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="B51" s="31">
-        <s:f>-SUMIF($D$13:$D$42,$A51,$E$13:$E$42)</s:f>
-        <s:v>-0.0</s:v>
-      </s:c>
-      <s:c r="C51" s="26">
-        <s:f>IFERROR($B51/$B$56,0)</s:f>
-        <s:v>-0.0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="52">
-      <s:c r="A52" s="20" t="inlineStr">
+      <s:c r="B71" s="31">
+        <s:f>-SUMIF($D$13:$D$62,$A71,$E$13:$E$62)</s:f>
+        <s:v>2819.65</s:v>
+      </s:c>
+      <s:c r="C71" s="26">
+        <s:f>IFERROR($B71/$B$76,0)</s:f>
+        <s:v>0.012813000939191403</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="72">
+      <s:c r="A72" s="20" t="inlineStr">
         <s:is>
           <s:t>მუშების კვება / Worker meals</s:t>
         </s:is>
       </s:c>
-      <s:c r="B52" s="31">
-        <s:f>-SUMIF($D$13:$D$42,$A52,$E$13:$E$42)</s:f>
+      <s:c r="B72" s="31">
+        <s:f>-SUMIF($D$13:$D$62,$A72,$E$13:$E$62)</s:f>
         <s:v>10000.0</s:v>
       </s:c>
-      <s:c r="C52" s="26">
-        <s:f>IFERROR($B52/$B$56,0)</s:f>
-        <s:v>0.04603161663175706</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="53">
-      <s:c r="A53" s="20" t="inlineStr">
+      <s:c r="C72" s="26">
+        <s:f>IFERROR($B72/$B$76,0)</s:f>
+        <s:v>0.045441813484621854</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="73">
+      <s:c r="A73" s="20" t="inlineStr">
         <s:is>
           <s:t>მასალები / Materials</s:t>
         </s:is>
       </s:c>
-      <s:c r="B53" s="31">
-        <s:f>-SUMIF($D$13:$D$42,$A53,$E$13:$E$42)</s:f>
+      <s:c r="B73" s="31">
+        <s:f>-SUMIF($D$13:$D$62,$A73,$E$13:$E$62)</s:f>
         <s:v>5722.7</s:v>
       </s:c>
-      <s:c r="C53" s="26">
-        <s:f>IFERROR($B53/$B$56,0)</s:f>
-        <s:v>0.026342513249855613</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="54">
-      <s:c r="A54" s="20" t="inlineStr">
+      <s:c r="C73" s="26">
+        <s:f>IFERROR($B73/$B$76,0)</s:f>
+        <s:v>0.02600498660284455</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="74">
+      <s:c r="A74" s="20" t="inlineStr">
         <s:is>
           <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
         </s:is>
       </s:c>
-      <s:c r="B54" s="31">
-        <s:f>-SUMIF($D$13:$D$42,$A54,$E$13:$E$42)</s:f>
+      <s:c r="B74" s="31">
+        <s:f>-SUMIF($D$13:$D$62,$A74,$E$13:$E$62)</s:f>
         <s:v>7505.41</s:v>
       </s:c>
-      <s:c r="C54" s="26">
-        <s:f>IFERROR($B54/$B$56,0)</s:f>
-        <s:v>0.03454861557841558</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="55">
-      <s:c r="A55" s="20" t="inlineStr">
+      <s:c r="C74" s="26">
+        <s:f>IFERROR($B74/$B$76,0)</s:f>
+        <s:v>0.03410594413456157</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="75">
+      <s:c r="A75" s="20" t="inlineStr">
         <s:is>
           <s:t>სხვა / Other</s:t>
         </s:is>
       </s:c>
-      <s:c r="B55" s="31">
-        <s:f>-SUMIF($D$13:$D$42,$A55,$E$13:$E$42)</s:f>
+      <s:c r="B75" s="31">
+        <s:f>-SUMIF($D$13:$D$62,$A75,$E$13:$E$62)</s:f>
         <s:v>929.08</s:v>
       </s:c>
-      <s:c r="C55" s="26">
-        <s:f>IFERROR($B55/$B$56,0)</s:f>
-        <s:v>0.004276705438023286</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="56">
-      <s:c r="A56" s="21" t="inlineStr">
+      <s:c r="C75" s="26">
+        <s:f>IFERROR($B75/$B$76,0)</s:f>
+        <s:v>0.0042219080072292475</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="76">
+      <s:c r="A76" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B56" s="30">
-        <s:f>SUM(B47:B55)</s:f>
-        <s:v>217241.98999999996</s:v>
-      </s:c>
-      <s:c r="C56" s="23">
-        <s:f>IFERROR(B56/B56,0)</s:f>
+      <s:c r="B76" s="30">
+        <s:f>SUM(B67:B75)</s:f>
+        <s:v>220061.63999999998</s:v>
+      </s:c>
+      <s:c r="C76" s="23">
+        <s:f>IFERROR(B76/B76,0)</s:f>
         <s:v>1.0</s:v>
       </s:c>
     </s:row>
-    <s:row r="57">
-      <s:c r="A57" s="3" t="inlineStr">
+    <s:row r="77">
+      <s:c r="A77" s="3" t="inlineStr">
         <s:is>
           <s:t>შემოწმება / Check vs statement total (must be 0)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B57" s="73">
-        <s:f>B56+E43</s:f>
-        <s:v>-2.9103830456733704e-11</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="59">
-      <s:c r="A59" s="10" t="inlineStr">
+      <s:c r="B77" s="73">
+        <s:f>B76+E63</s:f>
+        <s:v>0.0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="79">
+      <s:c r="A79" s="10" t="inlineStr">
         <s:is>
           <s:t>თვეების მიხედვით / BY MONTH</s:t>
         </s:is>
       </s:c>
-      <s:c r="B59" s="11" t="n"/>
-      <s:c r="C59" s="11" t="n"/>
-      <s:c r="D59" s="11" t="n"/>
-      <s:c r="E59" s="11" t="n"/>
-    </s:row>
-    <s:row r="60">
-      <s:c r="A60" s="59" t="inlineStr">
+      <s:c r="B79" s="11" t="n"/>
+      <s:c r="C79" s="11" t="n"/>
+      <s:c r="D79" s="11" t="n"/>
+      <s:c r="E79" s="11" t="n"/>
+    </s:row>
+    <s:row r="80">
+      <s:c r="A80" s="59" t="inlineStr">
         <s:is>
           <s:t>თვე / Month</s:t>
         </s:is>
       </s:c>
-      <s:c r="B60" s="12" t="inlineStr">
+      <s:c r="B80" s="12" t="inlineStr">
         <s:is>
           <s:t>თანხა GEL / Amount</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="61">
-      <s:c r="A61" s="20" t="inlineStr">
+    <s:row r="81">
+      <s:c r="A81" s="20" t="inlineStr">
         <s:is>
           <s:t>ივლისი 2026 / July</s:t>
         </s:is>
       </s:c>
-      <s:c r="B61" s="31">
-        <s:f>-SUMPRODUCT(($A$13:$A$42&gt;=DATE(2026,7,1))*($A$13:$A$42&lt;=DATE(2026,7,31))*$E$13:$E$42)</s:f>
-        <s:v>68664.21</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="62">
-      <s:c r="A62" s="20" t="inlineStr">
+      <s:c r="B81" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$62&gt;=DATE(2026,7,1))*($A$13:$A$62&lt;=DATE(2026,7,31))*$E$13:$E$62)</s:f>
+        <s:v>69796.68000000001</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="82">
+      <s:c r="A82" s="20" t="inlineStr">
         <s:is>
           <s:t>აგვისტო 2026 / August</s:t>
         </s:is>
       </s:c>
-      <s:c r="B62" s="31">
-        <s:f>-SUMPRODUCT(($A$13:$A$42&gt;=DATE(2026,8,1))*($A$13:$A$42&lt;=DATE(2026,8,31))*$E$13:$E$42)</s:f>
-        <s:v>21477.0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="63">
-      <s:c r="A63" s="20" t="inlineStr">
+      <s:c r="B82" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$62&gt;=DATE(2026,8,1))*($A$13:$A$62&lt;=DATE(2026,8,31))*$E$13:$E$62)</s:f>
+        <s:v>22040.5</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="83">
+      <s:c r="A83" s="20" t="inlineStr">
         <s:is>
           <s:t>სექტემბერი 2026 (21-მდე) / September (to the 21st)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B63" s="31">
-        <s:f>-SUMPRODUCT(($A$13:$A$42&gt;=DATE(2026,9,1))*($A$13:$A$42&lt;=DATE(2026,9,30))*$E$13:$E$42)</s:f>
-        <s:v>127100.78</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="64">
-      <s:c r="A64" s="21" t="inlineStr">
+      <s:c r="B83" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$62&gt;=DATE(2026,9,1))*($A$13:$A$62&lt;=DATE(2026,9,30))*$E$13:$E$62)</s:f>
+        <s:v>128224.45999999999</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="84">
+      <s:c r="A84" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B64" s="30">
-        <s:f>SUM(B61:B63)</s:f>
-        <s:v>217241.99</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="66">
-      <s:c r="A66" s="10" t="inlineStr">
+      <s:c r="B84" s="30">
+        <s:f>SUM(B81:B83)</s:f>
+        <s:v>220061.64</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="86">
+      <s:c r="A86" s="10" t="inlineStr">
         <s:is>
           <s:t>ძირითადი ფაქტები / KEY FACTS</s:t>
         </s:is>
       </s:c>
-      <s:c r="B66" s="11" t="n"/>
-      <s:c r="C66" s="11" t="n"/>
-      <s:c r="D66" s="11" t="n"/>
-      <s:c r="E66" s="11" t="n"/>
-    </s:row>
-    <s:row r="67">
-      <s:c r="A67" s="17" t="inlineStr">
+      <s:c r="B86" s="11" t="n"/>
+      <s:c r="C86" s="11" t="n"/>
+      <s:c r="D86" s="11" t="n"/>
+      <s:c r="E86" s="11" t="n"/>
+    </s:row>
+    <s:row r="87">
+      <s:c r="A87" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 09/07/2026 (22,000 USD) / FX rate on the 09/07/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B67" s="74">
+      <s:c r="B87" s="74">
         <s:f>-E17/22000</s:f>
         <s:v>2.6384000000000003</s:v>
       </s:c>
-      <s:c r="C67" s="42" t="inlineStr">
+      <s:c r="C87" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში მითითებული კურსი 2.6384 / the description states 2.6384</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="68">
-      <s:c r="A68" s="17" t="inlineStr">
+    <s:row r="88">
+      <s:c r="A88" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 04/08/2026 (5,000 USD) / FX rate on the 04/08/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B68" s="74">
+      <s:c r="B88" s="74">
         <s:f>-E20/5000</s:f>
         <s:v>2.62</s:v>
       </s:c>
-      <s:c r="C68" s="42" t="inlineStr">
+      <s:c r="C88" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში კურსი არ არის მითითებული / no rate stated in the description</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="69">
-      <s:c r="A69" s="17" t="inlineStr">
+    <s:row r="89">
+      <s:c r="A89" s="17" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსები / Construction advances paid (USD)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B69" s="75">
+      <s:c r="B89" s="75">
         <s:f>22000+5000</s:f>
         <s:v>27000.0</s:v>
       </s:c>
-      <s:c r="C69" s="42" t="inlineStr">
+      <s:c r="C89" s="42" t="inlineStr">
         <s:is>
           <s:t>ხელშეკრულება N1, 7/6/2026, შპს ჯიესენ გრუპ / contract N1 of 7/6/2026 with LLC GSN Group</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="70">
-      <s:c r="A70" s="17" t="inlineStr">
+    <s:row r="90">
+      <s:c r="A90" s="17" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსები / Construction advances paid (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B70" s="76">
-        <s:f>B47</s:f>
+      <s:c r="B90" s="76">
+        <s:f>B67</s:f>
         <s:v>178544.8</s:v>
       </s:c>
-      <s:c r="C70" s="42" t="inlineStr">
+      <s:c r="C90" s="42" t="inlineStr">
         <s:is>
           <s:t>ორივე გადარიცხვის ჯამი / the two transfers above</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="71">
-      <s:c r="A71" s="17" t="inlineStr">
+    <s:row r="91">
+      <s:c r="A91" s="17" t="inlineStr">
         <s:is>
           <s:t>სულ გადახდილი / Total paid out (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B71" s="38">
-        <s:f>-E43</s:f>
-        <s:v>217241.99</s:v>
-      </s:c>
-      <s:c r="C71" s="42" t="inlineStr">
+      <s:c r="B91" s="38">
+        <s:f>-E63</s:f>
+        <s:v>220061.63999999998</s:v>
+      </s:c>
+      <s:c r="C91" s="42" t="inlineStr">
         <s:is>
           <s:t>01/07–08/09/2026</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="72">
-      <s:c r="A72" s="17" t="inlineStr">
+    <s:row r="92">
+      <s:c r="A92" s="17" t="inlineStr">
         <s:is>
           <s:t>შემოსავალი ამონაწერში / Inflows in the statement (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B72" s="38">
+      <s:c r="B92" s="38">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C72" s="42" t="inlineStr">
+      <s:c r="C92" s="42" t="inlineStr">
         <s:is>
           <s:t>ამონაწერში შემოსავალი არ ფიქსირდება — 140,000 USD სესხი ამ ანგარიშზე ამ პერიოდში არ ჩანს. / The statement shows no inflows; the USD 140,000 loan is not visible in this account for this period.</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="74">
-      <s:c r="A74" s="2" t="inlineStr">
+    <s:row r="94">
+      <s:c r="A94" s="2" t="inlineStr">
         <s:is>
           <s:t>შენიშვნა: ამონაწერი მხოლოდ ერთ ანგარიშს ფარავს და მასში შემოსავალი არ არის. თუ სესხი სხვა ანგარიშზეა ჩარიცხული, დაამატეთ ის ამონაწერიც. / Note: the statement covers one account and contains no inflows. If the loan was disbursed into another account, add that statement too.</s:t>
         </s:is>

--- a/finance/Greenhouse_CashFlow_2000m2.xlsx
+++ b/finance/Greenhouse_CashFlow_2000m2.xlsx
@@ -1234,11 +1234,11 @@
       </s:c>
       <s:c r="B7" s="18">
         <s:f>B23</s:f>
-        <s:v>220061.63999999998</s:v>
+        <s:v>220261.63999999998</s:v>
       </s:c>
       <s:c r="C7" s="19">
         <s:f>IFERROR(B7/$B$6,0)</s:f>
-        <s:v>0.35209862399999997</s:v>
+        <s:v>0.35241862399999996</s:v>
       </s:c>
       <s:c r="D7" s="20" t="str">
         <s:f>REPT("|",ROUND(C7*40,0))</s:f>
@@ -1272,11 +1272,11 @@
       </s:c>
       <s:c r="B9" s="22">
         <s:f>B7+B8</s:f>
-        <s:v>370188.83999999997</s:v>
+        <s:v>370388.83999999997</s:v>
       </s:c>
       <s:c r="C9" s="23">
         <s:f>IFERROR(B9/$B$6,0)</s:f>
-        <s:v>0.5923021439999999</s:v>
+        <s:v>0.5926221439999999</s:v>
       </s:c>
       <s:c r="D9" s="24" t="str">
         <s:f>REPT("|",ROUND(C9*40,0))</s:f>
@@ -1291,11 +1291,11 @@
       </s:c>
       <s:c r="B10" s="22">
         <s:f>B6-B9</s:f>
-        <s:v>254811.16000000003</s:v>
+        <s:v>254611.16000000003</s:v>
       </s:c>
       <s:c r="C10" s="23">
         <s:f>IFERROR(B10/$B$6,0)</s:f>
-        <s:v>0.407697856</s:v>
+        <s:v>0.40737785600000004</s:v>
       </s:c>
       <s:c r="D10" s="24" t="str">
         <s:f>REPT("|",ROUND(C10*40,0))</s:f>
@@ -1353,12 +1353,12 @@
         </s:is>
       </s:c>
       <s:c r="B14" s="25">
-        <s:f>Actuals!B67</s:f>
+        <s:f>Actuals!B68</s:f>
         <s:v>178544.8</s:v>
       </s:c>
       <s:c r="C14" s="26">
         <s:f>IFERROR(B14/$B$23,0)</s:f>
-        <s:v>0.8113399500249112</s:v>
+        <s:v>0.8106032443960737</s:v>
       </s:c>
       <s:c r="D14" s="27" t="inlineStr">
         <s:is>
@@ -1383,12 +1383,12 @@
         </s:is>
       </s:c>
       <s:c r="B15" s="25">
-        <s:f>Actuals!B68</s:f>
+        <s:f>Actuals!B69</s:f>
         <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C15" s="26">
         <s:f>IFERROR(B15/$B$23,0)</s:f>
-        <s:v>0.045441813484621854</s:v>
+        <s:v>0.045400551816467</s:v>
       </s:c>
       <s:c r="D15" s="27" t="inlineStr">
         <s:is>
@@ -1408,12 +1408,12 @@
         </s:is>
       </s:c>
       <s:c r="B16" s="25">
-        <s:f>Actuals!B69</s:f>
+        <s:f>Actuals!B70</s:f>
         <s:v>1470.0</s:v>
       </s:c>
       <s:c r="C16" s="26">
         <s:f>IFERROR(B16/$B$23,0)</s:f>
-        <s:v>0.006679946582239413</s:v>
+        <s:v>0.006673881117020649</s:v>
       </s:c>
       <s:c r="D16" s="27" t="inlineStr">
         <s:is>
@@ -1433,12 +1433,12 @@
         </s:is>
       </s:c>
       <s:c r="B17" s="25">
-        <s:f>Actuals!B70</s:f>
+        <s:f>Actuals!B71</s:f>
         <s:v>3070.0</s:v>
       </s:c>
       <s:c r="C17" s="26">
         <s:f>IFERROR(B17/$B$23,0)</s:f>
-        <s:v>0.01395063673977891</s:v>
+        <s:v>0.01393796940765537</s:v>
       </s:c>
       <s:c r="D17" s="27" t="inlineStr">
         <s:is>
@@ -1458,12 +1458,12 @@
         </s:is>
       </s:c>
       <s:c r="B18" s="25">
-        <s:f>Actuals!B71</s:f>
-        <s:v>2819.65</s:v>
+        <s:f>Actuals!B72</s:f>
+        <s:v>3019.65</s:v>
       </s:c>
       <s:c r="C18" s="26">
         <s:f>IFERROR(B18/$B$23,0)</s:f>
-        <s:v>0.012813000939191403</s:v>
+        <s:v>0.013709377629259459</s:v>
       </s:c>
       <s:c r="D18" s="27" t="inlineStr">
         <s:is>
@@ -1483,12 +1483,12 @@
         </s:is>
       </s:c>
       <s:c r="B19" s="25">
-        <s:f>Actuals!B72</s:f>
+        <s:f>Actuals!B73</s:f>
         <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C19" s="26">
         <s:f>IFERROR(B19/$B$23,0)</s:f>
-        <s:v>0.045441813484621854</s:v>
+        <s:v>0.045400551816467</s:v>
       </s:c>
       <s:c r="D19" s="27" t="inlineStr">
         <s:is>
@@ -1508,12 +1508,12 @@
         </s:is>
       </s:c>
       <s:c r="B20" s="25">
-        <s:f>Actuals!B73</s:f>
+        <s:f>Actuals!B74</s:f>
         <s:v>5722.7</s:v>
       </s:c>
       <s:c r="C20" s="26">
         <s:f>IFERROR(B20/$B$23,0)</s:f>
-        <s:v>0.02600498660284455</s:v>
+        <s:v>0.02598137378800957</s:v>
       </s:c>
       <s:c r="D20" s="27" t="inlineStr">
         <s:is>
@@ -1533,12 +1533,12 @@
         </s:is>
       </s:c>
       <s:c r="B21" s="25">
-        <s:f>Actuals!B74</s:f>
+        <s:f>Actuals!B75</s:f>
         <s:v>7505.41</s:v>
       </s:c>
       <s:c r="C21" s="26">
         <s:f>IFERROR(B21/$B$23,0)</s:f>
-        <s:v>0.03410594413456157</s:v>
+        <s:v>0.03407497556088296</s:v>
       </s:c>
       <s:c r="D21" s="27" t="inlineStr">
         <s:is>
@@ -1558,12 +1558,12 @@
         </s:is>
       </s:c>
       <s:c r="B22" s="25">
-        <s:f>Actuals!B75</s:f>
+        <s:f>Actuals!B76</s:f>
         <s:v>929.08</s:v>
       </s:c>
       <s:c r="C22" s="26">
         <s:f>IFERROR(B22/$B$23,0)</s:f>
-        <s:v>0.0042219080072292475</s:v>
+        <s:v>0.004218074468164316</s:v>
       </s:c>
       <s:c r="D22" s="27" t="inlineStr">
         <s:is>
@@ -1584,7 +1584,7 @@
       </s:c>
       <s:c r="B23" s="30">
         <s:f>SUM(B14:B22)</s:f>
-        <s:v>220061.63999999998</s:v>
+        <s:v>220261.63999999998</s:v>
       </s:c>
       <s:c r="C23" s="23">
         <s:f>IFERROR(B23/B23,0)</s:f>
@@ -1641,7 +1641,7 @@
         </s:is>
       </s:c>
       <s:c r="B27" s="25">
-        <s:f>Actuals!B81</s:f>
+        <s:f>Actuals!B82</s:f>
         <s:v>69796.68000000001</s:v>
       </s:c>
       <s:c r="C27" s="31">
@@ -1660,7 +1660,7 @@
         </s:is>
       </s:c>
       <s:c r="B28" s="25">
-        <s:f>Actuals!B82</s:f>
+        <s:f>Actuals!B83</s:f>
         <s:v>22040.5</s:v>
       </s:c>
       <s:c r="C28" s="31">
@@ -1679,16 +1679,16 @@
         </s:is>
       </s:c>
       <s:c r="B29" s="25">
-        <s:f>Actuals!B83</s:f>
-        <s:v>128224.45999999999</s:v>
+        <s:f>Actuals!B84</s:f>
+        <s:v>128424.45999999999</s:v>
       </s:c>
       <s:c r="C29" s="31">
         <s:f>SUM($B$27:B29)</s:f>
-        <s:v>220061.64</s:v>
+        <s:v>220261.64</s:v>
       </s:c>
       <s:c r="D29" s="18">
         <s:f>$B$6-C29</s:f>
-        <s:v>404938.36</s:v>
+        <s:v>404738.36</s:v>
       </s:c>
     </s:row>
     <s:row r="30">
@@ -1699,7 +1699,7 @@
       </s:c>
       <s:c r="B30" s="30">
         <s:f>SUM(B27:B29)</s:f>
-        <s:v>220061.64</s:v>
+        <s:v>220261.64</s:v>
       </s:c>
       <s:c r="C30" s="30">
         <s:f>B30-B23</s:f>
@@ -1707,7 +1707,7 @@
       </s:c>
       <s:c r="D30" s="22">
         <s:f>$B$6-B30</s:f>
-        <s:v>404938.36</s:v>
+        <s:v>404738.36</s:v>
       </s:c>
       <s:c r="G30" s="2" t="inlineStr">
         <s:is>
@@ -1787,7 +1787,7 @@
         <s:v>2.6218359168443968</s:v>
       </s:c>
       <s:c r="D35" s="25">
-        <s:f>Actuals!B67</s:f>
+        <s:f>Actuals!B68</s:f>
         <s:v>178544.8</s:v>
       </s:c>
       <s:c r="G35" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </s:c>
       <s:c r="C40" s="19">
         <s:f>IFERROR(B40/$B$23,0)</s:f>
-        <s:v>0.8756727887695466</s:v>
+        <s:v>0.8748776682131305</s:v>
       </s:c>
       <s:c r="G40" s="2" t="inlineStr">
         <s:is>
@@ -1866,11 +1866,11 @@
       </s:c>
       <s:c r="B41" s="38">
         <s:f>SUMIF($D$14:$D$22,"OPEX",$B$14:$B$22)</s:f>
-        <s:v>27359.65</s:v>
+        <s:v>27559.65</s:v>
       </s:c>
       <s:c r="C41" s="19">
         <s:f>IFERROR(B41/$B$23,0)</s:f>
-        <s:v>0.12432721123045344</s:v>
+        <s:v>0.1251223317868695</s:v>
       </s:c>
       <s:c r="G41" s="2" t="inlineStr">
         <s:is>
@@ -13443,7 +13443,7 @@
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
     <s:pageSetUpPr/>
   </s:sheetPr>
-  <s:dimension ref="A1:E94"/>
+  <s:dimension ref="A1:E95"/>
   <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <s:cols>
     <s:col width="13" customWidth="1" min="1" max="1"/>
@@ -13524,7 +13524,7 @@
       </s:c>
       <s:c r="B8" s="20" t="inlineStr">
         <s:is>
-          <s:t>01/07/2026 – 21/09/2026 · 30 საბანკო + 20 საწვავი / 30 bank + 20 fuel-card</s:t>
+          <s:t>01/07/2026 – 22/09/2026 · 30 საბანკო + 21 საწვავი / 30 bank + 21 fuel</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -14649,384 +14649,403 @@
       </s:c>
     </s:row>
     <s:row r="63">
-      <s:c r="A63" s="21" t="inlineStr">
+      <s:c r="A63" s="71" t="n">
+        <s:v>46287</s:v>
+      </s:c>
+      <s:c r="B63" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C63" s="63" t="inlineStr"/>
+      <s:c r="D63" s="63" t="inlineStr">
+        <s:is>
+          <s:t>საწვავი / Fuel</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E63" s="72" t="n">
+        <s:v>-200</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="64">
+      <s:c r="A64" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B63" s="24" t="inlineStr"/>
-      <s:c r="C63" s="24" t="inlineStr"/>
-      <s:c r="D63" s="24" t="inlineStr"/>
-      <s:c r="E63" s="30">
-        <s:f>SUM(E13:E62)</s:f>
-        <s:v>-220061.63999999998</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="65">
-      <s:c r="A65" s="10" t="inlineStr">
+      <s:c r="B64" s="24" t="inlineStr"/>
+      <s:c r="C64" s="24" t="inlineStr"/>
+      <s:c r="D64" s="24" t="inlineStr"/>
+      <s:c r="E64" s="30">
+        <s:f>SUM(E13:E63)</s:f>
+        <s:v>-220261.63999999998</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="66">
+      <s:c r="A66" s="10" t="inlineStr">
         <s:is>
           <s:t>კატეგორიების მიხედვით / BY CATEGORY</s:t>
         </s:is>
       </s:c>
-      <s:c r="B65" s="11" t="n"/>
-      <s:c r="C65" s="11" t="n"/>
-      <s:c r="D65" s="11" t="n"/>
-      <s:c r="E65" s="11" t="n"/>
-    </s:row>
-    <s:row r="66">
-      <s:c r="A66" s="59" t="inlineStr">
+      <s:c r="B66" s="11" t="n"/>
+      <s:c r="C66" s="11" t="n"/>
+      <s:c r="D66" s="11" t="n"/>
+      <s:c r="E66" s="11" t="n"/>
+    </s:row>
+    <s:row r="67">
+      <s:c r="A67" s="59" t="inlineStr">
         <s:is>
           <s:t>კატეგორია / Category</s:t>
         </s:is>
       </s:c>
-      <s:c r="B66" s="12" t="inlineStr">
+      <s:c r="B67" s="12" t="inlineStr">
         <s:is>
           <s:t>თანხა GEL / Amount</s:t>
         </s:is>
       </s:c>
-      <s:c r="C66" s="12" t="inlineStr">
+      <s:c r="C67" s="12" t="inlineStr">
         <s:is>
           <s:t>% ჯამიდან / of total</s:t>
         </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="67">
-      <s:c r="A67" s="20" t="inlineStr">
-        <s:is>
-          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B67" s="31">
-        <s:f>-SUMIF($D$13:$D$62,$A67,$E$13:$E$62)</s:f>
-        <s:v>178544.8</s:v>
-      </s:c>
-      <s:c r="C67" s="26">
-        <s:f>IFERROR($B67/$B$76,0)</s:f>
-        <s:v>0.8113399500249112</s:v>
       </s:c>
     </s:row>
     <s:row r="68">
       <s:c r="A68" s="20" t="inlineStr">
         <s:is>
-          <s:t>ხელფასი / Salaries</s:t>
+          <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
       <s:c r="B68" s="31">
-        <s:f>-SUMIF($D$13:$D$62,$A68,$E$13:$E$62)</s:f>
-        <s:v>10000.0</s:v>
+        <s:f>-SUMIF($D$13:$D$63,$A68,$E$13:$E$63)</s:f>
+        <s:v>178544.8</s:v>
       </s:c>
       <s:c r="C68" s="26">
-        <s:f>IFERROR($B68/$B$76,0)</s:f>
-        <s:v>0.045441813484621854</s:v>
+        <s:f>IFERROR($B68/$B$77,0)</s:f>
+        <s:v>0.8106032443960737</s:v>
       </s:c>
     </s:row>
     <s:row r="69">
       <s:c r="A69" s="20" t="inlineStr">
         <s:is>
-          <s:t>გადასახადები / Taxes &amp; pension</s:t>
+          <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
       <s:c r="B69" s="31">
-        <s:f>-SUMIF($D$13:$D$62,$A69,$E$13:$E$62)</s:f>
-        <s:v>1470.0</s:v>
+        <s:f>-SUMIF($D$13:$D$63,$A69,$E$13:$E$63)</s:f>
+        <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C69" s="26">
-        <s:f>IFERROR($B69/$B$76,0)</s:f>
-        <s:v>0.006679946582239413</s:v>
+        <s:f>IFERROR($B69/$B$77,0)</s:f>
+        <s:v>0.045400551816467</s:v>
       </s:c>
     </s:row>
     <s:row r="70">
       <s:c r="A70" s="20" t="inlineStr">
         <s:is>
-          <s:t>მომსახურება / Services</s:t>
+          <s:t>გადასახადები / Taxes &amp; pension</s:t>
         </s:is>
       </s:c>
       <s:c r="B70" s="31">
-        <s:f>-SUMIF($D$13:$D$62,$A70,$E$13:$E$62)</s:f>
-        <s:v>3070.0</s:v>
+        <s:f>-SUMIF($D$13:$D$63,$A70,$E$13:$E$63)</s:f>
+        <s:v>1470.0</s:v>
       </s:c>
       <s:c r="C70" s="26">
-        <s:f>IFERROR($B70/$B$76,0)</s:f>
-        <s:v>0.01395063673977891</s:v>
+        <s:f>IFERROR($B70/$B$77,0)</s:f>
+        <s:v>0.006673881117020649</s:v>
       </s:c>
     </s:row>
     <s:row r="71">
       <s:c r="A71" s="20" t="inlineStr">
         <s:is>
-          <s:t>საწვავი / Fuel</s:t>
+          <s:t>მომსახურება / Services</s:t>
         </s:is>
       </s:c>
       <s:c r="B71" s="31">
-        <s:f>-SUMIF($D$13:$D$62,$A71,$E$13:$E$62)</s:f>
-        <s:v>2819.65</s:v>
+        <s:f>-SUMIF($D$13:$D$63,$A71,$E$13:$E$63)</s:f>
+        <s:v>3070.0</s:v>
       </s:c>
       <s:c r="C71" s="26">
-        <s:f>IFERROR($B71/$B$76,0)</s:f>
-        <s:v>0.012813000939191403</s:v>
+        <s:f>IFERROR($B71/$B$77,0)</s:f>
+        <s:v>0.01393796940765537</s:v>
       </s:c>
     </s:row>
     <s:row r="72">
       <s:c r="A72" s="20" t="inlineStr">
         <s:is>
-          <s:t>მუშების კვება / Worker meals</s:t>
+          <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
       <s:c r="B72" s="31">
-        <s:f>-SUMIF($D$13:$D$62,$A72,$E$13:$E$62)</s:f>
-        <s:v>10000.0</s:v>
+        <s:f>-SUMIF($D$13:$D$63,$A72,$E$13:$E$63)</s:f>
+        <s:v>3019.65</s:v>
       </s:c>
       <s:c r="C72" s="26">
-        <s:f>IFERROR($B72/$B$76,0)</s:f>
-        <s:v>0.045441813484621854</s:v>
+        <s:f>IFERROR($B72/$B$77,0)</s:f>
+        <s:v>0.013709377629259459</s:v>
       </s:c>
     </s:row>
     <s:row r="73">
       <s:c r="A73" s="20" t="inlineStr">
         <s:is>
-          <s:t>მასალები / Materials</s:t>
+          <s:t>მუშების კვება / Worker meals</s:t>
         </s:is>
       </s:c>
       <s:c r="B73" s="31">
-        <s:f>-SUMIF($D$13:$D$62,$A73,$E$13:$E$62)</s:f>
-        <s:v>5722.7</s:v>
+        <s:f>-SUMIF($D$13:$D$63,$A73,$E$13:$E$63)</s:f>
+        <s:v>10000.0</s:v>
       </s:c>
       <s:c r="C73" s="26">
-        <s:f>IFERROR($B73/$B$76,0)</s:f>
-        <s:v>0.02600498660284455</s:v>
+        <s:f>IFERROR($B73/$B$77,0)</s:f>
+        <s:v>0.045400551816467</s:v>
       </s:c>
     </s:row>
     <s:row r="74">
       <s:c r="A74" s="20" t="inlineStr">
         <s:is>
-          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+          <s:t>მასალები / Materials</s:t>
         </s:is>
       </s:c>
       <s:c r="B74" s="31">
-        <s:f>-SUMIF($D$13:$D$62,$A74,$E$13:$E$62)</s:f>
-        <s:v>7505.41</s:v>
+        <s:f>-SUMIF($D$13:$D$63,$A74,$E$13:$E$63)</s:f>
+        <s:v>5722.7</s:v>
       </s:c>
       <s:c r="C74" s="26">
-        <s:f>IFERROR($B74/$B$76,0)</s:f>
-        <s:v>0.03410594413456157</s:v>
+        <s:f>IFERROR($B74/$B$77,0)</s:f>
+        <s:v>0.02598137378800957</s:v>
       </s:c>
     </s:row>
     <s:row r="75">
       <s:c r="A75" s="20" t="inlineStr">
         <s:is>
+          <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B75" s="31">
+        <s:f>-SUMIF($D$13:$D$63,$A75,$E$13:$E$63)</s:f>
+        <s:v>7505.41</s:v>
+      </s:c>
+      <s:c r="C75" s="26">
+        <s:f>IFERROR($B75/$B$77,0)</s:f>
+        <s:v>0.03407497556088296</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="76">
+      <s:c r="A76" s="20" t="inlineStr">
+        <s:is>
           <s:t>სხვა / Other</s:t>
         </s:is>
       </s:c>
-      <s:c r="B75" s="31">
-        <s:f>-SUMIF($D$13:$D$62,$A75,$E$13:$E$62)</s:f>
+      <s:c r="B76" s="31">
+        <s:f>-SUMIF($D$13:$D$63,$A76,$E$13:$E$63)</s:f>
         <s:v>929.08</s:v>
       </s:c>
-      <s:c r="C75" s="26">
-        <s:f>IFERROR($B75/$B$76,0)</s:f>
-        <s:v>0.0042219080072292475</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="76">
-      <s:c r="A76" s="21" t="inlineStr">
+      <s:c r="C76" s="26">
+        <s:f>IFERROR($B76/$B$77,0)</s:f>
+        <s:v>0.004218074468164316</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="77">
+      <s:c r="A77" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B76" s="30">
-        <s:f>SUM(B67:B75)</s:f>
-        <s:v>220061.63999999998</s:v>
-      </s:c>
-      <s:c r="C76" s="23">
-        <s:f>IFERROR(B76/B76,0)</s:f>
+      <s:c r="B77" s="30">
+        <s:f>SUM(B68:B76)</s:f>
+        <s:v>220261.63999999998</s:v>
+      </s:c>
+      <s:c r="C77" s="23">
+        <s:f>IFERROR(B77/B77,0)</s:f>
         <s:v>1.0</s:v>
       </s:c>
     </s:row>
-    <s:row r="77">
-      <s:c r="A77" s="3" t="inlineStr">
+    <s:row r="78">
+      <s:c r="A78" s="3" t="inlineStr">
         <s:is>
           <s:t>შემოწმება / Check vs statement total (must be 0)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B77" s="73">
-        <s:f>B76+E63</s:f>
-        <s:v>0.0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="79">
-      <s:c r="A79" s="10" t="inlineStr">
+      <s:c r="B78" s="73">
+        <s:f>B77+E64</s:f>
+        <s:v>0.0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="80">
+      <s:c r="A80" s="10" t="inlineStr">
         <s:is>
           <s:t>თვეების მიხედვით / BY MONTH</s:t>
         </s:is>
       </s:c>
-      <s:c r="B79" s="11" t="n"/>
-      <s:c r="C79" s="11" t="n"/>
-      <s:c r="D79" s="11" t="n"/>
-      <s:c r="E79" s="11" t="n"/>
-    </s:row>
-    <s:row r="80">
-      <s:c r="A80" s="59" t="inlineStr">
+      <s:c r="B80" s="11" t="n"/>
+      <s:c r="C80" s="11" t="n"/>
+      <s:c r="D80" s="11" t="n"/>
+      <s:c r="E80" s="11" t="n"/>
+    </s:row>
+    <s:row r="81">
+      <s:c r="A81" s="59" t="inlineStr">
         <s:is>
           <s:t>თვე / Month</s:t>
         </s:is>
       </s:c>
-      <s:c r="B80" s="12" t="inlineStr">
+      <s:c r="B81" s="12" t="inlineStr">
         <s:is>
           <s:t>თანხა GEL / Amount</s:t>
         </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="81">
-      <s:c r="A81" s="20" t="inlineStr">
-        <s:is>
-          <s:t>ივლისი 2026 / July</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B81" s="31">
-        <s:f>-SUMPRODUCT(($A$13:$A$62&gt;=DATE(2026,7,1))*($A$13:$A$62&lt;=DATE(2026,7,31))*$E$13:$E$62)</s:f>
-        <s:v>69796.68000000001</s:v>
       </s:c>
     </s:row>
     <s:row r="82">
       <s:c r="A82" s="20" t="inlineStr">
         <s:is>
-          <s:t>აგვისტო 2026 / August</s:t>
+          <s:t>ივლისი 2026 / July</s:t>
         </s:is>
       </s:c>
       <s:c r="B82" s="31">
-        <s:f>-SUMPRODUCT(($A$13:$A$62&gt;=DATE(2026,8,1))*($A$13:$A$62&lt;=DATE(2026,8,31))*$E$13:$E$62)</s:f>
-        <s:v>22040.5</s:v>
+        <s:f>-SUMPRODUCT(($A$13:$A$63&gt;=DATE(2026,7,1))*($A$13:$A$63&lt;=DATE(2026,7,31))*$E$13:$E$63)</s:f>
+        <s:v>69796.68000000001</s:v>
       </s:c>
     </s:row>
     <s:row r="83">
       <s:c r="A83" s="20" t="inlineStr">
         <s:is>
+          <s:t>აგვისტო 2026 / August</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B83" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$63&gt;=DATE(2026,8,1))*($A$13:$A$63&lt;=DATE(2026,8,31))*$E$13:$E$63)</s:f>
+        <s:v>22040.5</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="84">
+      <s:c r="A84" s="20" t="inlineStr">
+        <s:is>
           <s:t>სექტემბერი 2026 (21-მდე) / September (to the 21st)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B83" s="31">
-        <s:f>-SUMPRODUCT(($A$13:$A$62&gt;=DATE(2026,9,1))*($A$13:$A$62&lt;=DATE(2026,9,30))*$E$13:$E$62)</s:f>
-        <s:v>128224.45999999999</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="84">
-      <s:c r="A84" s="21" t="inlineStr">
+      <s:c r="B84" s="31">
+        <s:f>-SUMPRODUCT(($A$13:$A$63&gt;=DATE(2026,9,1))*($A$13:$A$63&lt;=DATE(2026,9,30))*$E$13:$E$63)</s:f>
+        <s:v>128424.45999999999</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="85">
+      <s:c r="A85" s="21" t="inlineStr">
         <s:is>
           <s:t>სულ / TOTAL</s:t>
         </s:is>
       </s:c>
-      <s:c r="B84" s="30">
-        <s:f>SUM(B81:B83)</s:f>
-        <s:v>220061.64</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="86">
-      <s:c r="A86" s="10" t="inlineStr">
+      <s:c r="B85" s="30">
+        <s:f>SUM(B82:B84)</s:f>
+        <s:v>220261.64</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="87">
+      <s:c r="A87" s="10" t="inlineStr">
         <s:is>
           <s:t>ძირითადი ფაქტები / KEY FACTS</s:t>
         </s:is>
       </s:c>
-      <s:c r="B86" s="11" t="n"/>
-      <s:c r="C86" s="11" t="n"/>
-      <s:c r="D86" s="11" t="n"/>
-      <s:c r="E86" s="11" t="n"/>
-    </s:row>
-    <s:row r="87">
-      <s:c r="A87" s="17" t="inlineStr">
+      <s:c r="B87" s="11" t="n"/>
+      <s:c r="C87" s="11" t="n"/>
+      <s:c r="D87" s="11" t="n"/>
+      <s:c r="E87" s="11" t="n"/>
+    </s:row>
+    <s:row r="88">
+      <s:c r="A88" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 09/07/2026 (22,000 USD) / FX rate on the 09/07/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B87" s="74">
+      <s:c r="B88" s="74">
         <s:f>-E17/22000</s:f>
         <s:v>2.6384000000000003</s:v>
       </s:c>
-      <s:c r="C87" s="42" t="inlineStr">
+      <s:c r="C88" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში მითითებული კურსი 2.6384 / the description states 2.6384</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="88">
-      <s:c r="A88" s="17" t="inlineStr">
+    <s:row r="89">
+      <s:c r="A89" s="17" t="inlineStr">
         <s:is>
           <s:t>გაცვლითი კურსი 04/08/2026 (5,000 USD) / FX rate on the 04/08/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B88" s="74">
+      <s:c r="B89" s="74">
         <s:f>-E20/5000</s:f>
         <s:v>2.62</s:v>
       </s:c>
-      <s:c r="C88" s="42" t="inlineStr">
+      <s:c r="C89" s="42" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში კურსი არ არის მითითებული / no rate stated in the description</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="89">
-      <s:c r="A89" s="17" t="inlineStr">
+    <s:row r="90">
+      <s:c r="A90" s="17" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსები / Construction advances paid (USD)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B89" s="75">
+      <s:c r="B90" s="75">
         <s:f>22000+5000</s:f>
         <s:v>27000.0</s:v>
       </s:c>
-      <s:c r="C89" s="42" t="inlineStr">
+      <s:c r="C90" s="42" t="inlineStr">
         <s:is>
           <s:t>ხელშეკრულება N1, 7/6/2026, შპს ჯიესენ გრუპ / contract N1 of 7/6/2026 with LLC GSN Group</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="90">
-      <s:c r="A90" s="17" t="inlineStr">
-        <s:is>
-          <s:t>მშენებლობის ავანსები / Construction advances paid (GEL)</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B90" s="76">
-        <s:f>B67</s:f>
-        <s:v>178544.8</s:v>
-      </s:c>
-      <s:c r="C90" s="42" t="inlineStr">
-        <s:is>
-          <s:t>ორივე გადარიცხვის ჯამი / the two transfers above</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="91">
       <s:c r="A91" s="17" t="inlineStr">
         <s:is>
-          <s:t>სულ გადახდილი / Total paid out (GEL)</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B91" s="38">
-        <s:f>-E63</s:f>
-        <s:v>220061.63999999998</s:v>
+          <s:t>მშენებლობის ავანსები / Construction advances paid (GEL)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B91" s="76">
+        <s:f>B68</s:f>
+        <s:v>178544.8</s:v>
       </s:c>
       <s:c r="C91" s="42" t="inlineStr">
         <s:is>
-          <s:t>01/07–08/09/2026</s:t>
+          <s:t>ორივე გადარიცხვის ჯამი / the two transfers above</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="92">
       <s:c r="A92" s="17" t="inlineStr">
         <s:is>
+          <s:t>სულ გადახდილი / Total paid out (GEL)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B92" s="38">
+        <s:f>-E64</s:f>
+        <s:v>220261.63999999998</s:v>
+      </s:c>
+      <s:c r="C92" s="42" t="inlineStr">
+        <s:is>
+          <s:t>01/07–08/09/2026</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="93">
+      <s:c r="A93" s="17" t="inlineStr">
+        <s:is>
           <s:t>შემოსავალი ამონაწერში / Inflows in the statement (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B92" s="38">
+      <s:c r="B93" s="38">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C92" s="42" t="inlineStr">
+      <s:c r="C93" s="42" t="inlineStr">
         <s:is>
           <s:t>ამონაწერში შემოსავალი არ ფიქსირდება — 140,000 USD სესხი ამ ანგარიშზე ამ პერიოდში არ ჩანს. / The statement shows no inflows; the USD 140,000 loan is not visible in this account for this period.</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="94">
-      <s:c r="A94" s="2" t="inlineStr">
+    <s:row r="95">
+      <s:c r="A95" s="2" t="inlineStr">
         <s:is>
           <s:t>შენიშვნა: ამონაწერი მხოლოდ ერთ ანგარიშს ფარავს და მასში შემოსავალი არ არის. თუ სესხი სხვა ანგარიშზეა ჩარიცხული, დაამატეთ ის ამონაწერიც. / Note: the statement covers one account and contains no inflows. If the loan was disbursed into another account, add that statement too.</s:t>
         </s:is>

--- a/finance/Greenhouse_CashFlow_2000m2.xlsx
+++ b/finance/Greenhouse_CashFlow_2000m2.xlsx
@@ -221,6 +221,9 @@
     <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -334,9 +337,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1147,7 +1147,7 @@
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
     <s:pageSetUpPr/>
   </s:sheetPr>
-  <s:dimension ref="A1:G49"/>
+  <s:dimension ref="A1:G51"/>
   <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <s:cols>
     <s:col width="50" customWidth="1" min="1" max="1"/>
@@ -1248,20 +1248,20 @@
     <s:row r="8">
       <s:c r="A8" s="17" t="inlineStr">
         <s:is>
-          <s:t>ვალდებულება — ხელშ. N1-ის ნაშთი / COMMITTED — contract N1 outstanding</s:t>
+          <s:t>ვალდებულება — ხელშეკრულებების ნაშთი / COMMITTED — contracts outstanding</s:t>
         </s:is>
       </s:c>
       <s:c r="B8" s="18">
-        <s:f>D36</s:f>
-        <s:v>150127.19999999998</s:v>
+        <s:f>D38</s:f>
+        <s:v>176511.19999999998</s:v>
       </s:c>
       <s:c r="C8" s="19">
         <s:f>IFERROR(B8/$B$6,0)</s:f>
-        <s:v>0.24020351999999998</s:v>
+        <s:v>0.28241792</s:v>
       </s:c>
       <s:c r="D8" s="20" t="str">
         <s:f>REPT("|",ROUND(C8*40,0))</s:f>
-        <s:v>||||||||||</s:v>
+        <s:v>|||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="9">
@@ -1272,15 +1272,15 @@
       </s:c>
       <s:c r="B9" s="22">
         <s:f>B7+B8</s:f>
-        <s:v>370388.83999999997</s:v>
+        <s:v>396772.83999999997</s:v>
       </s:c>
       <s:c r="C9" s="23">
         <s:f>IFERROR(B9/$B$6,0)</s:f>
-        <s:v>0.5926221439999999</s:v>
+        <s:v>0.634836544</s:v>
       </s:c>
       <s:c r="D9" s="24" t="str">
         <s:f>REPT("|",ROUND(C9*40,0))</s:f>
-        <s:v>||||||||||||||||||||||||</s:v>
+        <s:v>|||||||||||||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="10">
@@ -1291,15 +1291,15 @@
       </s:c>
       <s:c r="B10" s="22">
         <s:f>B6-B9</s:f>
-        <s:v>254611.16000000003</s:v>
+        <s:v>228227.16000000003</s:v>
       </s:c>
       <s:c r="C10" s="23">
         <s:f>IFERROR(B10/$B$6,0)</s:f>
-        <s:v>0.40737785600000004</s:v>
+        <s:v>0.36516345600000005</s:v>
       </s:c>
       <s:c r="D10" s="24" t="str">
         <s:f>REPT("|",ROUND(C10*40,0))</s:f>
-        <s:v>||||||||||||||||</s:v>
+        <s:v>|||||||||||||||</s:v>
       </s:c>
     </s:row>
     <s:row r="12">
@@ -1718,7 +1718,7 @@
     <s:row r="32">
       <s:c r="A32" s="10" t="inlineStr">
         <s:is>
-          <s:t>4. ხელშეკრულება N1 — შპს ჯიესენ გრუპი / CONTRACT N1 — LLC GSN GROUP</s:t>
+          <s:t>4. ხელშეკრულებები — შპს ჯიესენ გრუპი / CONTRACTS — LLC GSN GROUP</s:t>
         </s:is>
       </s:c>
       <s:c r="B32" s="11" t="n"/>
@@ -1750,9 +1750,9 @@
       </s:c>
     </s:row>
     <s:row r="34">
-      <s:c r="A34" s="17" t="inlineStr">
-        <s:is>
-          <s:t>ჯამური ღირებულება / Total contract value</s:t>
+      <s:c r="A34" s="20" t="inlineStr">
+        <s:is>
+          <s:t>N1 — სათბური / the greenhouse</s:t>
         </s:is>
       </s:c>
       <s:c r="B34" s="32" t="n">
@@ -1762,170 +1762,212 @@
         <s:f>Assumptions!$B$28</s:f>
         <s:v>2.6384</s:v>
       </s:c>
-      <s:c r="D34" s="18">
+      <s:c r="D34" s="29">
         <s:f>B34*Assumptions!$B$28</s:f>
         <s:v>329800.0</s:v>
       </s:c>
       <s:c r="G34" s="2" t="inlineStr">
         <s:is>
-          <s:t>მფლობელის მონაცემი / given by the owner</s:t>
+          <s:t>ხელშეკრულება N1, 7/6/2026 / contract N1 of 7 June 2026</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="35">
       <s:c r="A35" s="20" t="inlineStr">
         <s:is>
+          <s:t>ტექნიკური ოთახი 200 მ² — პერიმეტრის ბეტონი და ბლოკი / technical room 200 m2 — perimeter concrete and blockwork</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B35" s="32" t="n">
+        <s:v>10000</s:v>
+      </s:c>
+      <s:c r="C35" s="33">
+        <s:f>Assumptions!$B$28</s:f>
+        <s:v>2.6384</s:v>
+      </s:c>
+      <s:c r="D35" s="29">
+        <s:f>B35*Assumptions!$B$28</s:f>
+        <s:v>26384.0</s:v>
+      </s:c>
+      <s:c r="G35" s="2" t="inlineStr">
+        <s:is>
+          <s:t>მფლობელის მონაცემი 22/09/2026 — ხელშეკრულების ნომერი დასადასტურებელია / owner-reported 22 Sep 2026; the contract reference still needs confirming</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="36">
+      <s:c r="A36" s="17" t="inlineStr">
+        <s:is>
+          <s:t>ჯამი / Total contracted</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B36" s="34">
+        <s:f>B34+B35</s:f>
+        <s:v>135000.0</s:v>
+      </s:c>
+      <s:c r="C36" s="33">
+        <s:f>Assumptions!$B$28</s:f>
+        <s:v>2.6384</s:v>
+      </s:c>
+      <s:c r="D36" s="18">
+        <s:f>B36*Assumptions!$B$28</s:f>
+        <s:v>356184.0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="37">
+      <s:c r="A37" s="20" t="inlineStr">
+        <s:is>
           <s:t>გადახდილი ავანსი / Advances paid</s:t>
         </s:is>
       </s:c>
-      <s:c r="B35" s="34">
+      <s:c r="B37" s="35">
         <s:f>22000+5000+40000+2900/Assumptions!$B$28</s:f>
         <s:v>68099.15100060643</s:v>
       </s:c>
-      <s:c r="C35" s="35">
-        <s:f>IFERROR(D35/B35,0)</s:f>
+      <s:c r="C37" s="36">
+        <s:f>IFERROR(D37/B37,0)</s:f>
         <s:v>2.6218359168443968</s:v>
       </s:c>
-      <s:c r="D35" s="25">
+      <s:c r="D37" s="25">
         <s:f>Actuals!B68</s:f>
         <s:v>178544.8</s:v>
       </s:c>
-      <s:c r="G35" s="2" t="inlineStr">
-        <s:is>
-          <s:t>09/07 — 22,000 $ · 04/08 — 5,000 $ · 14/09 — 2,900 ₾ ≈ 1,099 $ (ერ.კ. 2.6384) · 19/09 — 40,000 $ ერ.კ. 2.6125</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="36">
-      <s:c r="A36" s="21" t="inlineStr">
+      <s:c r="G37" s="2" t="inlineStr">
+        <s:is>
+          <s:t>09/07 — 22,000 $ · 04/08 — 5,000 $ · 14/09 — 2,900 ₾ ≈ 1,099 $ (ერ.კ. 2.6384) · 19/09 — 40,000 $ ერ.კ. 2.6125 · ყველა N1-ზე / all against N1</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="38">
+      <s:c r="A38" s="21" t="inlineStr">
         <s:is>
           <s:t>დარჩენილი გადასახდელი / Outstanding</s:t>
         </s:is>
       </s:c>
-      <s:c r="B36" s="36">
-        <s:f>B34-B35</s:f>
-        <s:v>56900.848999393565</s:v>
-      </s:c>
-      <s:c r="C36" s="37">
+      <s:c r="B38" s="37">
+        <s:f>B36-B37</s:f>
+        <s:v>66900.84899939357</s:v>
+      </s:c>
+      <s:c r="C38" s="38">
         <s:f>Assumptions!$B$28</s:f>
         <s:v>2.6384</s:v>
       </s:c>
-      <s:c r="D36" s="22">
-        <s:f>B36*Assumptions!$B$28</s:f>
-        <s:v>150127.19999999998</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="37">
-      <s:c r="A37" s="17" t="inlineStr">
-        <s:is>
-          <s:t>შესრულების წილი / Share of the contract paid</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B37" s="19">
-        <s:f>IFERROR(B35/B34,0)</s:f>
-        <s:v>0.5447932080048514</s:v>
+      <s:c r="D38" s="22">
+        <s:f>B38*Assumptions!$B$28</s:f>
+        <s:v>176511.19999999998</s:v>
       </s:c>
     </s:row>
     <s:row r="39">
-      <s:c r="A39" s="10" t="inlineStr">
+      <s:c r="A39" s="17" t="inlineStr">
+        <s:is>
+          <s:t>შესრულების წილი / Share of the contracted work paid</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B39" s="19">
+        <s:f>IFERROR(B37/B36,0)</s:f>
+        <s:v>0.5044381555600477</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="41">
+      <s:c r="A41" s="10" t="inlineStr">
         <s:is>
           <s:t>5. კაპიტალური თუ საოპერაციო / CAPITAL OR OPERATING</s:t>
         </s:is>
       </s:c>
-      <s:c r="B39" s="11" t="n"/>
-      <s:c r="C39" s="11" t="n"/>
-      <s:c r="D39" s="11" t="n"/>
-      <s:c r="E39" s="11" t="n"/>
-      <s:c r="F39" s="11" t="n"/>
-    </s:row>
-    <s:row r="40">
-      <s:c r="A40" s="17" t="inlineStr">
+      <s:c r="B41" s="11" t="n"/>
+      <s:c r="C41" s="11" t="n"/>
+      <s:c r="D41" s="11" t="n"/>
+      <s:c r="E41" s="11" t="n"/>
+      <s:c r="F41" s="11" t="n"/>
+    </s:row>
+    <s:row r="42">
+      <s:c r="A42" s="17" t="inlineStr">
         <s:is>
           <s:t>კაპიტალიზებული / Capitalised (CAPEX)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B40" s="38">
+      <s:c r="B42" s="39">
         <s:f>SUMIF($D$14:$D$22,"CAPEX",$B$14:$B$22)</s:f>
         <s:v>192701.99</s:v>
       </s:c>
-      <s:c r="C40" s="19">
-        <s:f>IFERROR(B40/$B$23,0)</s:f>
+      <s:c r="C42" s="19">
+        <s:f>IFERROR(B42/$B$23,0)</s:f>
         <s:v>0.8748776682131305</s:v>
       </s:c>
-      <s:c r="G40" s="2" t="inlineStr">
+      <s:c r="G42" s="2" t="inlineStr">
         <s:is>
           <s:t>სათბურის ღირებულებაში / into the cost of the greenhouse</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="41">
-      <s:c r="A41" s="17" t="inlineStr">
+    <s:row r="43">
+      <s:c r="A43" s="17" t="inlineStr">
         <s:is>
           <s:t>პრე-საოპერაციო ხარჯი / Pre-operating running costs</s:t>
         </s:is>
       </s:c>
-      <s:c r="B41" s="38">
+      <s:c r="B43" s="39">
         <s:f>SUMIF($D$14:$D$22,"OPEX",$B$14:$B$22)</s:f>
         <s:v>27559.65</s:v>
       </s:c>
-      <s:c r="C41" s="19">
-        <s:f>IFERROR(B41/$B$23,0)</s:f>
+      <s:c r="C43" s="19">
+        <s:f>IFERROR(B43/$B$23,0)</s:f>
         <s:v>0.1251223317868695</s:v>
       </s:c>
-      <s:c r="G41" s="2" t="inlineStr">
+      <s:c r="G43" s="2" t="inlineStr">
         <s:is>
           <s:t>ხელფასი, გადასახადები, მომსახურება მოსავლამდე / wages, taxes and services before the first crop</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="42">
-      <s:c r="A42" s="17" t="inlineStr">
+    <s:row r="44">
+      <s:c r="A44" s="17" t="inlineStr">
         <s:is>
           <s:t>შემოწმება / Check (must be 0)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B42" s="39">
-        <s:f>B40+B41-B23</s:f>
-        <s:v>0.0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="44">
-      <s:c r="A44" s="4" t="inlineStr">
-        <s:is>
-          <s:t>· ბიუჯეტი კრედიტის თანხაა (Assumptions!B27). ხარჯი — ბანკის ამონაწერიდან, ცვლილება Actuals-ზე ხდება.</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="45">
-      <s:c r="A45" s="4" t="inlineStr">
-        <s:is>
-          <s:t>· კრედიტი ტრანშებად გაიცემა, ამიტომ ამონაწერში ერთიანი ჩარიცხვა არ ჩანს.</s:t>
-        </s:is>
+      <s:c r="B44" s="40">
+        <s:f>B42+B43-B23</s:f>
+        <s:v>0.0</s:v>
       </s:c>
     </s:row>
     <s:row r="46">
       <s:c r="A46" s="4" t="inlineStr">
         <s:is>
+          <s:t>· ბიუჯეტი კრედიტის თანხაა (Assumptions!B27). ხარჯი — ბანკის ამონაწერიდან, ცვლილება Actuals-ზე ხდება.</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="47">
+      <s:c r="A47" s="4" t="inlineStr">
+        <s:is>
+          <s:t>· კრედიტი ტრანშებად გაიცემა, ამიტომ ამონაწერში ერთიანი ჩარიცხვა არ ჩანს.</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="48">
+      <s:c r="A48" s="4" t="inlineStr">
+        <s:is>
           <s:t>· ეს ფურცელი მშენებლობის ფაზაა; CF_Monthly და Annual პირველ სრულ საოპერაციო წელს ასახავს.</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="47">
-      <s:c r="A47" s="2" t="inlineStr">
-        <s:is>
-          <s:t>· The budget is the credit amount; the spend comes from the bank statement — edit it on Actuals.</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="48">
-      <s:c r="A48" s="2" t="inlineStr">
-        <s:is>
-          <s:t>· The credit is drawn in tranches, so no single disbursement shows in the statement.</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="49">
       <s:c r="A49" s="2" t="inlineStr">
+        <s:is>
+          <s:t>· The budget is the credit amount; the spend comes from the bank statement — edit it on Actuals.</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="50">
+      <s:c r="A50" s="2" t="inlineStr">
+        <s:is>
+          <s:t>· The credit is drawn in tranches, so no single disbursement shows in the statement.</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="51">
+      <s:c r="A51" s="2" t="inlineStr">
         <s:is>
           <s:t>· This sheet is the construction phase; CF_Monthly and Annual are the first full operating year.</s:t>
         </s:is>
@@ -2003,15 +2045,15 @@
           <s:t>სათბურის ფართობი / Greenhouse area</s:t>
         </s:is>
       </s:c>
-      <s:c r="B6" s="40" t="n">
+      <s:c r="B6" s="41" t="n">
         <s:v>2000</s:v>
       </s:c>
-      <s:c r="C6" s="41" t="inlineStr">
+      <s:c r="C6" s="42" t="inlineStr">
         <s:is>
           <s:t>m²</s:t>
         </s:is>
       </s:c>
-      <s:c r="D6" s="42" t="inlineStr">
+      <s:c r="D6" s="43" t="inlineStr">
         <s:is>
           <s:t>მომხმარებლის მონაცემი / Given</s:t>
         </s:is>
@@ -2023,15 +2065,15 @@
           <s:t>მოსავლის ციკლები წელიწადში / Harvest cycles per year</s:t>
         </s:is>
       </s:c>
-      <s:c r="B7" s="43" t="n">
+      <s:c r="B7" s="44" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C7" s="41" t="inlineStr">
+      <s:c r="C7" s="42" t="inlineStr">
         <s:is>
           <s:t>cycles</s:t>
         </s:is>
       </s:c>
-      <s:c r="D7" s="42" t="inlineStr">
+      <s:c r="D7" s="43" t="inlineStr">
         <s:is>
           <s:t>ზამთარი + ზაფხული / Winter + summer</s:t>
         </s:is>
@@ -2053,15 +2095,15 @@
           <s:t>ზამთრის მოსავალი / Winter harvest</s:t>
         </s:is>
       </s:c>
-      <s:c r="B10" s="44" t="n">
+      <s:c r="B10" s="45" t="n">
         <s:v>85</s:v>
       </s:c>
-      <s:c r="C10" s="41" t="inlineStr">
+      <s:c r="C10" s="42" t="inlineStr">
         <s:is>
           <s:t>tons</s:t>
         </s:is>
       </s:c>
-      <s:c r="D10" s="42" t="inlineStr">
+      <s:c r="D10" s="43" t="inlineStr">
         <s:is>
           <s:t>მითითებული დიაპაზონი 80–90 / Stated range 80–90; midpoint used</s:t>
         </s:is>
@@ -2077,12 +2119,12 @@
         <s:f>B10*1000</s:f>
         <s:v>85000.0</s:v>
       </s:c>
-      <s:c r="C11" s="41" t="inlineStr">
+      <s:c r="C11" s="42" t="inlineStr">
         <s:is>
           <s:t>kg</s:t>
         </s:is>
       </s:c>
-      <s:c r="D11" s="42" t="inlineStr">
+      <s:c r="D11" s="43" t="inlineStr">
         <s:is>
           <s:t>ავტომატური / Calculated</s:t>
         </s:is>
@@ -2094,16 +2136,16 @@
           <s:t xml:space="preserve">  ზამთრის მოსავლიანობა / Winter yield per m²</s:t>
         </s:is>
       </s:c>
-      <s:c r="B12" s="45">
+      <s:c r="B12" s="46">
         <s:f>B11/B6</s:f>
         <s:v>42.5</s:v>
       </s:c>
-      <s:c r="C12" s="41" t="inlineStr">
+      <s:c r="C12" s="42" t="inlineStr">
         <s:is>
           <s:t>kg/m²</s:t>
         </s:is>
       </s:c>
-      <s:c r="D12" s="42" t="inlineStr">
+      <s:c r="D12" s="43" t="inlineStr">
         <s:is>
           <s:t>ავტომატური / Calculated</s:t>
         </s:is>
@@ -2115,15 +2157,15 @@
           <s:t>ზამთრის ფასი / Winter selling price</s:t>
         </s:is>
       </s:c>
-      <s:c r="B13" s="46" t="n">
+      <s:c r="B13" s="47" t="n">
         <s:v>4.5</s:v>
       </s:c>
-      <s:c r="C13" s="41" t="inlineStr">
+      <s:c r="C13" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL/kg</s:t>
         </s:is>
       </s:c>
-      <s:c r="D13" s="42" t="inlineStr">
+      <s:c r="D13" s="43" t="inlineStr">
         <s:is>
           <s:t>მომხმარებლის მონაცემი / Given</s:t>
         </s:is>
@@ -2135,15 +2177,15 @@
           <s:t>ზაფხულის მოსავალი / Summer harvest</s:t>
         </s:is>
       </s:c>
-      <s:c r="B14" s="44" t="n">
+      <s:c r="B14" s="45" t="n">
         <s:v>70</s:v>
       </s:c>
-      <s:c r="C14" s="41" t="inlineStr">
+      <s:c r="C14" s="42" t="inlineStr">
         <s:is>
           <s:t>tons</s:t>
         </s:is>
       </s:c>
-      <s:c r="D14" s="42" t="inlineStr">
+      <s:c r="D14" s="43" t="inlineStr">
         <s:is>
           <s:t>მომხმარებლის მონაცემი / Given</s:t>
         </s:is>
@@ -2159,12 +2201,12 @@
         <s:f>B14*1000</s:f>
         <s:v>70000.0</s:v>
       </s:c>
-      <s:c r="C15" s="41" t="inlineStr">
+      <s:c r="C15" s="42" t="inlineStr">
         <s:is>
           <s:t>kg</s:t>
         </s:is>
       </s:c>
-      <s:c r="D15" s="42" t="inlineStr">
+      <s:c r="D15" s="43" t="inlineStr">
         <s:is>
           <s:t>ავტომატური / Calculated</s:t>
         </s:is>
@@ -2176,16 +2218,16 @@
           <s:t xml:space="preserve">  ზაფხულის მოსავლიანობა / Summer yield per m²</s:t>
         </s:is>
       </s:c>
-      <s:c r="B16" s="45">
+      <s:c r="B16" s="46">
         <s:f>B15/B6</s:f>
         <s:v>35.0</s:v>
       </s:c>
-      <s:c r="C16" s="41" t="inlineStr">
+      <s:c r="C16" s="42" t="inlineStr">
         <s:is>
           <s:t>kg/m²</s:t>
         </s:is>
       </s:c>
-      <s:c r="D16" s="42" t="inlineStr">
+      <s:c r="D16" s="43" t="inlineStr">
         <s:is>
           <s:t>ავტომატური / Calculated</s:t>
         </s:is>
@@ -2197,15 +2239,15 @@
           <s:t>ზაფხულის ფასი / Summer selling price</s:t>
         </s:is>
       </s:c>
-      <s:c r="B17" s="46" t="n">
+      <s:c r="B17" s="47" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C17" s="41" t="inlineStr">
+      <s:c r="C17" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL/kg</s:t>
         </s:is>
       </s:c>
-      <s:c r="D17" s="42" t="inlineStr">
+      <s:c r="D17" s="43" t="inlineStr">
         <s:is>
           <s:t>მომხმარებლის მონაცემი / Given</s:t>
         </s:is>
@@ -2217,16 +2259,16 @@
           <s:t>სულ მოსავალი / Total annual harvest</s:t>
         </s:is>
       </s:c>
-      <s:c r="B18" s="47">
+      <s:c r="B18" s="48">
         <s:f>B10+B14</s:f>
         <s:v>155.0</s:v>
       </s:c>
-      <s:c r="C18" s="41" t="inlineStr">
+      <s:c r="C18" s="42" t="inlineStr">
         <s:is>
           <s:t>tons</s:t>
         </s:is>
       </s:c>
-      <s:c r="D18" s="42" t="inlineStr">
+      <s:c r="D18" s="43" t="inlineStr">
         <s:is>
           <s:t>ავტომატური / Calculated</s:t>
         </s:is>
@@ -2238,16 +2280,16 @@
           <s:t>საშუალო შეწონილი ფასი / Blended average price</s:t>
         </s:is>
       </s:c>
-      <s:c r="B19" s="38">
+      <s:c r="B19" s="39">
         <s:f>(B11*B13+B15*B17)/(B11+B15)</s:f>
         <s:v>3.8225806451612905</s:v>
       </s:c>
-      <s:c r="C19" s="41" t="inlineStr">
+      <s:c r="C19" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL/kg</s:t>
         </s:is>
       </s:c>
-      <s:c r="D19" s="42" t="inlineStr">
+      <s:c r="D19" s="43" t="inlineStr">
         <s:is>
           <s:t>ავტომატური / Calculated</s:t>
         </s:is>
@@ -2269,15 +2311,15 @@
           <s:t>წლიური OPEX (მითითებული) / Annual OPEX as stated</s:t>
         </s:is>
       </s:c>
-      <s:c r="B22" s="48" t="n">
+      <s:c r="B22" s="49" t="n">
         <s:v>150000</s:v>
       </s:c>
-      <s:c r="C22" s="41" t="inlineStr">
+      <s:c r="C22" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D22" s="42" t="inlineStr">
+      <s:c r="D22" s="43" t="inlineStr">
         <s:is>
           <s:t>მომხმარებლის მონაცემი / Given</s:t>
         </s:is>
@@ -2289,16 +2331,16 @@
           <s:t>OPEX ფურცლის ჯამი / Total from OPEX sheet</s:t>
         </s:is>
       </s:c>
-      <s:c r="B23" s="49">
+      <s:c r="B23" s="50">
         <s:f>OPEX!B14</s:f>
         <s:v>150000.0</s:v>
       </s:c>
-      <s:c r="C23" s="41" t="inlineStr">
+      <s:c r="C23" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D23" s="42" t="inlineStr">
+      <s:c r="D23" s="43" t="inlineStr">
         <s:is>
           <s:t>8 კატეგორიის ჯამი / Sum of the 8 categories</s:t>
         </s:is>
@@ -2314,12 +2356,12 @@
         <s:f>B23-B22</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C24" s="41" t="inlineStr">
+      <s:c r="C24" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D24" s="42" t="inlineStr">
+      <s:c r="D24" s="43" t="inlineStr">
         <s:is>
           <s:t>თუ ≠ 0, გაასწორეთ OPEX კატეგორიები / If ≠ 0, adjust the OPEX categories</s:t>
         </s:is>
@@ -2341,15 +2383,15 @@
           <s:t>კრედიტის თანხა / Credit amount</s:t>
         </s:is>
       </s:c>
-      <s:c r="B27" s="50" t="n">
+      <s:c r="B27" s="51" t="n">
         <s:v>625000</s:v>
       </s:c>
-      <s:c r="C27" s="41" t="inlineStr">
+      <s:c r="C27" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D27" s="42" t="inlineStr">
+      <s:c r="D27" s="43" t="inlineStr">
         <s:is>
           <s:t>ხელშეკრულება GA/1-876787–001, პუნქტი 3.11 / contract clause 3.11</s:t>
         </s:is>
@@ -2361,15 +2403,15 @@
           <s:t>გაცვლითი კურსი / FX rate</s:t>
         </s:is>
       </s:c>
-      <s:c r="B28" s="51" t="n">
+      <s:c r="B28" s="52" t="n">
         <s:v>2.6384</s:v>
       </s:c>
-      <s:c r="C28" s="41" t="inlineStr">
+      <s:c r="C28" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL/USD</s:t>
         </s:is>
       </s:c>
-      <s:c r="D28" s="42" t="inlineStr">
+      <s:c r="D28" s="43" t="inlineStr">
         <s:is>
           <s:t>ფაქტი 09/07/2026 გადარიცხვიდან, USD ხელშეკრულებებისთვის / actual, used for the USD contracts</s:t>
         </s:is>
@@ -2385,12 +2427,12 @@
         <s:f>B27</s:f>
         <s:v>625000.0</s:v>
       </s:c>
-      <s:c r="C29" s="41" t="inlineStr">
+      <s:c r="C29" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D29" s="42" t="inlineStr">
+      <s:c r="D29" s="43" t="inlineStr">
         <s:is>
           <s:t>სრულად ათვისებულად ითვლება / assumed fully drawn</s:t>
         </s:is>
@@ -2402,15 +2444,15 @@
           <s:t>წლიური საპროცენტო განაკვეთი / Annual interest rate</s:t>
         </s:is>
       </s:c>
-      <s:c r="B30" s="52" t="n">
+      <s:c r="B30" s="53" t="n">
         <s:v>0.1264</s:v>
       </s:c>
-      <s:c r="C30" s="41" t="inlineStr">
+      <s:c r="C30" s="42" t="inlineStr">
         <s:is>
           <s:t>%</s:t>
         </s:is>
       </s:c>
-      <s:c r="D30" s="42" t="inlineStr">
+      <s:c r="D30" s="43" t="inlineStr">
         <s:is>
           <s:t>12.64% 17/06/2028-მდე; შემდეგ რეფინანსირება + 5.14%, min 10%, max 18% / 12.64% to 17/06/2028, indexed after</s:t>
         </s:is>
@@ -2422,15 +2464,15 @@
           <s:t>ვადა / Term</s:t>
         </s:is>
       </s:c>
-      <s:c r="B31" s="43" t="n">
+      <s:c r="B31" s="44" t="n">
         <s:v>120</s:v>
       </s:c>
-      <s:c r="C31" s="41" t="inlineStr">
+      <s:c r="C31" s="42" t="inlineStr">
         <s:is>
           <s:t>months</s:t>
         </s:is>
       </s:c>
-      <s:c r="D31" s="42" t="inlineStr">
+      <s:c r="D31" s="43" t="inlineStr">
         <s:is>
           <s:t>17/06/2026 – 17/06/2036 (პუნქტი 3.9) / clause 3.9</s:t>
         </s:is>
@@ -2442,15 +2484,15 @@
           <s:t>საშეღავათო პერიოდი / Grace period, no payments</s:t>
         </s:is>
       </s:c>
-      <s:c r="B32" s="43" t="n">
+      <s:c r="B32" s="44" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="C32" s="41" t="inlineStr">
+      <s:c r="C32" s="42" t="inlineStr">
         <s:is>
           <s:t>months</s:t>
         </s:is>
       </s:c>
-      <s:c r="D32" s="42" t="inlineStr">
+      <s:c r="D32" s="43" t="inlineStr">
         <s:is>
           <s:t>დანართი #1: თვე 1–12 გადახდის გარეშე / Annex 1: months 1–12 pay nothing</s:t>
         </s:is>
@@ -2466,12 +2508,12 @@
         <s:f>PMT(B30/12,B31-B32-1,-B29)</s:f>
         <s:v>9766.072742502936</s:v>
       </s:c>
-      <s:c r="C33" s="41" t="inlineStr">
+      <s:c r="C33" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D33" s="42" t="inlineStr">
+      <s:c r="D33" s="43" t="inlineStr">
         <s:is>
           <s:t>107 შენატანი მე-14 თვიდან / 107 instalments from month 14</s:t>
         </s:is>
@@ -2483,15 +2525,15 @@
           <s:t>სააგენტოს თანადაფინანსება / Agency co-financing rate</s:t>
         </s:is>
       </s:c>
-      <s:c r="B34" s="52" t="n">
+      <s:c r="B34" s="53" t="n">
         <s:v>0.11</s:v>
       </s:c>
-      <s:c r="C34" s="41" t="inlineStr">
+      <s:c r="C34" s="42" t="inlineStr">
         <s:is>
           <s:t>%</s:t>
         </s:is>
       </s:c>
-      <s:c r="D34" s="42" t="inlineStr">
+      <s:c r="D34" s="43" t="inlineStr">
         <s:is>
           <s:t>სოფლის განვითარების სააგენტო — ძირის 11% წლიურად (პუნქტი 3.5) / Rural Development Agency, clause 3.5</s:t>
         </s:is>
@@ -2503,15 +2545,15 @@
           <s:t>თანადაფინანსების ვადა / Co-financing period</s:t>
         </s:is>
       </s:c>
-      <s:c r="B35" s="43" t="n">
+      <s:c r="B35" s="44" t="n">
         <s:v>48</s:v>
       </s:c>
-      <s:c r="C35" s="41" t="inlineStr">
+      <s:c r="C35" s="42" t="inlineStr">
         <s:is>
           <s:t>months</s:t>
         </s:is>
       </s:c>
-      <s:c r="D35" s="42" t="inlineStr">
+      <s:c r="D35" s="43" t="inlineStr">
         <s:is>
           <s:t>არაუმეტეს 48 თვისა (პუნქტი 3.5) / up to 48 months, clause 3.5</s:t>
         </s:is>
@@ -2523,15 +2565,15 @@
           <s:t>განაკვეთი 17/06/2028-ის შემდეგ / Rate after 17/06/2028</s:t>
         </s:is>
       </s:c>
-      <s:c r="B36" s="52" t="n">
+      <s:c r="B36" s="53" t="n">
         <s:v>0.134</s:v>
       </s:c>
-      <s:c r="C36" s="41" t="inlineStr">
+      <s:c r="C36" s="42" t="inlineStr">
         <s:is>
           <s:t>%</s:t>
         </s:is>
       </s:c>
-      <s:c r="D36" s="42" t="inlineStr">
+      <s:c r="D36" s="43" t="inlineStr">
         <s:is>
           <s:t>რეფინანსირება 8.26% + მარჟა 5.14%; ბანკის დანართ #1-იდან ნაგულისხმევი / implied by the bank's Annex 1: refinancing 8.26% + 5.14% margin</s:t>
         </s:is>
@@ -2543,15 +2585,15 @@
           <s:t>თვე, საიდანაც მოქმედებს მე-2 განაკვეთი / Month the second rate starts</s:t>
         </s:is>
       </s:c>
-      <s:c r="B37" s="43" t="n">
+      <s:c r="B37" s="44" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="C37" s="41" t="inlineStr">
+      <s:c r="C37" s="42" t="inlineStr">
         <s:is>
           <s:t>month</s:t>
         </s:is>
       </s:c>
-      <s:c r="D37" s="42" t="inlineStr">
+      <s:c r="D37" s="43" t="inlineStr">
         <s:is>
           <s:t>19/06/2028, გრაფიკის 24-ე შენატანი / instalment 24, 19/06/2028</s:t>
         </s:is>
@@ -2573,15 +2615,15 @@
           <s:t>მოსავლის ზრდა / Yield growth p.a.</s:t>
         </s:is>
       </s:c>
-      <s:c r="B39" s="53" t="n">
+      <s:c r="B39" s="54" t="n">
         <s:v>0.02</s:v>
       </s:c>
-      <s:c r="C39" s="41" t="inlineStr">
+      <s:c r="C39" s="42" t="inlineStr">
         <s:is>
           <s:t>%</s:t>
         </s:is>
       </s:c>
-      <s:c r="D39" s="42" t="inlineStr">
+      <s:c r="D39" s="43" t="inlineStr">
         <s:is>
           <s:t>მოდელის დაშვება / Model assumption</s:t>
         </s:is>
@@ -2593,15 +2635,15 @@
           <s:t>ფასის ზრდა / Price growth p.a.</s:t>
         </s:is>
       </s:c>
-      <s:c r="B40" s="53" t="n">
+      <s:c r="B40" s="54" t="n">
         <s:v>0.03</s:v>
       </s:c>
-      <s:c r="C40" s="41" t="inlineStr">
+      <s:c r="C40" s="42" t="inlineStr">
         <s:is>
           <s:t>%</s:t>
         </s:is>
       </s:c>
-      <s:c r="D40" s="42" t="inlineStr">
+      <s:c r="D40" s="43" t="inlineStr">
         <s:is>
           <s:t>მოდელის დაშვება / Model assumption</s:t>
         </s:is>
@@ -2613,15 +2655,15 @@
           <s:t>OPEX ინფლაცია / OPEX inflation p.a.</s:t>
         </s:is>
       </s:c>
-      <s:c r="B41" s="53" t="n">
+      <s:c r="B41" s="54" t="n">
         <s:v>0.04</s:v>
       </s:c>
-      <s:c r="C41" s="41" t="inlineStr">
+      <s:c r="C41" s="42" t="inlineStr">
         <s:is>
           <s:t>%</s:t>
         </s:is>
       </s:c>
-      <s:c r="D41" s="42" t="inlineStr">
+      <s:c r="D41" s="43" t="inlineStr">
         <s:is>
           <s:t>მოდელის დაშვება / Model assumption</s:t>
         </s:is>
@@ -2643,15 +2685,15 @@
           <s:t>მოგების გადასახადი / Profit tax rate applied</s:t>
         </s:is>
       </s:c>
-      <s:c r="B44" s="52" t="n">
+      <s:c r="B44" s="53" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="C44" s="41" t="inlineStr">
+      <s:c r="C44" s="42" t="inlineStr">
         <s:is>
           <s:t>%</s:t>
         </s:is>
       </s:c>
-      <s:c r="D44" s="42" t="inlineStr">
+      <s:c r="D44" s="43" t="inlineStr">
         <s:is>
           <s:t>0% ნაგულისხმევად — იხ. Instructions / 0% by default</s:t>
         </s:is>
@@ -2663,15 +2705,15 @@
           <s:t>საწყისი ფულადი ნაშთი / Opening cash balance</s:t>
         </s:is>
       </s:c>
-      <s:c r="B45" s="54" t="n">
+      <s:c r="B45" s="55" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="C45" s="41" t="inlineStr">
+      <s:c r="C45" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D45" s="42" t="inlineStr">
+      <s:c r="D45" s="43" t="inlineStr">
         <s:is>
           <s:t>საოპერაციო წელი 1-ის დასაწყისი / start of operating Year 1</s:t>
         </s:is>
@@ -2683,15 +2725,15 @@
           <s:t>კრედიტის ათვისება წელი 1-ში? / Credit drawn in Year 1? (1=yes, 0=no)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B46" s="43" t="n">
+      <s:c r="B46" s="44" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="C46" s="41" t="inlineStr">
+      <s:c r="C46" s="42" t="inlineStr">
         <s:is>
           <s:t>1/0</s:t>
         </s:is>
       </s:c>
-      <s:c r="D46" s="42" t="inlineStr">
+      <s:c r="D46" s="43" t="inlineStr">
         <s:is>
           <s:t>0 = უკვე ათვისებული / 0 = already drawn</s:t>
         </s:is>
@@ -2707,12 +2749,12 @@
         <s:f>B46*B29</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C47" s="41" t="inlineStr">
+      <s:c r="C47" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D47" s="42" t="inlineStr">
+      <s:c r="D47" s="43" t="inlineStr">
         <s:is>
           <s:t>ტოლი ათვისებული კრედიტისა / equals the drawdown, net zero</s:t>
         </s:is>
@@ -2724,15 +2766,15 @@
           <s:t>სესხის წელი = საოპერაციო წელი 1 / Loan year mapped to operating Year 1</s:t>
         </s:is>
       </s:c>
-      <s:c r="B48" s="55" t="n">
+      <s:c r="B48" s="56" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C48" s="41" t="inlineStr">
+      <s:c r="C48" s="42" t="inlineStr">
         <s:is>
           <s:t>yr</s:t>
         </s:is>
       </s:c>
-      <s:c r="D48" s="42" t="inlineStr">
+      <s:c r="D48" s="43" t="inlineStr">
         <s:is>
           <s:t>სესხის მე-2 წელი = 07/2027–06/2028, ამორტიზაციის პირველი წელი / loan year 2 = Jul 2027 – Jun 2028</s:t>
         </s:is>
@@ -2754,16 +2796,16 @@
           <s:t>წლიური შემოსავალი / Annual revenue</s:t>
         </s:is>
       </s:c>
-      <s:c r="B51" s="56">
+      <s:c r="B51" s="57">
         <s:f>CF_Monthly!N19</s:f>
         <s:v>592500.0</s:v>
       </s:c>
-      <s:c r="C51" s="41" t="inlineStr">
+      <s:c r="C51" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D51" s="42" t="inlineStr">
+      <s:c r="D51" s="43" t="inlineStr">
         <s:is>
           <s:t>სხვა ფურცლიდან / from another sheet</s:t>
         </s:is>
@@ -2775,16 +2817,16 @@
           <s:t>წლიური OPEX / Annual OPEX</s:t>
         </s:is>
       </s:c>
-      <s:c r="B52" s="56">
+      <s:c r="B52" s="57">
         <s:f>CF_Monthly!N30</s:f>
         <s:v>150000.0</s:v>
       </s:c>
-      <s:c r="C52" s="41" t="inlineStr">
+      <s:c r="C52" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D52" s="42" t="inlineStr">
+      <s:c r="D52" s="43" t="inlineStr">
         <s:is>
           <s:t>სხვა ფურცლიდან / from another sheet</s:t>
         </s:is>
@@ -2796,16 +2838,16 @@
           <s:t>EBITDA</s:t>
         </s:is>
       </s:c>
-      <s:c r="B53" s="56">
+      <s:c r="B53" s="57">
         <s:f>CF_Monthly!N32</s:f>
         <s:v>442500.0</s:v>
       </s:c>
-      <s:c r="C53" s="41" t="inlineStr">
+      <s:c r="C53" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D53" s="42" t="inlineStr">
+      <s:c r="D53" s="43" t="inlineStr">
         <s:is>
           <s:t>სხვა ფურცლიდან / from another sheet</s:t>
         </s:is>
@@ -2817,12 +2859,12 @@
           <s:t>EBITDA მარჟა / margin</s:t>
         </s:is>
       </s:c>
-      <s:c r="B54" s="57">
+      <s:c r="B54" s="58">
         <s:f>IFERROR(B53/B51,0)</s:f>
         <s:v>0.7468354430379747</s:v>
       </s:c>
-      <s:c r="C54" s="41" t="inlineStr"/>
-      <s:c r="D54" s="42" t="inlineStr">
+      <s:c r="C54" s="42" t="inlineStr"/>
+      <s:c r="D54" s="43" t="inlineStr">
         <s:is>
           <s:t>სხვა ფურცლიდან / from another sheet</s:t>
         </s:is>
@@ -2834,16 +2876,16 @@
           <s:t>ვალის მომსახურება / Debt service</s:t>
         </s:is>
       </s:c>
-      <s:c r="B55" s="56">
+      <s:c r="B55" s="57">
         <s:f>CF_Monthly!N36</s:f>
         <s:v>47168.730570487125</s:v>
       </s:c>
-      <s:c r="C55" s="41" t="inlineStr">
+      <s:c r="C55" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D55" s="42" t="inlineStr">
+      <s:c r="D55" s="43" t="inlineStr">
         <s:is>
           <s:t>სხვა ფურცლიდან / from another sheet</s:t>
         </s:is>
@@ -2855,16 +2897,16 @@
           <s:t>წმინდა ფულადი ნაკადი / Net cash flow</s:t>
         </s:is>
       </s:c>
-      <s:c r="B56" s="56">
+      <s:c r="B56" s="57">
         <s:f>CF_Monthly!N43</s:f>
         <s:v>395331.2694295129</s:v>
       </s:c>
-      <s:c r="C56" s="41" t="inlineStr">
+      <s:c r="C56" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D56" s="42" t="inlineStr">
+      <s:c r="D56" s="43" t="inlineStr">
         <s:is>
           <s:t>სხვა ფურცლიდან / from another sheet</s:t>
         </s:is>
@@ -2876,12 +2918,12 @@
           <s:t>DSCR (EBITDA / ვალის მომსახურება)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B57" s="58">
+      <s:c r="B57" s="59">
         <s:f>IFERROR(B53/B55,0)</s:f>
         <s:v>9.381214941511837</s:v>
       </s:c>
-      <s:c r="C57" s="41" t="inlineStr"/>
-      <s:c r="D57" s="42" t="inlineStr">
+      <s:c r="C57" s="42" t="inlineStr"/>
+      <s:c r="D57" s="43" t="inlineStr">
         <s:is>
           <s:t>სხვა ფურცლიდან / from another sheet</s:t>
         </s:is>
@@ -2893,16 +2935,16 @@
           <s:t>პროექტში ჩადებული დღემდე / Project spend to date</s:t>
         </s:is>
       </s:c>
-      <s:c r="B58" s="56">
+      <s:c r="B58" s="57">
         <s:f>Budget!B21</s:f>
         <s:v>7505.41</s:v>
       </s:c>
-      <s:c r="C58" s="41" t="inlineStr">
+      <s:c r="C58" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D58" s="42" t="inlineStr">
+      <s:c r="D58" s="43" t="inlineStr">
         <s:is>
           <s:t>სხვა ფურცლიდან / from another sheet</s:t>
         </s:is>
@@ -2914,16 +2956,16 @@
           <s:t>აქედან კაპიტალური / of which capitalised</s:t>
         </s:is>
       </s:c>
-      <s:c r="B59" s="56">
+      <s:c r="B59" s="57">
         <s:f>Budget!B38</s:f>
-        <s:v>0.0</s:v>
-      </s:c>
-      <s:c r="C59" s="41" t="inlineStr">
+        <s:v>66900.84899939357</s:v>
+      </s:c>
+      <s:c r="C59" s="42" t="inlineStr">
         <s:is>
           <s:t>GEL</s:t>
         </s:is>
       </s:c>
-      <s:c r="D59" s="42" t="inlineStr">
+      <s:c r="D59" s="43" t="inlineStr">
         <s:is>
           <s:t>სხვა ფურცლიდან / from another sheet</s:t>
         </s:is>
@@ -2997,7 +3039,7 @@
       <s:c r="O4" s="11" t="n"/>
     </s:row>
     <s:row r="5">
-      <s:c r="A5" s="59" t="inlineStr">
+      <s:c r="A5" s="60" t="inlineStr">
         <s:is>
           <s:t>კატეგორია / Category</s:t>
         </s:is>
@@ -3079,43 +3121,43 @@
           <s:t>ხელფასები / Labour &amp; wages</s:t>
         </s:is>
       </s:c>
-      <s:c r="B6" s="54" t="n">
+      <s:c r="B6" s="55" t="n">
         <s:v>48000</s:v>
       </s:c>
-      <s:c r="C6" s="60" t="n">
+      <s:c r="C6" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="D6" s="60" t="n">
+      <s:c r="D6" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="E6" s="60" t="n">
+      <s:c r="E6" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="F6" s="60" t="n">
+      <s:c r="F6" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="G6" s="60" t="n">
+      <s:c r="G6" s="61" t="n">
         <s:v>0.07000000000000001</s:v>
       </s:c>
-      <s:c r="H6" s="60" t="n">
+      <s:c r="H6" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="I6" s="60" t="n">
+      <s:c r="I6" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="J6" s="60" t="n">
+      <s:c r="J6" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="K6" s="60" t="n">
+      <s:c r="K6" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="L6" s="60" t="n">
+      <s:c r="L6" s="61" t="n">
         <s:v>0.07000000000000001</s:v>
       </s:c>
-      <s:c r="M6" s="60" t="n">
+      <s:c r="M6" s="61" t="n">
         <s:v>0.07000000000000001</s:v>
       </s:c>
-      <s:c r="N6" s="60" t="n">
+      <s:c r="N6" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
       <s:c r="O6" s="19">
@@ -3129,43 +3171,43 @@
           <s:t>გათბობა (გაზი/საწვავი) / Heating (gas &amp; fuel)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B7" s="54" t="n">
+      <s:c r="B7" s="55" t="n">
         <s:v>36000</s:v>
       </s:c>
-      <s:c r="C7" s="60" t="n">
+      <s:c r="C7" s="61" t="n">
         <s:v>0.25</s:v>
       </s:c>
-      <s:c r="D7" s="60" t="n">
+      <s:c r="D7" s="61" t="n">
         <s:v>0.22</s:v>
       </s:c>
-      <s:c r="E7" s="60" t="n">
+      <s:c r="E7" s="61" t="n">
         <s:v>0.13</s:v>
       </s:c>
-      <s:c r="F7" s="60" t="n">
+      <s:c r="F7" s="61" t="n">
         <s:v>0.03</s:v>
       </s:c>
-      <s:c r="G7" s="60" t="n">
+      <s:c r="G7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="H7" s="60" t="n">
+      <s:c r="H7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="I7" s="60" t="n">
+      <s:c r="I7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="J7" s="60" t="n">
+      <s:c r="J7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="K7" s="60" t="n">
+      <s:c r="K7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="L7" s="60" t="n">
+      <s:c r="L7" s="61" t="n">
         <s:v>0.04</s:v>
       </s:c>
-      <s:c r="M7" s="60" t="n">
+      <s:c r="M7" s="61" t="n">
         <s:v>0.13</s:v>
       </s:c>
-      <s:c r="N7" s="60" t="n">
+      <s:c r="N7" s="61" t="n">
         <s:v>0.2</s:v>
       </s:c>
       <s:c r="O7" s="19">
@@ -3179,43 +3221,43 @@
           <s:t>ელექტროენერგია და წყალი / Electricity &amp; water</s:t>
         </s:is>
       </s:c>
-      <s:c r="B8" s="54" t="n">
+      <s:c r="B8" s="55" t="n">
         <s:v>12000</s:v>
       </s:c>
-      <s:c r="C8" s="60" t="n">
+      <s:c r="C8" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="D8" s="60" t="n">
+      <s:c r="D8" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="E8" s="60" t="n">
+      <s:c r="E8" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="F8" s="60" t="n">
+      <s:c r="F8" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="G8" s="60" t="n">
+      <s:c r="G8" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="H8" s="60" t="n">
+      <s:c r="H8" s="61" t="n">
         <s:v>0.1</s:v>
       </s:c>
-      <s:c r="I8" s="60" t="n">
+      <s:c r="I8" s="61" t="n">
         <s:v>0.11</s:v>
       </s:c>
-      <s:c r="J8" s="60" t="n">
+      <s:c r="J8" s="61" t="n">
         <s:v>0.11</s:v>
       </s:c>
-      <s:c r="K8" s="60" t="n">
+      <s:c r="K8" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="L8" s="60" t="n">
+      <s:c r="L8" s="61" t="n">
         <s:v>0.06</s:v>
       </s:c>
-      <s:c r="M8" s="60" t="n">
+      <s:c r="M8" s="61" t="n">
         <s:v>0.06</s:v>
       </s:c>
-      <s:c r="N8" s="60" t="n">
+      <s:c r="N8" s="61" t="n">
         <s:v>0.06</s:v>
       </s:c>
       <s:c r="O8" s="19">
@@ -3229,43 +3271,43 @@
           <s:t>ნერგები და თესლი / Seedlings &amp; seeds</s:t>
         </s:is>
       </s:c>
-      <s:c r="B9" s="54" t="n">
+      <s:c r="B9" s="55" t="n">
         <s:v>14000</s:v>
       </s:c>
-      <s:c r="C9" s="60" t="n">
+      <s:c r="C9" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="D9" s="60" t="n">
+      <s:c r="D9" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="E9" s="60" t="n">
+      <s:c r="E9" s="61" t="n">
         <s:v>0.2</s:v>
       </s:c>
-      <s:c r="F9" s="60" t="n">
+      <s:c r="F9" s="61" t="n">
         <s:v>0.25</s:v>
       </s:c>
-      <s:c r="G9" s="60" t="n">
+      <s:c r="G9" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="H9" s="60" t="n">
+      <s:c r="H9" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="I9" s="60" t="n">
+      <s:c r="I9" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="J9" s="60" t="n">
+      <s:c r="J9" s="61" t="n">
         <s:v>0.3</s:v>
       </s:c>
-      <s:c r="K9" s="60" t="n">
+      <s:c r="K9" s="61" t="n">
         <s:v>0.25</s:v>
       </s:c>
-      <s:c r="L9" s="60" t="n">
+      <s:c r="L9" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="M9" s="60" t="n">
+      <s:c r="M9" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="N9" s="60" t="n">
+      <s:c r="N9" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
       <s:c r="O9" s="19">
@@ -3279,43 +3321,43 @@
           <s:t>სასუქი და მცენარეთა დაცვა / Fertiliser &amp; crop protection</s:t>
         </s:is>
       </s:c>
-      <s:c r="B10" s="54" t="n">
+      <s:c r="B10" s="55" t="n">
         <s:v>18000</s:v>
       </s:c>
-      <s:c r="C10" s="60" t="n">
+      <s:c r="C10" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="D10" s="60" t="n">
+      <s:c r="D10" s="61" t="n">
         <s:v>0.1</s:v>
       </s:c>
-      <s:c r="E10" s="60" t="n">
+      <s:c r="E10" s="61" t="n">
         <s:v>0.12</s:v>
       </s:c>
-      <s:c r="F10" s="60" t="n">
+      <s:c r="F10" s="61" t="n">
         <s:v>0.1</s:v>
       </s:c>
-      <s:c r="G10" s="60" t="n">
+      <s:c r="G10" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="H10" s="60" t="n">
+      <s:c r="H10" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="I10" s="60" t="n">
+      <s:c r="I10" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="J10" s="60" t="n">
+      <s:c r="J10" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="K10" s="60" t="n">
+      <s:c r="K10" s="61" t="n">
         <s:v>0.1</s:v>
       </s:c>
-      <s:c r="L10" s="60" t="n">
+      <s:c r="L10" s="61" t="n">
         <s:v>0.1</s:v>
       </s:c>
-      <s:c r="M10" s="60" t="n">
+      <s:c r="M10" s="61" t="n">
         <s:v>0.04</s:v>
       </s:c>
-      <s:c r="N10" s="60" t="n">
+      <s:c r="N10" s="61" t="n">
         <s:v>0.04</s:v>
       </s:c>
       <s:c r="O10" s="19">
@@ -3329,43 +3371,43 @@
           <s:t>შეფუთვა და ლოგისტიკა / Packaging &amp; logistics</s:t>
         </s:is>
       </s:c>
-      <s:c r="B11" s="54" t="n">
+      <s:c r="B11" s="55" t="n">
         <s:v>10000</s:v>
       </s:c>
-      <s:c r="C11" s="60" t="n">
+      <s:c r="C11" s="61" t="n">
         <s:v>0.12</s:v>
       </s:c>
-      <s:c r="D11" s="60" t="n">
+      <s:c r="D11" s="61" t="n">
         <s:v>0.14</s:v>
       </s:c>
-      <s:c r="E11" s="60" t="n">
+      <s:c r="E11" s="61" t="n">
         <s:v>0.14</s:v>
       </s:c>
-      <s:c r="F11" s="60" t="n">
+      <s:c r="F11" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="G11" s="60" t="n">
+      <s:c r="G11" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="H11" s="60" t="n">
+      <s:c r="H11" s="61" t="n">
         <s:v>0.07000000000000001</s:v>
       </s:c>
-      <s:c r="I11" s="60" t="n">
+      <s:c r="I11" s="61" t="n">
         <s:v>0.11</s:v>
       </s:c>
-      <s:c r="J11" s="60" t="n">
+      <s:c r="J11" s="61" t="n">
         <s:v>0.11</s:v>
       </s:c>
-      <s:c r="K11" s="60" t="n">
+      <s:c r="K11" s="61" t="n">
         <s:v>0.07000000000000001</s:v>
       </s:c>
-      <s:c r="L11" s="60" t="n">
+      <s:c r="L11" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="M11" s="60" t="n">
+      <s:c r="M11" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="N11" s="60" t="n">
+      <s:c r="N11" s="61" t="n">
         <s:v>0.16</s:v>
       </s:c>
       <s:c r="O11" s="19">
@@ -3379,43 +3421,43 @@
           <s:t>რემონტი და მოვლა / Maintenance &amp; repairs</s:t>
         </s:is>
       </s:c>
-      <s:c r="B12" s="54" t="n">
+      <s:c r="B12" s="55" t="n">
         <s:v>6000</s:v>
       </s:c>
-      <s:c r="C12" s="60" t="n">
+      <s:c r="C12" s="61" t="n">
         <s:v>0.02</s:v>
       </s:c>
-      <s:c r="D12" s="60" t="n">
+      <s:c r="D12" s="61" t="n">
         <s:v>0.02</s:v>
       </s:c>
-      <s:c r="E12" s="60" t="n">
+      <s:c r="E12" s="61" t="n">
         <s:v>0.02</s:v>
       </s:c>
-      <s:c r="F12" s="60" t="n">
+      <s:c r="F12" s="61" t="n">
         <s:v>0.04</s:v>
       </s:c>
-      <s:c r="G12" s="60" t="n">
+      <s:c r="G12" s="61" t="n">
         <s:v>0.2</s:v>
       </s:c>
-      <s:c r="H12" s="60" t="n">
+      <s:c r="H12" s="61" t="n">
         <s:v>0.1</s:v>
       </s:c>
-      <s:c r="I12" s="60" t="n">
+      <s:c r="I12" s="61" t="n">
         <s:v>0.02</s:v>
       </s:c>
-      <s:c r="J12" s="60" t="n">
+      <s:c r="J12" s="61" t="n">
         <s:v>0.02</s:v>
       </s:c>
-      <s:c r="K12" s="60" t="n">
+      <s:c r="K12" s="61" t="n">
         <s:v>0.03</s:v>
       </s:c>
-      <s:c r="L12" s="60" t="n">
+      <s:c r="L12" s="61" t="n">
         <s:v>0.25</s:v>
       </s:c>
-      <s:c r="M12" s="60" t="n">
+      <s:c r="M12" s="61" t="n">
         <s:v>0.25</s:v>
       </s:c>
-      <s:c r="N12" s="60" t="n">
+      <s:c r="N12" s="61" t="n">
         <s:v>0.03</s:v>
       </s:c>
       <s:c r="O12" s="19">
@@ -3429,43 +3471,43 @@
           <s:t>ადმინისტრაცია, დაზღვევა, ბუღალტერია / Admin, insurance, accounting</s:t>
         </s:is>
       </s:c>
-      <s:c r="B13" s="54" t="n">
+      <s:c r="B13" s="55" t="n">
         <s:v>6000</s:v>
       </s:c>
-      <s:c r="C13" s="60" t="n">
+      <s:c r="C13" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="D13" s="60" t="n">
+      <s:c r="D13" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="E13" s="60" t="n">
+      <s:c r="E13" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="F13" s="60" t="n">
+      <s:c r="F13" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="G13" s="60" t="n">
+      <s:c r="G13" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="H13" s="60" t="n">
+      <s:c r="H13" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="I13" s="60" t="n">
+      <s:c r="I13" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="J13" s="60" t="n">
+      <s:c r="J13" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="K13" s="60" t="n">
+      <s:c r="K13" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
-      <s:c r="L13" s="60" t="n">
+      <s:c r="L13" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="M13" s="60" t="n">
+      <s:c r="M13" s="61" t="n">
         <s:v>0.08</s:v>
       </s:c>
-      <s:c r="N13" s="60" t="n">
+      <s:c r="N13" s="61" t="n">
         <s:v>0.09</s:v>
       </s:c>
       <s:c r="O13" s="19">
@@ -3565,7 +3607,7 @@
       <s:c r="O17" s="11" t="n"/>
     </s:row>
     <s:row r="18">
-      <s:c r="A18" s="59" t="inlineStr">
+      <s:c r="A18" s="60" t="inlineStr">
         <s:is>
           <s:t>კატეგორია / Category</s:t>
         </s:is>
@@ -4309,18 +4351,18 @@
       </s:c>
     </s:row>
     <s:row r="5">
-      <s:c r="A5" s="61" t="n">
+      <s:c r="A5" s="62" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="B5" s="62">
+      <s:c r="B5" s="63">
         <s:f>EDATE(DATE(2026,6,17),A5)</s:f>
         <s:v>46220.0</s:v>
       </s:c>
-      <s:c r="C5" s="61">
+      <s:c r="C5" s="62">
         <s:f>INT((A5-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
-      <s:c r="D5" s="49">
+      <s:c r="D5" s="50">
         <s:f>Assumptions!$B$29</s:f>
         <s:v>625000.0</s:v>
       </s:c>
@@ -4352,7 +4394,7 @@
         <s:f>IF(A5&lt;=Assumptions!$B$32,0+G5,0)</s:f>
         <s:v>854.1666666666679</s:v>
       </s:c>
-      <s:c r="M5" s="61" t="n">
+      <s:c r="M5" s="62" t="n">
         <s:v>1</s:v>
       </s:c>
       <s:c r="N5" s="29">
@@ -4381,14 +4423,14 @@
       </s:c>
     </s:row>
     <s:row r="6">
-      <s:c r="A6" s="61" t="n">
+      <s:c r="A6" s="62" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="B6" s="62">
+      <s:c r="B6" s="63">
         <s:f>EDATE(DATE(2026,6,17),A6)</s:f>
         <s:v>46251.0</s:v>
       </s:c>
-      <s:c r="C6" s="61">
+      <s:c r="C6" s="62">
         <s:f>INT((A6-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -4424,7 +4466,7 @@
         <s:f>IF(A6&lt;=Assumptions!$B$32,K5+G6,0)</s:f>
         <s:v>1708.3333333333358</s:v>
       </s:c>
-      <s:c r="M6" s="61" t="n">
+      <s:c r="M6" s="62" t="n">
         <s:v>2</s:v>
       </s:c>
       <s:c r="N6" s="29">
@@ -4453,14 +4495,14 @@
       </s:c>
     </s:row>
     <s:row r="7">
-      <s:c r="A7" s="61" t="n">
+      <s:c r="A7" s="62" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="B7" s="62">
+      <s:c r="B7" s="63">
         <s:f>EDATE(DATE(2026,6,17),A7)</s:f>
         <s:v>46282.0</s:v>
       </s:c>
-      <s:c r="C7" s="61">
+      <s:c r="C7" s="62">
         <s:f>INT((A7-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -4496,7 +4538,7 @@
         <s:f>IF(A7&lt;=Assumptions!$B$32,K6+G7,0)</s:f>
         <s:v>2562.5000000000036</s:v>
       </s:c>
-      <s:c r="M7" s="61" t="n">
+      <s:c r="M7" s="62" t="n">
         <s:v>3</s:v>
       </s:c>
       <s:c r="N7" s="29">
@@ -4525,14 +4567,14 @@
       </s:c>
     </s:row>
     <s:row r="8">
-      <s:c r="A8" s="61" t="n">
+      <s:c r="A8" s="62" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="B8" s="62">
+      <s:c r="B8" s="63">
         <s:f>EDATE(DATE(2026,6,17),A8)</s:f>
         <s:v>46312.0</s:v>
       </s:c>
-      <s:c r="C8" s="61">
+      <s:c r="C8" s="62">
         <s:f>INT((A8-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -4568,7 +4610,7 @@
         <s:f>IF(A8&lt;=Assumptions!$B$32,K7+G8,0)</s:f>
         <s:v>3416.6666666666715</s:v>
       </s:c>
-      <s:c r="M8" s="61" t="n">
+      <s:c r="M8" s="62" t="n">
         <s:v>4</s:v>
       </s:c>
       <s:c r="N8" s="29">
@@ -4597,14 +4639,14 @@
       </s:c>
     </s:row>
     <s:row r="9">
-      <s:c r="A9" s="61" t="n">
+      <s:c r="A9" s="62" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="B9" s="62">
+      <s:c r="B9" s="63">
         <s:f>EDATE(DATE(2026,6,17),A9)</s:f>
         <s:v>46343.0</s:v>
       </s:c>
-      <s:c r="C9" s="61">
+      <s:c r="C9" s="62">
         <s:f>INT((A9-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -4640,7 +4682,7 @@
         <s:f>IF(A9&lt;=Assumptions!$B$32,K8+G9,0)</s:f>
         <s:v>4270.833333333339</s:v>
       </s:c>
-      <s:c r="M9" s="61" t="n">
+      <s:c r="M9" s="62" t="n">
         <s:v>5</s:v>
       </s:c>
       <s:c r="N9" s="29">
@@ -4669,14 +4711,14 @@
       </s:c>
     </s:row>
     <s:row r="10">
-      <s:c r="A10" s="61" t="n">
+      <s:c r="A10" s="62" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="B10" s="62">
+      <s:c r="B10" s="63">
         <s:f>EDATE(DATE(2026,6,17),A10)</s:f>
         <s:v>46373.0</s:v>
       </s:c>
-      <s:c r="C10" s="61">
+      <s:c r="C10" s="62">
         <s:f>INT((A10-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -4712,7 +4754,7 @@
         <s:f>IF(A10&lt;=Assumptions!$B$32,K9+G10,0)</s:f>
         <s:v>5125.000000000007</s:v>
       </s:c>
-      <s:c r="M10" s="61" t="n">
+      <s:c r="M10" s="62" t="n">
         <s:v>6</s:v>
       </s:c>
       <s:c r="N10" s="29">
@@ -4741,14 +4783,14 @@
       </s:c>
     </s:row>
     <s:row r="11">
-      <s:c r="A11" s="61" t="n">
+      <s:c r="A11" s="62" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="B11" s="62">
+      <s:c r="B11" s="63">
         <s:f>EDATE(DATE(2026,6,17),A11)</s:f>
         <s:v>46404.0</s:v>
       </s:c>
-      <s:c r="C11" s="61">
+      <s:c r="C11" s="62">
         <s:f>INT((A11-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -4784,7 +4826,7 @@
         <s:f>IF(A11&lt;=Assumptions!$B$32,K10+G11,0)</s:f>
         <s:v>5979.166666666675</s:v>
       </s:c>
-      <s:c r="M11" s="61" t="n">
+      <s:c r="M11" s="62" t="n">
         <s:v>7</s:v>
       </s:c>
       <s:c r="N11" s="29">
@@ -4813,14 +4855,14 @@
       </s:c>
     </s:row>
     <s:row r="12">
-      <s:c r="A12" s="61" t="n">
+      <s:c r="A12" s="62" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="B12" s="62">
+      <s:c r="B12" s="63">
         <s:f>EDATE(DATE(2026,6,17),A12)</s:f>
         <s:v>46435.0</s:v>
       </s:c>
-      <s:c r="C12" s="61">
+      <s:c r="C12" s="62">
         <s:f>INT((A12-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -4856,7 +4898,7 @@
         <s:f>IF(A12&lt;=Assumptions!$B$32,K11+G12,0)</s:f>
         <s:v>6833.333333333343</s:v>
       </s:c>
-      <s:c r="M12" s="61" t="n">
+      <s:c r="M12" s="62" t="n">
         <s:v>8</s:v>
       </s:c>
       <s:c r="N12" s="29">
@@ -4885,14 +4927,14 @@
       </s:c>
     </s:row>
     <s:row r="13">
-      <s:c r="A13" s="61" t="n">
+      <s:c r="A13" s="62" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="B13" s="62">
+      <s:c r="B13" s="63">
         <s:f>EDATE(DATE(2026,6,17),A13)</s:f>
         <s:v>46463.0</s:v>
       </s:c>
-      <s:c r="C13" s="61">
+      <s:c r="C13" s="62">
         <s:f>INT((A13-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -4928,7 +4970,7 @@
         <s:f>IF(A13&lt;=Assumptions!$B$32,K12+G13,0)</s:f>
         <s:v>7687.500000000011</s:v>
       </s:c>
-      <s:c r="M13" s="61" t="n">
+      <s:c r="M13" s="62" t="n">
         <s:v>9</s:v>
       </s:c>
       <s:c r="N13" s="29">
@@ -4957,14 +4999,14 @@
       </s:c>
     </s:row>
     <s:row r="14">
-      <s:c r="A14" s="61" t="n">
+      <s:c r="A14" s="62" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="B14" s="62">
+      <s:c r="B14" s="63">
         <s:f>EDATE(DATE(2026,6,17),A14)</s:f>
         <s:v>46494.0</s:v>
       </s:c>
-      <s:c r="C14" s="61">
+      <s:c r="C14" s="62">
         <s:f>INT((A14-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -5000,7 +5042,7 @@
         <s:f>IF(A14&lt;=Assumptions!$B$32,K13+G14,0)</s:f>
         <s:v>8541.666666666679</s:v>
       </s:c>
-      <s:c r="M14" s="61" t="n">
+      <s:c r="M14" s="62" t="n">
         <s:v>10</s:v>
       </s:c>
       <s:c r="N14" s="29">
@@ -5029,14 +5071,14 @@
       </s:c>
     </s:row>
     <s:row r="15">
-      <s:c r="A15" s="61" t="n">
+      <s:c r="A15" s="62" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="B15" s="62">
+      <s:c r="B15" s="63">
         <s:f>EDATE(DATE(2026,6,17),A15)</s:f>
         <s:v>46524.0</s:v>
       </s:c>
-      <s:c r="C15" s="61">
+      <s:c r="C15" s="62">
         <s:f>INT((A15-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -5100,14 +5142,14 @@
       <s:c r="S15" s="24" t="inlineStr"/>
     </s:row>
     <s:row r="16">
-      <s:c r="A16" s="61" t="n">
+      <s:c r="A16" s="62" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="B16" s="62">
+      <s:c r="B16" s="63">
         <s:f>EDATE(DATE(2026,6,17),A16)</s:f>
         <s:v>46555.0</s:v>
       </s:c>
-      <s:c r="C16" s="61">
+      <s:c r="C16" s="62">
         <s:f>INT((A16-1)/12)+1</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -5145,14 +5187,14 @@
       </s:c>
     </s:row>
     <s:row r="17">
-      <s:c r="A17" s="61" t="n">
+      <s:c r="A17" s="62" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="B17" s="62">
+      <s:c r="B17" s="63">
         <s:f>EDATE(DATE(2026,6,17),A17)</s:f>
         <s:v>46585.0</s:v>
       </s:c>
-      <s:c r="C17" s="61">
+      <s:c r="C17" s="62">
         <s:f>INT((A17-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5201,14 +5243,14 @@
       <s:c r="S17" s="11" t="n"/>
     </s:row>
     <s:row r="18">
-      <s:c r="A18" s="61" t="n">
+      <s:c r="A18" s="62" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="B18" s="62">
+      <s:c r="B18" s="63">
         <s:f>EDATE(DATE(2026,6,17),A18)</s:f>
         <s:v>46616.0</s:v>
       </s:c>
-      <s:c r="C18" s="61">
+      <s:c r="C18" s="62">
         <s:f>INT((A18-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5244,7 +5286,7 @@
         <s:f>IF(A18&lt;=Assumptions!$B$32,K17+G18,0)</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="M18" s="59" t="inlineStr">
+      <s:c r="M18" s="60" t="inlineStr">
         <s:is>
           <s:t>მაჩვენებელი / Item</s:t>
         </s:is>
@@ -5266,14 +5308,14 @@
       </s:c>
     </s:row>
     <s:row r="19">
-      <s:c r="A19" s="61" t="n">
+      <s:c r="A19" s="62" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="B19" s="62">
+      <s:c r="B19" s="63">
         <s:f>EDATE(DATE(2026,6,17),A19)</s:f>
         <s:v>46647.0</s:v>
       </s:c>
-      <s:c r="C19" s="61">
+      <s:c r="C19" s="62">
         <s:f>INT((A19-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5314,7 +5356,7 @@
           <s:t>სულ ძირი / Total principal</s:t>
         </s:is>
       </s:c>
-      <s:c r="P19" s="54" t="n">
+      <s:c r="P19" s="55" t="n">
         <s:v>625000</s:v>
       </s:c>
       <s:c r="Q19" s="29">
@@ -5327,14 +5369,14 @@
       </s:c>
     </s:row>
     <s:row r="20">
-      <s:c r="A20" s="61" t="n">
+      <s:c r="A20" s="62" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="B20" s="62">
+      <s:c r="B20" s="63">
         <s:f>EDATE(DATE(2026,6,17),A20)</s:f>
         <s:v>46677.0</s:v>
       </s:c>
-      <s:c r="C20" s="61">
+      <s:c r="C20" s="62">
         <s:f>INT((A20-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5375,7 +5417,7 @@
           <s:t>სულ პროცენტი / Total interest</s:t>
         </s:is>
       </s:c>
-      <s:c r="P20" s="54" t="n">
+      <s:c r="P20" s="55" t="n">
         <s:v>529681.25</s:v>
       </s:c>
       <s:c r="Q20" s="29">
@@ -5388,14 +5430,14 @@
       </s:c>
     </s:row>
     <s:row r="21">
-      <s:c r="A21" s="61" t="n">
+      <s:c r="A21" s="62" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="B21" s="62">
+      <s:c r="B21" s="63">
         <s:f>EDATE(DATE(2026,6,17),A21)</s:f>
         <s:v>46708.0</s:v>
       </s:c>
-      <s:c r="C21" s="61">
+      <s:c r="C21" s="62">
         <s:f>INT((A21-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5436,7 +5478,7 @@
           <s:t>სულ გადასახდელი / Total repayable</s:t>
         </s:is>
       </s:c>
-      <s:c r="P21" s="54" t="n">
+      <s:c r="P21" s="55" t="n">
         <s:v>1154681.25</s:v>
       </s:c>
       <s:c r="Q21" s="29">
@@ -5449,14 +5491,14 @@
       </s:c>
     </s:row>
     <s:row r="22">
-      <s:c r="A22" s="61" t="n">
+      <s:c r="A22" s="62" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="B22" s="62">
+      <s:c r="B22" s="63">
         <s:f>EDATE(DATE(2026,6,17),A22)</s:f>
         <s:v>46738.0</s:v>
       </s:c>
-      <s:c r="C22" s="61">
+      <s:c r="C22" s="62">
         <s:f>INT((A22-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5499,14 +5541,14 @@
       </s:c>
     </s:row>
     <s:row r="23">
-      <s:c r="A23" s="61" t="n">
+      <s:c r="A23" s="62" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="B23" s="62">
+      <s:c r="B23" s="63">
         <s:f>EDATE(DATE(2026,6,17),A23)</s:f>
         <s:v>46769.0</s:v>
       </s:c>
-      <s:c r="C23" s="61">
+      <s:c r="C23" s="62">
         <s:f>INT((A23-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5549,14 +5591,14 @@
       </s:c>
     </s:row>
     <s:row r="24">
-      <s:c r="A24" s="61" t="n">
+      <s:c r="A24" s="62" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="B24" s="62">
+      <s:c r="B24" s="63">
         <s:f>EDATE(DATE(2026,6,17),A24)</s:f>
         <s:v>46800.0</s:v>
       </s:c>
-      <s:c r="C24" s="61">
+      <s:c r="C24" s="62">
         <s:f>INT((A24-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5594,14 +5636,14 @@
       </s:c>
     </s:row>
     <s:row r="25">
-      <s:c r="A25" s="61" t="n">
+      <s:c r="A25" s="62" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="B25" s="62">
+      <s:c r="B25" s="63">
         <s:f>EDATE(DATE(2026,6,17),A25)</s:f>
         <s:v>46829.0</s:v>
       </s:c>
-      <s:c r="C25" s="61">
+      <s:c r="C25" s="62">
         <s:f>INT((A25-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5646,21 +5688,21 @@
         <s:f>H18+E18</s:f>
         <s:v>9766.072742502936</s:v>
       </s:c>
-      <s:c r="O25" s="42" t="inlineStr">
+      <s:c r="O25" s="43" t="inlineStr">
         <s:is>
           <s:t>ბანკის გრაფიკი / bank: 9,768.75</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="26">
-      <s:c r="A26" s="61" t="n">
+      <s:c r="A26" s="62" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="B26" s="62">
+      <s:c r="B26" s="63">
         <s:f>EDATE(DATE(2026,6,17),A26)</s:f>
         <s:v>46860.0</s:v>
       </s:c>
-      <s:c r="C26" s="61">
+      <s:c r="C26" s="62">
         <s:f>INT((A26-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5705,21 +5747,21 @@
         <s:f>H28+E28</s:f>
         <s:v>10018.248216575024</s:v>
       </s:c>
-      <s:c r="O26" s="42" t="inlineStr">
+      <s:c r="O26" s="43" t="inlineStr">
         <s:is>
           <s:t>ბანკის გრაფიკი / bank: 10,012.50</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="27">
-      <s:c r="A27" s="61" t="n">
+      <s:c r="A27" s="62" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="B27" s="62">
+      <s:c r="B27" s="63">
         <s:f>EDATE(DATE(2026,6,17),A27)</s:f>
         <s:v>46890.0</s:v>
       </s:c>
-      <s:c r="C27" s="61">
+      <s:c r="C27" s="62">
         <s:f>INT((A27-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5757,14 +5799,14 @@
       </s:c>
     </s:row>
     <s:row r="28">
-      <s:c r="A28" s="61" t="n">
+      <s:c r="A28" s="62" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="B28" s="62">
+      <s:c r="B28" s="63">
         <s:f>EDATE(DATE(2026,6,17),A28)</s:f>
         <s:v>46921.0</s:v>
       </s:c>
-      <s:c r="C28" s="61">
+      <s:c r="C28" s="62">
         <s:f>INT((A28-1)/12)+1</s:f>
         <s:v>2.0</s:v>
       </s:c>
@@ -5807,14 +5849,14 @@
       </s:c>
     </s:row>
     <s:row r="29">
-      <s:c r="A29" s="61" t="n">
+      <s:c r="A29" s="62" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="B29" s="62">
+      <s:c r="B29" s="63">
         <s:f>EDATE(DATE(2026,6,17),A29)</s:f>
         <s:v>46951.0</s:v>
       </s:c>
-      <s:c r="C29" s="61">
+      <s:c r="C29" s="62">
         <s:f>INT((A29-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -5852,14 +5894,14 @@
       </s:c>
     </s:row>
     <s:row r="30">
-      <s:c r="A30" s="61" t="n">
+      <s:c r="A30" s="62" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="B30" s="62">
+      <s:c r="B30" s="63">
         <s:f>EDATE(DATE(2026,6,17),A30)</s:f>
         <s:v>46982.0</s:v>
       </s:c>
-      <s:c r="C30" s="61">
+      <s:c r="C30" s="62">
         <s:f>INT((A30-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -5897,14 +5939,14 @@
       </s:c>
     </s:row>
     <s:row r="31">
-      <s:c r="A31" s="61" t="n">
+      <s:c r="A31" s="62" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="B31" s="62">
+      <s:c r="B31" s="63">
         <s:f>EDATE(DATE(2026,6,17),A31)</s:f>
         <s:v>47013.0</s:v>
       </s:c>
-      <s:c r="C31" s="61">
+      <s:c r="C31" s="62">
         <s:f>INT((A31-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -5942,14 +5984,14 @@
       </s:c>
     </s:row>
     <s:row r="32">
-      <s:c r="A32" s="61" t="n">
+      <s:c r="A32" s="62" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="B32" s="62">
+      <s:c r="B32" s="63">
         <s:f>EDATE(DATE(2026,6,17),A32)</s:f>
         <s:v>47043.0</s:v>
       </s:c>
-      <s:c r="C32" s="61">
+      <s:c r="C32" s="62">
         <s:f>INT((A32-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -5987,14 +6029,14 @@
       </s:c>
     </s:row>
     <s:row r="33">
-      <s:c r="A33" s="61" t="n">
+      <s:c r="A33" s="62" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="B33" s="62">
+      <s:c r="B33" s="63">
         <s:f>EDATE(DATE(2026,6,17),A33)</s:f>
         <s:v>47074.0</s:v>
       </s:c>
-      <s:c r="C33" s="61">
+      <s:c r="C33" s="62">
         <s:f>INT((A33-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -6032,14 +6074,14 @@
       </s:c>
     </s:row>
     <s:row r="34">
-      <s:c r="A34" s="61" t="n">
+      <s:c r="A34" s="62" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="B34" s="62">
+      <s:c r="B34" s="63">
         <s:f>EDATE(DATE(2026,6,17),A34)</s:f>
         <s:v>47104.0</s:v>
       </s:c>
-      <s:c r="C34" s="61">
+      <s:c r="C34" s="62">
         <s:f>INT((A34-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -6077,14 +6119,14 @@
       </s:c>
     </s:row>
     <s:row r="35">
-      <s:c r="A35" s="61" t="n">
+      <s:c r="A35" s="62" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="B35" s="62">
+      <s:c r="B35" s="63">
         <s:f>EDATE(DATE(2026,6,17),A35)</s:f>
         <s:v>47135.0</s:v>
       </s:c>
-      <s:c r="C35" s="61">
+      <s:c r="C35" s="62">
         <s:f>INT((A35-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -6122,14 +6164,14 @@
       </s:c>
     </s:row>
     <s:row r="36">
-      <s:c r="A36" s="61" t="n">
+      <s:c r="A36" s="62" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="B36" s="62">
+      <s:c r="B36" s="63">
         <s:f>EDATE(DATE(2026,6,17),A36)</s:f>
         <s:v>47166.0</s:v>
       </s:c>
-      <s:c r="C36" s="61">
+      <s:c r="C36" s="62">
         <s:f>INT((A36-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -6167,14 +6209,14 @@
       </s:c>
     </s:row>
     <s:row r="37">
-      <s:c r="A37" s="61" t="n">
+      <s:c r="A37" s="62" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="B37" s="62">
+      <s:c r="B37" s="63">
         <s:f>EDATE(DATE(2026,6,17),A37)</s:f>
         <s:v>47194.0</s:v>
       </s:c>
-      <s:c r="C37" s="61">
+      <s:c r="C37" s="62">
         <s:f>INT((A37-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -6212,14 +6254,14 @@
       </s:c>
     </s:row>
     <s:row r="38">
-      <s:c r="A38" s="61" t="n">
+      <s:c r="A38" s="62" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="B38" s="62">
+      <s:c r="B38" s="63">
         <s:f>EDATE(DATE(2026,6,17),A38)</s:f>
         <s:v>47225.0</s:v>
       </s:c>
-      <s:c r="C38" s="61">
+      <s:c r="C38" s="62">
         <s:f>INT((A38-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -6257,14 +6299,14 @@
       </s:c>
     </s:row>
     <s:row r="39">
-      <s:c r="A39" s="61" t="n">
+      <s:c r="A39" s="62" t="n">
         <s:v>35</s:v>
       </s:c>
-      <s:c r="B39" s="62">
+      <s:c r="B39" s="63">
         <s:f>EDATE(DATE(2026,6,17),A39)</s:f>
         <s:v>47255.0</s:v>
       </s:c>
-      <s:c r="C39" s="61">
+      <s:c r="C39" s="62">
         <s:f>INT((A39-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -6302,14 +6344,14 @@
       </s:c>
     </s:row>
     <s:row r="40">
-      <s:c r="A40" s="61" t="n">
+      <s:c r="A40" s="62" t="n">
         <s:v>36</s:v>
       </s:c>
-      <s:c r="B40" s="62">
+      <s:c r="B40" s="63">
         <s:f>EDATE(DATE(2026,6,17),A40)</s:f>
         <s:v>47286.0</s:v>
       </s:c>
-      <s:c r="C40" s="61">
+      <s:c r="C40" s="62">
         <s:f>INT((A40-1)/12)+1</s:f>
         <s:v>3.0</s:v>
       </s:c>
@@ -6347,14 +6389,14 @@
       </s:c>
     </s:row>
     <s:row r="41">
-      <s:c r="A41" s="61" t="n">
+      <s:c r="A41" s="62" t="n">
         <s:v>37</s:v>
       </s:c>
-      <s:c r="B41" s="62">
+      <s:c r="B41" s="63">
         <s:f>EDATE(DATE(2026,6,17),A41)</s:f>
         <s:v>47316.0</s:v>
       </s:c>
-      <s:c r="C41" s="61">
+      <s:c r="C41" s="62">
         <s:f>INT((A41-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6392,14 +6434,14 @@
       </s:c>
     </s:row>
     <s:row r="42">
-      <s:c r="A42" s="61" t="n">
+      <s:c r="A42" s="62" t="n">
         <s:v>38</s:v>
       </s:c>
-      <s:c r="B42" s="62">
+      <s:c r="B42" s="63">
         <s:f>EDATE(DATE(2026,6,17),A42)</s:f>
         <s:v>47347.0</s:v>
       </s:c>
-      <s:c r="C42" s="61">
+      <s:c r="C42" s="62">
         <s:f>INT((A42-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6437,14 +6479,14 @@
       </s:c>
     </s:row>
     <s:row r="43">
-      <s:c r="A43" s="61" t="n">
+      <s:c r="A43" s="62" t="n">
         <s:v>39</s:v>
       </s:c>
-      <s:c r="B43" s="62">
+      <s:c r="B43" s="63">
         <s:f>EDATE(DATE(2026,6,17),A43)</s:f>
         <s:v>47378.0</s:v>
       </s:c>
-      <s:c r="C43" s="61">
+      <s:c r="C43" s="62">
         <s:f>INT((A43-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6482,14 +6524,14 @@
       </s:c>
     </s:row>
     <s:row r="44">
-      <s:c r="A44" s="61" t="n">
+      <s:c r="A44" s="62" t="n">
         <s:v>40</s:v>
       </s:c>
-      <s:c r="B44" s="62">
+      <s:c r="B44" s="63">
         <s:f>EDATE(DATE(2026,6,17),A44)</s:f>
         <s:v>47408.0</s:v>
       </s:c>
-      <s:c r="C44" s="61">
+      <s:c r="C44" s="62">
         <s:f>INT((A44-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6527,14 +6569,14 @@
       </s:c>
     </s:row>
     <s:row r="45">
-      <s:c r="A45" s="61" t="n">
+      <s:c r="A45" s="62" t="n">
         <s:v>41</s:v>
       </s:c>
-      <s:c r="B45" s="62">
+      <s:c r="B45" s="63">
         <s:f>EDATE(DATE(2026,6,17),A45)</s:f>
         <s:v>47439.0</s:v>
       </s:c>
-      <s:c r="C45" s="61">
+      <s:c r="C45" s="62">
         <s:f>INT((A45-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6572,14 +6614,14 @@
       </s:c>
     </s:row>
     <s:row r="46">
-      <s:c r="A46" s="61" t="n">
+      <s:c r="A46" s="62" t="n">
         <s:v>42</s:v>
       </s:c>
-      <s:c r="B46" s="62">
+      <s:c r="B46" s="63">
         <s:f>EDATE(DATE(2026,6,17),A46)</s:f>
         <s:v>47469.0</s:v>
       </s:c>
-      <s:c r="C46" s="61">
+      <s:c r="C46" s="62">
         <s:f>INT((A46-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6617,14 +6659,14 @@
       </s:c>
     </s:row>
     <s:row r="47">
-      <s:c r="A47" s="61" t="n">
+      <s:c r="A47" s="62" t="n">
         <s:v>43</s:v>
       </s:c>
-      <s:c r="B47" s="62">
+      <s:c r="B47" s="63">
         <s:f>EDATE(DATE(2026,6,17),A47)</s:f>
         <s:v>47500.0</s:v>
       </s:c>
-      <s:c r="C47" s="61">
+      <s:c r="C47" s="62">
         <s:f>INT((A47-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6662,14 +6704,14 @@
       </s:c>
     </s:row>
     <s:row r="48">
-      <s:c r="A48" s="61" t="n">
+      <s:c r="A48" s="62" t="n">
         <s:v>44</s:v>
       </s:c>
-      <s:c r="B48" s="62">
+      <s:c r="B48" s="63">
         <s:f>EDATE(DATE(2026,6,17),A48)</s:f>
         <s:v>47531.0</s:v>
       </s:c>
-      <s:c r="C48" s="61">
+      <s:c r="C48" s="62">
         <s:f>INT((A48-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6707,14 +6749,14 @@
       </s:c>
     </s:row>
     <s:row r="49">
-      <s:c r="A49" s="61" t="n">
+      <s:c r="A49" s="62" t="n">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="B49" s="62">
+      <s:c r="B49" s="63">
         <s:f>EDATE(DATE(2026,6,17),A49)</s:f>
         <s:v>47559.0</s:v>
       </s:c>
-      <s:c r="C49" s="61">
+      <s:c r="C49" s="62">
         <s:f>INT((A49-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6752,14 +6794,14 @@
       </s:c>
     </s:row>
     <s:row r="50">
-      <s:c r="A50" s="61" t="n">
+      <s:c r="A50" s="62" t="n">
         <s:v>46</s:v>
       </s:c>
-      <s:c r="B50" s="62">
+      <s:c r="B50" s="63">
         <s:f>EDATE(DATE(2026,6,17),A50)</s:f>
         <s:v>47590.0</s:v>
       </s:c>
-      <s:c r="C50" s="61">
+      <s:c r="C50" s="62">
         <s:f>INT((A50-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6797,14 +6839,14 @@
       </s:c>
     </s:row>
     <s:row r="51">
-      <s:c r="A51" s="61" t="n">
+      <s:c r="A51" s="62" t="n">
         <s:v>47</s:v>
       </s:c>
-      <s:c r="B51" s="62">
+      <s:c r="B51" s="63">
         <s:f>EDATE(DATE(2026,6,17),A51)</s:f>
         <s:v>47620.0</s:v>
       </s:c>
-      <s:c r="C51" s="61">
+      <s:c r="C51" s="62">
         <s:f>INT((A51-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6842,14 +6884,14 @@
       </s:c>
     </s:row>
     <s:row r="52">
-      <s:c r="A52" s="61" t="n">
+      <s:c r="A52" s="62" t="n">
         <s:v>48</s:v>
       </s:c>
-      <s:c r="B52" s="62">
+      <s:c r="B52" s="63">
         <s:f>EDATE(DATE(2026,6,17),A52)</s:f>
         <s:v>47651.0</s:v>
       </s:c>
-      <s:c r="C52" s="61">
+      <s:c r="C52" s="62">
         <s:f>INT((A52-1)/12)+1</s:f>
         <s:v>4.0</s:v>
       </s:c>
@@ -6887,14 +6929,14 @@
       </s:c>
     </s:row>
     <s:row r="53">
-      <s:c r="A53" s="61" t="n">
+      <s:c r="A53" s="62" t="n">
         <s:v>49</s:v>
       </s:c>
-      <s:c r="B53" s="62">
+      <s:c r="B53" s="63">
         <s:f>EDATE(DATE(2026,6,17),A53)</s:f>
         <s:v>47681.0</s:v>
       </s:c>
-      <s:c r="C53" s="61">
+      <s:c r="C53" s="62">
         <s:f>INT((A53-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -6932,14 +6974,14 @@
       </s:c>
     </s:row>
     <s:row r="54">
-      <s:c r="A54" s="61" t="n">
+      <s:c r="A54" s="62" t="n">
         <s:v>50</s:v>
       </s:c>
-      <s:c r="B54" s="62">
+      <s:c r="B54" s="63">
         <s:f>EDATE(DATE(2026,6,17),A54)</s:f>
         <s:v>47712.0</s:v>
       </s:c>
-      <s:c r="C54" s="61">
+      <s:c r="C54" s="62">
         <s:f>INT((A54-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -6977,14 +7019,14 @@
       </s:c>
     </s:row>
     <s:row r="55">
-      <s:c r="A55" s="61" t="n">
+      <s:c r="A55" s="62" t="n">
         <s:v>51</s:v>
       </s:c>
-      <s:c r="B55" s="62">
+      <s:c r="B55" s="63">
         <s:f>EDATE(DATE(2026,6,17),A55)</s:f>
         <s:v>47743.0</s:v>
       </s:c>
-      <s:c r="C55" s="61">
+      <s:c r="C55" s="62">
         <s:f>INT((A55-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7022,14 +7064,14 @@
       </s:c>
     </s:row>
     <s:row r="56">
-      <s:c r="A56" s="61" t="n">
+      <s:c r="A56" s="62" t="n">
         <s:v>52</s:v>
       </s:c>
-      <s:c r="B56" s="62">
+      <s:c r="B56" s="63">
         <s:f>EDATE(DATE(2026,6,17),A56)</s:f>
         <s:v>47773.0</s:v>
       </s:c>
-      <s:c r="C56" s="61">
+      <s:c r="C56" s="62">
         <s:f>INT((A56-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7067,14 +7109,14 @@
       </s:c>
     </s:row>
     <s:row r="57">
-      <s:c r="A57" s="61" t="n">
+      <s:c r="A57" s="62" t="n">
         <s:v>53</s:v>
       </s:c>
-      <s:c r="B57" s="62">
+      <s:c r="B57" s="63">
         <s:f>EDATE(DATE(2026,6,17),A57)</s:f>
         <s:v>47804.0</s:v>
       </s:c>
-      <s:c r="C57" s="61">
+      <s:c r="C57" s="62">
         <s:f>INT((A57-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7112,14 +7154,14 @@
       </s:c>
     </s:row>
     <s:row r="58">
-      <s:c r="A58" s="61" t="n">
+      <s:c r="A58" s="62" t="n">
         <s:v>54</s:v>
       </s:c>
-      <s:c r="B58" s="62">
+      <s:c r="B58" s="63">
         <s:f>EDATE(DATE(2026,6,17),A58)</s:f>
         <s:v>47834.0</s:v>
       </s:c>
-      <s:c r="C58" s="61">
+      <s:c r="C58" s="62">
         <s:f>INT((A58-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7157,14 +7199,14 @@
       </s:c>
     </s:row>
     <s:row r="59">
-      <s:c r="A59" s="61" t="n">
+      <s:c r="A59" s="62" t="n">
         <s:v>55</s:v>
       </s:c>
-      <s:c r="B59" s="62">
+      <s:c r="B59" s="63">
         <s:f>EDATE(DATE(2026,6,17),A59)</s:f>
         <s:v>47865.0</s:v>
       </s:c>
-      <s:c r="C59" s="61">
+      <s:c r="C59" s="62">
         <s:f>INT((A59-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7202,14 +7244,14 @@
       </s:c>
     </s:row>
     <s:row r="60">
-      <s:c r="A60" s="61" t="n">
+      <s:c r="A60" s="62" t="n">
         <s:v>56</s:v>
       </s:c>
-      <s:c r="B60" s="62">
+      <s:c r="B60" s="63">
         <s:f>EDATE(DATE(2026,6,17),A60)</s:f>
         <s:v>47896.0</s:v>
       </s:c>
-      <s:c r="C60" s="61">
+      <s:c r="C60" s="62">
         <s:f>INT((A60-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7247,14 +7289,14 @@
       </s:c>
     </s:row>
     <s:row r="61">
-      <s:c r="A61" s="61" t="n">
+      <s:c r="A61" s="62" t="n">
         <s:v>57</s:v>
       </s:c>
-      <s:c r="B61" s="62">
+      <s:c r="B61" s="63">
         <s:f>EDATE(DATE(2026,6,17),A61)</s:f>
         <s:v>47924.0</s:v>
       </s:c>
-      <s:c r="C61" s="61">
+      <s:c r="C61" s="62">
         <s:f>INT((A61-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7292,14 +7334,14 @@
       </s:c>
     </s:row>
     <s:row r="62">
-      <s:c r="A62" s="61" t="n">
+      <s:c r="A62" s="62" t="n">
         <s:v>58</s:v>
       </s:c>
-      <s:c r="B62" s="62">
+      <s:c r="B62" s="63">
         <s:f>EDATE(DATE(2026,6,17),A62)</s:f>
         <s:v>47955.0</s:v>
       </s:c>
-      <s:c r="C62" s="61">
+      <s:c r="C62" s="62">
         <s:f>INT((A62-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7337,14 +7379,14 @@
       </s:c>
     </s:row>
     <s:row r="63">
-      <s:c r="A63" s="61" t="n">
+      <s:c r="A63" s="62" t="n">
         <s:v>59</s:v>
       </s:c>
-      <s:c r="B63" s="62">
+      <s:c r="B63" s="63">
         <s:f>EDATE(DATE(2026,6,17),A63)</s:f>
         <s:v>47985.0</s:v>
       </s:c>
-      <s:c r="C63" s="61">
+      <s:c r="C63" s="62">
         <s:f>INT((A63-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7382,14 +7424,14 @@
       </s:c>
     </s:row>
     <s:row r="64">
-      <s:c r="A64" s="61" t="n">
+      <s:c r="A64" s="62" t="n">
         <s:v>60</s:v>
       </s:c>
-      <s:c r="B64" s="62">
+      <s:c r="B64" s="63">
         <s:f>EDATE(DATE(2026,6,17),A64)</s:f>
         <s:v>48016.0</s:v>
       </s:c>
-      <s:c r="C64" s="61">
+      <s:c r="C64" s="62">
         <s:f>INT((A64-1)/12)+1</s:f>
         <s:v>5.0</s:v>
       </s:c>
@@ -7427,14 +7469,14 @@
       </s:c>
     </s:row>
     <s:row r="65">
-      <s:c r="A65" s="61" t="n">
+      <s:c r="A65" s="62" t="n">
         <s:v>61</s:v>
       </s:c>
-      <s:c r="B65" s="62">
+      <s:c r="B65" s="63">
         <s:f>EDATE(DATE(2026,6,17),A65)</s:f>
         <s:v>48046.0</s:v>
       </s:c>
-      <s:c r="C65" s="61">
+      <s:c r="C65" s="62">
         <s:f>INT((A65-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7472,14 +7514,14 @@
       </s:c>
     </s:row>
     <s:row r="66">
-      <s:c r="A66" s="61" t="n">
+      <s:c r="A66" s="62" t="n">
         <s:v>62</s:v>
       </s:c>
-      <s:c r="B66" s="62">
+      <s:c r="B66" s="63">
         <s:f>EDATE(DATE(2026,6,17),A66)</s:f>
         <s:v>48077.0</s:v>
       </s:c>
-      <s:c r="C66" s="61">
+      <s:c r="C66" s="62">
         <s:f>INT((A66-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7517,14 +7559,14 @@
       </s:c>
     </s:row>
     <s:row r="67">
-      <s:c r="A67" s="61" t="n">
+      <s:c r="A67" s="62" t="n">
         <s:v>63</s:v>
       </s:c>
-      <s:c r="B67" s="62">
+      <s:c r="B67" s="63">
         <s:f>EDATE(DATE(2026,6,17),A67)</s:f>
         <s:v>48108.0</s:v>
       </s:c>
-      <s:c r="C67" s="61">
+      <s:c r="C67" s="62">
         <s:f>INT((A67-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7562,14 +7604,14 @@
       </s:c>
     </s:row>
     <s:row r="68">
-      <s:c r="A68" s="61" t="n">
+      <s:c r="A68" s="62" t="n">
         <s:v>64</s:v>
       </s:c>
-      <s:c r="B68" s="62">
+      <s:c r="B68" s="63">
         <s:f>EDATE(DATE(2026,6,17),A68)</s:f>
         <s:v>48138.0</s:v>
       </s:c>
-      <s:c r="C68" s="61">
+      <s:c r="C68" s="62">
         <s:f>INT((A68-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7607,14 +7649,14 @@
       </s:c>
     </s:row>
     <s:row r="69">
-      <s:c r="A69" s="61" t="n">
+      <s:c r="A69" s="62" t="n">
         <s:v>65</s:v>
       </s:c>
-      <s:c r="B69" s="62">
+      <s:c r="B69" s="63">
         <s:f>EDATE(DATE(2026,6,17),A69)</s:f>
         <s:v>48169.0</s:v>
       </s:c>
-      <s:c r="C69" s="61">
+      <s:c r="C69" s="62">
         <s:f>INT((A69-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7652,14 +7694,14 @@
       </s:c>
     </s:row>
     <s:row r="70">
-      <s:c r="A70" s="61" t="n">
+      <s:c r="A70" s="62" t="n">
         <s:v>66</s:v>
       </s:c>
-      <s:c r="B70" s="62">
+      <s:c r="B70" s="63">
         <s:f>EDATE(DATE(2026,6,17),A70)</s:f>
         <s:v>48199.0</s:v>
       </s:c>
-      <s:c r="C70" s="61">
+      <s:c r="C70" s="62">
         <s:f>INT((A70-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7697,14 +7739,14 @@
       </s:c>
     </s:row>
     <s:row r="71">
-      <s:c r="A71" s="61" t="n">
+      <s:c r="A71" s="62" t="n">
         <s:v>67</s:v>
       </s:c>
-      <s:c r="B71" s="62">
+      <s:c r="B71" s="63">
         <s:f>EDATE(DATE(2026,6,17),A71)</s:f>
         <s:v>48230.0</s:v>
       </s:c>
-      <s:c r="C71" s="61">
+      <s:c r="C71" s="62">
         <s:f>INT((A71-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7742,14 +7784,14 @@
       </s:c>
     </s:row>
     <s:row r="72">
-      <s:c r="A72" s="61" t="n">
+      <s:c r="A72" s="62" t="n">
         <s:v>68</s:v>
       </s:c>
-      <s:c r="B72" s="62">
+      <s:c r="B72" s="63">
         <s:f>EDATE(DATE(2026,6,17),A72)</s:f>
         <s:v>48261.0</s:v>
       </s:c>
-      <s:c r="C72" s="61">
+      <s:c r="C72" s="62">
         <s:f>INT((A72-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7787,14 +7829,14 @@
       </s:c>
     </s:row>
     <s:row r="73">
-      <s:c r="A73" s="61" t="n">
+      <s:c r="A73" s="62" t="n">
         <s:v>69</s:v>
       </s:c>
-      <s:c r="B73" s="62">
+      <s:c r="B73" s="63">
         <s:f>EDATE(DATE(2026,6,17),A73)</s:f>
         <s:v>48290.0</s:v>
       </s:c>
-      <s:c r="C73" s="61">
+      <s:c r="C73" s="62">
         <s:f>INT((A73-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7832,14 +7874,14 @@
       </s:c>
     </s:row>
     <s:row r="74">
-      <s:c r="A74" s="61" t="n">
+      <s:c r="A74" s="62" t="n">
         <s:v>70</s:v>
       </s:c>
-      <s:c r="B74" s="62">
+      <s:c r="B74" s="63">
         <s:f>EDATE(DATE(2026,6,17),A74)</s:f>
         <s:v>48321.0</s:v>
       </s:c>
-      <s:c r="C74" s="61">
+      <s:c r="C74" s="62">
         <s:f>INT((A74-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7877,14 +7919,14 @@
       </s:c>
     </s:row>
     <s:row r="75">
-      <s:c r="A75" s="61" t="n">
+      <s:c r="A75" s="62" t="n">
         <s:v>71</s:v>
       </s:c>
-      <s:c r="B75" s="62">
+      <s:c r="B75" s="63">
         <s:f>EDATE(DATE(2026,6,17),A75)</s:f>
         <s:v>48351.0</s:v>
       </s:c>
-      <s:c r="C75" s="61">
+      <s:c r="C75" s="62">
         <s:f>INT((A75-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7922,14 +7964,14 @@
       </s:c>
     </s:row>
     <s:row r="76">
-      <s:c r="A76" s="61" t="n">
+      <s:c r="A76" s="62" t="n">
         <s:v>72</s:v>
       </s:c>
-      <s:c r="B76" s="62">
+      <s:c r="B76" s="63">
         <s:f>EDATE(DATE(2026,6,17),A76)</s:f>
         <s:v>48382.0</s:v>
       </s:c>
-      <s:c r="C76" s="61">
+      <s:c r="C76" s="62">
         <s:f>INT((A76-1)/12)+1</s:f>
         <s:v>6.0</s:v>
       </s:c>
@@ -7967,14 +8009,14 @@
       </s:c>
     </s:row>
     <s:row r="77">
-      <s:c r="A77" s="61" t="n">
+      <s:c r="A77" s="62" t="n">
         <s:v>73</s:v>
       </s:c>
-      <s:c r="B77" s="62">
+      <s:c r="B77" s="63">
         <s:f>EDATE(DATE(2026,6,17),A77)</s:f>
         <s:v>48412.0</s:v>
       </s:c>
-      <s:c r="C77" s="61">
+      <s:c r="C77" s="62">
         <s:f>INT((A77-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8012,14 +8054,14 @@
       </s:c>
     </s:row>
     <s:row r="78">
-      <s:c r="A78" s="61" t="n">
+      <s:c r="A78" s="62" t="n">
         <s:v>74</s:v>
       </s:c>
-      <s:c r="B78" s="62">
+      <s:c r="B78" s="63">
         <s:f>EDATE(DATE(2026,6,17),A78)</s:f>
         <s:v>48443.0</s:v>
       </s:c>
-      <s:c r="C78" s="61">
+      <s:c r="C78" s="62">
         <s:f>INT((A78-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8057,14 +8099,14 @@
       </s:c>
     </s:row>
     <s:row r="79">
-      <s:c r="A79" s="61" t="n">
+      <s:c r="A79" s="62" t="n">
         <s:v>75</s:v>
       </s:c>
-      <s:c r="B79" s="62">
+      <s:c r="B79" s="63">
         <s:f>EDATE(DATE(2026,6,17),A79)</s:f>
         <s:v>48474.0</s:v>
       </s:c>
-      <s:c r="C79" s="61">
+      <s:c r="C79" s="62">
         <s:f>INT((A79-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8102,14 +8144,14 @@
       </s:c>
     </s:row>
     <s:row r="80">
-      <s:c r="A80" s="61" t="n">
+      <s:c r="A80" s="62" t="n">
         <s:v>76</s:v>
       </s:c>
-      <s:c r="B80" s="62">
+      <s:c r="B80" s="63">
         <s:f>EDATE(DATE(2026,6,17),A80)</s:f>
         <s:v>48504.0</s:v>
       </s:c>
-      <s:c r="C80" s="61">
+      <s:c r="C80" s="62">
         <s:f>INT((A80-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8147,14 +8189,14 @@
       </s:c>
     </s:row>
     <s:row r="81">
-      <s:c r="A81" s="61" t="n">
+      <s:c r="A81" s="62" t="n">
         <s:v>77</s:v>
       </s:c>
-      <s:c r="B81" s="62">
+      <s:c r="B81" s="63">
         <s:f>EDATE(DATE(2026,6,17),A81)</s:f>
         <s:v>48535.0</s:v>
       </s:c>
-      <s:c r="C81" s="61">
+      <s:c r="C81" s="62">
         <s:f>INT((A81-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8192,14 +8234,14 @@
       </s:c>
     </s:row>
     <s:row r="82">
-      <s:c r="A82" s="61" t="n">
+      <s:c r="A82" s="62" t="n">
         <s:v>78</s:v>
       </s:c>
-      <s:c r="B82" s="62">
+      <s:c r="B82" s="63">
         <s:f>EDATE(DATE(2026,6,17),A82)</s:f>
         <s:v>48565.0</s:v>
       </s:c>
-      <s:c r="C82" s="61">
+      <s:c r="C82" s="62">
         <s:f>INT((A82-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8237,14 +8279,14 @@
       </s:c>
     </s:row>
     <s:row r="83">
-      <s:c r="A83" s="61" t="n">
+      <s:c r="A83" s="62" t="n">
         <s:v>79</s:v>
       </s:c>
-      <s:c r="B83" s="62">
+      <s:c r="B83" s="63">
         <s:f>EDATE(DATE(2026,6,17),A83)</s:f>
         <s:v>48596.0</s:v>
       </s:c>
-      <s:c r="C83" s="61">
+      <s:c r="C83" s="62">
         <s:f>INT((A83-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8282,14 +8324,14 @@
       </s:c>
     </s:row>
     <s:row r="84">
-      <s:c r="A84" s="61" t="n">
+      <s:c r="A84" s="62" t="n">
         <s:v>80</s:v>
       </s:c>
-      <s:c r="B84" s="62">
+      <s:c r="B84" s="63">
         <s:f>EDATE(DATE(2026,6,17),A84)</s:f>
         <s:v>48627.0</s:v>
       </s:c>
-      <s:c r="C84" s="61">
+      <s:c r="C84" s="62">
         <s:f>INT((A84-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8327,14 +8369,14 @@
       </s:c>
     </s:row>
     <s:row r="85">
-      <s:c r="A85" s="61" t="n">
+      <s:c r="A85" s="62" t="n">
         <s:v>81</s:v>
       </s:c>
-      <s:c r="B85" s="62">
+      <s:c r="B85" s="63">
         <s:f>EDATE(DATE(2026,6,17),A85)</s:f>
         <s:v>48655.0</s:v>
       </s:c>
-      <s:c r="C85" s="61">
+      <s:c r="C85" s="62">
         <s:f>INT((A85-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8372,14 +8414,14 @@
       </s:c>
     </s:row>
     <s:row r="86">
-      <s:c r="A86" s="61" t="n">
+      <s:c r="A86" s="62" t="n">
         <s:v>82</s:v>
       </s:c>
-      <s:c r="B86" s="62">
+      <s:c r="B86" s="63">
         <s:f>EDATE(DATE(2026,6,17),A86)</s:f>
         <s:v>48686.0</s:v>
       </s:c>
-      <s:c r="C86" s="61">
+      <s:c r="C86" s="62">
         <s:f>INT((A86-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8417,14 +8459,14 @@
       </s:c>
     </s:row>
     <s:row r="87">
-      <s:c r="A87" s="61" t="n">
+      <s:c r="A87" s="62" t="n">
         <s:v>83</s:v>
       </s:c>
-      <s:c r="B87" s="62">
+      <s:c r="B87" s="63">
         <s:f>EDATE(DATE(2026,6,17),A87)</s:f>
         <s:v>48716.0</s:v>
       </s:c>
-      <s:c r="C87" s="61">
+      <s:c r="C87" s="62">
         <s:f>INT((A87-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8462,14 +8504,14 @@
       </s:c>
     </s:row>
     <s:row r="88">
-      <s:c r="A88" s="61" t="n">
+      <s:c r="A88" s="62" t="n">
         <s:v>84</s:v>
       </s:c>
-      <s:c r="B88" s="62">
+      <s:c r="B88" s="63">
         <s:f>EDATE(DATE(2026,6,17),A88)</s:f>
         <s:v>48747.0</s:v>
       </s:c>
-      <s:c r="C88" s="61">
+      <s:c r="C88" s="62">
         <s:f>INT((A88-1)/12)+1</s:f>
         <s:v>7.0</s:v>
       </s:c>
@@ -8507,14 +8549,14 @@
       </s:c>
     </s:row>
     <s:row r="89">
-      <s:c r="A89" s="61" t="n">
+      <s:c r="A89" s="62" t="n">
         <s:v>85</s:v>
       </s:c>
-      <s:c r="B89" s="62">
+      <s:c r="B89" s="63">
         <s:f>EDATE(DATE(2026,6,17),A89)</s:f>
         <s:v>48777.0</s:v>
       </s:c>
-      <s:c r="C89" s="61">
+      <s:c r="C89" s="62">
         <s:f>INT((A89-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8552,14 +8594,14 @@
       </s:c>
     </s:row>
     <s:row r="90">
-      <s:c r="A90" s="61" t="n">
+      <s:c r="A90" s="62" t="n">
         <s:v>86</s:v>
       </s:c>
-      <s:c r="B90" s="62">
+      <s:c r="B90" s="63">
         <s:f>EDATE(DATE(2026,6,17),A90)</s:f>
         <s:v>48808.0</s:v>
       </s:c>
-      <s:c r="C90" s="61">
+      <s:c r="C90" s="62">
         <s:f>INT((A90-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8597,14 +8639,14 @@
       </s:c>
     </s:row>
     <s:row r="91">
-      <s:c r="A91" s="61" t="n">
+      <s:c r="A91" s="62" t="n">
         <s:v>87</s:v>
       </s:c>
-      <s:c r="B91" s="62">
+      <s:c r="B91" s="63">
         <s:f>EDATE(DATE(2026,6,17),A91)</s:f>
         <s:v>48839.0</s:v>
       </s:c>
-      <s:c r="C91" s="61">
+      <s:c r="C91" s="62">
         <s:f>INT((A91-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8642,14 +8684,14 @@
       </s:c>
     </s:row>
     <s:row r="92">
-      <s:c r="A92" s="61" t="n">
+      <s:c r="A92" s="62" t="n">
         <s:v>88</s:v>
       </s:c>
-      <s:c r="B92" s="62">
+      <s:c r="B92" s="63">
         <s:f>EDATE(DATE(2026,6,17),A92)</s:f>
         <s:v>48869.0</s:v>
       </s:c>
-      <s:c r="C92" s="61">
+      <s:c r="C92" s="62">
         <s:f>INT((A92-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8687,14 +8729,14 @@
       </s:c>
     </s:row>
     <s:row r="93">
-      <s:c r="A93" s="61" t="n">
+      <s:c r="A93" s="62" t="n">
         <s:v>89</s:v>
       </s:c>
-      <s:c r="B93" s="62">
+      <s:c r="B93" s="63">
         <s:f>EDATE(DATE(2026,6,17),A93)</s:f>
         <s:v>48900.0</s:v>
       </s:c>
-      <s:c r="C93" s="61">
+      <s:c r="C93" s="62">
         <s:f>INT((A93-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8732,14 +8774,14 @@
       </s:c>
     </s:row>
     <s:row r="94">
-      <s:c r="A94" s="61" t="n">
+      <s:c r="A94" s="62" t="n">
         <s:v>90</s:v>
       </s:c>
-      <s:c r="B94" s="62">
+      <s:c r="B94" s="63">
         <s:f>EDATE(DATE(2026,6,17),A94)</s:f>
         <s:v>48930.0</s:v>
       </s:c>
-      <s:c r="C94" s="61">
+      <s:c r="C94" s="62">
         <s:f>INT((A94-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8777,14 +8819,14 @@
       </s:c>
     </s:row>
     <s:row r="95">
-      <s:c r="A95" s="61" t="n">
+      <s:c r="A95" s="62" t="n">
         <s:v>91</s:v>
       </s:c>
-      <s:c r="B95" s="62">
+      <s:c r="B95" s="63">
         <s:f>EDATE(DATE(2026,6,17),A95)</s:f>
         <s:v>48961.0</s:v>
       </s:c>
-      <s:c r="C95" s="61">
+      <s:c r="C95" s="62">
         <s:f>INT((A95-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8822,14 +8864,14 @@
       </s:c>
     </s:row>
     <s:row r="96">
-      <s:c r="A96" s="61" t="n">
+      <s:c r="A96" s="62" t="n">
         <s:v>92</s:v>
       </s:c>
-      <s:c r="B96" s="62">
+      <s:c r="B96" s="63">
         <s:f>EDATE(DATE(2026,6,17),A96)</s:f>
         <s:v>48992.0</s:v>
       </s:c>
-      <s:c r="C96" s="61">
+      <s:c r="C96" s="62">
         <s:f>INT((A96-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8867,14 +8909,14 @@
       </s:c>
     </s:row>
     <s:row r="97">
-      <s:c r="A97" s="61" t="n">
+      <s:c r="A97" s="62" t="n">
         <s:v>93</s:v>
       </s:c>
-      <s:c r="B97" s="62">
+      <s:c r="B97" s="63">
         <s:f>EDATE(DATE(2026,6,17),A97)</s:f>
         <s:v>49020.0</s:v>
       </s:c>
-      <s:c r="C97" s="61">
+      <s:c r="C97" s="62">
         <s:f>INT((A97-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8912,14 +8954,14 @@
       </s:c>
     </s:row>
     <s:row r="98">
-      <s:c r="A98" s="61" t="n">
+      <s:c r="A98" s="62" t="n">
         <s:v>94</s:v>
       </s:c>
-      <s:c r="B98" s="62">
+      <s:c r="B98" s="63">
         <s:f>EDATE(DATE(2026,6,17),A98)</s:f>
         <s:v>49051.0</s:v>
       </s:c>
-      <s:c r="C98" s="61">
+      <s:c r="C98" s="62">
         <s:f>INT((A98-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -8957,14 +8999,14 @@
       </s:c>
     </s:row>
     <s:row r="99">
-      <s:c r="A99" s="61" t="n">
+      <s:c r="A99" s="62" t="n">
         <s:v>95</s:v>
       </s:c>
-      <s:c r="B99" s="62">
+      <s:c r="B99" s="63">
         <s:f>EDATE(DATE(2026,6,17),A99)</s:f>
         <s:v>49081.0</s:v>
       </s:c>
-      <s:c r="C99" s="61">
+      <s:c r="C99" s="62">
         <s:f>INT((A99-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -9002,14 +9044,14 @@
       </s:c>
     </s:row>
     <s:row r="100">
-      <s:c r="A100" s="61" t="n">
+      <s:c r="A100" s="62" t="n">
         <s:v>96</s:v>
       </s:c>
-      <s:c r="B100" s="62">
+      <s:c r="B100" s="63">
         <s:f>EDATE(DATE(2026,6,17),A100)</s:f>
         <s:v>49112.0</s:v>
       </s:c>
-      <s:c r="C100" s="61">
+      <s:c r="C100" s="62">
         <s:f>INT((A100-1)/12)+1</s:f>
         <s:v>8.0</s:v>
       </s:c>
@@ -9047,14 +9089,14 @@
       </s:c>
     </s:row>
     <s:row r="101">
-      <s:c r="A101" s="61" t="n">
+      <s:c r="A101" s="62" t="n">
         <s:v>97</s:v>
       </s:c>
-      <s:c r="B101" s="62">
+      <s:c r="B101" s="63">
         <s:f>EDATE(DATE(2026,6,17),A101)</s:f>
         <s:v>49142.0</s:v>
       </s:c>
-      <s:c r="C101" s="61">
+      <s:c r="C101" s="62">
         <s:f>INT((A101-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9092,14 +9134,14 @@
       </s:c>
     </s:row>
     <s:row r="102">
-      <s:c r="A102" s="61" t="n">
+      <s:c r="A102" s="62" t="n">
         <s:v>98</s:v>
       </s:c>
-      <s:c r="B102" s="62">
+      <s:c r="B102" s="63">
         <s:f>EDATE(DATE(2026,6,17),A102)</s:f>
         <s:v>49173.0</s:v>
       </s:c>
-      <s:c r="C102" s="61">
+      <s:c r="C102" s="62">
         <s:f>INT((A102-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9137,14 +9179,14 @@
       </s:c>
     </s:row>
     <s:row r="103">
-      <s:c r="A103" s="61" t="n">
+      <s:c r="A103" s="62" t="n">
         <s:v>99</s:v>
       </s:c>
-      <s:c r="B103" s="62">
+      <s:c r="B103" s="63">
         <s:f>EDATE(DATE(2026,6,17),A103)</s:f>
         <s:v>49204.0</s:v>
       </s:c>
-      <s:c r="C103" s="61">
+      <s:c r="C103" s="62">
         <s:f>INT((A103-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9182,14 +9224,14 @@
       </s:c>
     </s:row>
     <s:row r="104">
-      <s:c r="A104" s="61" t="n">
+      <s:c r="A104" s="62" t="n">
         <s:v>100</s:v>
       </s:c>
-      <s:c r="B104" s="62">
+      <s:c r="B104" s="63">
         <s:f>EDATE(DATE(2026,6,17),A104)</s:f>
         <s:v>49234.0</s:v>
       </s:c>
-      <s:c r="C104" s="61">
+      <s:c r="C104" s="62">
         <s:f>INT((A104-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9227,14 +9269,14 @@
       </s:c>
     </s:row>
     <s:row r="105">
-      <s:c r="A105" s="61" t="n">
+      <s:c r="A105" s="62" t="n">
         <s:v>101</s:v>
       </s:c>
-      <s:c r="B105" s="62">
+      <s:c r="B105" s="63">
         <s:f>EDATE(DATE(2026,6,17),A105)</s:f>
         <s:v>49265.0</s:v>
       </s:c>
-      <s:c r="C105" s="61">
+      <s:c r="C105" s="62">
         <s:f>INT((A105-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9272,14 +9314,14 @@
       </s:c>
     </s:row>
     <s:row r="106">
-      <s:c r="A106" s="61" t="n">
+      <s:c r="A106" s="62" t="n">
         <s:v>102</s:v>
       </s:c>
-      <s:c r="B106" s="62">
+      <s:c r="B106" s="63">
         <s:f>EDATE(DATE(2026,6,17),A106)</s:f>
         <s:v>49295.0</s:v>
       </s:c>
-      <s:c r="C106" s="61">
+      <s:c r="C106" s="62">
         <s:f>INT((A106-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9317,14 +9359,14 @@
       </s:c>
     </s:row>
     <s:row r="107">
-      <s:c r="A107" s="61" t="n">
+      <s:c r="A107" s="62" t="n">
         <s:v>103</s:v>
       </s:c>
-      <s:c r="B107" s="62">
+      <s:c r="B107" s="63">
         <s:f>EDATE(DATE(2026,6,17),A107)</s:f>
         <s:v>49326.0</s:v>
       </s:c>
-      <s:c r="C107" s="61">
+      <s:c r="C107" s="62">
         <s:f>INT((A107-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9362,14 +9404,14 @@
       </s:c>
     </s:row>
     <s:row r="108">
-      <s:c r="A108" s="61" t="n">
+      <s:c r="A108" s="62" t="n">
         <s:v>104</s:v>
       </s:c>
-      <s:c r="B108" s="62">
+      <s:c r="B108" s="63">
         <s:f>EDATE(DATE(2026,6,17),A108)</s:f>
         <s:v>49357.0</s:v>
       </s:c>
-      <s:c r="C108" s="61">
+      <s:c r="C108" s="62">
         <s:f>INT((A108-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9407,14 +9449,14 @@
       </s:c>
     </s:row>
     <s:row r="109">
-      <s:c r="A109" s="61" t="n">
+      <s:c r="A109" s="62" t="n">
         <s:v>105</s:v>
       </s:c>
-      <s:c r="B109" s="62">
+      <s:c r="B109" s="63">
         <s:f>EDATE(DATE(2026,6,17),A109)</s:f>
         <s:v>49385.0</s:v>
       </s:c>
-      <s:c r="C109" s="61">
+      <s:c r="C109" s="62">
         <s:f>INT((A109-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9452,14 +9494,14 @@
       </s:c>
     </s:row>
     <s:row r="110">
-      <s:c r="A110" s="61" t="n">
+      <s:c r="A110" s="62" t="n">
         <s:v>106</s:v>
       </s:c>
-      <s:c r="B110" s="62">
+      <s:c r="B110" s="63">
         <s:f>EDATE(DATE(2026,6,17),A110)</s:f>
         <s:v>49416.0</s:v>
       </s:c>
-      <s:c r="C110" s="61">
+      <s:c r="C110" s="62">
         <s:f>INT((A110-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9497,14 +9539,14 @@
       </s:c>
     </s:row>
     <s:row r="111">
-      <s:c r="A111" s="61" t="n">
+      <s:c r="A111" s="62" t="n">
         <s:v>107</s:v>
       </s:c>
-      <s:c r="B111" s="62">
+      <s:c r="B111" s="63">
         <s:f>EDATE(DATE(2026,6,17),A111)</s:f>
         <s:v>49446.0</s:v>
       </s:c>
-      <s:c r="C111" s="61">
+      <s:c r="C111" s="62">
         <s:f>INT((A111-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9542,14 +9584,14 @@
       </s:c>
     </s:row>
     <s:row r="112">
-      <s:c r="A112" s="61" t="n">
+      <s:c r="A112" s="62" t="n">
         <s:v>108</s:v>
       </s:c>
-      <s:c r="B112" s="62">
+      <s:c r="B112" s="63">
         <s:f>EDATE(DATE(2026,6,17),A112)</s:f>
         <s:v>49477.0</s:v>
       </s:c>
-      <s:c r="C112" s="61">
+      <s:c r="C112" s="62">
         <s:f>INT((A112-1)/12)+1</s:f>
         <s:v>9.0</s:v>
       </s:c>
@@ -9587,14 +9629,14 @@
       </s:c>
     </s:row>
     <s:row r="113">
-      <s:c r="A113" s="61" t="n">
+      <s:c r="A113" s="62" t="n">
         <s:v>109</s:v>
       </s:c>
-      <s:c r="B113" s="62">
+      <s:c r="B113" s="63">
         <s:f>EDATE(DATE(2026,6,17),A113)</s:f>
         <s:v>49507.0</s:v>
       </s:c>
-      <s:c r="C113" s="61">
+      <s:c r="C113" s="62">
         <s:f>INT((A113-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -9632,14 +9674,14 @@
       </s:c>
     </s:row>
     <s:row r="114">
-      <s:c r="A114" s="61" t="n">
+      <s:c r="A114" s="62" t="n">
         <s:v>110</s:v>
       </s:c>
-      <s:c r="B114" s="62">
+      <s:c r="B114" s="63">
         <s:f>EDATE(DATE(2026,6,17),A114)</s:f>
         <s:v>49538.0</s:v>
       </s:c>
-      <s:c r="C114" s="61">
+      <s:c r="C114" s="62">
         <s:f>INT((A114-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -9677,14 +9719,14 @@
       </s:c>
     </s:row>
     <s:row r="115">
-      <s:c r="A115" s="61" t="n">
+      <s:c r="A115" s="62" t="n">
         <s:v>111</s:v>
       </s:c>
-      <s:c r="B115" s="62">
+      <s:c r="B115" s="63">
         <s:f>EDATE(DATE(2026,6,17),A115)</s:f>
         <s:v>49569.0</s:v>
       </s:c>
-      <s:c r="C115" s="61">
+      <s:c r="C115" s="62">
         <s:f>INT((A115-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -9722,14 +9764,14 @@
       </s:c>
     </s:row>
     <s:row r="116">
-      <s:c r="A116" s="61" t="n">
+      <s:c r="A116" s="62" t="n">
         <s:v>112</s:v>
       </s:c>
-      <s:c r="B116" s="62">
+      <s:c r="B116" s="63">
         <s:f>EDATE(DATE(2026,6,17),A116)</s:f>
         <s:v>49599.0</s:v>
       </s:c>
-      <s:c r="C116" s="61">
+      <s:c r="C116" s="62">
         <s:f>INT((A116-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -9767,14 +9809,14 @@
       </s:c>
     </s:row>
     <s:row r="117">
-      <s:c r="A117" s="61" t="n">
+      <s:c r="A117" s="62" t="n">
         <s:v>113</s:v>
       </s:c>
-      <s:c r="B117" s="62">
+      <s:c r="B117" s="63">
         <s:f>EDATE(DATE(2026,6,17),A117)</s:f>
         <s:v>49630.0</s:v>
       </s:c>
-      <s:c r="C117" s="61">
+      <s:c r="C117" s="62">
         <s:f>INT((A117-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -9812,14 +9854,14 @@
       </s:c>
     </s:row>
     <s:row r="118">
-      <s:c r="A118" s="61" t="n">
+      <s:c r="A118" s="62" t="n">
         <s:v>114</s:v>
       </s:c>
-      <s:c r="B118" s="62">
+      <s:c r="B118" s="63">
         <s:f>EDATE(DATE(2026,6,17),A118)</s:f>
         <s:v>49660.0</s:v>
       </s:c>
-      <s:c r="C118" s="61">
+      <s:c r="C118" s="62">
         <s:f>INT((A118-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -9857,14 +9899,14 @@
       </s:c>
     </s:row>
     <s:row r="119">
-      <s:c r="A119" s="61" t="n">
+      <s:c r="A119" s="62" t="n">
         <s:v>115</s:v>
       </s:c>
-      <s:c r="B119" s="62">
+      <s:c r="B119" s="63">
         <s:f>EDATE(DATE(2026,6,17),A119)</s:f>
         <s:v>49691.0</s:v>
       </s:c>
-      <s:c r="C119" s="61">
+      <s:c r="C119" s="62">
         <s:f>INT((A119-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -9902,14 +9944,14 @@
       </s:c>
     </s:row>
     <s:row r="120">
-      <s:c r="A120" s="61" t="n">
+      <s:c r="A120" s="62" t="n">
         <s:v>116</s:v>
       </s:c>
-      <s:c r="B120" s="62">
+      <s:c r="B120" s="63">
         <s:f>EDATE(DATE(2026,6,17),A120)</s:f>
         <s:v>49722.0</s:v>
       </s:c>
-      <s:c r="C120" s="61">
+      <s:c r="C120" s="62">
         <s:f>INT((A120-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -9947,14 +9989,14 @@
       </s:c>
     </s:row>
     <s:row r="121">
-      <s:c r="A121" s="61" t="n">
+      <s:c r="A121" s="62" t="n">
         <s:v>117</s:v>
       </s:c>
-      <s:c r="B121" s="62">
+      <s:c r="B121" s="63">
         <s:f>EDATE(DATE(2026,6,17),A121)</s:f>
         <s:v>49751.0</s:v>
       </s:c>
-      <s:c r="C121" s="61">
+      <s:c r="C121" s="62">
         <s:f>INT((A121-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -9992,14 +10034,14 @@
       </s:c>
     </s:row>
     <s:row r="122">
-      <s:c r="A122" s="61" t="n">
+      <s:c r="A122" s="62" t="n">
         <s:v>118</s:v>
       </s:c>
-      <s:c r="B122" s="62">
+      <s:c r="B122" s="63">
         <s:f>EDATE(DATE(2026,6,17),A122)</s:f>
         <s:v>49782.0</s:v>
       </s:c>
-      <s:c r="C122" s="61">
+      <s:c r="C122" s="62">
         <s:f>INT((A122-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -10037,14 +10079,14 @@
       </s:c>
     </s:row>
     <s:row r="123">
-      <s:c r="A123" s="61" t="n">
+      <s:c r="A123" s="62" t="n">
         <s:v>119</s:v>
       </s:c>
-      <s:c r="B123" s="62">
+      <s:c r="B123" s="63">
         <s:f>EDATE(DATE(2026,6,17),A123)</s:f>
         <s:v>49812.0</s:v>
       </s:c>
-      <s:c r="C123" s="61">
+      <s:c r="C123" s="62">
         <s:f>INT((A123-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -10082,14 +10124,14 @@
       </s:c>
     </s:row>
     <s:row r="124">
-      <s:c r="A124" s="61" t="n">
+      <s:c r="A124" s="62" t="n">
         <s:v>120</s:v>
       </s:c>
-      <s:c r="B124" s="62">
+      <s:c r="B124" s="63">
         <s:f>EDATE(DATE(2026,6,17),A124)</s:f>
         <s:v>49843.0</s:v>
       </s:c>
-      <s:c r="C124" s="61">
+      <s:c r="C124" s="62">
         <s:f>INT((A124-1)/12)+1</s:f>
         <s:v>10.0</s:v>
       </s:c>
@@ -10203,7 +10245,7 @@
       </s:c>
     </s:row>
     <s:row r="4">
-      <s:c r="A4" s="59" t="inlineStr">
+      <s:c r="A4" s="60" t="inlineStr">
         <s:is>
           <s:t>მაჩვენებელი / Item</s:t>
         </s:is>
@@ -10295,45 +10337,45 @@
       <s:c r="N6" s="11" t="n"/>
     </s:row>
     <s:row r="7">
-      <s:c r="A7" s="63" t="inlineStr">
+      <s:c r="A7" s="64" t="inlineStr">
         <s:is>
           <s:t>ზამთრის მოსავლის რეალიზაცია / Winter crop sold (%)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B7" s="60" t="n">
+      <s:c r="B7" s="61" t="n">
         <s:v>0.2</s:v>
       </s:c>
-      <s:c r="C7" s="60" t="n">
+      <s:c r="C7" s="61" t="n">
         <s:v>0.25</s:v>
       </s:c>
-      <s:c r="D7" s="60" t="n">
+      <s:c r="D7" s="61" t="n">
         <s:v>0.25</s:v>
       </s:c>
-      <s:c r="E7" s="60" t="n">
+      <s:c r="E7" s="61" t="n">
         <s:v>0.15</s:v>
       </s:c>
-      <s:c r="F7" s="60" t="n">
+      <s:c r="F7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="G7" s="60" t="n">
+      <s:c r="G7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="H7" s="60" t="n">
+      <s:c r="H7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="I7" s="60" t="n">
+      <s:c r="I7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="J7" s="60" t="n">
+      <s:c r="J7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="K7" s="60" t="n">
+      <s:c r="K7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="L7" s="60" t="n">
+      <s:c r="L7" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="M7" s="60" t="n">
+      <s:c r="M7" s="61" t="n">
         <s:v>0.15</s:v>
       </s:c>
       <s:c r="N7" s="19">
@@ -10342,45 +10384,45 @@
       </s:c>
     </s:row>
     <s:row r="8">
-      <s:c r="A8" s="63" t="inlineStr">
+      <s:c r="A8" s="64" t="inlineStr">
         <s:is>
           <s:t>ზაფხულის მოსავლის რეალიზაცია / Summer crop sold (%)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B8" s="60" t="n">
+      <s:c r="B8" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="C8" s="60" t="n">
+      <s:c r="C8" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="D8" s="60" t="n">
+      <s:c r="D8" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="E8" s="60" t="n">
+      <s:c r="E8" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="F8" s="60" t="n">
+      <s:c r="F8" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="G8" s="60" t="n">
+      <s:c r="G8" s="61" t="n">
         <s:v>0.2</s:v>
       </s:c>
-      <s:c r="H8" s="60" t="n">
+      <s:c r="H8" s="61" t="n">
         <s:v>0.3</s:v>
       </s:c>
-      <s:c r="I8" s="60" t="n">
+      <s:c r="I8" s="61" t="n">
         <s:v>0.3</s:v>
       </s:c>
-      <s:c r="J8" s="60" t="n">
+      <s:c r="J8" s="61" t="n">
         <s:v>0.2</s:v>
       </s:c>
-      <s:c r="K8" s="60" t="n">
+      <s:c r="K8" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="L8" s="60" t="n">
+      <s:c r="L8" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="M8" s="60" t="n">
+      <s:c r="M8" s="61" t="n">
         <s:v>0</s:v>
       </s:c>
       <s:c r="N8" s="19">
@@ -10777,7 +10819,7 @@
         <s:f>IFERROR(M19/M13,0)</s:f>
         <s:v>4.5</s:v>
       </s:c>
-      <s:c r="N18" s="38">
+      <s:c r="N18" s="39">
         <s:f>IFERROR(AVERAGE(B18:M18),0)</s:f>
         <s:v>2.875</s:v>
       </s:c>
@@ -10862,56 +10904,56 @@
       <s:c r="N21" s="11" t="n"/>
     </s:row>
     <s:row r="22">
-      <s:c r="A22" s="64" t="inlineStr">
+      <s:c r="A22" s="65" t="inlineStr">
         <s:is>
           <s:t>ხელფასები / Labour &amp; wages</s:t>
         </s:is>
       </s:c>
-      <s:c r="B22" s="49">
+      <s:c r="B22" s="50">
         <s:f>OPEX!B19</s:f>
         <s:v>4320.0</s:v>
       </s:c>
-      <s:c r="C22" s="49">
+      <s:c r="C22" s="50">
         <s:f>OPEX!C19</s:f>
         <s:v>4320.0</s:v>
       </s:c>
-      <s:c r="D22" s="49">
+      <s:c r="D22" s="50">
         <s:f>OPEX!D19</s:f>
         <s:v>4320.0</s:v>
       </s:c>
-      <s:c r="E22" s="49">
+      <s:c r="E22" s="50">
         <s:f>OPEX!E19</s:f>
         <s:v>3840.0</s:v>
       </s:c>
-      <s:c r="F22" s="49">
+      <s:c r="F22" s="50">
         <s:f>OPEX!F19</s:f>
         <s:v>3360.0000000000005</s:v>
       </s:c>
-      <s:c r="G22" s="49">
+      <s:c r="G22" s="50">
         <s:f>OPEX!G19</s:f>
         <s:v>4320.0</s:v>
       </s:c>
-      <s:c r="H22" s="49">
+      <s:c r="H22" s="50">
         <s:f>OPEX!H19</s:f>
         <s:v>4320.0</s:v>
       </s:c>
-      <s:c r="I22" s="49">
+      <s:c r="I22" s="50">
         <s:f>OPEX!I19</s:f>
         <s:v>4320.0</s:v>
       </s:c>
-      <s:c r="J22" s="49">
+      <s:c r="J22" s="50">
         <s:f>OPEX!J19</s:f>
         <s:v>3840.0</s:v>
       </s:c>
-      <s:c r="K22" s="49">
+      <s:c r="K22" s="50">
         <s:f>OPEX!K19</s:f>
         <s:v>3360.0000000000005</s:v>
       </s:c>
-      <s:c r="L22" s="49">
+      <s:c r="L22" s="50">
         <s:f>OPEX!L19</s:f>
         <s:v>3360.0000000000005</s:v>
       </s:c>
-      <s:c r="M22" s="49">
+      <s:c r="M22" s="50">
         <s:f>OPEX!M19</s:f>
         <s:v>4320.0</s:v>
       </s:c>
@@ -10921,56 +10963,56 @@
       </s:c>
     </s:row>
     <s:row r="23">
-      <s:c r="A23" s="64" t="inlineStr">
+      <s:c r="A23" s="65" t="inlineStr">
         <s:is>
           <s:t>გათბობა (გაზი/საწვავი) / Heating (gas &amp; fuel)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B23" s="49">
+      <s:c r="B23" s="50">
         <s:f>OPEX!B20</s:f>
         <s:v>9000.0</s:v>
       </s:c>
-      <s:c r="C23" s="49">
+      <s:c r="C23" s="50">
         <s:f>OPEX!C20</s:f>
         <s:v>7920.0</s:v>
       </s:c>
-      <s:c r="D23" s="49">
+      <s:c r="D23" s="50">
         <s:f>OPEX!D20</s:f>
         <s:v>4680.0</s:v>
       </s:c>
-      <s:c r="E23" s="49">
+      <s:c r="E23" s="50">
         <s:f>OPEX!E20</s:f>
         <s:v>1080.0</s:v>
       </s:c>
-      <s:c r="F23" s="49">
+      <s:c r="F23" s="50">
         <s:f>OPEX!F20</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="G23" s="49">
+      <s:c r="G23" s="50">
         <s:f>OPEX!G20</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="H23" s="49">
+      <s:c r="H23" s="50">
         <s:f>OPEX!H20</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="I23" s="49">
+      <s:c r="I23" s="50">
         <s:f>OPEX!I20</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="J23" s="49">
+      <s:c r="J23" s="50">
         <s:f>OPEX!J20</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="K23" s="49">
+      <s:c r="K23" s="50">
         <s:f>OPEX!K20</s:f>
         <s:v>1440.0</s:v>
       </s:c>
-      <s:c r="L23" s="49">
+      <s:c r="L23" s="50">
         <s:f>OPEX!L20</s:f>
         <s:v>4680.0</s:v>
       </s:c>
-      <s:c r="M23" s="49">
+      <s:c r="M23" s="50">
         <s:f>OPEX!M20</s:f>
         <s:v>7200.0</s:v>
       </s:c>
@@ -10980,56 +11022,56 @@
       </s:c>
     </s:row>
     <s:row r="24">
-      <s:c r="A24" s="64" t="inlineStr">
+      <s:c r="A24" s="65" t="inlineStr">
         <s:is>
           <s:t>ელექტროენერგია და წყალი / Electricity &amp; water</s:t>
         </s:is>
       </s:c>
-      <s:c r="B24" s="49">
+      <s:c r="B24" s="50">
         <s:f>OPEX!B21</s:f>
         <s:v>960.0</s:v>
       </s:c>
-      <s:c r="C24" s="49">
+      <s:c r="C24" s="50">
         <s:f>OPEX!C21</s:f>
         <s:v>960.0</s:v>
       </s:c>
-      <s:c r="D24" s="49">
+      <s:c r="D24" s="50">
         <s:f>OPEX!D21</s:f>
         <s:v>960.0</s:v>
       </s:c>
-      <s:c r="E24" s="49">
+      <s:c r="E24" s="50">
         <s:f>OPEX!E21</s:f>
         <s:v>960.0</s:v>
       </s:c>
-      <s:c r="F24" s="49">
+      <s:c r="F24" s="50">
         <s:f>OPEX!F21</s:f>
         <s:v>1080.0</s:v>
       </s:c>
-      <s:c r="G24" s="49">
+      <s:c r="G24" s="50">
         <s:f>OPEX!G21</s:f>
         <s:v>1200.0</s:v>
       </s:c>
-      <s:c r="H24" s="49">
+      <s:c r="H24" s="50">
         <s:f>OPEX!H21</s:f>
         <s:v>1320.0</s:v>
       </s:c>
-      <s:c r="I24" s="49">
+      <s:c r="I24" s="50">
         <s:f>OPEX!I21</s:f>
         <s:v>1320.0</s:v>
       </s:c>
-      <s:c r="J24" s="49">
+      <s:c r="J24" s="50">
         <s:f>OPEX!J21</s:f>
         <s:v>1080.0</s:v>
       </s:c>
-      <s:c r="K24" s="49">
+      <s:c r="K24" s="50">
         <s:f>OPEX!K21</s:f>
         <s:v>720.0</s:v>
       </s:c>
-      <s:c r="L24" s="49">
+      <s:c r="L24" s="50">
         <s:f>OPEX!L21</s:f>
         <s:v>720.0</s:v>
       </s:c>
-      <s:c r="M24" s="49">
+      <s:c r="M24" s="50">
         <s:f>OPEX!M21</s:f>
         <s:v>720.0</s:v>
       </s:c>
@@ -11039,56 +11081,56 @@
       </s:c>
     </s:row>
     <s:row r="25">
-      <s:c r="A25" s="64" t="inlineStr">
+      <s:c r="A25" s="65" t="inlineStr">
         <s:is>
           <s:t>ნერგები და თესლი / Seedlings &amp; seeds</s:t>
         </s:is>
       </s:c>
-      <s:c r="B25" s="49">
+      <s:c r="B25" s="50">
         <s:f>OPEX!B22</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C25" s="49">
+      <s:c r="C25" s="50">
         <s:f>OPEX!C22</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="D25" s="49">
+      <s:c r="D25" s="50">
         <s:f>OPEX!D22</s:f>
         <s:v>2800.0</s:v>
       </s:c>
-      <s:c r="E25" s="49">
+      <s:c r="E25" s="50">
         <s:f>OPEX!E22</s:f>
         <s:v>3500.0</s:v>
       </s:c>
-      <s:c r="F25" s="49">
+      <s:c r="F25" s="50">
         <s:f>OPEX!F22</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="G25" s="49">
+      <s:c r="G25" s="50">
         <s:f>OPEX!G22</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="H25" s="49">
+      <s:c r="H25" s="50">
         <s:f>OPEX!H22</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="I25" s="49">
+      <s:c r="I25" s="50">
         <s:f>OPEX!I22</s:f>
         <s:v>4200.0</s:v>
       </s:c>
-      <s:c r="J25" s="49">
+      <s:c r="J25" s="50">
         <s:f>OPEX!J22</s:f>
         <s:v>3500.0</s:v>
       </s:c>
-      <s:c r="K25" s="49">
+      <s:c r="K25" s="50">
         <s:f>OPEX!K22</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="L25" s="49">
+      <s:c r="L25" s="50">
         <s:f>OPEX!L22</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="M25" s="49">
+      <s:c r="M25" s="50">
         <s:f>OPEX!M22</s:f>
         <s:v>0.0</s:v>
       </s:c>
@@ -11098,56 +11140,56 @@
       </s:c>
     </s:row>
     <s:row r="26">
-      <s:c r="A26" s="64" t="inlineStr">
+      <s:c r="A26" s="65" t="inlineStr">
         <s:is>
           <s:t>სასუქი და მცენარეთა დაცვა / Fertiliser &amp; crop protection</s:t>
         </s:is>
       </s:c>
-      <s:c r="B26" s="49">
+      <s:c r="B26" s="50">
         <s:f>OPEX!B23</s:f>
         <s:v>1440.0</s:v>
       </s:c>
-      <s:c r="C26" s="49">
+      <s:c r="C26" s="50">
         <s:f>OPEX!C23</s:f>
         <s:v>1800.0</s:v>
       </s:c>
-      <s:c r="D26" s="49">
+      <s:c r="D26" s="50">
         <s:f>OPEX!D23</s:f>
         <s:v>2160.0</s:v>
       </s:c>
-      <s:c r="E26" s="49">
+      <s:c r="E26" s="50">
         <s:f>OPEX!E23</s:f>
         <s:v>1800.0</s:v>
       </s:c>
-      <s:c r="F26" s="49">
+      <s:c r="F26" s="50">
         <s:f>OPEX!F23</s:f>
         <s:v>1440.0</s:v>
       </s:c>
-      <s:c r="G26" s="49">
+      <s:c r="G26" s="50">
         <s:f>OPEX!G23</s:f>
         <s:v>1440.0</s:v>
       </s:c>
-      <s:c r="H26" s="49">
+      <s:c r="H26" s="50">
         <s:f>OPEX!H23</s:f>
         <s:v>1440.0</s:v>
       </s:c>
-      <s:c r="I26" s="49">
+      <s:c r="I26" s="50">
         <s:f>OPEX!I23</s:f>
         <s:v>1440.0</s:v>
       </s:c>
-      <s:c r="J26" s="49">
+      <s:c r="J26" s="50">
         <s:f>OPEX!J23</s:f>
         <s:v>1800.0</s:v>
       </s:c>
-      <s:c r="K26" s="49">
+      <s:c r="K26" s="50">
         <s:f>OPEX!K23</s:f>
         <s:v>1800.0</s:v>
       </s:c>
-      <s:c r="L26" s="49">
+      <s:c r="L26" s="50">
         <s:f>OPEX!L23</s:f>
         <s:v>720.0</s:v>
       </s:c>
-      <s:c r="M26" s="49">
+      <s:c r="M26" s="50">
         <s:f>OPEX!M23</s:f>
         <s:v>720.0</s:v>
       </s:c>
@@ -11157,56 +11199,56 @@
       </s:c>
     </s:row>
     <s:row r="27">
-      <s:c r="A27" s="64" t="inlineStr">
+      <s:c r="A27" s="65" t="inlineStr">
         <s:is>
           <s:t>შეფუთვა და ლოგისტიკა / Packaging &amp; logistics</s:t>
         </s:is>
       </s:c>
-      <s:c r="B27" s="49">
+      <s:c r="B27" s="50">
         <s:f>OPEX!B24</s:f>
         <s:v>1200.0</s:v>
       </s:c>
-      <s:c r="C27" s="49">
+      <s:c r="C27" s="50">
         <s:f>OPEX!C24</s:f>
         <s:v>1400.0000000000002</s:v>
       </s:c>
-      <s:c r="D27" s="49">
+      <s:c r="D27" s="50">
         <s:f>OPEX!D24</s:f>
         <s:v>1400.0000000000002</s:v>
       </s:c>
-      <s:c r="E27" s="49">
+      <s:c r="E27" s="50">
         <s:f>OPEX!E24</s:f>
         <s:v>800.0</s:v>
       </s:c>
-      <s:c r="F27" s="49">
+      <s:c r="F27" s="50">
         <s:f>OPEX!F24</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="G27" s="49">
+      <s:c r="G27" s="50">
         <s:f>OPEX!G24</s:f>
         <s:v>700.0000000000001</s:v>
       </s:c>
-      <s:c r="H27" s="49">
+      <s:c r="H27" s="50">
         <s:f>OPEX!H24</s:f>
         <s:v>1100.0</s:v>
       </s:c>
-      <s:c r="I27" s="49">
+      <s:c r="I27" s="50">
         <s:f>OPEX!I24</s:f>
         <s:v>1100.0</s:v>
       </s:c>
-      <s:c r="J27" s="49">
+      <s:c r="J27" s="50">
         <s:f>OPEX!J24</s:f>
         <s:v>700.0000000000001</s:v>
       </s:c>
-      <s:c r="K27" s="49">
+      <s:c r="K27" s="50">
         <s:f>OPEX!K24</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="L27" s="49">
+      <s:c r="L27" s="50">
         <s:f>OPEX!L24</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="M27" s="49">
+      <s:c r="M27" s="50">
         <s:f>OPEX!M24</s:f>
         <s:v>1600.0</s:v>
       </s:c>
@@ -11216,56 +11258,56 @@
       </s:c>
     </s:row>
     <s:row r="28">
-      <s:c r="A28" s="64" t="inlineStr">
+      <s:c r="A28" s="65" t="inlineStr">
         <s:is>
           <s:t>რემონტი და მოვლა / Maintenance &amp; repairs</s:t>
         </s:is>
       </s:c>
-      <s:c r="B28" s="49">
+      <s:c r="B28" s="50">
         <s:f>OPEX!B25</s:f>
         <s:v>120.0</s:v>
       </s:c>
-      <s:c r="C28" s="49">
+      <s:c r="C28" s="50">
         <s:f>OPEX!C25</s:f>
         <s:v>120.0</s:v>
       </s:c>
-      <s:c r="D28" s="49">
+      <s:c r="D28" s="50">
         <s:f>OPEX!D25</s:f>
         <s:v>120.0</s:v>
       </s:c>
-      <s:c r="E28" s="49">
+      <s:c r="E28" s="50">
         <s:f>OPEX!E25</s:f>
         <s:v>240.0</s:v>
       </s:c>
-      <s:c r="F28" s="49">
+      <s:c r="F28" s="50">
         <s:f>OPEX!F25</s:f>
         <s:v>1200.0</s:v>
       </s:c>
-      <s:c r="G28" s="49">
+      <s:c r="G28" s="50">
         <s:f>OPEX!G25</s:f>
         <s:v>600.0</s:v>
       </s:c>
-      <s:c r="H28" s="49">
+      <s:c r="H28" s="50">
         <s:f>OPEX!H25</s:f>
         <s:v>120.0</s:v>
       </s:c>
-      <s:c r="I28" s="49">
+      <s:c r="I28" s="50">
         <s:f>OPEX!I25</s:f>
         <s:v>120.0</s:v>
       </s:c>
-      <s:c r="J28" s="49">
+      <s:c r="J28" s="50">
         <s:f>OPEX!J25</s:f>
         <s:v>180.0</s:v>
       </s:c>
-      <s:c r="K28" s="49">
+      <s:c r="K28" s="50">
         <s:f>OPEX!K25</s:f>
         <s:v>1500.0</s:v>
       </s:c>
-      <s:c r="L28" s="49">
+      <s:c r="L28" s="50">
         <s:f>OPEX!L25</s:f>
         <s:v>1500.0</s:v>
       </s:c>
-      <s:c r="M28" s="49">
+      <s:c r="M28" s="50">
         <s:f>OPEX!M25</s:f>
         <s:v>180.0</s:v>
       </s:c>
@@ -11275,56 +11317,56 @@
       </s:c>
     </s:row>
     <s:row r="29">
-      <s:c r="A29" s="64" t="inlineStr">
+      <s:c r="A29" s="65" t="inlineStr">
         <s:is>
           <s:t>ადმინისტრაცია, დაზღვევა, ბუღალტერია / Admin, insurance, accounting</s:t>
         </s:is>
       </s:c>
-      <s:c r="B29" s="49">
+      <s:c r="B29" s="50">
         <s:f>OPEX!B26</s:f>
         <s:v>480.0</s:v>
       </s:c>
-      <s:c r="C29" s="49">
+      <s:c r="C29" s="50">
         <s:f>OPEX!C26</s:f>
         <s:v>480.0</s:v>
       </s:c>
-      <s:c r="D29" s="49">
+      <s:c r="D29" s="50">
         <s:f>OPEX!D26</s:f>
         <s:v>540.0</s:v>
       </s:c>
-      <s:c r="E29" s="49">
+      <s:c r="E29" s="50">
         <s:f>OPEX!E26</s:f>
         <s:v>480.0</s:v>
       </s:c>
-      <s:c r="F29" s="49">
+      <s:c r="F29" s="50">
         <s:f>OPEX!F26</s:f>
         <s:v>480.0</s:v>
       </s:c>
-      <s:c r="G29" s="49">
+      <s:c r="G29" s="50">
         <s:f>OPEX!G26</s:f>
         <s:v>540.0</s:v>
       </s:c>
-      <s:c r="H29" s="49">
+      <s:c r="H29" s="50">
         <s:f>OPEX!H26</s:f>
         <s:v>480.0</s:v>
       </s:c>
-      <s:c r="I29" s="49">
+      <s:c r="I29" s="50">
         <s:f>OPEX!I26</s:f>
         <s:v>480.0</s:v>
       </s:c>
-      <s:c r="J29" s="49">
+      <s:c r="J29" s="50">
         <s:f>OPEX!J26</s:f>
         <s:v>540.0</s:v>
       </s:c>
-      <s:c r="K29" s="49">
+      <s:c r="K29" s="50">
         <s:f>OPEX!K26</s:f>
         <s:v>480.0</s:v>
       </s:c>
-      <s:c r="L29" s="49">
+      <s:c r="L29" s="50">
         <s:f>OPEX!L26</s:f>
         <s:v>480.0</s:v>
       </s:c>
-      <s:c r="M29" s="49">
+      <s:c r="M29" s="50">
         <s:f>OPEX!M26</s:f>
         <s:v>540.0</s:v>
       </s:c>
@@ -11531,56 +11573,56 @@
       </s:c>
     </s:row>
     <s:row r="34">
-      <s:c r="A34" s="64" t="inlineStr">
+      <s:c r="A34" s="65" t="inlineStr">
         <s:is>
           <s:t>სესხის პროცენტი, სააგენტოს გამოკლებით / Loan interest, net of agency</s:t>
         </s:is>
       </s:c>
-      <s:c r="B34" s="49">
+      <s:c r="B34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+1)</s:f>
         <s:v>-854.1666666666679</s:v>
       </s:c>
-      <s:c r="C34" s="49">
+      <s:c r="C34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+2)</s:f>
         <s:v>-854.1666666666679</s:v>
       </s:c>
-      <s:c r="D34" s="49">
+      <s:c r="D34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+3)</s:f>
         <s:v>-849.8169228074685</s:v>
       </s:c>
-      <s:c r="E34" s="49">
+      <s:c r="E34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+4)</s:f>
         <s:v>-845.4213616462866</s:v>
       </s:c>
-      <s:c r="F34" s="49">
+      <s:c r="F34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+5)</s:f>
         <s:v>-840.979500574208</s:v>
       </s:c>
-      <s:c r="G34" s="49">
+      <s:c r="G34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+6)</s:f>
         <s:v>-836.4908518988341</s:v>
       </s:c>
-      <s:c r="H34" s="49">
+      <s:c r="H34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+7)</s:f>
         <s:v>-831.9549227907482</s:v>
       </s:c>
-      <s:c r="I34" s="49">
+      <s:c r="I34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+8)</s:f>
         <s:v>-827.371215229391</s:v>
       </s:c>
-      <s:c r="J34" s="49">
+      <s:c r="J34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+9)</s:f>
         <s:v>-822.7392259483859</s:v>
       </s:c>
-      <s:c r="K34" s="49">
+      <s:c r="K34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+10)</s:f>
         <s:v>-818.0584463802879</s:v>
       </s:c>
-      <s:c r="L34" s="49">
+      <s:c r="L34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+11)</s:f>
         <s:v>-813.3283626007396</s:v>
       </s:c>
-      <s:c r="M34" s="49">
+      <s:c r="M34" s="50">
         <s:f>-INDEX(Loan!$G$5:$G$124,(Assumptions!$B$48-1)*12+12)</s:f>
         <s:v>-1183.2416418615312</s:v>
       </s:c>
@@ -11590,56 +11632,56 @@
       </s:c>
     </s:row>
     <s:row r="35">
-      <s:c r="A35" s="64" t="inlineStr">
+      <s:c r="A35" s="65" t="inlineStr">
         <s:is>
           <s:t>სესხის ძირი / Loan principal repayment</s:t>
         </s:is>
       </s:c>
-      <s:c r="B35" s="49">
+      <s:c r="B35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+1)</s:f>
         <s:v>-0.0</s:v>
       </s:c>
-      <s:c r="C35" s="49">
+      <s:c r="C35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+2)</s:f>
         <s:v>-3182.7394091696015</s:v>
       </s:c>
-      <s:c r="D35" s="49">
+      <s:c r="D35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+3)</s:f>
         <s:v>-3216.2642642795226</s:v>
       </s:c>
-      <s:c r="E35" s="49">
+      <s:c r="E35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+4)</s:f>
         <s:v>-3250.1422478632667</s:v>
       </s:c>
-      <s:c r="F35" s="49">
+      <s:c r="F35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+5)</s:f>
         <s:v>-3284.377079540757</s:v>
       </s:c>
-      <s:c r="G35" s="49">
+      <s:c r="G35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+6)</s:f>
         <s:v>-3318.97251811192</s:v>
       </s:c>
-      <s:c r="H35" s="49">
+      <s:c r="H35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+7)</s:f>
         <s:v>-3353.932361969368</s:v>
       </s:c>
-      <s:c r="I35" s="49">
+      <s:c r="I35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+8)</s:f>
         <s:v>-3389.260449515443</s:v>
       </s:c>
-      <s:c r="J35" s="49">
+      <s:c r="J35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+9)</s:f>
         <s:v>-3424.960659583674</s:v>
       </s:c>
-      <s:c r="K35" s="49">
+      <s:c r="K35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+10)</s:f>
         <s:v>-3461.0369118646204</s:v>
       </s:c>
-      <s:c r="L35" s="49">
+      <s:c r="L35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+11)</s:f>
         <s:v>-3497.49316733626</s:v>
       </s:c>
-      <s:c r="M35" s="49">
+      <s:c r="M35" s="50">
         <s:f>-INDEX(Loan!$H$5:$H$124,(Assumptions!$B$48-1)*12+12)</s:f>
         <s:v>-3411.815716181475</s:v>
       </s:c>
@@ -11989,7 +12031,7 @@
           <s:t>საწყისი ნაშთი / Opening cash</s:t>
         </s:is>
       </s:c>
-      <s:c r="B44" s="49">
+      <s:c r="B44" s="50">
         <s:f>Assumptions!$B$45</s:f>
         <s:v>0.0</s:v>
       </s:c>
@@ -12166,7 +12208,7 @@
           <s:t>საბრუნავი კაპიტალის საჭიროება / Working-capital requirement (largest cash shortfall)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B48" s="65">
+      <s:c r="B48" s="66">
         <s:f>MIN(0,MIN(B45:M45))</s:f>
         <s:v>0.0</s:v>
       </s:c>
@@ -12182,7 +12224,7 @@
           <s:t>DSCR (EBITDA / ვალის მომსახურება), წელი 1</s:t>
         </s:is>
       </s:c>
-      <s:c r="B49" s="66">
+      <s:c r="B49" s="67">
         <s:f>IFERROR(N32/N36,0)</s:f>
         <s:v>9.381214941511837</s:v>
       </s:c>
@@ -12198,11 +12240,11 @@
           <s:t>შემოწმება — სეზონურობის ჯამი / Check — seasonality totals (both must be 100%)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B50" s="67">
+      <s:c r="B50" s="68">
         <s:f>SUM(B7:M7)</s:f>
         <s:v>1.0</s:v>
       </s:c>
-      <s:c r="C50" s="67">
+      <s:c r="C50" s="68">
         <s:f>SUM(B8:M8)</s:f>
         <s:v>1.0</s:v>
       </s:c>
@@ -12244,7 +12286,7 @@
       </s:c>
     </s:row>
     <s:row r="4">
-      <s:c r="A4" s="59" t="inlineStr">
+      <s:c r="A4" s="60" t="inlineStr">
         <s:is>
           <s:t>მაჩვენებელი / Item</s:t>
         </s:is>
@@ -12516,28 +12558,28 @@
       </s:c>
     </s:row>
     <s:row r="16">
-      <s:c r="A16" s="64" t="inlineStr">
+      <s:c r="A16" s="65" t="inlineStr">
         <s:is>
           <s:t>საოპერაციო ხარჯი / Operating expenses</s:t>
         </s:is>
       </s:c>
-      <s:c r="B16" s="49">
+      <s:c r="B16" s="50">
         <s:f>-CF_Monthly!$N$30</s:f>
         <s:v>-150000.0</s:v>
       </s:c>
-      <s:c r="C16" s="49">
+      <s:c r="C16" s="50">
         <s:f>B16*(1+Assumptions!$B$41)</s:f>
         <s:v>-156000.0</s:v>
       </s:c>
-      <s:c r="D16" s="49">
+      <s:c r="D16" s="50">
         <s:f>C16*(1+Assumptions!$B$41)</s:f>
         <s:v>-162240.0</s:v>
       </s:c>
-      <s:c r="E16" s="49">
+      <s:c r="E16" s="50">
         <s:f>D16*(1+Assumptions!$B$41)</s:f>
         <s:v>-168729.6</s:v>
       </s:c>
-      <s:c r="F16" s="49">
+      <s:c r="F16" s="50">
         <s:f>E16*(1+Assumptions!$B$41)</s:f>
         <s:v>-175478.784</s:v>
       </s:c>
@@ -12609,55 +12651,55 @@
       <s:c r="F20" s="11" t="n"/>
     </s:row>
     <s:row r="21">
-      <s:c r="A21" s="64" t="inlineStr">
+      <s:c r="A21" s="65" t="inlineStr">
         <s:is>
           <s:t>სესხის პროცენტი, სააგენტოს გამოკლებით / Loan interest, net of agency</s:t>
         </s:is>
       </s:c>
-      <s:c r="B21" s="49">
+      <s:c r="B21" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+0,Loan!$G$5:$G$124)</s:f>
         <s:v>-10377.735785071218</s:v>
       </s:c>
-      <s:c r="C21" s="49">
+      <s:c r="C21" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+1,Loan!$G$5:$G$124)</s:f>
         <s:v>-13644.24326269929</s:v>
       </s:c>
-      <s:c r="D21" s="49">
+      <s:c r="D21" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+2,Loan!$G$5:$G$124)</s:f>
         <s:v>-12519.925437700906</s:v>
       </s:c>
-      <s:c r="E21" s="49">
+      <s:c r="E21" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+3,Loan!$G$5:$G$124)</s:f>
         <s:v>-62730.664248429326</s:v>
       </s:c>
-      <s:c r="F21" s="49">
+      <s:c r="F21" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+4,Loan!$G$5:$G$124)</s:f>
         <s:v>-54536.04985562658</s:v>
       </s:c>
     </s:row>
     <s:row r="22">
-      <s:c r="A22" s="64" t="inlineStr">
+      <s:c r="A22" s="65" t="inlineStr">
         <s:is>
           <s:t>სესხის ძირი / Loan principal</s:t>
         </s:is>
       </s:c>
-      <s:c r="B22" s="49">
+      <s:c r="B22" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+0,Loan!$H$5:$H$124)</s:f>
         <s:v>-36790.9947854159</s:v>
       </s:c>
-      <s:c r="C22" s="49">
+      <s:c r="C22" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+1,Loan!$H$5:$H$124)</s:f>
         <s:v>-44038.62038216267</s:v>
       </s:c>
-      <s:c r="D22" s="49">
+      <s:c r="D22" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+2,Loan!$H$5:$H$124)</s:f>
         <s:v>-50316.06157173713</s:v>
       </s:c>
-      <s:c r="E22" s="49">
+      <s:c r="E22" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+3,Loan!$H$5:$H$124)</s:f>
         <s:v>-57488.31435047132</s:v>
       </s:c>
-      <s:c r="F22" s="49">
+      <s:c r="F22" s="50">
         <s:f>-SUMIF(Loan!$C$5:$C$124,Assumptions!$B$48+4,Loan!$H$5:$H$124)</s:f>
         <s:v>-65682.92874327421</s:v>
       </s:c>
@@ -12690,28 +12732,28 @@
       </s:c>
     </s:row>
     <s:row r="24">
-      <s:c r="A24" s="64" t="inlineStr">
+      <s:c r="A24" s="65" t="inlineStr">
         <s:is>
           <s:t>ნაშთი წლის ბოლოს / Loan balance, year-end</s:t>
         </s:is>
       </s:c>
-      <s:c r="B24" s="49">
+      <s:c r="B24" s="50">
         <s:f>INDEX(Loan!$J$5:$J$124,MATCH((Assumptions!$B$48+0)*12,Loan!$A$5:$A$124,0))</s:f>
         <s:v>588209.0052145841</s:v>
       </s:c>
-      <s:c r="C24" s="49">
+      <s:c r="C24" s="50">
         <s:f>INDEX(Loan!$J$5:$J$124,MATCH((Assumptions!$B$48+1)*12,Loan!$A$5:$A$124,0))</s:f>
         <s:v>544170.3848324217</s:v>
       </s:c>
-      <s:c r="D24" s="49">
+      <s:c r="D24" s="50">
         <s:f>INDEX(Loan!$J$5:$J$124,MATCH((Assumptions!$B$48+2)*12,Loan!$A$5:$A$124,0))</s:f>
         <s:v>493854.3232606846</s:v>
       </s:c>
-      <s:c r="E24" s="49">
+      <s:c r="E24" s="50">
         <s:f>INDEX(Loan!$J$5:$J$124,MATCH((Assumptions!$B$48+3)*12,Loan!$A$5:$A$124,0))</s:f>
         <s:v>436366.00891021336</s:v>
       </s:c>
-      <s:c r="F24" s="49">
+      <s:c r="F24" s="50">
         <s:f>INDEX(Loan!$J$5:$J$124,MATCH((Assumptions!$B$48+4)*12,Loan!$A$5:$A$124,0))</s:f>
         <s:v>370683.0801669391</s:v>
       </s:c>
@@ -12756,28 +12798,28 @@
       </s:c>
     </s:row>
     <s:row r="28">
-      <s:c r="A28" s="64" t="inlineStr">
+      <s:c r="A28" s="65" t="inlineStr">
         <s:is>
           <s:t>საინვესტიციო/საფინანსო / Investing &amp; financing</s:t>
         </s:is>
       </s:c>
-      <s:c r="B28" s="49">
+      <s:c r="B28" s="50">
         <s:f>CF_Monthly!$N$40+CF_Monthly!$N$41</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C28" s="49">
+      <s:c r="C28" s="50">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="D28" s="49">
+      <s:c r="D28" s="50">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="E28" s="49">
+      <s:c r="E28" s="50">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="F28" s="49">
+      <s:c r="F28" s="50">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
@@ -12854,23 +12896,23 @@
           <s:t>DSCR (EBITDA / ვალის მომსახურება)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B33" s="68">
+      <s:c r="B33" s="69">
         <s:f>IFERROR(B17/B23,0)</s:f>
         <s:v>9.381214941511837</s:v>
       </s:c>
-      <s:c r="C33" s="68">
+      <s:c r="C33" s="69">
         <s:f>IFERROR(C17/C23,0)</s:f>
         <s:v>8.086985813880467</s:v>
       </s:c>
-      <s:c r="D33" s="68">
+      <s:c r="D33" s="69">
         <s:f>IFERROR(D17/D23,0)</s:f>
         <s:v>7.825738668291156</s:v>
       </s:c>
-      <s:c r="E33" s="68">
+      <s:c r="E33" s="69">
         <s:f>IFERROR(E17/E23,0)</s:f>
         <s:v>4.311629551456862</s:v>
       </s:c>
-      <s:c r="F33" s="68">
+      <s:c r="F33" s="69">
         <s:f>IFERROR(F17/F23,0)</s:f>
         <s:v>4.544675306342092</s:v>
       </s:c>
@@ -12962,7 +13004,7 @@
           <s:t>შემოწმება — წელი 1 ემთხვევა CF_Monthly-ს / Check — Year 1 ties to CF_Monthly (must be 0)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B38" s="65">
+      <s:c r="B38" s="66">
         <s:f>B29-CF_Monthly!$N$43</s:f>
         <s:v>0.0</s:v>
       </s:c>
@@ -13023,24 +13065,24 @@
           <s:t>მოსავალი ↓ / ფასი → | Yield ↓ / Price →</s:t>
         </s:is>
       </s:c>
-      <s:c r="B5" s="69" t="n">
+      <s:c r="B5" s="70" t="n">
         <s:v>-0.2</s:v>
       </s:c>
-      <s:c r="C5" s="69" t="n">
+      <s:c r="C5" s="70" t="n">
         <s:v>-0.1</s:v>
       </s:c>
-      <s:c r="D5" s="69" t="n">
+      <s:c r="D5" s="70" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="E5" s="69" t="n">
+      <s:c r="E5" s="70" t="n">
         <s:v>0.1</s:v>
       </s:c>
-      <s:c r="F5" s="69" t="n">
+      <s:c r="F5" s="70" t="n">
         <s:v>0.2</s:v>
       </s:c>
     </s:row>
     <s:row r="6">
-      <s:c r="A6" s="69" t="n">
+      <s:c r="A6" s="70" t="n">
         <s:v>-0.2</s:v>
       </s:c>
       <s:c r="B6" s="29">
@@ -13065,7 +13107,7 @@
       </s:c>
     </s:row>
     <s:row r="7">
-      <s:c r="A7" s="69" t="n">
+      <s:c r="A7" s="70" t="n">
         <s:v>-0.1</s:v>
       </s:c>
       <s:c r="B7" s="29">
@@ -13090,7 +13132,7 @@
       </s:c>
     </s:row>
     <s:row r="8">
-      <s:c r="A8" s="69" t="n">
+      <s:c r="A8" s="70" t="n">
         <s:v>0</s:v>
       </s:c>
       <s:c r="B8" s="29">
@@ -13115,7 +13157,7 @@
       </s:c>
     </s:row>
     <s:row r="9">
-      <s:c r="A9" s="69" t="n">
+      <s:c r="A9" s="70" t="n">
         <s:v>0.1</s:v>
       </s:c>
       <s:c r="B9" s="29">
@@ -13140,7 +13182,7 @@
       </s:c>
     </s:row>
     <s:row r="10">
-      <s:c r="A10" s="69" t="n">
+      <s:c r="A10" s="70" t="n">
         <s:v>0.2</s:v>
       </s:c>
       <s:c r="B10" s="29">
@@ -13183,143 +13225,143 @@
           <s:t>მოსავალი ↓ / ფასი →</s:t>
         </s:is>
       </s:c>
-      <s:c r="B13" s="69" t="n">
+      <s:c r="B13" s="70" t="n">
         <s:v>-0.2</s:v>
       </s:c>
-      <s:c r="C13" s="69" t="n">
+      <s:c r="C13" s="70" t="n">
         <s:v>-0.1</s:v>
       </s:c>
-      <s:c r="D13" s="69" t="n">
+      <s:c r="D13" s="70" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="E13" s="69" t="n">
+      <s:c r="E13" s="70" t="n">
         <s:v>0.1</s:v>
       </s:c>
-      <s:c r="F13" s="69" t="n">
+      <s:c r="F13" s="70" t="n">
         <s:v>0.2</s:v>
       </s:c>
     </s:row>
     <s:row r="14">
-      <s:c r="A14" s="69" t="n">
+      <s:c r="A14" s="70" t="n">
         <s:v>-0.2</s:v>
       </s:c>
-      <s:c r="B14" s="70">
+      <s:c r="B14" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A14)*Assumptions!$B$13*(1+B$13)+Assumptions!$B$15*(1+$A14)*Assumptions!$B$17*(1+B$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>4.859151332416979</s:v>
       </s:c>
-      <s:c r="C14" s="70">
+      <s:c r="C14" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A14)*Assumptions!$B$13*(1+C$13)+Assumptions!$B$15*(1+$A14)*Assumptions!$B$17*(1+C$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>5.864054356660281</s:v>
       </s:c>
-      <s:c r="D14" s="70">
+      <s:c r="D14" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A14)*Assumptions!$B$13*(1+D$13)+Assumptions!$B$15*(1+$A14)*Assumptions!$B$17*(1+D$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>6.868957380903582</s:v>
       </s:c>
-      <s:c r="E14" s="70">
+      <s:c r="E14" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A14)*Assumptions!$B$13*(1+E$13)+Assumptions!$B$15*(1+$A14)*Assumptions!$B$17*(1+E$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>7.873860405146885</s:v>
       </s:c>
-      <s:c r="F14" s="70">
+      <s:c r="F14" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A14)*Assumptions!$B$13*(1+F$13)+Assumptions!$B$15*(1+$A14)*Assumptions!$B$17*(1+F$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>8.878763429390187</s:v>
       </s:c>
     </s:row>
     <s:row r="15">
-      <s:c r="A15" s="69" t="n">
+      <s:c r="A15" s="70" t="n">
         <s:v>-0.1</s:v>
       </s:c>
-      <s:c r="B15" s="70">
+      <s:c r="B15" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A15)*Assumptions!$B$13*(1+B$13)+Assumptions!$B$15*(1+$A15)*Assumptions!$B$17*(1+B$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>5.864054356660281</s:v>
       </s:c>
-      <s:c r="C15" s="70">
+      <s:c r="C15" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A15)*Assumptions!$B$13*(1+C$13)+Assumptions!$B$15*(1+$A15)*Assumptions!$B$17*(1+C$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>6.9945702589339955</s:v>
       </s:c>
-      <s:c r="D15" s="70">
+      <s:c r="D15" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A15)*Assumptions!$B$13*(1+D$13)+Assumptions!$B$15*(1+$A15)*Assumptions!$B$17*(1+D$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>8.12508616120771</s:v>
       </s:c>
-      <s:c r="E15" s="70">
+      <s:c r="E15" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A15)*Assumptions!$B$13*(1+E$13)+Assumptions!$B$15*(1+$A15)*Assumptions!$B$17*(1+E$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>9.255602063481428</s:v>
       </s:c>
-      <s:c r="F15" s="70">
+      <s:c r="F15" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A15)*Assumptions!$B$13*(1+F$13)+Assumptions!$B$15*(1+$A15)*Assumptions!$B$17*(1+F$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>10.38611796575514</s:v>
       </s:c>
     </s:row>
     <s:row r="16">
-      <s:c r="A16" s="69" t="n">
+      <s:c r="A16" s="70" t="n">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="B16" s="70">
+      <s:c r="B16" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A16)*Assumptions!$B$13*(1+B$13)+Assumptions!$B$15*(1+$A16)*Assumptions!$B$17*(1+B$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>6.868957380903582</s:v>
       </s:c>
-      <s:c r="C16" s="70">
+      <s:c r="C16" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A16)*Assumptions!$B$13*(1+C$13)+Assumptions!$B$15*(1+$A16)*Assumptions!$B$17*(1+C$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>8.12508616120771</s:v>
       </s:c>
-      <s:c r="D16" s="70">
+      <s:c r="D16" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A16)*Assumptions!$B$13*(1+D$13)+Assumptions!$B$15*(1+$A16)*Assumptions!$B$17*(1+D$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>9.381214941511837</s:v>
       </s:c>
-      <s:c r="E16" s="70">
+      <s:c r="E16" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A16)*Assumptions!$B$13*(1+E$13)+Assumptions!$B$15*(1+$A16)*Assumptions!$B$17*(1+E$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>10.637343721815968</s:v>
       </s:c>
-      <s:c r="F16" s="70">
+      <s:c r="F16" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A16)*Assumptions!$B$13*(1+F$13)+Assumptions!$B$15*(1+$A16)*Assumptions!$B$17*(1+F$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>11.893472502120092</s:v>
       </s:c>
     </s:row>
     <s:row r="17">
-      <s:c r="A17" s="69" t="n">
+      <s:c r="A17" s="70" t="n">
         <s:v>0.1</s:v>
       </s:c>
-      <s:c r="B17" s="70">
+      <s:c r="B17" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A17)*Assumptions!$B$13*(1+B$13)+Assumptions!$B$15*(1+$A17)*Assumptions!$B$17*(1+B$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>7.873860405146886</s:v>
       </s:c>
-      <s:c r="C17" s="70">
+      <s:c r="C17" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A17)*Assumptions!$B$13*(1+C$13)+Assumptions!$B$15*(1+$A17)*Assumptions!$B$17*(1+C$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>9.255602063481424</s:v>
       </s:c>
-      <s:c r="D17" s="70">
+      <s:c r="D17" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A17)*Assumptions!$B$13*(1+D$13)+Assumptions!$B$15*(1+$A17)*Assumptions!$B$17*(1+D$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>10.637343721815965</s:v>
       </s:c>
-      <s:c r="E17" s="70">
+      <s:c r="E17" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A17)*Assumptions!$B$13*(1+E$13)+Assumptions!$B$15*(1+$A17)*Assumptions!$B$17*(1+E$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>12.019085380150507</s:v>
       </s:c>
-      <s:c r="F17" s="70">
+      <s:c r="F17" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A17)*Assumptions!$B$13*(1+F$13)+Assumptions!$B$15*(1+$A17)*Assumptions!$B$17*(1+F$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>13.400827038485046</s:v>
       </s:c>
     </s:row>
     <s:row r="18">
-      <s:c r="A18" s="69" t="n">
+      <s:c r="A18" s="70" t="n">
         <s:v>0.2</s:v>
       </s:c>
-      <s:c r="B18" s="70">
+      <s:c r="B18" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A18)*Assumptions!$B$13*(1+B$13)+Assumptions!$B$15*(1+$A18)*Assumptions!$B$17*(1+B$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>8.878763429390187</s:v>
       </s:c>
-      <s:c r="C18" s="70">
+      <s:c r="C18" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A18)*Assumptions!$B$13*(1+C$13)+Assumptions!$B$15*(1+$A18)*Assumptions!$B$17*(1+C$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>10.38611796575514</s:v>
       </s:c>
-      <s:c r="D18" s="70">
+      <s:c r="D18" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A18)*Assumptions!$B$13*(1+D$13)+Assumptions!$B$15*(1+$A18)*Assumptions!$B$17*(1+D$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>11.893472502120092</s:v>
       </s:c>
-      <s:c r="E18" s="70">
+      <s:c r="E18" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A18)*Assumptions!$B$13*(1+E$13)+Assumptions!$B$15*(1+$A18)*Assumptions!$B$17*(1+E$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>13.400827038485046</s:v>
       </s:c>
-      <s:c r="F18" s="70">
+      <s:c r="F18" s="71">
         <s:f>IFERROR(((Assumptions!$B$11*(1+$A18)*Assumptions!$B$13*(1+F$13)+Assumptions!$B$15*(1+$A18)*Assumptions!$B$17*(1+F$13))-CF_Monthly!$N$30)/CF_Monthly!$N$36,0)</s:f>
         <s:v>14.908181574849998</s:v>
       </s:c>
@@ -13376,7 +13418,7 @@
           <s:t>საჭირო საშუალო ფასი / Break-even blended price</s:t>
         </s:is>
       </s:c>
-      <s:c r="B24" s="38">
+      <s:c r="B24" s="39">
         <s:f>IFERROR(B21/CF_Monthly!$N$13,0)</s:f>
         <s:v>1.2720563262612072</s:v>
       </s:c>
@@ -13387,7 +13429,7 @@
           <s:t>ფაქტობრივი საშუალო ფასი / Actual blended price</s:t>
         </s:is>
       </s:c>
-      <s:c r="B25" s="38">
+      <s:c r="B25" s="39">
         <s:f>Assumptions!$B$19</s:f>
         <s:v>3.8225806451612905</s:v>
       </s:c>
@@ -13579,1091 +13621,1175 @@
       </s:c>
     </s:row>
     <s:row r="13">
-      <s:c r="A13" s="71" t="n">
+      <s:c r="A13" s="72" t="n">
         <s:v>46204</s:v>
       </s:c>
-      <s:c r="B13" s="63" t="inlineStr">
+      <s:c r="B13" s="64" t="inlineStr">
         <s:is>
           <s:t>ინვოისი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C13" s="63" t="inlineStr">
+      <s:c r="C13" s="64" t="inlineStr">
         <s:is>
           <s:t>შპს ტერმინალ ვესტ თრეიდინგ</s:t>
         </s:is>
       </s:c>
-      <s:c r="D13" s="63" t="inlineStr">
+      <s:c r="D13" s="64" t="inlineStr">
         <s:is>
           <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
         </s:is>
       </s:c>
-      <s:c r="E13" s="72" t="n">
+      <s:c r="E13" s="73" t="n">
         <s:v>-1409.41</s:v>
       </s:c>
     </s:row>
     <s:row r="14">
-      <s:c r="A14" s="71" t="n">
+      <s:c r="A14" s="72" t="n">
         <s:v>46204</s:v>
       </s:c>
-      <s:c r="B14" s="63" t="inlineStr">
+      <s:c r="B14" s="64" t="inlineStr">
         <s:is>
           <s:t>მომსახურების ანაზღაურება</s:t>
         </s:is>
       </s:c>
-      <s:c r="C14" s="63" t="inlineStr">
+      <s:c r="C14" s="64" t="inlineStr">
         <s:is>
           <s:t>ნუგზარი ბუნტური</s:t>
         </s:is>
       </s:c>
-      <s:c r="D14" s="63" t="inlineStr">
+      <s:c r="D14" s="64" t="inlineStr">
         <s:is>
           <s:t>მომსახურება / Services</s:t>
         </s:is>
       </s:c>
-      <s:c r="E14" s="72" t="n">
+      <s:c r="E14" s="73" t="n">
         <s:v>-500</s:v>
       </s:c>
     </s:row>
     <s:row r="15">
-      <s:c r="A15" s="71" t="n">
+      <s:c r="A15" s="72" t="n">
         <s:v>46204</s:v>
       </s:c>
-      <s:c r="B15" s="63" t="inlineStr">
+      <s:c r="B15" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C15" s="63" t="inlineStr">
+      <s:c r="C15" s="64" t="inlineStr">
         <s:is>
           <s:t>ნატალია ქანანელი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D15" s="63" t="inlineStr">
+      <s:c r="D15" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
-      <s:c r="E15" s="72" t="n">
+      <s:c r="E15" s="73" t="n">
         <s:v>-1000</s:v>
       </s:c>
     </s:row>
     <s:row r="16">
-      <s:c r="A16" s="71" t="n">
+      <s:c r="A16" s="72" t="n">
         <s:v>46204</s:v>
       </s:c>
-      <s:c r="B16" s="63" t="inlineStr">
+      <s:c r="B16" s="64" t="inlineStr">
         <s:is>
           <s:t>თანახმად ხელშეკრულებისა; მომსახურება</s:t>
         </s:is>
       </s:c>
-      <s:c r="C16" s="63" t="inlineStr">
+      <s:c r="C16" s="64" t="inlineStr">
         <s:is>
           <s:t>გიორგი მღებრიშვილი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D16" s="63" t="inlineStr">
+      <s:c r="D16" s="64" t="inlineStr">
         <s:is>
           <s:t>მომსახურება / Services</s:t>
         </s:is>
       </s:c>
-      <s:c r="E16" s="72" t="n">
+      <s:c r="E16" s="73" t="n">
         <s:v>-1600</s:v>
       </s:c>
     </s:row>
     <s:row r="17">
-      <s:c r="A17" s="71" t="n">
+      <s:c r="A17" s="72" t="n">
         <s:v>46212</s:v>
       </s:c>
-      <s:c r="B17" s="63" t="inlineStr">
+      <s:c r="B17" s="64" t="inlineStr">
         <s:is>
           <s:t>ავანსი თანახმად ხელშეკრულება N1 7/6/2026 (22 000 აშშ დოლარი, ერ.კ. 2.6384)</s:t>
         </s:is>
       </s:c>
-      <s:c r="C17" s="63" t="inlineStr">
+      <s:c r="C17" s="64" t="inlineStr">
         <s:is>
           <s:t>შპს ჯიესენ გრუპ</s:t>
         </s:is>
       </s:c>
-      <s:c r="D17" s="63" t="inlineStr">
+      <s:c r="D17" s="64" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
-      <s:c r="E17" s="72" t="n">
+      <s:c r="E17" s="73" t="n">
         <s:v>-58044.8</s:v>
       </s:c>
     </s:row>
     <s:row r="18">
-      <s:c r="A18" s="71" t="n">
+      <s:c r="A18" s="72" t="n">
         <s:v>46216</s:v>
       </s:c>
-      <s:c r="B18" s="63" t="inlineStr">
+      <s:c r="B18" s="64" t="inlineStr">
         <s:is>
           <s:t>ელექტრო მასალების შეძენა; ლითონის სამონტაჟო მასალები</s:t>
         </s:is>
       </s:c>
-      <s:c r="C18" s="63" t="inlineStr">
+      <s:c r="C18" s="64" t="inlineStr">
         <s:is>
           <s:t>ი.მ. შოთა კერესელიძე</s:t>
         </s:is>
       </s:c>
-      <s:c r="D18" s="63" t="inlineStr">
+      <s:c r="D18" s="64" t="inlineStr">
         <s:is>
           <s:t>მასალები / Materials</s:t>
         </s:is>
       </s:c>
-      <s:c r="E18" s="72" t="n">
+      <s:c r="E18" s="73" t="n">
         <s:v>-4660</s:v>
       </s:c>
     </s:row>
     <s:row r="19">
-      <s:c r="A19" s="71" t="n">
+      <s:c r="A19" s="72" t="n">
         <s:v>46219</s:v>
       </s:c>
-      <s:c r="B19" s="63" t="inlineStr">
+      <s:c r="B19" s="64" t="inlineStr">
         <s:is>
           <s:t>ინვოისი 154-729 27/06/2026</s:t>
         </s:is>
       </s:c>
-      <s:c r="C19" s="63" t="inlineStr">
+      <s:c r="C19" s="64" t="inlineStr">
         <s:is>
           <s:t>შპს ენ ბი სი ჯგუფი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D19" s="63" t="inlineStr">
+      <s:c r="D19" s="64" t="inlineStr">
         <s:is>
           <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
         </s:is>
       </s:c>
-      <s:c r="E19" s="72" t="n">
+      <s:c r="E19" s="73" t="n">
         <s:v>-1450</s:v>
       </s:c>
     </s:row>
     <s:row r="20">
-      <s:c r="A20" s="71" t="n">
+      <s:c r="A20" s="72" t="n">
         <s:v>46238</s:v>
       </s:c>
-      <s:c r="B20" s="63" t="inlineStr">
+      <s:c r="B20" s="64" t="inlineStr">
         <s:is>
           <s:t>ავანსი თანახმად ხელშეკრულება N1 7/6/2026 (5 000 აშშ დოლარი)</s:t>
         </s:is>
       </s:c>
-      <s:c r="C20" s="63" t="inlineStr">
+      <s:c r="C20" s="64" t="inlineStr">
         <s:is>
           <s:t>შპს ჯიესენ გრუპ</s:t>
         </s:is>
       </s:c>
-      <s:c r="D20" s="63" t="inlineStr">
+      <s:c r="D20" s="64" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
-      <s:c r="E20" s="72" t="n">
+      <s:c r="E20" s="73" t="n">
         <s:v>-13100</s:v>
       </s:c>
     </s:row>
     <s:row r="21">
-      <s:c r="A21" s="71" t="n">
+      <s:c r="A21" s="72" t="n">
         <s:v>46238</s:v>
       </s:c>
-      <s:c r="B21" s="63" t="inlineStr">
+      <s:c r="B21" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C21" s="63" t="inlineStr">
+      <s:c r="C21" s="64" t="inlineStr">
         <s:is>
           <s:t>გოდერძი მეტრეველი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D21" s="63" t="inlineStr">
+      <s:c r="D21" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
-      <s:c r="E21" s="72" t="n">
+      <s:c r="E21" s="73" t="n">
         <s:v>-2000</s:v>
       </s:c>
     </s:row>
     <s:row r="22">
-      <s:c r="A22" s="71" t="n">
+      <s:c r="A22" s="72" t="n">
         <s:v>46244</s:v>
       </s:c>
-      <s:c r="B22" s="63" t="inlineStr">
+      <s:c r="B22" s="64" t="inlineStr">
         <s:is>
           <s:t>საქვეანგარიშოდ საჯარო რეესტრში გაწეული ხარჯისათვის</s:t>
         </s:is>
       </s:c>
-      <s:c r="C22" s="63" t="inlineStr">
+      <s:c r="C22" s="64" t="inlineStr">
         <s:is>
           <s:t>გოდერძი მეტრეველი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D22" s="63" t="inlineStr">
+      <s:c r="D22" s="64" t="inlineStr">
         <s:is>
           <s:t>სხვა / Other</s:t>
         </s:is>
       </s:c>
-      <s:c r="E22" s="72" t="n">
+      <s:c r="E22" s="73" t="n">
         <s:v>-307</s:v>
       </s:c>
     </s:row>
     <s:row r="23">
-      <s:c r="A23" s="71" t="n">
+      <s:c r="A23" s="72" t="n">
         <s:v>46244</s:v>
       </s:c>
-      <s:c r="B23" s="63" t="inlineStr">
+      <s:c r="B23" s="64" t="inlineStr">
         <s:is>
           <s:t>საპენსიო გადასახადი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C23" s="63" t="inlineStr">
+      <s:c r="C23" s="64" t="inlineStr">
         <s:is>
           <s:t>სსიპ საქართველოს საპენსიო ფონდი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D23" s="63" t="inlineStr">
+      <s:c r="D23" s="64" t="inlineStr">
         <s:is>
           <s:t>გადასახადები / Taxes &amp; pension</s:t>
         </s:is>
       </s:c>
-      <s:c r="E23" s="72" t="n">
+      <s:c r="E23" s="73" t="n">
         <s:v>-170</s:v>
       </s:c>
     </s:row>
     <s:row r="24">
-      <s:c r="A24" s="71" t="n">
+      <s:c r="A24" s="72" t="n">
         <s:v>46260</s:v>
       </s:c>
-      <s:c r="B24" s="63" t="inlineStr">
+      <s:c r="B24" s="64" t="inlineStr">
         <s:is>
           <s:t>გადასახადების ერთიანი კოდი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C24" s="63" t="inlineStr">
+      <s:c r="C24" s="64" t="inlineStr">
         <s:is>
           <s:t>ხაზინის ერთიანი ანგარიში (RS)</s:t>
         </s:is>
       </s:c>
-      <s:c r="D24" s="63" t="inlineStr">
+      <s:c r="D24" s="64" t="inlineStr">
         <s:is>
           <s:t>გადასახადები / Taxes &amp; pension</s:t>
         </s:is>
       </s:c>
-      <s:c r="E24" s="72" t="n">
+      <s:c r="E24" s="73" t="n">
         <s:v>-900</s:v>
       </s:c>
     </s:row>
     <s:row r="25">
-      <s:c r="A25" s="71" t="n">
+      <s:c r="A25" s="72" t="n">
         <s:v>46260</s:v>
       </s:c>
-      <s:c r="B25" s="63" t="inlineStr">
+      <s:c r="B25" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C25" s="63" t="inlineStr">
+      <s:c r="C25" s="64" t="inlineStr">
         <s:is>
           <s:t>ნატალია ქანანელი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D25" s="63" t="inlineStr">
+      <s:c r="D25" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
-      <s:c r="E25" s="72" t="n">
+      <s:c r="E25" s="73" t="n">
         <s:v>-2000</s:v>
       </s:c>
     </s:row>
     <s:row r="26">
-      <s:c r="A26" s="71" t="n">
+      <s:c r="A26" s="72" t="n">
         <s:v>46265</s:v>
       </s:c>
-      <s:c r="B26" s="63" t="inlineStr">
+      <s:c r="B26" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C26" s="63" t="inlineStr">
+      <s:c r="C26" s="64" t="inlineStr">
         <s:is>
           <s:t>გოდერძი მეტრეველი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D26" s="63" t="inlineStr">
+      <s:c r="D26" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
-      <s:c r="E26" s="72" t="n">
+      <s:c r="E26" s="73" t="n">
         <s:v>-3000</s:v>
       </s:c>
     </s:row>
     <s:row r="27">
-      <s:c r="A27" s="71" t="n">
+      <s:c r="A27" s="72" t="n">
         <s:v>46273</s:v>
       </s:c>
-      <s:c r="B27" s="63" t="inlineStr">
+      <s:c r="B27" s="64" t="inlineStr">
         <s:is>
           <s:t>საპენსიო გადასახადი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C27" s="63" t="inlineStr">
+      <s:c r="C27" s="64" t="inlineStr">
         <s:is>
           <s:t>სსიპ საქართველოს საპენსიო ფონდი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D27" s="63" t="inlineStr">
+      <s:c r="D27" s="64" t="inlineStr">
         <s:is>
           <s:t>გადასახადები / Taxes &amp; pension</s:t>
         </s:is>
       </s:c>
-      <s:c r="E27" s="72" t="n">
+      <s:c r="E27" s="73" t="n">
         <s:v>-400</s:v>
       </s:c>
     </s:row>
     <s:row r="28">
-      <s:c r="A28" s="71" t="n">
+      <s:c r="A28" s="72" t="n">
         <s:v>46279</s:v>
       </s:c>
-      <s:c r="B28" s="63" t="inlineStr">
+      <s:c r="B28" s="64" t="inlineStr">
         <s:is>
           <s:t>ავანსი თანახმად ხელშეკრულება (ხელშ. N1)</s:t>
         </s:is>
       </s:c>
-      <s:c r="C28" s="63" t="inlineStr">
+      <s:c r="C28" s="64" t="inlineStr">
         <s:is>
           <s:t>შპს ჯიესენ გრუპ</s:t>
         </s:is>
       </s:c>
-      <s:c r="D28" s="63" t="inlineStr">
+      <s:c r="D28" s="64" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
-      <s:c r="E28" s="72" t="n">
+      <s:c r="E28" s="73" t="n">
         <s:v>-1500</s:v>
       </s:c>
     </s:row>
     <s:row r="29">
-      <s:c r="A29" s="71" t="n">
+      <s:c r="A29" s="72" t="n">
         <s:v>46279</s:v>
       </s:c>
-      <s:c r="B29" s="63" t="inlineStr">
+      <s:c r="B29" s="64" t="inlineStr">
         <s:is>
           <s:t>ავანსი თანახმად ხელშეკრულება (ხელშ. N1)</s:t>
         </s:is>
       </s:c>
-      <s:c r="C29" s="63" t="inlineStr">
+      <s:c r="C29" s="64" t="inlineStr">
         <s:is>
           <s:t>შპს ჯიესენ გრუპ</s:t>
         </s:is>
       </s:c>
-      <s:c r="D29" s="63" t="inlineStr">
+      <s:c r="D29" s="64" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
-      <s:c r="E29" s="72" t="n">
+      <s:c r="E29" s="73" t="n">
         <s:v>-1400</s:v>
       </s:c>
     </s:row>
     <s:row r="30">
-      <s:c r="A30" s="71" t="n">
+      <s:c r="A30" s="72" t="n">
         <s:v>46279</s:v>
       </s:c>
-      <s:c r="B30" s="63" t="inlineStr">
+      <s:c r="B30" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C30" s="63" t="inlineStr">
+      <s:c r="C30" s="64" t="inlineStr">
         <s:is>
           <s:t>გოდერძი მეტრეველი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D30" s="63" t="inlineStr">
+      <s:c r="D30" s="64" t="inlineStr">
         <s:is>
           <s:t>ხელფასი / Salaries</s:t>
         </s:is>
       </s:c>
-      <s:c r="E30" s="72" t="n">
+      <s:c r="E30" s="73" t="n">
         <s:v>-2000</s:v>
       </s:c>
     </s:row>
     <s:row r="31">
-      <s:c r="A31" s="71" t="n">
+      <s:c r="A31" s="72" t="n">
         <s:v>46279</s:v>
       </s:c>
-      <s:c r="B31" s="63" t="inlineStr">
+      <s:c r="B31" s="64" t="inlineStr">
         <s:is>
           <s:t>ინვოისი 12866 14/09/2026</s:t>
         </s:is>
       </s:c>
-      <s:c r="C31" s="63" t="inlineStr">
+      <s:c r="C31" s="64" t="inlineStr">
         <s:is>
           <s:t>შპს კლუგერი 1</s:t>
         </s:is>
       </s:c>
-      <s:c r="D31" s="63" t="inlineStr">
+      <s:c r="D31" s="64" t="inlineStr">
         <s:is>
           <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
         </s:is>
       </s:c>
-      <s:c r="E31" s="72" t="n">
+      <s:c r="E31" s="73" t="n">
         <s:v>-1616</s:v>
       </s:c>
     </s:row>
     <s:row r="32">
-      <s:c r="A32" s="71" t="n">
+      <s:c r="A32" s="72" t="n">
         <s:v>46279</s:v>
       </s:c>
-      <s:c r="B32" s="63" t="inlineStr">
+      <s:c r="B32" s="64" t="inlineStr">
         <s:is>
           <s:t>მომსახურება</s:t>
         </s:is>
       </s:c>
-      <s:c r="C32" s="63" t="inlineStr">
+      <s:c r="C32" s="64" t="inlineStr">
         <s:is>
           <s:t>ვაჟა ბოდაველი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D32" s="63" t="inlineStr">
+      <s:c r="D32" s="64" t="inlineStr">
         <s:is>
           <s:t>მომსახურება / Services</s:t>
         </s:is>
       </s:c>
-      <s:c r="E32" s="72" t="n">
+      <s:c r="E32" s="73" t="n">
         <s:v>-150</s:v>
       </s:c>
     </s:row>
     <s:row r="33">
-      <s:c r="A33" s="71" t="n">
+      <s:c r="A33" s="72" t="n">
         <s:v>46279</s:v>
       </s:c>
-      <s:c r="B33" s="63" t="inlineStr">
+      <s:c r="B33" s="64" t="inlineStr">
         <s:is>
           <s:t>სესხის ერთჯერადი მომსახურების საკომისიო GA/1-876787-001</s:t>
         </s:is>
       </s:c>
-      <s:c r="C33" s="63" t="inlineStr">
+      <s:c r="C33" s="64" t="inlineStr">
         <s:is>
           <s:t>სს ბანკი ქართუ</s:t>
         </s:is>
       </s:c>
-      <s:c r="D33" s="63" t="inlineStr">
+      <s:c r="D33" s="64" t="inlineStr">
         <s:is>
           <s:t>სხვა / Other</s:t>
         </s:is>
       </s:c>
-      <s:c r="E33" s="72" t="n">
+      <s:c r="E33" s="73" t="n">
         <s:v>-60</s:v>
       </s:c>
     </s:row>
     <s:row r="34">
-      <s:c r="A34" s="71" t="n">
+      <s:c r="A34" s="72" t="n">
         <s:v>46281</s:v>
       </s:c>
-      <s:c r="B34" s="63" t="inlineStr">
+      <s:c r="B34" s="64" t="inlineStr">
         <s:is>
           <s:t>ინვოისი 20260916A 16/09/2026</s:t>
         </s:is>
       </s:c>
-      <s:c r="C34" s="63" t="inlineStr">
+      <s:c r="C34" s="64" t="inlineStr">
         <s:is>
           <s:t>შპს იბოსთარ</s:t>
         </s:is>
       </s:c>
-      <s:c r="D34" s="63" t="inlineStr">
+      <s:c r="D34" s="64" t="inlineStr">
         <s:is>
           <s:t>მომწოდებლის ინვოისი / Supplier invoice</s:t>
         </s:is>
       </s:c>
-      <s:c r="E34" s="72" t="n">
+      <s:c r="E34" s="73" t="n">
         <s:v>-3030</s:v>
       </s:c>
     </s:row>
     <s:row r="35">
-      <s:c r="A35" s="71" t="n">
+      <s:c r="A35" s="72" t="n">
         <s:v>46281</s:v>
       </s:c>
-      <s:c r="B35" s="63" t="inlineStr">
+      <s:c r="B35" s="64" t="inlineStr">
         <s:is>
           <s:t>სასაქონლო ზედნადებებით პროდუქციის საფასური</s:t>
         </s:is>
       </s:c>
-      <s:c r="C35" s="63" t="inlineStr">
+      <s:c r="C35" s="64" t="inlineStr">
         <s:is>
           <s:t>ი.მ. ლალი ზეიკიძე</s:t>
         </s:is>
       </s:c>
-      <s:c r="D35" s="63" t="inlineStr">
+      <s:c r="D35" s="64" t="inlineStr">
         <s:is>
           <s:t>მასალები / Materials</s:t>
         </s:is>
       </s:c>
-      <s:c r="E35" s="72" t="n">
+      <s:c r="E35" s="73" t="n">
         <s:v>-467.7</s:v>
       </s:c>
     </s:row>
     <s:row r="36">
-      <s:c r="A36" s="71" t="n">
+      <s:c r="A36" s="72" t="n">
         <s:v>46281</s:v>
       </s:c>
-      <s:c r="B36" s="63" t="inlineStr">
+      <s:c r="B36" s="64" t="inlineStr">
         <s:is>
           <s:t>ცემენტის ღირებულება</s:t>
         </s:is>
       </s:c>
-      <s:c r="C36" s="63" t="inlineStr">
+      <s:c r="C36" s="64" t="inlineStr">
         <s:is>
           <s:t>სოსო ხლუსიძე</s:t>
         </s:is>
       </s:c>
-      <s:c r="D36" s="63" t="inlineStr">
+      <s:c r="D36" s="64" t="inlineStr">
         <s:is>
           <s:t>მასალები / Materials</s:t>
         </s:is>
       </s:c>
-      <s:c r="E36" s="72" t="n">
+      <s:c r="E36" s="73" t="n">
         <s:v>-170</s:v>
       </s:c>
     </s:row>
     <s:row r="37">
-      <s:c r="A37" s="71" t="n">
+      <s:c r="A37" s="72" t="n">
         <s:v>46283</s:v>
       </s:c>
-      <s:c r="B37" s="63" t="inlineStr">
+      <s:c r="B37" s="64" t="inlineStr">
         <s:is>
           <s:t>ცემენტის ღირებულება, ზედნადები 1008422939 18/09/2026</s:t>
         </s:is>
       </s:c>
-      <s:c r="C37" s="63" t="inlineStr">
+      <s:c r="C37" s="64" t="inlineStr">
         <s:is>
           <s:t>სოსო ხლუსიძე</s:t>
         </s:is>
       </s:c>
-      <s:c r="D37" s="63" t="inlineStr">
+      <s:c r="D37" s="64" t="inlineStr">
         <s:is>
           <s:t>მასალები / Materials</s:t>
         </s:is>
       </s:c>
-      <s:c r="E37" s="72" t="n">
+      <s:c r="E37" s="73" t="n">
         <s:v>-425</s:v>
       </s:c>
     </s:row>
     <s:row r="38">
-      <s:c r="A38" s="71" t="n">
+      <s:c r="A38" s="72" t="n">
         <s:v>46283</s:v>
       </s:c>
-      <s:c r="B38" s="63" t="inlineStr">
+      <s:c r="B38" s="64" t="inlineStr">
         <s:is>
           <s:t>მომსახურება</s:t>
         </s:is>
       </s:c>
-      <s:c r="C38" s="63" t="inlineStr">
+      <s:c r="C38" s="64" t="inlineStr">
         <s:is>
           <s:t>რაუფ ბაირამოვი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D38" s="63" t="inlineStr">
+      <s:c r="D38" s="64" t="inlineStr">
         <s:is>
           <s:t>მომსახურება / Services</s:t>
         </s:is>
       </s:c>
-      <s:c r="E38" s="72" t="n">
+      <s:c r="E38" s="73" t="n">
         <s:v>-820</s:v>
       </s:c>
     </s:row>
     <s:row r="39">
-      <s:c r="A39" s="71" t="n">
+      <s:c r="A39" s="72" t="n">
         <s:v>46283</s:v>
       </s:c>
-      <s:c r="B39" s="63" t="inlineStr">
+      <s:c r="B39" s="64" t="inlineStr">
         <s:is>
           <s:t>ამწე მომსახურება — სამონტაჟო სამუშაო, კაპიტალიზებული</s:t>
         </s:is>
       </s:c>
-      <s:c r="C39" s="63" t="inlineStr">
+      <s:c r="C39" s="64" t="inlineStr">
         <s:is>
           <s:t>აკაკი ბუჩაშვილი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D39" s="63" t="inlineStr">
+      <s:c r="D39" s="64" t="inlineStr">
         <s:is>
           <s:t>სხვა / Other</s:t>
         </s:is>
       </s:c>
-      <s:c r="E39" s="72" t="n">
+      <s:c r="E39" s="73" t="n">
         <s:v>-550</s:v>
       </s:c>
     </s:row>
     <s:row r="40">
-      <s:c r="A40" s="71" t="n">
+      <s:c r="A40" s="72" t="n">
         <s:v>46283</s:v>
       </s:c>
-      <s:c r="B40" s="63" t="inlineStr">
+      <s:c r="B40" s="64" t="inlineStr">
         <s:is>
           <s:t>საბანკო საკომისიოები — 11 გადარიცხვა, 11–18/09/2026</s:t>
         </s:is>
       </s:c>
-      <s:c r="C40" s="63" t="inlineStr">
+      <s:c r="C40" s="64" t="inlineStr">
         <s:is>
           <s:t>სს ბანკი ქართუ</s:t>
         </s:is>
       </s:c>
-      <s:c r="D40" s="63" t="inlineStr">
+      <s:c r="D40" s="64" t="inlineStr">
         <s:is>
           <s:t>სხვა / Other</s:t>
         </s:is>
       </s:c>
-      <s:c r="E40" s="72" t="n">
+      <s:c r="E40" s="73" t="n">
         <s:v>-12.08</s:v>
       </s:c>
     </s:row>
     <s:row r="41">
-      <s:c r="A41" s="71" t="n">
+      <s:c r="A41" s="72" t="n">
         <s:v>46284</s:v>
       </s:c>
-      <s:c r="B41" s="63" t="inlineStr">
+      <s:c r="B41" s="64" t="inlineStr">
         <s:is>
           <s:t>ავანსი ხელშეკრულება N1 (40 000 აშშ დოლარი, ერ.კ. 2.6125)</s:t>
         </s:is>
       </s:c>
-      <s:c r="C41" s="63" t="inlineStr">
+      <s:c r="C41" s="64" t="inlineStr">
         <s:is>
           <s:t>შპს ჯიესენ გრუპ</s:t>
         </s:is>
       </s:c>
-      <s:c r="D41" s="63" t="inlineStr">
+      <s:c r="D41" s="64" t="inlineStr">
         <s:is>
           <s:t>მშენებლობის ავანსი / Construction advance</s:t>
         </s:is>
       </s:c>
-      <s:c r="E41" s="72" t="n">
+      <s:c r="E41" s="73" t="n">
         <s:v>-104500</s:v>
       </s:c>
     </s:row>
     <s:row r="42">
-      <s:c r="A42" s="71" t="n">
+      <s:c r="A42" s="72" t="n">
         <s:v>46286</s:v>
       </s:c>
-      <s:c r="B42" s="63" t="inlineStr">
+      <s:c r="B42" s="64" t="inlineStr">
         <s:is>
           <s:t>მუშების კვება — საქვეანგარიშოდ დირექტორზე</s:t>
         </s:is>
       </s:c>
-      <s:c r="C42" s="63" t="inlineStr">
+      <s:c r="C42" s="64" t="inlineStr">
         <s:is>
           <s:t>გოდერძი მეტრეველი</s:t>
         </s:is>
       </s:c>
-      <s:c r="D42" s="63" t="inlineStr">
+      <s:c r="D42" s="64" t="inlineStr">
         <s:is>
           <s:t>მუშების კვება / Worker meals</s:t>
         </s:is>
       </s:c>
-      <s:c r="E42" s="72" t="n">
+      <s:c r="E42" s="73" t="n">
         <s:v>-10000</s:v>
       </s:c>
     </s:row>
     <s:row r="43">
-      <s:c r="A43" s="71" t="n">
+      <s:c r="A43" s="72" t="n">
         <s:v>46205</s:v>
       </s:c>
-      <s:c r="B43" s="63" t="inlineStr">
+      <s:c r="B43" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 27.62 ლ — SANAPIRO</s:t>
         </s:is>
       </s:c>
-      <s:c r="C43" s="63" t="inlineStr"/>
-      <s:c r="D43" s="63" t="inlineStr">
+      <s:c r="C43" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D43" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E43" s="72" t="n">
+      <s:c r="E43" s="73" t="n">
         <s:v>-100</s:v>
       </s:c>
     </s:row>
     <s:row r="44">
-      <s:c r="A44" s="71" t="n">
+      <s:c r="A44" s="72" t="n">
         <s:v>46208</s:v>
       </s:c>
-      <s:c r="B44" s="63" t="inlineStr">
+      <s:c r="B44" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 29.67 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C44" s="63" t="inlineStr"/>
-      <s:c r="D44" s="63" t="inlineStr">
+      <s:c r="C44" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D44" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E44" s="72" t="n">
+      <s:c r="E44" s="73" t="n">
         <s:v>-100</s:v>
       </s:c>
     </s:row>
     <s:row r="45">
-      <s:c r="A45" s="71" t="n">
+      <s:c r="A45" s="72" t="n">
         <s:v>46212</s:v>
       </s:c>
-      <s:c r="B45" s="63" t="inlineStr">
+      <s:c r="B45" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 65 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C45" s="63" t="inlineStr"/>
-      <s:c r="D45" s="63" t="inlineStr">
+      <s:c r="C45" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D45" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E45" s="72" t="n">
+      <s:c r="E45" s="73" t="n">
         <s:v>-222.3</s:v>
       </s:c>
     </s:row>
     <s:row r="46">
-      <s:c r="A46" s="71" t="n">
+      <s:c r="A46" s="72" t="n">
         <s:v>46220</s:v>
       </s:c>
-      <s:c r="B46" s="63" t="inlineStr">
+      <s:c r="B46" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 50 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C46" s="63" t="inlineStr"/>
-      <s:c r="D46" s="63" t="inlineStr">
+      <s:c r="C46" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D46" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E46" s="72" t="n">
+      <s:c r="E46" s="73" t="n">
         <s:v>-171</s:v>
       </s:c>
     </s:row>
     <s:row r="47">
-      <s:c r="A47" s="71" t="n">
+      <s:c r="A47" s="72" t="n">
         <s:v>46222</s:v>
       </s:c>
-      <s:c r="B47" s="63" t="inlineStr">
+      <s:c r="B47" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი Euro Diesel 11.55 ლ — SAGAREJO</s:t>
         </s:is>
       </s:c>
-      <s:c r="C47" s="63" t="inlineStr"/>
-      <s:c r="D47" s="63" t="inlineStr">
+      <s:c r="C47" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D47" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E47" s="72" t="n">
+      <s:c r="E47" s="73" t="n">
         <s:v>-44.12</s:v>
       </s:c>
     </s:row>
     <s:row r="48">
-      <s:c r="A48" s="71" t="n">
+      <s:c r="A48" s="72" t="n">
         <s:v>46225</s:v>
       </s:c>
-      <s:c r="B48" s="63" t="inlineStr">
+      <s:c r="B48" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 65 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C48" s="63" t="inlineStr"/>
-      <s:c r="D48" s="63" t="inlineStr">
+      <s:c r="C48" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D48" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E48" s="72" t="n">
+      <s:c r="E48" s="73" t="n">
         <s:v>-219.05</s:v>
       </s:c>
     </s:row>
     <s:row r="49">
-      <s:c r="A49" s="71" t="n">
+      <s:c r="A49" s="72" t="n">
         <s:v>46229</s:v>
       </s:c>
-      <s:c r="B49" s="63" t="inlineStr">
+      <s:c r="B49" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 30 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C49" s="63" t="inlineStr"/>
-      <s:c r="D49" s="63" t="inlineStr">
+      <s:c r="C49" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D49" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E49" s="72" t="n">
+      <s:c r="E49" s="73" t="n">
         <s:v>-103.5</s:v>
       </s:c>
     </s:row>
     <s:row r="50">
-      <s:c r="A50" s="71" t="n">
+      <s:c r="A50" s="72" t="n">
         <s:v>46232</s:v>
       </s:c>
-      <s:c r="B50" s="63" t="inlineStr">
+      <s:c r="B50" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 50 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C50" s="63" t="inlineStr"/>
-      <s:c r="D50" s="63" t="inlineStr">
+      <s:c r="C50" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D50" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E50" s="72" t="n">
+      <s:c r="E50" s="73" t="n">
         <s:v>-172.5</s:v>
       </s:c>
     </s:row>
     <s:row r="51">
-      <s:c r="A51" s="71" t="n">
+      <s:c r="A51" s="72" t="n">
         <s:v>46238</s:v>
       </s:c>
-      <s:c r="B51" s="63" t="inlineStr">
+      <s:c r="B51" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 50 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C51" s="63" t="inlineStr"/>
-      <s:c r="D51" s="63" t="inlineStr">
+      <s:c r="C51" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D51" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E51" s="72" t="n">
+      <s:c r="E51" s="73" t="n">
         <s:v>-175</s:v>
       </s:c>
     </s:row>
     <s:row r="52">
-      <s:c r="A52" s="71" t="n">
+      <s:c r="A52" s="72" t="n">
         <s:v>46240</s:v>
       </s:c>
-      <s:c r="B52" s="63" t="inlineStr">
+      <s:c r="B52" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 60 ლ — BIO</s:t>
         </s:is>
       </s:c>
-      <s:c r="C52" s="63" t="inlineStr"/>
-      <s:c r="D52" s="63" t="inlineStr">
+      <s:c r="C52" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D52" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E52" s="72" t="n">
+      <s:c r="E52" s="73" t="n">
         <s:v>-210</s:v>
       </s:c>
     </s:row>
     <s:row r="53">
-      <s:c r="A53" s="71" t="n">
+      <s:c r="A53" s="72" t="n">
         <s:v>46241</s:v>
       </s:c>
-      <s:c r="B53" s="63" t="inlineStr">
+      <s:c r="B53" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი Euro Diesel 11 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C53" s="63" t="inlineStr"/>
-      <s:c r="D53" s="63" t="inlineStr">
+      <s:c r="C53" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D53" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E53" s="72" t="n">
+      <s:c r="E53" s="73" t="n">
         <s:v>-42.9</s:v>
       </s:c>
     </s:row>
     <s:row r="54">
-      <s:c r="A54" s="71" t="n">
+      <s:c r="A54" s="72" t="n">
         <s:v>46243</s:v>
       </s:c>
-      <s:c r="B54" s="63" t="inlineStr">
+      <s:c r="B54" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 28.99 ლ — BIO</s:t>
         </s:is>
       </s:c>
-      <s:c r="C54" s="63" t="inlineStr"/>
-      <s:c r="D54" s="63" t="inlineStr">
+      <s:c r="C54" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D54" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E54" s="72" t="n">
+      <s:c r="E54" s="73" t="n">
         <s:v>-100</s:v>
       </s:c>
     </s:row>
     <s:row r="55">
-      <s:c r="A55" s="71" t="n">
+      <s:c r="A55" s="72" t="n">
         <s:v>46254</s:v>
       </s:c>
-      <s:c r="B55" s="63" t="inlineStr">
+      <s:c r="B55" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 10 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C55" s="63" t="inlineStr"/>
-      <s:c r="D55" s="63" t="inlineStr">
+      <s:c r="C55" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D55" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E55" s="72" t="n">
+      <s:c r="E55" s="73" t="n">
         <s:v>-35.6</s:v>
       </s:c>
     </s:row>
     <s:row r="56">
-      <s:c r="A56" s="71" t="n">
+      <s:c r="A56" s="72" t="n">
         <s:v>46268</s:v>
       </s:c>
-      <s:c r="B56" s="63" t="inlineStr">
+      <s:c r="B56" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 10 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C56" s="63" t="inlineStr"/>
-      <s:c r="D56" s="63" t="inlineStr">
+      <s:c r="C56" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D56" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E56" s="72" t="n">
+      <s:c r="E56" s="73" t="n">
         <s:v>-36.6</s:v>
       </s:c>
     </s:row>
     <s:row r="57">
-      <s:c r="A57" s="71" t="n">
+      <s:c r="A57" s="72" t="n">
         <s:v>46268</s:v>
       </s:c>
-      <s:c r="B57" s="63" t="inlineStr">
+      <s:c r="B57" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 40 ლ — COSMONAVTI EXPRESS</s:t>
         </s:is>
       </s:c>
-      <s:c r="C57" s="63" t="inlineStr"/>
-      <s:c r="D57" s="63" t="inlineStr">
+      <s:c r="C57" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D57" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E57" s="72" t="n">
+      <s:c r="E57" s="73" t="n">
         <s:v>-146.4</s:v>
       </s:c>
     </s:row>
     <s:row r="58">
-      <s:c r="A58" s="71" t="n">
+      <s:c r="A58" s="72" t="n">
         <s:v>46273</s:v>
       </s:c>
-      <s:c r="B58" s="63" t="inlineStr">
+      <s:c r="B58" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 21.38 ლ — LILO</s:t>
         </s:is>
       </s:c>
-      <s:c r="C58" s="63" t="inlineStr"/>
-      <s:c r="D58" s="63" t="inlineStr">
+      <s:c r="C58" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D58" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E58" s="72" t="n">
+      <s:c r="E58" s="73" t="n">
         <s:v>-81.03</s:v>
       </s:c>
     </s:row>
     <s:row r="59">
-      <s:c r="A59" s="71" t="n">
+      <s:c r="A59" s="72" t="n">
         <s:v>46274</s:v>
       </s:c>
-      <s:c r="B59" s="63" t="inlineStr">
+      <s:c r="B59" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 60 ლ — ZESTAPHONI</s:t>
         </s:is>
       </s:c>
-      <s:c r="C59" s="63" t="inlineStr"/>
-      <s:c r="D59" s="63" t="inlineStr">
+      <s:c r="C59" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D59" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E59" s="72" t="n">
+      <s:c r="E59" s="73" t="n">
         <s:v>-224.4</s:v>
       </s:c>
     </s:row>
     <s:row r="60">
-      <s:c r="A60" s="71" t="n">
+      <s:c r="A60" s="72" t="n">
         <s:v>46276</s:v>
       </s:c>
-      <s:c r="B60" s="63" t="inlineStr">
+      <s:c r="B60" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 50 ლ — PIKRIS GORA</s:t>
         </s:is>
       </s:c>
-      <s:c r="C60" s="63" t="inlineStr"/>
-      <s:c r="D60" s="63" t="inlineStr">
+      <s:c r="C60" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D60" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E60" s="72" t="n">
+      <s:c r="E60" s="73" t="n">
         <s:v>-192.5</s:v>
       </s:c>
     </s:row>
     <s:row r="61">
-      <s:c r="A61" s="71" t="n">
+      <s:c r="A61" s="72" t="n">
         <s:v>46279</s:v>
       </s:c>
-      <s:c r="B61" s="63" t="inlineStr">
+      <s:c r="B61" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 65 ლ — TSEROVANI</s:t>
         </s:is>
       </s:c>
-      <s:c r="C61" s="63" t="inlineStr"/>
-      <s:c r="D61" s="63" t="inlineStr">
+      <s:c r="C61" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D61" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E61" s="72" t="n">
+      <s:c r="E61" s="73" t="n">
         <s:v>-250.25</s:v>
       </s:c>
     </s:row>
     <s:row r="62">
-      <s:c r="A62" s="71" t="n">
+      <s:c r="A62" s="72" t="n">
         <s:v>46282</s:v>
       </s:c>
-      <s:c r="B62" s="63" t="inlineStr">
+      <s:c r="B62" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი G-Force Premium 50 ლ — NAREKVAVI</s:t>
         </s:is>
       </s:c>
-      <s:c r="C62" s="63" t="inlineStr"/>
-      <s:c r="D62" s="63" t="inlineStr">
+      <s:c r="C62" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D62" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E62" s="72" t="n">
+      <s:c r="E62" s="73" t="n">
         <s:v>-192.5</s:v>
       </s:c>
     </s:row>
     <s:row r="63">
-      <s:c r="A63" s="71" t="n">
+      <s:c r="A63" s="72" t="n">
         <s:v>46287</s:v>
       </s:c>
-      <s:c r="B63" s="63" t="inlineStr">
+      <s:c r="B63" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი</s:t>
         </s:is>
       </s:c>
-      <s:c r="C63" s="63" t="inlineStr"/>
-      <s:c r="D63" s="63" t="inlineStr">
+      <s:c r="C63" s="64" t="inlineStr">
+        <s:is>
+          <s:t>Gulf</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D63" s="64" t="inlineStr">
         <s:is>
           <s:t>საწვავი / Fuel</s:t>
         </s:is>
       </s:c>
-      <s:c r="E63" s="72" t="n">
+      <s:c r="E63" s="73" t="n">
         <s:v>-200</s:v>
       </s:c>
     </s:row>
@@ -14693,7 +14819,7 @@
       <s:c r="E66" s="11" t="n"/>
     </s:row>
     <s:row r="67">
-      <s:c r="A67" s="59" t="inlineStr">
+      <s:c r="A67" s="60" t="inlineStr">
         <s:is>
           <s:t>კატეგორია / Category</s:t>
         </s:is>
@@ -14865,7 +14991,7 @@
           <s:t>შემოწმება / Check vs statement total (must be 0)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B78" s="73">
+      <s:c r="B78" s="74">
         <s:f>B77+E64</s:f>
         <s:v>0.0</s:v>
       </s:c>
@@ -14882,7 +15008,7 @@
       <s:c r="E80" s="11" t="n"/>
     </s:row>
     <s:row r="81">
-      <s:c r="A81" s="59" t="inlineStr">
+      <s:c r="A81" s="60" t="inlineStr">
         <s:is>
           <s:t>თვე / Month</s:t>
         </s:is>
@@ -14954,11 +15080,11 @@
           <s:t>გაცვლითი კურსი 09/07/2026 (22,000 USD) / FX rate on the 09/07/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B88" s="74">
+      <s:c r="B88" s="75">
         <s:f>-E17/22000</s:f>
         <s:v>2.6384000000000003</s:v>
       </s:c>
-      <s:c r="C88" s="42" t="inlineStr">
+      <s:c r="C88" s="43" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში მითითებული კურსი 2.6384 / the description states 2.6384</s:t>
         </s:is>
@@ -14970,11 +15096,11 @@
           <s:t>გაცვლითი კურსი 04/08/2026 (5,000 USD) / FX rate on the 04/08/2026 transfer</s:t>
         </s:is>
       </s:c>
-      <s:c r="B89" s="74">
+      <s:c r="B89" s="75">
         <s:f>-E20/5000</s:f>
         <s:v>2.62</s:v>
       </s:c>
-      <s:c r="C89" s="42" t="inlineStr">
+      <s:c r="C89" s="43" t="inlineStr">
         <s:is>
           <s:t>დანიშნულებაში კურსი არ არის მითითებული / no rate stated in the description</s:t>
         </s:is>
@@ -14986,11 +15112,11 @@
           <s:t>მშენებლობის ავანსები / Construction advances paid (USD)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B90" s="75">
+      <s:c r="B90" s="34">
         <s:f>22000+5000</s:f>
         <s:v>27000.0</s:v>
       </s:c>
-      <s:c r="C90" s="42" t="inlineStr">
+      <s:c r="C90" s="43" t="inlineStr">
         <s:is>
           <s:t>ხელშეკრულება N1, 7/6/2026, შპს ჯიესენ გრუპ / contract N1 of 7/6/2026 with LLC GSN Group</s:t>
         </s:is>
@@ -15006,7 +15132,7 @@
         <s:f>B68</s:f>
         <s:v>178544.8</s:v>
       </s:c>
-      <s:c r="C91" s="42" t="inlineStr">
+      <s:c r="C91" s="43" t="inlineStr">
         <s:is>
           <s:t>ორივე გადარიცხვის ჯამი / the two transfers above</s:t>
         </s:is>
@@ -15018,11 +15144,11 @@
           <s:t>სულ გადახდილი / Total paid out (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B92" s="38">
+      <s:c r="B92" s="39">
         <s:f>-E64</s:f>
         <s:v>220261.63999999998</s:v>
       </s:c>
-      <s:c r="C92" s="42" t="inlineStr">
+      <s:c r="C92" s="43" t="inlineStr">
         <s:is>
           <s:t>01/07–08/09/2026</s:t>
         </s:is>
@@ -15034,11 +15160,11 @@
           <s:t>შემოსავალი ამონაწერში / Inflows in the statement (GEL)</s:t>
         </s:is>
       </s:c>
-      <s:c r="B93" s="38">
+      <s:c r="B93" s="39">
         <s:f>0</s:f>
         <s:v>0.0</s:v>
       </s:c>
-      <s:c r="C93" s="42" t="inlineStr">
+      <s:c r="C93" s="43" t="inlineStr">
         <s:is>
           <s:t>ამონაწერში შემოსავალი არ ფიქსირდება — 140,000 USD სესხი ამ ანგარიშზე ამ პერიოდში არ ჩანს. / The statement shows no inflows; the USD 140,000 loan is not visible in this account for this period.</s:t>
         </s:is>

--- a/finance/Greenhouse_CashFlow_2000m2.xlsx
+++ b/finance/Greenhouse_CashFlow_2000m2.xlsx
@@ -1275,11 +1275,11 @@
         </s:is>
       </s:c>
       <s:c r="B9" s="24" t="n">
-        <s:v>200</s:v>
+        <s:v>3019.65</s:v>
       </s:c>
       <s:c r="C9" s="25">
         <s:f>IFERROR(B9/$B$6,0)</s:f>
-        <s:v>0.00032</s:v>
+        <s:v>0.00483144</s:v>
       </s:c>
       <s:c r="D9" s="16" t="str">
         <s:f>REPT("|",ROUND(C9*40,0))</s:f>
@@ -1313,11 +1313,11 @@
       </s:c>
       <s:c r="B11" s="27">
         <s:f>B7+(B8-B9)+B10</s:f>
-        <s:v>396572.83999999997</s:v>
+        <s:v>393753.18999999994</s:v>
       </s:c>
       <s:c r="C11" s="28">
         <s:f>IFERROR(B11/$B$6,0)</s:f>
-        <s:v>0.6345165439999999</s:v>
+        <s:v>0.6300051039999999</s:v>
       </s:c>
       <s:c r="D11" s="29" t="str">
         <s:f>REPT("|",ROUND(C11*40,0))</s:f>
@@ -1332,11 +1332,11 @@
       </s:c>
       <s:c r="B12" s="27">
         <s:f>B6-B11</s:f>
-        <s:v>228427.16000000003</s:v>
+        <s:v>231246.81000000006</s:v>
       </s:c>
       <s:c r="C12" s="28">
         <s:f>IFERROR(B12/$B$6,0)</s:f>
-        <s:v>0.36548345600000004</s:v>
+        <s:v>0.3699948960000001</s:v>
       </s:c>
       <s:c r="D12" s="29" t="str">
         <s:f>REPT("|",ROUND(C12*40,0))</s:f>
